--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC21" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Spain_La_L" displayName="AveragesTable_Spain_La_L" ref="A1:EC21" headerRowCount="1">
   <autoFilter ref="A1:EC21"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0.14</v>
@@ -1472,49 +1472,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH2" t="n">
         <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>99.59999999999999</v>
+        <v>96.33</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="AL2" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.6</v>
+        <v>45.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.8</v>
+        <v>13</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>6.83</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.8</v>
+        <v>46</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.4</v>
+        <v>11.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>19.33</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.92</v>
+        <v>10.08</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.42</v>
+        <v>4.62</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS2" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY2" t="n">
         <v>1.58</v>
@@ -1610,55 +1610,55 @@
         <v>1.63</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.57</v>
+        <v>3.68</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.54</v>
+        <v>3.67</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="CD2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CG2" t="n">
         <v>2.75</v>
       </c>
-      <c r="CE2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>2.63</v>
-      </c>
       <c r="CH2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.12</v>
+        <v>3.97</v>
       </c>
       <c r="CR2" t="n">
         <v>1.49</v>
@@ -1673,106 +1673,106 @@
         <v>1.35</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="CX2" t="n">
         <v>1.66</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.25</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="DB2" t="n">
         <v>1.43</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="DE2" t="n">
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="DH2" t="n">
-        <v>110.84</v>
+        <v>108.46</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.58</v>
+        <v>5.69</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.42</v>
+        <v>50.54</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.84</v>
+        <v>12.54</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.5</v>
+        <v>13.16</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.08</v>
+        <v>49.61</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.09</v>
+        <v>13.08</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.58</v>
+        <v>20.77</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="3">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>83.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>37.8</v>
+        <v>35.33</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.4</v>
+        <v>13.67</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.4</v>
+        <v>9.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>46.4</v>
+        <v>46.67</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="BC5" t="n">
         <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.2</v>
+        <v>18.17</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.58</v>
+        <v>9.31</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.42</v>
+        <v>5.31</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX5" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BY5" t="n">
         <v>2.75</v>
@@ -2819,55 +2819,55 @@
         <v>2.87</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CD5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CG5" t="n">
         <v>2.9</v>
       </c>
-      <c r="CE5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>2.94</v>
-      </c>
       <c r="CH5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK5" t="n">
         <v>1.63</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN5" t="n">
         <v>1.75</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2882,10 +2882,10 @@
         <v>1.46</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX5" t="n">
         <v>1.67</v>
@@ -2900,10 +2900,10 @@
         <v>1.78</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="DD5" t="n">
         <v>3.08</v>
@@ -2912,13 +2912,13 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="DG5" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.25</v>
+        <v>98.69</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2927,58 +2927,58 @@
         <v>2.08</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.83</v>
+        <v>4.61</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>48.17</v>
+        <v>46.23</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.92</v>
+        <v>12.16</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.33</v>
+        <v>12</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.34</v>
+        <v>7.62</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51</v>
+        <v>50.77</v>
       </c>
       <c r="DW5" t="n">
         <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.58</v>
+        <v>11.23</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.84</v>
+        <v>7.46</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.75</v>
+        <v>19.23</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="EC5" t="n">
         <v>2</v>
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="H6" t="n">
-        <v>115.83</v>
+        <v>110.86</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="K6" t="n">
-        <v>6.17</v>
+        <v>5.86</v>
       </c>
       <c r="L6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>46</v>
+        <v>43.71</v>
       </c>
       <c r="N6" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="P6" t="n">
-        <v>14.17</v>
+        <v>15.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.83</v>
+        <v>14.86</v>
       </c>
       <c r="R6" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>52.33</v>
+        <v>52.29</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.17</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.33</v>
+        <v>8.43</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.17</v>
+        <v>20.71</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,49 +3162,49 @@
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.75</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN6" t="n">
         <v>1</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS6" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CC6" t="n">
         <v>4.23</v>
@@ -3234,10 +3234,10 @@
         <v>4.54</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CG6" t="n">
         <v>2.4</v>
@@ -3246,31 +3246,31 @@
         <v>1.28</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CK6" t="n">
         <v>1.59</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CN6" t="n">
         <v>1.77</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CQ6" t="n">
-        <v>5.17</v>
+        <v>5.09</v>
       </c>
       <c r="CR6" t="n">
         <v>1.53</v>
@@ -3285,10 +3285,10 @@
         <v>1.34</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CX6" t="n">
         <v>1.68</v>
@@ -3303,86 +3303,86 @@
         <v>1.77</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="DD6" t="inlineStr"/>
       <c r="DE6" t="n">
         <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DG6" t="n">
         <v>2.92</v>
       </c>
       <c r="DH6" t="n">
-        <v>107.25</v>
+        <v>105.23</v>
       </c>
       <c r="DI6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.92</v>
+        <v>42.84</v>
       </c>
       <c r="DN6" t="n">
         <v>0.92</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.58</v>
+        <v>2.47</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.58</v>
+        <v>16</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.83</v>
+        <v>13.92</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.58</v>
+        <v>7.31</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.33</v>
+        <v>51.39</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.84</v>
+        <v>11.31</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.17</v>
+        <v>7.77</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="7">
@@ -3795,61 +3795,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>116.6</v>
+        <v>110.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="K8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>60.4</v>
+        <v>57.83</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="O8" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.8</v>
+        <v>11.33</v>
       </c>
       <c r="R8" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3861,28 +3861,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>67</v>
+        <v>67.17</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.2</v>
+        <v>20.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.6</v>
+        <v>8.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.8</v>
+        <v>17.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AF8" t="n">
         <v>0.29</v>
@@ -3969,34 +3969,34 @@
         <v>3.92</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.33</v>
+        <v>11.38</v>
       </c>
       <c r="BI8" t="n">
         <v>3.92</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BP8" t="n">
-        <v>6.17</v>
+        <v>6.08</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.17</v>
+        <v>5.31</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4005,31 +4005,31 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BV8" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BW8" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX8" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.66</v>
+        <v>5.61</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.01</v>
+        <v>5.96</v>
       </c>
       <c r="CC8" t="n">
         <v>1.67</v>
@@ -4041,13 +4041,13 @@
         <v>1.21</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CI8" t="n">
         <v>2.24</v>
@@ -4059,10 +4059,10 @@
         <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CN8" t="n">
         <v>2.09</v>
@@ -4071,7 +4071,7 @@
         <v>1.1</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CQ8" t="n">
         <v>2.06</v>
@@ -4107,82 +4107,82 @@
         <v>1.42</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="DH8" t="n">
-        <v>115.84</v>
+        <v>113.08</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.83</v>
+        <v>6.69</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DM8" t="n">
-        <v>62.75</v>
+        <v>61.38</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.42</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.25</v>
+        <v>4.54</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>67.83</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>20.25</v>
+        <v>20.15</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.17</v>
+        <v>12.16</v>
       </c>
       <c r="DZ8" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.5</v>
+        <v>18.08</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="9">
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.4</v>
@@ -5091,49 +5091,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO11" t="n">
         <v>1</v>
       </c>
-      <c r="AH11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>85.56999999999999</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>39</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.86</v>
-      </c>
       <c r="AP11" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.14</v>
+        <v>13.38</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>11.62</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.14</v>
+        <v>10.62</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5145,82 +5145,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>41.14</v>
+        <v>41</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.86</v>
+        <v>10.38</v>
       </c>
       <c r="BB11" t="n">
         <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="BD11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="BH11" t="n">
-        <v>11.5</v>
+        <v>11.15</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.67</v>
+        <v>5.46</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.83</v>
+        <v>5.69</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU11" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY11" t="n">
         <v>5.37</v>
@@ -5229,70 +5229,70 @@
         <v>5.78</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.06</v>
+        <v>3.99</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.81</v>
+        <v>4.65</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.1</v>
+        <v>4.94</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO11" t="n">
         <v>1.27</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.37</v>
+        <v>3.33</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="CT11" t="n">
         <v>2.96</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW11" t="n">
         <v>1.85</v>
@@ -5313,52 +5313,52 @@
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DG11" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="DH11" t="n">
-        <v>80.58</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.33</v>
+        <v>3.08</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM11" t="n">
-        <v>37.75</v>
+        <v>36</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.58</v>
+        <v>12.77</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.08</v>
+        <v>11.46</v>
       </c>
       <c r="DR11" t="n">
-        <v>10.5</v>
+        <v>10.23</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5370,28 +5370,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.83</v>
+        <v>38.92</v>
       </c>
       <c r="DW11" t="n">
         <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.5</v>
+        <v>10.23</v>
       </c>
       <c r="DY11" t="n">
         <v>6.92</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.58</v>
+        <v>3.31</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.5</v>
+        <v>17.23</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="12">
@@ -8625,61 +8625,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="G20" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="H20" t="n">
-        <v>96.17</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="K20" t="n">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
       <c r="L20" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M20" t="n">
-        <v>45.83</v>
+        <v>42.57</v>
       </c>
       <c r="N20" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O20" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="P20" t="n">
-        <v>12.67</v>
+        <v>13.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.17</v>
+        <v>10.86</v>
       </c>
       <c r="R20" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="T20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8691,28 +8691,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>52.17</v>
+        <v>53.29</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.33</v>
+        <v>14.29</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="AC20" t="n">
-        <v>17.17</v>
+        <v>17.71</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8796,70 +8796,70 @@
         <v>1.67</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.92</v>
+        <v>9.69</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.58</v>
+        <v>5.46</v>
       </c>
       <c r="BR20" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS20" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT20" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU20" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV20" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX20" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CC20" t="n">
         <v>5.96</v>
@@ -8868,10 +8868,10 @@
         <v>7.05</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CG20" t="n">
         <v>2.89</v>
@@ -8880,49 +8880,49 @@
         <v>1.41</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CN20" t="n">
         <v>1.93</v>
       </c>
-      <c r="CM20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CN20" t="n">
-        <v>1.92</v>
-      </c>
       <c r="CO20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX20" t="n">
         <v>1.63</v>
@@ -8937,55 +8937,55 @@
         <v>1.94</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="DE20" t="n">
         <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="DH20" t="n">
-        <v>87.67</v>
+        <v>85.77</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.92</v>
+        <v>5.08</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM20" t="n">
-        <v>37.66</v>
+        <v>36.54</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.08</v>
+        <v>12.38</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.08</v>
+        <v>11.39</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.08</v>
+        <v>7.93</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8997,28 +8997,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>46.34</v>
+        <v>47.39</v>
       </c>
       <c r="DW20" t="n">
         <v>0.08</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.42</v>
+        <v>10.69</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.42</v>
+        <v>7.69</v>
       </c>
       <c r="DZ20" t="n">
         <v>3</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.25</v>
+        <v>17.53</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0.29</v>
@@ -1872,52 +1872,52 @@
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AI3" t="n">
-        <v>101.6</v>
+        <v>99.17</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.4</v>
+        <v>47.33</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.4</v>
+        <v>13.17</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>9.17</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.2</v>
+        <v>53.33</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.4</v>
+        <v>11.67</v>
       </c>
       <c r="BB3" t="n">
         <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="BD3" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.5</v>
+        <v>10.69</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.75</v>
+        <v>5.62</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.75</v>
+        <v>5.08</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BT3" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY3" t="n">
         <v>1.62</v>
@@ -2013,169 +2013,169 @@
         <v>1.68</v>
       </c>
       <c r="CA3" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="CB3" t="n">
         <v>4.41</v>
       </c>
-      <c r="CB3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="CC3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CS3" t="n">
         <v>2.75</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="CU3" t="n">
         <v>1.48</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CW3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="DD3" t="n">
         <v>3.04</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.83</v>
+        <v>102.54</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="DK3" t="n">
-        <v>7.5</v>
+        <v>7.46</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="DM3" t="n">
-        <v>56.42</v>
+        <v>55.3</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.25</v>
+        <v>11.69</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.5</v>
+        <v>10.38</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.83</v>
+        <v>55.15</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.08</v>
+        <v>14</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.17</v>
+        <v>8.08</v>
       </c>
       <c r="DZ3" t="n">
         <v>5.92</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.92</v>
+        <v>18.46</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
-        <v>97.40000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>50.4</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>13.4</v>
+        <v>13.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.6</v>
+        <v>10.83</v>
       </c>
       <c r="R4" t="n">
-        <v>7</v>
+        <v>7.17</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="AD4" t="n">
         <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,28 +2356,28 @@
         <v>1.86</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.25</v>
+        <v>7.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="BO4" t="n">
         <v>0.92</v>
@@ -2386,40 +2386,40 @@
         <v>3.08</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS4" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BT4" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BU4" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="CC4" t="n">
         <v>5.81</v>
@@ -2428,19 +2428,19 @@
         <v>6.02</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CH4" t="n">
         <v>1.35</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ4" t="n">
         <v>2</v>
@@ -2449,19 +2449,19 @@
         <v>1.59</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM4" t="n">
         <v>2.26</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO4" t="n">
         <v>1.39</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ4" t="n">
         <v>3.96</v>
@@ -2479,7 +2479,7 @@
         <v>1.41</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW4" t="n">
         <v>2.08</v>
@@ -2491,94 +2491,94 @@
         <v>2.02</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB4" t="n">
         <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DD4" t="n">
         <v>3.05</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.58</v>
+        <v>86.62</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.75</v>
+        <v>41.31</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.66</v>
+        <v>12.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12</v>
+        <v>11.62</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.75</v>
+        <v>8.69</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.58</v>
+        <v>46.54</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.75</v>
+        <v>10.08</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.42</v>
+        <v>6.69</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.91</v>
+        <v>19.84</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="5">
@@ -3392,61 +3392,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F7" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="G7" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>111</v>
+        <v>107.14</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="K7" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="L7" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>55.5</v>
+        <v>56</v>
       </c>
       <c r="N7" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="P7" t="n">
-        <v>11.83</v>
+        <v>11.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.83</v>
+        <v>15.57</v>
       </c>
       <c r="R7" t="n">
-        <v>6.67</v>
+        <v>7.43</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="T7" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3458,28 +3458,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>65</v>
+        <v>62.71</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.5</v>
+        <v>13.71</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.67</v>
+        <v>4.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>14.67</v>
+        <v>15.29</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3563,49 +3563,49 @@
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.58</v>
+        <v>7.77</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.58</v>
+        <v>4.69</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="BR7" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT7" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3614,19 +3614,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.01</v>
+        <v>3.58</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="CC7" t="n">
         <v>6.6</v>
@@ -3635,157 +3635,157 @@
         <v>7.31</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="CT7" t="n">
         <v>2.72</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB7" t="n">
         <v>1.41</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="DE7" t="n">
         <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.92</v>
+        <v>1.16</v>
       </c>
       <c r="DG7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="EB7" t="n">
         <v>1.34</v>
       </c>
-      <c r="DH7" t="n">
-        <v>99.92</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>45</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DO7" t="n">
+      <c r="EC7" t="n">
         <v>1.84</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>59.25</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>11</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="EC7" t="n">
-        <v>1.75</v>
       </c>
     </row>
     <row r="8">
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -4204,49 +4204,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="H9" t="n">
-        <v>101.2</v>
+        <v>104.17</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="M9" t="n">
-        <v>40.2</v>
+        <v>41.33</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>15.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>16.17</v>
       </c>
       <c r="R9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4258,28 +4258,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>42.4</v>
+        <v>42.17</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>24.6</v>
+        <v>25.17</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4363,46 +4363,46 @@
         <v>2.43</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.92</v>
+        <v>9.23</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.58</v>
+        <v>4.92</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT9" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4414,19 +4414,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CC9" t="n">
         <v>5.27</v>
@@ -4438,10 +4438,10 @@
         <v>1.58</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CH9" t="n">
         <v>1.28</v>
@@ -4456,7 +4456,7 @@
         <v>1.83</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CM9" t="n">
         <v>1.92</v>
@@ -4468,10 +4468,10 @@
         <v>1.54</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
       <c r="CR9" t="n">
         <v>1.62</v>
@@ -4486,7 +4486,7 @@
         <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CW9" t="n">
         <v>2.44</v>
@@ -4516,43 +4516,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="DH9" t="n">
-        <v>97.5</v>
+        <v>99.16</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="DK9" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.66</v>
+        <v>42.07</v>
       </c>
       <c r="DN9" t="n">
         <v>0.92</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.42</v>
+        <v>14.93</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.42</v>
+        <v>14.62</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.09</v>
+        <v>6.92</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4564,28 +4564,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>40.75</v>
+        <v>40.77</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX9" t="n">
         <v>9</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.25</v>
+        <v>6.39</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="EA9" t="n">
-        <v>25.25</v>
+        <v>25.46</v>
       </c>
       <c r="EB9" t="n">
         <v>1.07</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="10">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4685,139 +4685,139 @@
         <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>70.8</v>
+        <v>73.17</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT10" t="n">
         <v>2</v>
       </c>
-      <c r="AL10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AU10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.4</v>
+        <v>14.33</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.67</v>
+        <v>10.46</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL10" t="n">
         <v>0.92</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.08</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS10" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV10" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY10" t="n">
         <v>2.21</v>
@@ -4826,55 +4826,55 @@
         <v>2.28</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.81</v>
+        <v>3.87</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.91</v>
+        <v>6.8</v>
       </c>
       <c r="CD10" t="n">
-        <v>7.17</v>
+        <v>7.03</v>
       </c>
       <c r="CE10" t="n">
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.81</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.47</v>
+        <v>3.38</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
@@ -4889,106 +4889,106 @@
         <v>1.41</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.64</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.29</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="DH10" t="n">
-        <v>83.34</v>
+        <v>83.47</v>
       </c>
       <c r="DI10" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.66</v>
+        <v>4.31</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.25</v>
+        <v>40.54</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.25</v>
+        <v>10.69</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.34</v>
+        <v>13.08</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.59</v>
+        <v>9.92</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47.67</v>
+        <v>47.54</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.58</v>
+        <v>5.69</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.67</v>
+        <v>16.46</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="11">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
         <v>1.5</v>
@@ -5103,7 +5103,7 @@
         <v>0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AL11" t="n">
         <v>2.5</v>
@@ -5145,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>41</v>
+        <v>41.12</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
         <v>1.16</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BG11" t="n">
         <v>3.08</v>
@@ -5322,7 +5322,7 @@
         <v>0.15</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="DG11" t="n">
         <v>1.85</v>
@@ -5334,7 +5334,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DK11" t="n">
         <v>3.08</v>
@@ -5370,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.92</v>
+        <v>39</v>
       </c>
       <c r="DW11" t="n">
         <v>0.08</v>
@@ -5391,7 +5391,7 @@
         <v>1.14</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
@@ -5413,82 +5413,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
-        <v>97.86</v>
+        <v>95.25</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>53.14</v>
+        <v>50.88</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="O12" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>12.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="R12" t="n">
-        <v>6.14</v>
+        <v>6.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.14</v>
+        <v>43.62</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.29</v>
+        <v>12.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>8</v>
+        <v>7.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.29</v>
+        <v>19.62</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
         <v>0.2</v>
@@ -5572,70 +5572,70 @@
         <v>1.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.42</v>
+        <v>9.08</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.42</v>
+        <v>4.92</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.01</v>
+        <v>2.87</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC12" t="n">
         <v>5.43</v>
@@ -5647,13 +5647,13 @@
         <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CG12" t="n">
         <v>2.84</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI12" t="n">
         <v>1.9</v>
@@ -5662,25 +5662,25 @@
         <v>1.87</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM12" t="n">
         <v>2.41</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CR12" t="n">
         <v>1.46</v>
@@ -5701,16 +5701,16 @@
         <v>1.92</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB12" t="n">
         <v>1.38</v>
@@ -5725,76 +5725,76 @@
         <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.92</v>
+        <v>1.15</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DH12" t="n">
-        <v>94.75</v>
+        <v>93.38</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DM12" t="n">
-        <v>50.16</v>
+        <v>49</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.75</v>
+        <v>13.15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.17</v>
+        <v>10.85</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.58</v>
+        <v>6.92</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.25</v>
+        <v>41.54</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.34</v>
+        <v>13.84</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.34</v>
+        <v>20.07</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="13">
@@ -5804,13 +5804,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5894,139 +5894,139 @@
         <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AI13" t="n">
-        <v>91.5</v>
+        <v>93.86</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.17</v>
+        <v>3.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>35.67</v>
+        <v>35.71</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>11.43</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.33</v>
+        <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46.33</v>
+        <v>45.71</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.17</v>
+        <v>10.86</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.67</v>
+        <v>6.57</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="BD13" t="n">
-        <v>17.33</v>
+        <v>17</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BF13" t="n">
         <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.33</v>
+        <v>9.85</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ13" t="n">
         <v>0.92</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN13" t="n">
         <v>1.08</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.92</v>
+        <v>5.54</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU13" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY13" t="n">
         <v>3.98</v>
@@ -6035,55 +6035,55 @@
         <v>4.11</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.83</v>
+        <v>3.94</v>
       </c>
       <c r="CB13" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="CC13" t="n">
-        <v>6.46</v>
+        <v>6.7</v>
       </c>
       <c r="CD13" t="n">
-        <v>7.02</v>
+        <v>7.15</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.01</v>
+        <v>3.9</v>
       </c>
       <c r="CR13" t="n">
         <v>1.47</v>
@@ -6098,73 +6098,73 @@
         <v>1.45</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DB13" t="n">
         <v>1.44</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DH13" t="n">
-        <v>90</v>
+        <v>91.39</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.67</v>
+        <v>3.46</v>
       </c>
       <c r="DL13" t="n">
         <v>0.16</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.75</v>
+        <v>37.61</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.92</v>
+        <v>11.61</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.58</v>
+        <v>12.92</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.42</v>
+        <v>7.77</v>
       </c>
       <c r="DS13" t="n">
         <v>0.08</v>
@@ -6176,25 +6176,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.08</v>
+        <v>44.84</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.75</v>
+        <v>10.62</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.92</v>
+        <v>6.85</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.58</v>
+        <v>18.31</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC13" t="n">
         <v>1.92</v>
@@ -6207,13 +6207,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6300,136 +6300,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG14" t="n">
         <v>2</v>
       </c>
-      <c r="AI14" t="n">
-        <v>90.86</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>38.57</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.17</v>
-      </c>
       <c r="BH14" t="n">
-        <v>11.58</v>
+        <v>11.54</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.83</v>
+        <v>5.77</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.75</v>
+        <v>5.77</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BS14" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BT14" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BY14" t="n">
         <v>3.65</v>
@@ -6438,43 +6438,43 @@
         <v>3.79</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.17</v>
+        <v>3.93</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.35</v>
+        <v>4.09</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH14" t="n">
         <v>1.41</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.84</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN14" t="n">
         <v>1.95</v>
@@ -6483,19 +6483,19 @@
         <v>1.3</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CU14" t="n">
         <v>1.4</v>
@@ -6504,16 +6504,16 @@
         <v>2.02</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY14" t="n">
         <v>1.85</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA14" t="n">
         <v>1.99</v>
@@ -6522,7 +6522,7 @@
         <v>1.39</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DD14" t="n">
         <v>3.14</v>
@@ -6531,76 +6531,76 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.42</v>
+        <v>94</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.16</v>
+        <v>6.15</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.33</v>
+        <v>46.46</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.58</v>
+        <v>13.54</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.67</v>
+        <v>9.77</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.75</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>52.67</v>
+        <v>53.31</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.75</v>
+        <v>12.62</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.42</v>
+        <v>19.77</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="15">
@@ -6610,61 +6610,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="G15" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="H15" t="n">
-        <v>111.5</v>
+        <v>111.14</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="K15" t="n">
-        <v>3.83</v>
+        <v>4.43</v>
       </c>
       <c r="L15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="P15" t="n">
-        <v>8.33</v>
+        <v>8.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>14.33</v>
+        <v>14.57</v>
       </c>
       <c r="R15" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="S15" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6676,28 +6676,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>51.5</v>
+        <v>51.86</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>16.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.67</v>
+        <v>10.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.83</v>
+        <v>17.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,49 +6781,49 @@
         <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.33</v>
+        <v>10.15</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.83</v>
+        <v>5.77</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6832,19 +6832,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.45</v>
+        <v>3.53</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="CC15" t="n">
         <v>2.69</v>
@@ -6853,16 +6853,16 @@
         <v>2.69</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CI15" t="n">
         <v>2.06</v>
@@ -6871,25 +6871,25 @@
         <v>1.77</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CO15" t="n">
         <v>1.28</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6907,70 +6907,70 @@
         <v>2.19</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX15" t="n">
         <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.4</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB15" t="n">
         <v>1.31</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="DE15" t="n">
         <v>0.16</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="DH15" t="n">
-        <v>103.84</v>
+        <v>104.23</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM15" t="n">
-        <v>49.08</v>
+        <v>50.08</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.08</v>
+        <v>9.15</v>
       </c>
       <c r="DQ15" t="n">
-        <v>14.5</v>
+        <v>14.62</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.92</v>
+        <v>7.54</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6982,28 +6982,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.34</v>
+        <v>52.46</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.5</v>
+        <v>15.15</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.92</v>
+        <v>10.39</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.58</v>
+        <v>4.77</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.25</v>
+        <v>16.46</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="16">
@@ -7013,13 +7013,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7106,136 +7106,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>120.5</v>
+        <v>119.29</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>56.5</v>
+        <v>58.43</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.17</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AU16" t="n">
         <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>59.5</v>
+        <v>58.29</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>19.33</v>
+        <v>19.43</v>
       </c>
       <c r="BB16" t="n">
-        <v>12.17</v>
+        <v>12.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.17</v>
+        <v>7.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.17</v>
+        <v>16.71</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BG16" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.42</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT16" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV16" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY16" t="n">
         <v>1.28</v>
@@ -7244,16 +7244,16 @@
         <v>1.34</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.4</v>
+        <v>5.37</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.81</v>
+        <v>5.77</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CE16" t="n">
         <v>1.25</v>
@@ -7262,43 +7262,43 @@
         <v>2.2</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="CH16" t="n">
         <v>1.66</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CO16" t="n">
         <v>1.15</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CR16" t="n">
         <v>1.34</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CT16" t="n">
         <v>3.28</v>
@@ -7307,22 +7307,22 @@
         <v>1.67</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CX16" t="n">
         <v>1.59</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
@@ -7331,82 +7331,82 @@
         <v>1.56</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="DH16" t="n">
-        <v>125.92</v>
+        <v>124.85</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.08</v>
+        <v>6.23</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM16" t="n">
-        <v>68.5</v>
+        <v>68.62</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.92</v>
+        <v>13.61</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.58</v>
+        <v>6.7</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>60.42</v>
+        <v>59.69</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX16" t="n">
-        <v>19.75</v>
+        <v>19.77</v>
       </c>
       <c r="DY16" t="n">
-        <v>12.42</v>
+        <v>12.47</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.34</v>
+        <v>7.31</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.92</v>
+        <v>17.61</v>
       </c>
       <c r="EB16" t="n">
         <v>2.26</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="17">
@@ -7416,10 +7416,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -7428,49 +7428,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="H17" t="n">
-        <v>73.67</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="L17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M17" t="n">
-        <v>35.5</v>
+        <v>36.57</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>10.17</v>
+        <v>10.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>11.29</v>
       </c>
       <c r="R17" t="n">
-        <v>7.17</v>
+        <v>7.14</v>
       </c>
       <c r="S17" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="T17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7482,28 +7482,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>45</v>
+        <v>44.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.17</v>
+        <v>9</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.67</v>
+        <v>6.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.67</v>
+        <v>17.71</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7587,70 +7587,70 @@
         <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BM17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT17" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU17" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX17" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BY17" t="n">
-        <v>5.37</v>
+        <v>5.1</v>
       </c>
       <c r="BZ17" t="n">
-        <v>5.84</v>
+        <v>5.52</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="CC17" t="n">
         <v>6.06</v>
@@ -7662,10 +7662,10 @@
         <v>1.45</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH17" t="n">
         <v>1.36</v>
@@ -7674,7 +7674,7 @@
         <v>1.74</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CK17" t="n">
         <v>1.54</v>
@@ -7683,10 +7683,10 @@
         <v>2.02</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO17" t="n">
         <v>1.38</v>
@@ -7695,37 +7695,37 @@
         <v>2.19</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DB17" t="n">
         <v>1.42</v>
@@ -7743,40 +7743,40 @@
         <v>2</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DH17" t="n">
-        <v>71.08</v>
+        <v>70.69</v>
       </c>
       <c r="DI17" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DM17" t="n">
-        <v>31.42</v>
+        <v>32.31</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.75</v>
+        <v>11.69</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.16</v>
+        <v>11.31</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.33</v>
+        <v>8.23</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7788,28 +7788,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.58</v>
+        <v>43.23</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DX17" t="n">
-        <v>8.42</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="DZ17" t="n">
         <v>2.92</v>
       </c>
       <c r="EA17" t="n">
-        <v>19</v>
+        <v>18.92</v>
       </c>
       <c r="EB17" t="n">
         <v>0.97</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="18">
@@ -7819,13 +7819,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7912,136 +7912,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AI18" t="n">
-        <v>94.17</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AL18" t="n">
-        <v>6</v>
+        <v>5.57</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN18" t="n">
-        <v>44.67</v>
+        <v>44.57</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>14.71</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.83</v>
+        <v>8.57</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.83</v>
+        <v>8.43</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>45.67</v>
+        <v>46.86</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.17</v>
+        <v>14</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.67</v>
+        <v>5.29</v>
       </c>
       <c r="BD18" t="n">
-        <v>19</v>
+        <v>18.29</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.67</v>
+        <v>10.31</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.5</v>
+        <v>5.31</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT18" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV18" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY18" t="n">
         <v>2.56</v>
@@ -8050,55 +8050,55 @@
         <v>2.71</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.26</v>
+        <v>4.03</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI18" t="n">
         <v>1.9</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL18" t="n">
         <v>1.93</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="CR18" t="n">
         <v>1.44</v>
@@ -8113,28 +8113,28 @@
         <v>1.45</v>
       </c>
       <c r="CV18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW18" t="n">
         <v>1.9</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="DD18" t="n">
         <v>3.14</v>
@@ -8143,76 +8143,76 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="DH18" t="n">
-        <v>98.58</v>
+        <v>96.77</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.5</v>
+        <v>6.23</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM18" t="n">
-        <v>47.08</v>
+        <v>46.85</v>
       </c>
       <c r="DN18" t="n">
         <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="DP18" t="n">
-        <v>16.16</v>
+        <v>15.46</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.66</v>
+        <v>10.85</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.25</v>
+        <v>7.62</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.5</v>
+        <v>50.77</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.17</v>
+        <v>13.62</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.67</v>
+        <v>8.77</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.58</v>
+        <v>19.16</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="19">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8312,52 +8312,52 @@
         <v>3.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>84.83</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.17</v>
+        <v>5.43</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AN19" t="n">
-        <v>31.5</v>
+        <v>33.86</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.33</v>
+        <v>3.43</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.33</v>
+        <v>13.29</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.17</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.33</v>
+        <v>5.86</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8369,82 +8369,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>49.33</v>
+        <v>51.86</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>9</v>
+        <v>10.86</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.17</v>
+        <v>7.57</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.83</v>
+        <v>3.29</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.83</v>
+        <v>19.71</v>
       </c>
       <c r="BE19" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BF19" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="BG19" t="n">
         <v>3.08</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.42</v>
+        <v>10.92</v>
       </c>
       <c r="BI19" t="n">
         <v>3.08</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BM19" t="n">
         <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.17</v>
+        <v>5.62</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.25</v>
+        <v>5.31</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT19" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU19" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV19" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY19" t="n">
         <v>2.77</v>
@@ -8453,22 +8453,22 @@
         <v>2.96</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.93</v>
+        <v>4.77</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="CE19" t="n">
         <v>1.42</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CG19" t="n">
         <v>2.83</v>
@@ -8477,16 +8477,16 @@
         <v>1.4</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CM19" t="n">
         <v>2.33</v>
@@ -8498,10 +8498,10 @@
         <v>1.35</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
@@ -8522,16 +8522,16 @@
         <v>1.98</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB19" t="n">
         <v>1.41</v>
@@ -8546,76 +8546,76 @@
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.08</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.67</v>
+        <v>5.31</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.58</v>
+        <v>42.08</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.16</v>
+        <v>2.77</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.92</v>
+        <v>15.23</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.58</v>
+        <v>13.92</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.42</v>
+        <v>53.54</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.42</v>
+        <v>11.31</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.25</v>
+        <v>7.92</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.75</v>
+        <v>19.69</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="20">
@@ -8637,7 +8637,7 @@
         <v>0.14</v>
       </c>
       <c r="F20" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="G20" t="n">
         <v>4.29</v>
@@ -8649,7 +8649,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>6.71</v>
@@ -8691,7 +8691,7 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>53.29</v>
+        <v>53.14</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -8712,7 +8712,7 @@
         <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8949,7 +8949,7 @@
         <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="DG20" t="n">
         <v>3.31</v>
@@ -8961,7 +8961,7 @@
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DK20" t="n">
         <v>5.08</v>
@@ -8997,7 +8997,7 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.39</v>
+        <v>47.31</v>
       </c>
       <c r="DW20" t="n">
         <v>0.08</v>
@@ -9018,7 +9018,7 @@
         <v>1.15</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="21">
@@ -9028,61 +9028,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="F21" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="H21" t="n">
-        <v>94.33</v>
+        <v>98</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="K21" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>58</v>
+        <v>59.14</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O21" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="P21" t="n">
-        <v>10.17</v>
+        <v>11.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.17</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>7</v>
+        <v>6.71</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="T21" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9094,28 +9094,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>52.67</v>
+        <v>53.43</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>17.83</v>
+        <v>17.29</v>
       </c>
       <c r="AA21" t="n">
-        <v>11.17</v>
+        <v>10.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
       <c r="AC21" t="n">
-        <v>17.67</v>
+        <v>17.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9199,70 +9199,70 @@
         <v>2.83</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.5</v>
+        <v>8.15</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.42</v>
+        <v>4.15</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU21" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV21" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.81</v>
+        <v>3.92</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="CC21" t="n">
         <v>3.27</v>
@@ -9274,16 +9274,16 @@
         <v>1.34</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI21" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CJ21" t="n">
         <v>1.72</v>
@@ -9292,22 +9292,22 @@
         <v>1.53</v>
       </c>
       <c r="CL21" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO21" t="n">
         <v>1.23</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ21" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CR21" t="n">
         <v>1.38</v>
@@ -9322,73 +9322,73 @@
         <v>1.49</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB21" t="n">
         <v>1.28</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="DH21" t="n">
-        <v>84.83</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DM21" t="n">
-        <v>46.25</v>
+        <v>47.77</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DP21" t="n">
-        <v>11.25</v>
+        <v>11.69</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.92</v>
+        <v>10.7</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.34</v>
+        <v>7.15</v>
       </c>
       <c r="DS21" t="n">
         <v>0.08</v>
@@ -9400,25 +9400,25 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>45.25</v>
+        <v>46.23</v>
       </c>
       <c r="DW21" t="n">
         <v>0.08</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.75</v>
+        <v>13.77</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.83</v>
+        <v>8.69</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4.92</v>
+        <v>5.08</v>
       </c>
       <c r="EA21" t="n">
         <v>17</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="EC21" t="n">
         <v>2.08</v>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -5449,7 +5449,7 @@
         <v>10.5</v>
       </c>
       <c r="R12" t="n">
-        <v>6.75</v>
+        <v>6.62</v>
       </c>
       <c r="S12" t="n">
         <v>1.25</v>
@@ -5629,13 +5629,13 @@
         <v>2.87</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CA12" t="n">
         <v>3.62</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="CC12" t="n">
         <v>5.43</v>
@@ -5695,7 +5695,7 @@
         <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW12" t="n">
         <v>1.92</v>
@@ -5716,10 +5716,10 @@
         <v>1.38</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="DE12" t="n">
         <v>0.08</v>
@@ -5761,7 +5761,7 @@
         <v>10.85</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.92</v>
+        <v>6.84</v>
       </c>
       <c r="DS12" t="n">
         <v>0.15</v>
@@ -6333,7 +6333,7 @@
         <v>13.88</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.5</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AS14" t="n">
         <v>8.380000000000001</v>
@@ -6360,19 +6360,19 @@
         <v>0.12</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.38</v>
+        <v>11.5</v>
       </c>
       <c r="BB14" t="n">
         <v>7.88</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="BD14" t="n">
         <v>18.88</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BF14" t="n">
         <v>2.25</v>
@@ -6564,7 +6564,7 @@
         <v>13.54</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.77</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DR14" t="n">
         <v>8.460000000000001</v>
@@ -6585,19 +6585,19 @@
         <v>0.15</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.62</v>
+        <v>12.69</v>
       </c>
       <c r="DY14" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="EA14" t="n">
         <v>19.77</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC14" t="n">
         <v>2.31</v>
@@ -8384,7 +8384,7 @@
         <v>3.29</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.71</v>
+        <v>19.86</v>
       </c>
       <c r="BE19" t="n">
         <v>1.17</v>
@@ -8456,13 +8456,13 @@
         <v>3.51</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="CC19" t="n">
         <v>4.77</v>
       </c>
       <c r="CD19" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="CE19" t="n">
         <v>1.42</v>
@@ -8516,10 +8516,10 @@
         <v>1.41</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX19" t="n">
         <v>1.63</v>
@@ -8534,13 +8534,13 @@
         <v>1.86</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="DE19" t="n">
         <v>0.08</v>
@@ -8609,7 +8609,7 @@
         <v>3.39</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.69</v>
+        <v>19.77</v>
       </c>
       <c r="EB19" t="n">
         <v>1.26</v>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0.14</v>
@@ -3485,49 +3485,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="AO7" t="n">
         <v>1</v>
       </c>
-      <c r="AH7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>88.83</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AP7" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.17</v>
+        <v>12.86</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.83</v>
+        <v>16.14</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.17</v>
+        <v>7.29</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3539,73 +3539,73 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.5</v>
+        <v>55.29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="BC7" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.67</v>
+        <v>17.43</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF7" t="n">
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.77</v>
+        <v>7.79</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BR7" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU7" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY7" t="n">
         <v>3.28</v>
@@ -3623,106 +3623,106 @@
         <v>3.58</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="CB7" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.6</v>
+        <v>6.18</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.31</v>
+        <v>6.82</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS7" t="n">
         <v>3</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="CU7" t="n">
         <v>1.45</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="DD7" t="n">
         <v>2.72</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="DH7" t="n">
-        <v>98.69</v>
+        <v>97.28</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
@@ -3731,28 +3731,28 @@
         <v>2.08</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.08</v>
+        <v>45.22</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.31</v>
+        <v>12.22</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.69</v>
+        <v>15.86</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.31</v>
+        <v>7.36</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3764,28 +3764,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.46</v>
+        <v>59</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.31</v>
+        <v>11.14</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.31</v>
+        <v>7.14</v>
       </c>
       <c r="DZ7" t="n">
         <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>15.93</v>
+        <v>16.36</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="8">
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -4204,46 +4204,46 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="G9" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="H9" t="n">
-        <v>104.17</v>
+        <v>101.43</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J9" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>41.33</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O9" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>15.67</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.17</v>
+        <v>15.43</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="S9" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -4258,28 +4258,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>42.17</v>
+        <v>41</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.33</v>
+        <v>10.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>7</v>
+        <v>7.29</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>25.17</v>
+        <v>25.71</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4363,46 +4363,46 @@
         <v>2.43</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.23</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.62</v>
+        <v>3.79</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.92</v>
+        <v>4.71</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4414,19 +4414,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.49</v>
+        <v>3.32</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CC9" t="n">
         <v>5.27</v>
@@ -4438,7 +4438,7 @@
         <v>1.58</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CG9" t="n">
         <v>2.4</v>
@@ -4447,19 +4447,19 @@
         <v>1.28</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CJ9" t="n">
         <v>2.32</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CL9" t="n">
         <v>2.6</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CN9" t="n">
         <v>1.55</v>
@@ -4468,10 +4468,10 @@
         <v>1.54</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.19</v>
+        <v>5.25</v>
       </c>
       <c r="CR9" t="n">
         <v>1.62</v>
@@ -4480,34 +4480,34 @@
         <v>2.82</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CU9" t="n">
         <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CX9" t="n">
         <v>1.97</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CZ9" t="n">
         <v>1.87</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="DD9" t="n">
         <v>2.81</v>
@@ -4516,43 +4516,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="DH9" t="n">
-        <v>99.16</v>
+        <v>98.14</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
       <c r="DM9" t="n">
-        <v>42.07</v>
+        <v>41.86</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.93</v>
+        <v>15.14</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.62</v>
+        <v>14.36</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.92</v>
+        <v>6.86</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4564,28 +4564,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>40.77</v>
+        <v>40.29</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>9</v>
+        <v>9.43</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.39</v>
+        <v>6.58</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="EA9" t="n">
-        <v>25.46</v>
+        <v>25.71</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="10">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>80.56999999999999</v>
+        <v>81.38</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>35.57</v>
+        <v>38.25</v>
       </c>
       <c r="AO4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BL4" t="n">
         <v>0.71</v>
       </c>
-      <c r="AP4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.62</v>
-      </c>
       <c r="BM4" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.38</v>
+        <v>3.64</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS4" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT4" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU4" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY4" t="n">
         <v>2.34</v>
@@ -2416,25 +2416,25 @@
         <v>2.41</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.81</v>
+        <v>5.5</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.02</v>
+        <v>5.7</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CH4" t="n">
         <v>1.35</v>
@@ -2446,25 +2446,25 @@
         <v>2</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL4" t="n">
         <v>1.98</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO4" t="n">
         <v>1.39</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
@@ -2473,7 +2473,7 @@
         <v>3.06</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CU4" t="n">
         <v>1.41</v>
@@ -2488,97 +2488,97 @@
         <v>1.65</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB4" t="n">
         <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DD4" t="n">
         <v>3.05</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.84</v>
+        <v>1.21</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.62</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.31</v>
+        <v>42.43</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.69</v>
+        <v>12.86</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.62</v>
+        <v>11.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.69</v>
+        <v>8.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.54</v>
+        <v>46.57</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.08</v>
+        <v>10.35</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.69</v>
+        <v>7.07</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.39</v>
+        <v>3.29</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.84</v>
+        <v>19.85</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0.14</v>
@@ -3081,16 +3081,16 @@
         <v>1.71</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AI6" t="n">
-        <v>98.67</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -3099,34 +3099,34 @@
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AN6" t="n">
-        <v>41.83</v>
+        <v>39.71</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AQ6" t="n">
         <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.83</v>
+        <v>12.43</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,73 +3138,73 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>50.33</v>
+        <v>47.57</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.5</v>
+        <v>10.29</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.83</v>
+        <v>18.71</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BF6" t="n">
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.460000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
         <v>1</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS6" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BT6" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU6" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>2.75</v>
@@ -3222,167 +3222,169 @@
         <v>2.87</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.23</v>
+        <v>4.91</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.54</v>
+        <v>5.79</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="CQ6" t="n">
-        <v>5.09</v>
+        <v>4.87</v>
       </c>
       <c r="CR6" t="n">
         <v>1.53</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="CT6" t="n">
         <v>2.57</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CX6" t="n">
         <v>1.68</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.24</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="DB6" t="n">
         <v>1.51</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="DD6" t="inlineStr"/>
+        <v>2.53</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>2</v>
+      </c>
       <c r="DE6" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="DH6" t="n">
-        <v>105.23</v>
+        <v>102.64</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.38</v>
+        <v>5.29</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.84</v>
+        <v>41.71</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="DP6" t="n">
-        <v>16</v>
+        <v>16.07</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.92</v>
+        <v>13.64</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.31</v>
+        <v>7.43</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.39</v>
+        <v>49.93</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.31</v>
+        <v>11.14</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.77</v>
+        <v>7.64</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.3</v>
+        <v>19.71</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="7">
@@ -3795,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="H8" t="n">
-        <v>110.5</v>
+        <v>117.14</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>6.71</v>
       </c>
       <c r="L8" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>57.83</v>
+        <v>58.57</v>
       </c>
       <c r="N8" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>9.17</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.33</v>
+        <v>12.14</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>4.71</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="T8" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3861,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>67.17</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.83</v>
+        <v>20.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.5</v>
+        <v>12.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.83</v>
+        <v>17.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AF8" t="n">
         <v>0.29</v>
@@ -3966,37 +3968,37 @@
         <v>2.29</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.38</v>
+        <v>11.21</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="BP8" t="n">
-        <v>6.08</v>
+        <v>5.86</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4005,31 +4007,31 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BU8" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BV8" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW8" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX8" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.61</v>
+        <v>5.64</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.96</v>
+        <v>6.06</v>
       </c>
       <c r="CC8" t="n">
         <v>1.67</v>
@@ -4044,19 +4046,19 @@
         <v>2.04</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="CH8" t="n">
         <v>1.81</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL8" t="n">
         <v>1.69</v>
@@ -4078,17 +4080,17 @@
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
         <v>1.82</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX8" t="n">
         <v>1.49</v>
@@ -4100,7 +4102,7 @@
         <v>2.57</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB8" t="inlineStr"/>
       <c r="DC8" t="n">
@@ -4110,79 +4112,79 @@
         <v>2.04</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="DH8" t="n">
-        <v>113.08</v>
+        <v>116.22</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.69</v>
+        <v>6.57</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DM8" t="n">
-        <v>61.38</v>
+        <v>61.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.54</v>
+        <v>3.36</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.390000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12</v>
+        <v>12.36</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.54</v>
+        <v>4.42</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>67.84999999999999</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>20.15</v>
+        <v>20</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.16</v>
+        <v>12.14</v>
       </c>
       <c r="DZ8" t="n">
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.08</v>
+        <v>18</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="9">
@@ -5804,10 +5806,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
@@ -5816,82 +5818,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="G13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H13" t="n">
+        <v>89</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P13" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>13</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE13" t="n">
         <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>39.83</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P13" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>43.83</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>19.83</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
         <v>0.14</v>
@@ -5975,70 +5977,70 @@
         <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.54</v>
+        <v>5.64</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU13" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.11</v>
+        <v>3.87</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="CC13" t="n">
         <v>6.7</v>
@@ -6047,16 +6049,16 @@
         <v>7.15</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI13" t="n">
         <v>1.77</v>
@@ -6065,139 +6067,139 @@
         <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL13" t="n">
         <v>1.94</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CO13" t="n">
         <v>1.37</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS13" t="n">
         <v>2.91</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="CU13" t="n">
         <v>1.45</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW13" t="n">
         <v>2.08</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB13" t="n">
         <v>1.44</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DD13" t="n">
         <v>2.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF13" t="n">
         <v>1</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="DH13" t="n">
-        <v>91.39</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.61</v>
+        <v>37.71</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.61</v>
+        <v>11.5</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.92</v>
+        <v>13</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.77</v>
+        <v>7.93</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.84</v>
+        <v>45.42</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.62</v>
+        <v>10.36</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.85</v>
+        <v>6.57</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.31</v>
+        <v>18.36</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0.14</v>
@@ -1469,139 +1469,139 @@
         <v>1.43</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
         <v>3</v>
       </c>
-      <c r="AI2" t="n">
-        <v>96.33</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3.17</v>
-      </c>
       <c r="AL2" t="n">
-        <v>5.33</v>
+        <v>4.86</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="AN2" t="n">
-        <v>45.5</v>
+        <v>45.86</v>
       </c>
       <c r="AO2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.54</v>
-      </c>
       <c r="BK2" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.46</v>
+        <v>5.43</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.62</v>
+        <v>4.36</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS2" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT2" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY2" t="n">
         <v>1.58</v>
@@ -1610,46 +1610,46 @@
         <v>1.63</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.35</v>
+        <v>3.19</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.46</v>
+        <v>3.26</v>
       </c>
       <c r="CE2" t="n">
         <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH2" t="n">
         <v>1.36</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CK2" t="n">
         <v>1.55</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM2" t="n">
         <v>2.3</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO2" t="n">
         <v>1.37</v>
@@ -1658,7 +1658,7 @@
         <v>2.2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CR2" t="n">
         <v>1.49</v>
@@ -1673,106 +1673,106 @@
         <v>1.35</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CZ2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DC2" t="n">
         <v>2.25</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>2.26</v>
       </c>
       <c r="DD2" t="n">
         <v>2.72</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="DH2" t="n">
-        <v>108.46</v>
+        <v>109.14</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.69</v>
+        <v>5.43</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.54</v>
+        <v>50.36</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.54</v>
+        <v>13</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.16</v>
+        <v>13</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.38</v>
+        <v>5.64</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.61</v>
+        <v>49.21</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.08</v>
+        <v>13.14</v>
       </c>
       <c r="DY2" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.77</v>
+        <v>21</v>
       </c>
       <c r="EB2" t="n">
         <v>1.48</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F3" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="H3" t="n">
-        <v>105.43</v>
+        <v>105.12</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="K3" t="n">
-        <v>9.57</v>
+        <v>9.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>62.14</v>
+        <v>61.12</v>
       </c>
       <c r="N3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="P3" t="n">
-        <v>10.43</v>
+        <v>9.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.71</v>
+        <v>10.38</v>
       </c>
       <c r="R3" t="n">
-        <v>6.57</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.71</v>
+        <v>56.12</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>15.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>7.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.29</v>
+        <v>20.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
         <v>0.5</v>
@@ -1953,70 +1953,70 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.69</v>
+        <v>10.57</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.62</v>
+        <v>5.64</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX3" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.34</v>
+        <v>4.46</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.41</v>
+        <v>4.54</v>
       </c>
       <c r="CC3" t="n">
         <v>1.86</v>
@@ -2028,154 +2028,154 @@
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CX3" t="n">
         <v>1.63</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.3</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="DH3" t="n">
-        <v>102.54</v>
+        <v>102.57</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="DK3" t="n">
-        <v>7.46</v>
+        <v>7.43</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DM3" t="n">
-        <v>55.3</v>
+        <v>55.21</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO3" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.69</v>
+        <v>11.22</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.38</v>
+        <v>10.22</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.77</v>
+        <v>7.93</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>55.15</v>
+        <v>54.92</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX3" t="n">
         <v>14</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.08</v>
+        <v>7.93</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.92</v>
+        <v>6.07</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.46</v>
+        <v>19.07</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="4">
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.38</v>
+        <v>44.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.25</v>
@@ -2425,7 +2425,7 @@
         <v>5.5</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.7</v>
+        <v>5.69</v>
       </c>
       <c r="CE4" t="n">
         <v>1.47</v>
@@ -2473,7 +2473,7 @@
         <v>3.06</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CU4" t="n">
         <v>1.41</v>
@@ -2482,7 +2482,7 @@
         <v>1.83</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX4" t="n">
         <v>1.65</v>
@@ -2500,7 +2500,7 @@
         <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DD4" t="n">
         <v>3.05</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.57</v>
+        <v>46.64</v>
       </c>
       <c r="DW4" t="n">
         <v>0.28</v>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="H5" t="n">
-        <v>113.86</v>
+        <v>114.88</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.57</v>
+        <v>5.38</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>55.57</v>
+        <v>53.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>12.38</v>
       </c>
       <c r="R5" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="S5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54.29</v>
+        <v>55</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.86</v>
+        <v>11.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.289999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.14</v>
+        <v>20.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,67 +2759,67 @@
         <v>2.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.31</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BU5" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX5" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>2.75</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>2.87</v>
-      </c>
       <c r="CA5" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CB5" t="n">
         <v>3.52</v>
@@ -2834,7 +2834,7 @@
         <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG5" t="n">
         <v>2.9</v>
@@ -2846,7 +2846,7 @@
         <v>2.05</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK5" t="n">
         <v>1.63</v>
@@ -2855,7 +2855,7 @@
         <v>2.16</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN5" t="n">
         <v>1.75</v>
@@ -2864,10 +2864,10 @@
         <v>1.3</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2894,94 +2894,94 @@
         <v>2.1</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DH5" t="n">
-        <v>98.69</v>
+        <v>100.36</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.61</v>
+        <v>4.57</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.23</v>
+        <v>45.86</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.16</v>
+        <v>12.14</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12</v>
+        <v>12.22</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.62</v>
+        <v>7.43</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.77</v>
+        <v>51.43</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.23</v>
+        <v>11.21</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.46</v>
+        <v>7.43</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.23</v>
+        <v>19.36</v>
       </c>
       <c r="EB5" t="n">
         <v>1.31</v>
       </c>
       <c r="EC5" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="6">
@@ -3147,16 +3147,16 @@
         <v>10.29</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="BD6" t="n">
         <v>18.71</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BF6" t="n">
         <v>3</v>
@@ -3225,13 +3225,13 @@
         <v>3.32</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="CC6" t="n">
         <v>4.91</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.79</v>
+        <v>5.5</v>
       </c>
       <c r="CE6" t="n">
         <v>1.54</v>
@@ -3276,19 +3276,19 @@
         <v>1.53</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CT6" t="n">
         <v>2.57</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CX6" t="n">
         <v>1.68</v>
@@ -3309,7 +3309,7 @@
         <v>2.53</v>
       </c>
       <c r="DD6" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DE6" t="n">
         <v>0.14</v>
@@ -3372,10 +3372,10 @@
         <v>11.14</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.64</v>
+        <v>7.71</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="EA6" t="n">
         <v>19.71</v>
@@ -4031,7 +4031,7 @@
         <v>5.64</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.06</v>
+        <v>6.01</v>
       </c>
       <c r="CC8" t="n">
         <v>1.67</v>
@@ -4080,14 +4080,14 @@
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW8" t="n">
         <v>1.71</v>
@@ -4102,7 +4102,7 @@
         <v>2.57</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB8" t="inlineStr"/>
       <c r="DC8" t="n">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -4609,82 +4609,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="H10" t="n">
-        <v>92.29000000000001</v>
+        <v>88.88</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="K10" t="n">
-        <v>6.14</v>
+        <v>5.62</v>
       </c>
       <c r="L10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M10" t="n">
-        <v>48.86</v>
+        <v>45.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O10" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>9.710000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.29</v>
+        <v>14.12</v>
       </c>
       <c r="R10" t="n">
-        <v>6.86</v>
+        <v>7.38</v>
       </c>
       <c r="S10" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51.43</v>
+        <v>50</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.710000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.43</v>
+        <v>6.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.29</v>
+        <v>17.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
         <v>0.17</v>
@@ -4768,70 +4768,70 @@
         <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.46</v>
+        <v>10.21</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6</v>
+        <v>5.79</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS10" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV10" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX10" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.21</v>
+        <v>2.77</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.28</v>
+        <v>2.87</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.94</v>
+        <v>4.07</v>
       </c>
       <c r="CC10" t="n">
         <v>6.8</v>
@@ -4840,61 +4840,61 @@
         <v>7.03</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="CT10" t="n">
         <v>2.91</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CX10" t="n">
         <v>1.64</v>
@@ -4912,85 +4912,85 @@
         <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>83.47</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.31</v>
+        <v>4.14</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.54</v>
+        <v>39.21</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.69</v>
+        <v>10.57</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.08</v>
+        <v>13.07</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47.54</v>
+        <v>47</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.380000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.69</v>
+        <v>5.72</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.46</v>
+        <v>16.36</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5000,31 +5000,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="H11" t="n">
-        <v>73.59999999999999</v>
+        <v>77.17</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
@@ -5033,61 +5033,61 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="O11" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
-        <v>11.8</v>
+        <v>11.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="R11" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>35.6</v>
+        <v>39</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.8</v>
+        <v>6.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.8</v>
+        <v>17.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5171,70 +5171,70 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>11.15</v>
+        <v>10.79</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM11" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.46</v>
+        <v>5.43</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.69</v>
+        <v>5.36</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT11" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU11" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.37</v>
+        <v>5.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.78</v>
+        <v>5.48</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.99</v>
+        <v>3.94</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="CC11" t="n">
         <v>4.65</v>
@@ -5243,16 +5243,16 @@
         <v>4.94</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI11" t="n">
         <v>1.97</v>
@@ -5267,19 +5267,19 @@
         <v>1.91</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN11" t="n">
         <v>1.92</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5294,7 +5294,7 @@
         <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW11" t="n">
         <v>1.85</v>
@@ -5303,10 +5303,10 @@
         <v>1.6</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="DA11" t="n">
         <v>1.9</v>
@@ -5315,85 +5315,85 @@
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DD11" t="n">
         <v>2.96</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="DH11" t="n">
-        <v>78.45999999999999</v>
+        <v>79.64</v>
       </c>
       <c r="DI11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM11" t="n">
-        <v>36</v>
+        <v>35.36</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.77</v>
+        <v>12.65</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.46</v>
+        <v>12</v>
       </c>
       <c r="DR11" t="n">
-        <v>10.23</v>
+        <v>10.14</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>39</v>
+        <v>40.21</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.23</v>
+        <v>10.29</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.92</v>
+        <v>6.93</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.23</v>
+        <v>17.57</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="12">
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5493,139 +5493,139 @@
         <v>2.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>90.40000000000001</v>
+        <v>90.17</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>46</v>
+        <v>45.17</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>15.8</v>
+        <v>14.67</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.6</v>
+        <v>10.83</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.8</v>
+        <v>21.33</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.08</v>
+        <v>8.93</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.92</v>
+        <v>4.71</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV12" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
         <v>2.87</v>
@@ -5634,22 +5634,22 @@
         <v>2.84</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.43</v>
+        <v>5.18</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.73</v>
+        <v>5.52</v>
       </c>
       <c r="CE12" t="n">
         <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CG12" t="n">
         <v>2.84</v>
@@ -5658,31 +5658,31 @@
         <v>1.39</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CR12" t="n">
         <v>1.46</v>
@@ -5697,43 +5697,43 @@
         <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.38</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
@@ -5742,61 +5742,61 @@
         <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="DM12" t="n">
-        <v>49</v>
+        <v>48.43</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.15</v>
+        <v>13.29</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.85</v>
+        <v>10.93</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.84</v>
+        <v>6.78</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>41.54</v>
+        <v>41.43</v>
       </c>
       <c r="DW12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.84</v>
+        <v>13.5</v>
       </c>
       <c r="DY12" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.85</v>
+        <v>4.64</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.07</v>
+        <v>20.35</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="13">
@@ -5872,7 +5872,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>45.14</v>
+        <v>45</v>
       </c>
       <c r="Y13" t="n">
         <v>0.29</v>
@@ -6034,7 +6034,7 @@
         <v>3.75</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CA13" t="n">
         <v>3.87</v>
@@ -6094,13 +6094,13 @@
         <v>2.91</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CU13" t="n">
         <v>1.45</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW13" t="n">
         <v>2.08</v>
@@ -6121,7 +6121,7 @@
         <v>1.44</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD13" t="n">
         <v>2.71</v>
@@ -6178,7 +6178,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.42</v>
+        <v>45.36</v>
       </c>
       <c r="DW13" t="n">
         <v>0.22</v>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0.29</v>
@@ -6708,124 +6708,124 @@
         <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AI15" t="n">
-        <v>96.17</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>50.17</v>
+        <v>48.71</v>
       </c>
       <c r="AO15" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BK15" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP15" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.54</v>
-      </c>
       <c r="BL15" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.38</v>
+        <v>4.21</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.77</v>
+        <v>5.93</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT15" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU15" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6834,7 +6834,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY15" t="n">
         <v>2.14</v>
@@ -6843,31 +6843,31 @@
         <v>2.23</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CC15" t="n">
         <v>2.69</v>
       </c>
       <c r="CD15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CF15" t="n">
         <v>2.69</v>
       </c>
-      <c r="CE15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CF15" t="n">
-        <v>2.68</v>
-      </c>
       <c r="CG15" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.77</v>
@@ -6879,7 +6879,7 @@
         <v>1.98</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CN15" t="n">
         <v>1.88</v>
@@ -6888,124 +6888,124 @@
         <v>1.28</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CT15" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CU15" t="n">
         <v>1.41</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB15" t="n">
         <v>1.31</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>17</v>
+      </c>
+      <c r="EB15" t="n">
         <v>1.62</v>
       </c>
-      <c r="DG15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DH15" t="n">
-        <v>104.23</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="DK15" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>50.08</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>52.46</v>
-      </c>
-      <c r="DW15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DX15" t="n">
-        <v>15.15</v>
-      </c>
-      <c r="DY15" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="DZ15" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="EA15" t="n">
-        <v>16.46</v>
-      </c>
-      <c r="EB15" t="n">
-        <v>1.65</v>
-      </c>
       <c r="EC15" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7108,136 +7108,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>119.29</v>
+        <v>117.62</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>58.43</v>
+        <v>64.38</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.859999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AU16" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>58.29</v>
+        <v>58.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>19.43</v>
+        <v>20.12</v>
       </c>
       <c r="BB16" t="n">
-        <v>12.29</v>
+        <v>13.38</v>
       </c>
       <c r="BC16" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="BW16" t="n">
         <v>7.14</v>
       </c>
-      <c r="BD16" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>92.31</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>76.92</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>69.23</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>7.69</v>
-      </c>
       <c r="BX16" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY16" t="n">
         <v>1.28</v>
@@ -7246,73 +7246,73 @@
         <v>1.34</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.37</v>
+        <v>5.35</v>
       </c>
       <c r="CB16" t="n">
         <v>5.77</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CE16" t="n">
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK16" t="n">
         <v>1.43</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN16" t="n">
         <v>2.13</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CR16" t="n">
         <v>1.34</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CT16" t="n">
         <v>3.28</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX16" t="n">
         <v>1.59</v>
@@ -7330,85 +7330,85 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="DH16" t="n">
-        <v>124.85</v>
+        <v>123.5</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.23</v>
+        <v>6.15</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM16" t="n">
-        <v>68.62</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="DP16" t="n">
-        <v>10</v>
+        <v>10.22</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.61</v>
+        <v>13.21</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>59.69</v>
+        <v>59.71</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX16" t="n">
-        <v>19.77</v>
+        <v>20.14</v>
       </c>
       <c r="DY16" t="n">
-        <v>12.47</v>
+        <v>13.08</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.31</v>
+        <v>7.07</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.61</v>
+        <v>17.21</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="17">
@@ -7418,13 +7418,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7511,136 +7511,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AH17" t="n">
         <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>68.5</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AL17" t="n">
         <v>3</v>
       </c>
-      <c r="AL17" t="n">
-        <v>3.17</v>
-      </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>27.33</v>
+        <v>31.14</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.33</v>
+        <v>12.57</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.33</v>
+        <v>10.43</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>42.17</v>
+        <v>43</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.33</v>
+        <v>5.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.33</v>
+        <v>18.86</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.15</v>
+        <v>10.07</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BR17" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BU17" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV17" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX17" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BY17" t="n">
         <v>5.1</v>
@@ -7649,169 +7649,169 @@
         <v>5.52</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.06</v>
+        <v>7.14</v>
       </c>
       <c r="CD17" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI17" t="n">
         <v>1.74</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CX17" t="n">
         <v>1.65</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.26</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DH17" t="n">
-        <v>70.69</v>
+        <v>72.5</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.69</v>
+        <v>3.57</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM17" t="n">
-        <v>32.31</v>
+        <v>33.86</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.69</v>
+        <v>11.43</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.31</v>
+        <v>10.86</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.23</v>
+        <v>8.07</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.23</v>
+        <v>43.57</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX17" t="n">
-        <v>8.390000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.46</v>
+        <v>5.86</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.92</v>
+        <v>18.28</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="18">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
@@ -7833,82 +7833,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="G18" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>103</v>
+        <v>108.57</v>
       </c>
       <c r="I18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J18" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M18" t="n">
-        <v>49.5</v>
+        <v>50.14</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O18" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="P18" t="n">
-        <v>16.33</v>
+        <v>16.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.5</v>
+        <v>14.14</v>
       </c>
       <c r="R18" t="n">
-        <v>6.67</v>
+        <v>6.57</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>55.33</v>
+        <v>56</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.17</v>
+        <v>13.86</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.17</v>
+        <v>21.29</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7992,70 +7992,70 @@
         <v>2.71</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.31</v>
+        <v>10.29</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.31</v>
+        <v>5.07</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5</v>
+        <v>5.21</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU18" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CC18" t="n">
         <v>4.03</v>
@@ -8067,154 +8067,154 @@
         <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CG18" t="n">
         <v>2.86</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CK18" t="n">
         <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN18" t="n">
         <v>1.93</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CU18" t="n">
         <v>1.45</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="DH18" t="n">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.23</v>
+        <v>6.36</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM18" t="n">
-        <v>46.85</v>
+        <v>47.36</v>
       </c>
       <c r="DN18" t="n">
         <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.46</v>
+        <v>15.42</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.85</v>
+        <v>11.36</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.62</v>
+        <v>7.5</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.77</v>
+        <v>51.43</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.62</v>
+        <v>13.93</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.77</v>
+        <v>8.93</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.16</v>
+        <v>19.79</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="19">
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -8236,82 +8236,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="G19" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="H19" t="n">
-        <v>97.33</v>
+        <v>100.71</v>
       </c>
       <c r="I19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J19" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="K19" t="n">
-        <v>5.17</v>
+        <v>5.29</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>51.67</v>
+        <v>52.14</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="P19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R19" t="n">
-        <v>4.17</v>
+        <v>4.86</v>
       </c>
       <c r="S19" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="U19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>55.5</v>
+        <v>56.86</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.83</v>
+        <v>11.43</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.67</v>
+        <v>19.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="AF19" t="n">
         <v>0.14</v>
@@ -8395,70 +8395,70 @@
         <v>2.71</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.92</v>
+        <v>10.86</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.62</v>
+        <v>5.36</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV19" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CC19" t="n">
         <v>4.77</v>
@@ -8470,19 +8470,19 @@
         <v>1.42</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK19" t="n">
         <v>1.55</v>
@@ -8491,19 +8491,19 @@
         <v>1.98</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CN19" t="n">
         <v>1.83</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP19" t="n">
         <v>2.1</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
@@ -8512,112 +8512,112 @@
         <v>3.07</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CU19" t="n">
         <v>1.41</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CY19" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC19" t="n">
         <v>2.16</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.54000000000001</v>
+        <v>93.64</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.08</v>
+        <v>43</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.23</v>
+        <v>15.14</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.92</v>
+        <v>14.5</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.08</v>
+        <v>5.36</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.54</v>
+        <v>54.36</v>
       </c>
       <c r="DW19" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.31</v>
+        <v>11.14</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.92</v>
+        <v>7.79</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.77</v>
+        <v>19.78</v>
       </c>
       <c r="EB19" t="n">
         <v>1.26</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="20">
@@ -9030,13 +9030,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>0.29</v>
@@ -9123,136 +9123,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI21" t="n">
-        <v>75.33</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BG21" t="n">
         <v>3</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="BH21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BI21" t="n">
         <v>3</v>
       </c>
-      <c r="AM21" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>37.83</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.85</v>
-      </c>
       <c r="BJ21" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP21" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.15</v>
+        <v>4.43</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT21" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU21" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV21" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
         <v>1.64</v>
@@ -9261,28 +9261,28 @@
         <v>1.72</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="CE21" t="n">
         <v>1.34</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI21" t="n">
         <v>2.09</v>
@@ -9294,7 +9294,7 @@
         <v>1.53</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM21" t="n">
         <v>2.35</v>
@@ -9306,25 +9306,25 @@
         <v>1.23</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ21" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS21" t="n">
         <v>2.73</v>
       </c>
       <c r="CT21" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CU21" t="n">
         <v>1.49</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW21" t="n">
         <v>1.78</v>
@@ -9333,7 +9333,7 @@
         <v>1.58</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.38</v>
@@ -9345,85 +9345,85 @@
         <v>1.28</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DH21" t="n">
-        <v>87.54000000000001</v>
+        <v>86.28</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.62</v>
+        <v>4.43</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DM21" t="n">
-        <v>47.77</v>
+        <v>47.28</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="DP21" t="n">
-        <v>11.69</v>
+        <v>12.14</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.23</v>
+        <v>45.78</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.77</v>
+        <v>13.5</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.69</v>
+        <v>8.43</v>
       </c>
       <c r="DZ21" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="EA21" t="n">
         <v>17</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.08</v>
+        <v>2.43</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H2" t="n">
-        <v>118.86</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.14</v>
-      </c>
       <c r="M2" t="n">
-        <v>54.86</v>
+        <v>55.88</v>
       </c>
       <c r="N2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O2" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="P2" t="n">
-        <v>14.29</v>
+        <v>14.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.29</v>
+        <v>12.12</v>
       </c>
       <c r="R2" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="S2" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="T2" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>52.71</v>
+        <v>50.88</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.29</v>
+        <v>13.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>22</v>
+        <v>21.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0.14</v>
@@ -1550,67 +1550,67 @@
         <v>2.14</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.789999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.36</v>
+        <v>4.53</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT2" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="CB2" t="n">
         <v>3.66</v>
@@ -1622,67 +1622,67 @@
         <v>3.26</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CK2" t="n">
         <v>1.55</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CN2" t="n">
         <v>1.81</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CX2" t="n">
         <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.27</v>
@@ -1691,76 +1691,76 @@
         <v>1.8</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="DH2" t="n">
-        <v>109.14</v>
+        <v>109.73</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.36</v>
+        <v>51.2</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="DP2" t="n">
-        <v>13</v>
+        <v>13.13</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.64</v>
+        <v>5.4</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.21</v>
+        <v>48.47</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.14</v>
+        <v>12.86</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.07</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.07</v>
@@ -1769,10 +1769,10 @@
         <v>21</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0.25</v>
@@ -1872,139 +1872,139 @@
         <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AI3" t="n">
-        <v>99.17</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AL3" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>5</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>4.93</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
         <v>1.57</v>
@@ -2013,34 +2013,34 @@
         <v>1.63</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.84</v>
+        <v>2.21</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="CK3" t="n">
         <v>1.56</v>
@@ -2049,19 +2049,19 @@
         <v>2.02</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CN3" t="n">
         <v>1.83</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
@@ -2076,22 +2076,22 @@
         <v>1.49</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
@@ -2103,79 +2103,79 @@
         <v>3</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DH3" t="n">
-        <v>102.57</v>
+        <v>102.06</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>7.43</v>
+        <v>7.2</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="DM3" t="n">
-        <v>55.21</v>
+        <v>54.06</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DO3" t="n">
-        <v>4.21</v>
+        <v>4</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.22</v>
+        <v>11.07</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.22</v>
+        <v>10.34</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.93</v>
+        <v>8.33</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.92</v>
+        <v>54.06</v>
       </c>
       <c r="DW3" t="n">
         <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>14</v>
+        <v>13.53</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.93</v>
+        <v>7.73</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.07</v>
+        <v>5.8</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.07</v>
+        <v>19.34</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55</v>
+        <v>55.12</v>
       </c>
       <c r="Y5" t="n">
         <v>0.12</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.43</v>
+        <v>51.5</v>
       </c>
       <c r="DW5" t="n">
         <v>0.07000000000000001</v>
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F8" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="H8" t="n">
-        <v>117.14</v>
+        <v>114.75</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="K8" t="n">
-        <v>6.71</v>
+        <v>6.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M8" t="n">
-        <v>58.57</v>
+        <v>58.12</v>
       </c>
       <c r="N8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>9.289999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.14</v>
+        <v>11.62</v>
       </c>
       <c r="R8" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="S8" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="T8" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>67.43000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.43</v>
+        <v>20.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.71</v>
+        <v>17.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AF8" t="n">
         <v>0.29</v>
@@ -3971,34 +3971,34 @@
         <v>3.93</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.21</v>
+        <v>11.07</v>
       </c>
       <c r="BI8" t="n">
         <v>3.93</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.86</v>
+        <v>5.67</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.36</v>
+        <v>5.4</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4007,31 +4007,31 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BV8" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.64</v>
+        <v>5.54</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.01</v>
+        <v>5.91</v>
       </c>
       <c r="CC8" t="n">
         <v>1.67</v>
@@ -4046,28 +4046,28 @@
         <v>2.04</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO8" t="n">
         <v>1.1</v>
@@ -4087,22 +4087,22 @@
         <v>1.84</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="CW8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CY8" t="n">
         <v>1.71</v>
       </c>
-      <c r="CX8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>1.7</v>
-      </c>
       <c r="CZ8" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DB8" t="inlineStr"/>
       <c r="DC8" t="n">
@@ -4112,46 +4112,46 @@
         <v>2.04</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DH8" t="n">
-        <v>116.22</v>
+        <v>115</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.57</v>
+        <v>6.47</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DM8" t="n">
-        <v>61.5</v>
+        <v>61.06</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.43</v>
+        <v>9.6</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.36</v>
+        <v>12.06</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="DS8" t="n">
         <v>0.14</v>
@@ -4163,28 +4163,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>67.93000000000001</v>
+        <v>67.27</v>
       </c>
       <c r="DW8" t="n">
         <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>20</v>
+        <v>19.93</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.14</v>
+        <v>12.2</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.86</v>
+        <v>7.73</v>
       </c>
       <c r="EA8" t="n">
         <v>18</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="9">
@@ -5550,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>38.5</v>
+        <v>38.33</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>41.43</v>
+        <v>41.35</v>
       </c>
       <c r="DW12" t="n">
         <v>0.07000000000000001</v>
@@ -6209,10 +6209,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
@@ -6221,49 +6221,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="H14" t="n">
-        <v>99.40000000000001</v>
+        <v>98.33</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="M14" t="n">
-        <v>54.8</v>
+        <v>54.17</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>4.17</v>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>8.6</v>
+        <v>8.17</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6275,28 +6275,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>53.2</v>
+        <v>53.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.6</v>
+        <v>15.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.8</v>
+        <v>5.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.2</v>
+        <v>22.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6383,67 +6383,67 @@
         <v>2</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.54</v>
+        <v>11.79</v>
       </c>
       <c r="BI14" t="n">
         <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.77</v>
+        <v>6</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.77</v>
+        <v>5.79</v>
       </c>
       <c r="BR14" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT14" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV14" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.79</v>
+        <v>3.51</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CC14" t="n">
         <v>3.93</v>
@@ -6452,19 +6452,19 @@
         <v>4.09</v>
       </c>
       <c r="CE14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CH14" t="n">
         <v>1.4</v>
       </c>
-      <c r="CF14" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>1.41</v>
-      </c>
       <c r="CI14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.84</v>
@@ -6473,22 +6473,22 @@
         <v>1.46</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP14" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="CR14" t="n">
         <v>1.44</v>
@@ -6503,7 +6503,7 @@
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW14" t="n">
         <v>1.9</v>
@@ -6533,43 +6533,43 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="DH14" t="n">
-        <v>94</v>
+        <v>93.92</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.15</v>
+        <v>6.43</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.46</v>
+        <v>46.79</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.54</v>
+        <v>13.36</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.460000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.07000000000000001</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.31</v>
+        <v>53.5</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.69</v>
+        <v>13.14</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.619999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.07</v>
+        <v>4.28</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.77</v>
+        <v>20.36</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="15">
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7105,139 +7105,139 @@
         <v>2.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AI16" t="n">
-        <v>117.62</v>
+        <v>115.11</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN16" t="n">
-        <v>64.38</v>
+        <v>62.11</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.5</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AR16" t="n">
         <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.619999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>58.5</v>
+        <v>58.89</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>20.12</v>
+        <v>19.33</v>
       </c>
       <c r="BB16" t="n">
-        <v>13.38</v>
+        <v>12.44</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.75</v>
+        <v>6.89</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.12</v>
+        <v>16.22</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>3</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.289999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI16" t="n">
         <v>3</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.43</v>
+        <v>4.6</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU16" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY16" t="n">
         <v>1.28</v>
@@ -7246,73 +7246,73 @@
         <v>1.34</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.35</v>
+        <v>5.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.77</v>
+        <v>5.63</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CE16" t="n">
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CO16" t="n">
         <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX16" t="n">
         <v>1.59</v>
@@ -7330,85 +7330,85 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DH16" t="n">
-        <v>123.5</v>
+        <v>121.6</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM16" t="n">
-        <v>71.29000000000001</v>
+        <v>69.47</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.21</v>
+        <v>13.33</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.71</v>
+        <v>6.94</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>59.71</v>
+        <v>59.87</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX16" t="n">
-        <v>20.14</v>
+        <v>19.67</v>
       </c>
       <c r="DY16" t="n">
-        <v>13.08</v>
+        <v>12.53</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.07</v>
+        <v>7.13</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.21</v>
+        <v>17.2</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="17">
@@ -8627,13 +8627,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
         <v>0.14</v>
@@ -8720,136 +8720,136 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AI20" t="n">
-        <v>79.17</v>
+        <v>80.14</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>29.5</v>
+        <v>33</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP20" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.5</v>
+        <v>11.14</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>11.86</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>41</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BG20" t="n">
         <v>2.5</v>
       </c>
-      <c r="AU20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BH20" t="n">
-        <v>9.69</v>
+        <v>10.07</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.46</v>
+        <v>5.5</v>
       </c>
       <c r="BR20" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS20" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU20" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV20" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX20" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY20" t="n">
         <v>2.59</v>
@@ -8858,25 +8858,25 @@
         <v>2.83</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="CC20" t="n">
-        <v>5.96</v>
+        <v>5.63</v>
       </c>
       <c r="CD20" t="n">
-        <v>7.05</v>
+        <v>6.63</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF20" t="n">
         <v>3</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CH20" t="n">
         <v>1.41</v>
@@ -8885,19 +8885,19 @@
         <v>1.87</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO20" t="n">
         <v>1.33</v>
@@ -8906,7 +8906,7 @@
         <v>2.09</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
@@ -8921,7 +8921,7 @@
         <v>1.47</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW20" t="n">
         <v>1.97</v>
@@ -8948,46 +8948,46 @@
         <v>3</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="DH20" t="n">
-        <v>85.77</v>
+        <v>85.78</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM20" t="n">
-        <v>36.54</v>
+        <v>37.79</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.38</v>
+        <v>12.14</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.39</v>
+        <v>11.36</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.93</v>
+        <v>8</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8999,28 +8999,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.31</v>
+        <v>47.07</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.69</v>
+        <v>10.64</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.69</v>
+        <v>7.72</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.53</v>
+        <v>18.21</v>
       </c>
       <c r="EB20" t="n">
         <v>1.15</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5896,139 +5896,139 @@
         <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>93.86</v>
+        <v>93</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>35.71</v>
+        <v>35.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.43</v>
+        <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>13.12</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.289999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="AT13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.71</v>
+        <v>44.75</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.86</v>
+        <v>11.12</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.57</v>
+        <v>6.75</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="BD13" t="n">
-        <v>17</v>
+        <v>18.25</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BF13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.859999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.21</v>
+        <v>4.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
         <v>3.75</v>
@@ -6037,28 +6037,28 @@
         <v>3.88</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="CB13" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="CC13" t="n">
-        <v>6.7</v>
+        <v>6.24</v>
       </c>
       <c r="CD13" t="n">
-        <v>7.15</v>
+        <v>6.64</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI13" t="n">
         <v>1.77</v>
@@ -6070,49 +6070,49 @@
         <v>1.56</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN13" t="n">
         <v>1.84</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.93</v>
+        <v>3.98</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS13" t="n">
         <v>2.91</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CU13" t="n">
         <v>1.45</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW13" t="n">
         <v>2.08</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY13" t="n">
         <v>2.06</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA13" t="n">
         <v>1.83</v>
@@ -6121,85 +6121,85 @@
         <v>1.44</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="DD13" t="n">
         <v>2.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="DH13" t="n">
-        <v>91.43000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="DI13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.71</v>
+        <v>37.46</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.5</v>
+        <v>11.53</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13</v>
+        <v>13.06</v>
       </c>
       <c r="DR13" t="n">
         <v>7.93</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.36</v>
+        <v>44.87</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.36</v>
+        <v>10.53</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.57</v>
+        <v>6.67</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.36</v>
+        <v>18.93</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="14">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
@@ -7430,49 +7430,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="G17" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="H17" t="n">
-        <v>72.56999999999999</v>
+        <v>74</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="K17" t="n">
-        <v>4.14</v>
+        <v>4.62</v>
       </c>
       <c r="L17" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M17" t="n">
-        <v>36.57</v>
+        <v>38.62</v>
       </c>
       <c r="N17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="P17" t="n">
-        <v>10.29</v>
+        <v>10.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.29</v>
+        <v>11.38</v>
       </c>
       <c r="R17" t="n">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="S17" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7484,28 +7484,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>44.14</v>
+        <v>46.38</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.43</v>
+        <v>7.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.71</v>
+        <v>17.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7589,70 +7589,70 @@
         <v>2.29</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.07</v>
+        <v>10.27</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.36</v>
+        <v>5.47</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="BR17" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS17" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT17" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX17" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BY17" t="n">
-        <v>5.1</v>
+        <v>4.79</v>
       </c>
       <c r="BZ17" t="n">
-        <v>5.52</v>
+        <v>5.16</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="CC17" t="n">
         <v>7.14</v>
@@ -7661,22 +7661,22 @@
         <v>6.99</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI17" t="n">
         <v>1.74</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK17" t="n">
         <v>1.53</v>
@@ -7685,7 +7685,7 @@
         <v>2</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN17" t="n">
         <v>1.87</v>
@@ -7694,19 +7694,19 @@
         <v>1.37</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS17" t="n">
         <v>2.92</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
@@ -7718,7 +7718,7 @@
         <v>2.16</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY17" t="n">
         <v>2.01</v>
@@ -7733,7 +7733,7 @@
         <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="DD17" t="n">
         <v>3.14</v>
@@ -7742,43 +7742,43 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="DH17" t="n">
-        <v>72.5</v>
+        <v>73.27</v>
       </c>
       <c r="DI17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.57</v>
+        <v>3.86</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM17" t="n">
-        <v>33.86</v>
+        <v>35.13</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.43</v>
+        <v>11.6</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.86</v>
+        <v>10.94</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.07</v>
+        <v>8</v>
       </c>
       <c r="DS17" t="n">
         <v>0.07000000000000001</v>
@@ -7790,28 +7790,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.57</v>
+        <v>44.8</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="DX17" t="n">
-        <v>8.640000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.86</v>
+        <v>6.27</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.28</v>
+        <v>18.34</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H2" t="n">
-        <v>118.75</v>
+        <v>119</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="K2" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="L2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M2" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="P2" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S2" t="n">
         <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="P2" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.12</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>50.88</v>
+        <v>50.11</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.62</v>
+        <v>13.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.25</v>
+        <v>9.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.88</v>
+        <v>22</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF2" t="n">
         <v>0.14</v>
@@ -1550,70 +1550,70 @@
         <v>2.14</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS2" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BT2" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CC2" t="n">
         <v>3.19</v>
@@ -1625,7 +1625,7 @@
         <v>1.42</v>
       </c>
       <c r="CF2" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CG2" t="n">
         <v>2.78</v>
@@ -1637,22 +1637,22 @@
         <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP2" t="n">
         <v>2.17</v>
@@ -1661,31 +1661,31 @@
         <v>3.88</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS2" t="n">
         <v>3.22</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CU2" t="n">
         <v>1.36</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY2" t="n">
         <v>2.05</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA2" t="n">
         <v>1.8</v>
@@ -1700,79 +1700,79 @@
         <v>2.89</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DH2" t="n">
-        <v>109.73</v>
+        <v>110.44</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.4</v>
+        <v>5.38</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.2</v>
+        <v>51.38</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.13</v>
+        <v>12.87</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.4</v>
+        <v>12.37</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.4</v>
+        <v>5.56</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.47</v>
+        <v>48.18</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.86</v>
+        <v>12.94</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="EA2" t="n">
-        <v>21</v>
+        <v>21.12</v>
       </c>
       <c r="EB2" t="n">
         <v>1.47</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0.25</v>
@@ -1872,115 +1872,115 @@
         <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AG3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AH3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>98.56999999999999</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>51.71</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>18.29</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.47</v>
+        <v>10.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="BQ3" t="n">
         <v>5</v>
@@ -1989,22 +1989,22 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BT3" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY3" t="n">
         <v>1.57</v>
@@ -2013,106 +2013,106 @@
         <v>1.63</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.43</v>
+        <v>4.35</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.93</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.31</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DD3" t="n">
         <v>3</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="DH3" t="n">
-        <v>102.06</v>
+        <v>102.12</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
@@ -2121,61 +2121,61 @@
         <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>7.2</v>
+        <v>7.12</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DM3" t="n">
-        <v>54.06</v>
+        <v>53.68</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.07</v>
+        <v>11.12</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.34</v>
+        <v>10.25</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.33</v>
+        <v>8.56</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.06</v>
+        <v>54.18</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.53</v>
+        <v>13.12</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.73</v>
+        <v>7.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.8</v>
+        <v>5.62</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.34</v>
+        <v>19.94</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>81</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AN5" t="n">
-        <v>35.33</v>
+        <v>32.86</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.67</v>
+        <v>13.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>11.14</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.67</v>
+        <v>10.29</v>
       </c>
       <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.17</v>
       </c>
-      <c r="AU5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BF5" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.140000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.29</v>
+        <v>5.13</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BY5" t="n">
         <v>2.66</v>
@@ -2819,55 +2819,55 @@
         <v>2.75</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.76</v>
+        <v>3.73</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.92</v>
+        <v>4.07</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.8</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2891,97 +2891,97 @@
         <v>1.67</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.25</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.36</v>
+        <v>98.27</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.57</v>
+        <v>4.33</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.86</v>
+        <v>44</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.14</v>
+        <v>12.13</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.22</v>
+        <v>11.8</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.43</v>
+        <v>7.87</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.5</v>
+        <v>50.86</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.21</v>
+        <v>10.93</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.43</v>
+        <v>7.07</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.36</v>
+        <v>18.8</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="G6" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>110.86</v>
+        <v>108.75</v>
       </c>
       <c r="I6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="K6" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>43.71</v>
+        <v>44.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>15.14</v>
+        <v>15.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.86</v>
+        <v>14.88</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>52.29</v>
+        <v>50.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.43</v>
+        <v>8.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.71</v>
+        <v>20.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
         <v>0.14</v>
@@ -3162,49 +3162,49 @@
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.43</v>
+        <v>9.67</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BO6" t="n">
         <v>0.93</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.07</v>
+        <v>5.33</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY6" t="n">
         <v>2.75</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CC6" t="n">
         <v>4.91</v>
@@ -3237,7 +3237,7 @@
         <v>1.54</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CG6" t="n">
         <v>2.5</v>
@@ -3249,7 +3249,7 @@
         <v>1.7</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CK6" t="n">
         <v>1.58</v>
@@ -3258,7 +3258,7 @@
         <v>2.17</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN6" t="n">
         <v>1.79</v>
@@ -3267,19 +3267,19 @@
         <v>1.47</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CS6" t="n">
         <v>3.05</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CU6" t="n">
         <v>1.46</v>
@@ -3291,10 +3291,10 @@
         <v>2.19</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.24</v>
@@ -3303,88 +3303,88 @@
         <v>1.8</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DD6" t="n">
         <v>2.06</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DH6" t="n">
-        <v>102.64</v>
+        <v>102.07</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.29</v>
+        <v>5.26</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.71</v>
+        <v>42.13</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DP6" t="n">
-        <v>16.07</v>
+        <v>16.33</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.64</v>
+        <v>13.74</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.43</v>
+        <v>7.6</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.93</v>
+        <v>49.13</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.14</v>
+        <v>11.34</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.71</v>
+        <v>7.93</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.71</v>
+        <v>19.53</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="7">
@@ -3394,61 +3394,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="H7" t="n">
-        <v>107.14</v>
+        <v>105.88</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="K7" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M7" t="n">
-        <v>56</v>
+        <v>54.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>11.57</v>
+        <v>12.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.57</v>
+        <v>15.25</v>
       </c>
       <c r="R7" t="n">
-        <v>7.43</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T7" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>62.71</v>
+        <v>62.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.71</v>
+        <v>13.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.29</v>
+        <v>15</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,49 +3565,49 @@
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.79</v>
+        <v>7.53</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.79</v>
+        <v>4.67</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="BR7" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,19 +3616,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="CC7" t="n">
         <v>6.18</v>
@@ -3640,7 +3640,7 @@
         <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG7" t="n">
         <v>2.79</v>
@@ -3649,31 +3649,31 @@
         <v>1.39</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK7" t="n">
         <v>1.65</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CM7" t="n">
         <v>2.17</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO7" t="n">
         <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="CR7" t="n">
         <v>1.49</v>
@@ -3688,19 +3688,19 @@
         <v>1.45</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX7" t="n">
         <v>1.71</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DA7" t="n">
         <v>1.75</v>
@@ -3715,46 +3715,46 @@
         <v>2.72</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DH7" t="n">
-        <v>97.28</v>
+        <v>97.27</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.22</v>
+        <v>45.13</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.22</v>
+        <v>12.6</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.86</v>
+        <v>15.67</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.36</v>
+        <v>7.14</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59</v>
+        <v>58.93</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX7" t="n">
         <v>11.14</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.36</v>
+        <v>16.13</v>
       </c>
       <c r="EB7" t="n">
         <v>1.32</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.38</v>
@@ -3887,118 +3887,118 @@
         <v>0.88</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>115.29</v>
+        <v>110.25</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>6.43</v>
+        <v>6.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.43000000000001</v>
+        <v>60.88</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.57</v>
+        <v>12.62</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.14</v>
+        <v>4.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>68.43000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA8" t="n">
-        <v>19.57</v>
+        <v>19.12</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.86</v>
+        <v>11.38</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.71</v>
+        <v>7.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.29</v>
+        <v>17</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.93</v>
+        <v>4.19</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.07</v>
+        <v>11.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.93</v>
+        <v>4.19</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4007,19 +4007,19 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BU8" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BX8" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY8" t="n">
         <v>1.29</v>
@@ -4028,16 +4028,16 @@
         <v>1.34</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.54</v>
+        <v>5.47</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.91</v>
+        <v>5.79</v>
       </c>
       <c r="CC8" t="n">
         <v>1.67</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CE8" t="n">
         <v>1.21</v>
@@ -4046,28 +4046,28 @@
         <v>2.04</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CK8" t="n">
         <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO8" t="n">
         <v>1.1</v>
@@ -4076,115 +4076,115 @@
         <v>1.4</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CX8" t="n">
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.52</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DB8" t="inlineStr"/>
       <c r="DC8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="DH8" t="n">
-        <v>115</v>
+        <v>112.5</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DM8" t="n">
-        <v>61.06</v>
+        <v>59.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.6</v>
+        <v>9.56</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.06</v>
+        <v>12.12</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.4</v>
+        <v>4.56</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>67.27</v>
+        <v>66.94</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>19.93</v>
+        <v>19.69</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.2</v>
+        <v>11.94</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.73</v>
+        <v>7.75</v>
       </c>
       <c r="EA8" t="n">
-        <v>18</v>
+        <v>17.38</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="9">
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4287,49 +4287,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AI9" t="n">
-        <v>94.86</v>
+        <v>96.12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.57</v>
+        <v>5.25</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>42.71</v>
+        <v>40.62</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.29</v>
+        <v>14.38</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.29</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.86</v>
+        <v>6.62</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4341,70 +4341,70 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>39.57</v>
+        <v>39.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.710000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>25.71</v>
+        <v>23.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="BG9" t="n">
         <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.140000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="BI9" t="n">
         <v>2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.79</v>
+        <v>3.93</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.71</v>
+        <v>4.53</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY9" t="n">
         <v>3.25</v>
@@ -4425,40 +4425,40 @@
         <v>3.32</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.79</v>
+        <v>5.86</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CH9" t="n">
         <v>1.28</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CJ9" t="n">
         <v>2.32</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="CM9" t="n">
         <v>1.91</v>
@@ -4467,49 +4467,49 @@
         <v>1.55</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.25</v>
+        <v>5.14</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.82</v>
+        <v>3.06</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="CV9" t="n">
         <v>1.62</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DA9" t="n">
         <v>1.56</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DD9" t="n">
         <v>2.81</v>
@@ -4518,43 +4518,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="DH9" t="n">
-        <v>98.14</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.86</v>
+        <v>40.8</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DP9" t="n">
         <v>15.14</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.36</v>
+        <v>14.67</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.86</v>
+        <v>6.73</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>40.29</v>
+        <v>40.2</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.43</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.58</v>
+        <v>6.54</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="EA9" t="n">
-        <v>25.71</v>
+        <v>24.66</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="10">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="n">
         <v>2</v>
@@ -4696,130 +4696,130 @@
         <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>73.17</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>30.83</v>
+        <v>33.57</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.83</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.67</v>
+        <v>12.57</v>
       </c>
       <c r="AS10" t="n">
-        <v>13.5</v>
+        <v>12.43</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>43</v>
+        <v>42.86</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.33</v>
+        <v>15.71</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.79</v>
+        <v>5.47</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX10" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>2.77</v>
@@ -4828,25 +4828,25 @@
         <v>2.87</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.8</v>
+        <v>6.31</v>
       </c>
       <c r="CD10" t="n">
-        <v>7.03</v>
+        <v>6.56</v>
       </c>
       <c r="CE10" t="n">
         <v>1.37</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CH10" t="n">
         <v>1.48</v>
@@ -4858,13 +4858,13 @@
         <v>1.79</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN10" t="n">
         <v>1.84</v>
@@ -4876,7 +4876,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
@@ -4900,13 +4900,13 @@
         <v>1.64</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
@@ -4921,76 +4921,76 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DH10" t="n">
-        <v>82.15000000000001</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.21</v>
+        <v>39.93</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.57</v>
+        <v>10.73</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.07</v>
+        <v>13.4</v>
       </c>
       <c r="DR10" t="n">
-        <v>10</v>
+        <v>9.74</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47</v>
+        <v>46.67</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.43</v>
+        <v>9.33</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.72</v>
+        <v>5.6</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.36</v>
+        <v>16.87</v>
       </c>
       <c r="EB10" t="n">
         <v>1.14</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="11">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
@@ -5415,82 +5415,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="H12" t="n">
-        <v>95.25</v>
+        <v>91.67</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="M12" t="n">
-        <v>50.88</v>
+        <v>50.33</v>
       </c>
       <c r="N12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="P12" t="n">
-        <v>12.75</v>
+        <v>13.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.5</v>
+        <v>11.67</v>
       </c>
       <c r="R12" t="n">
-        <v>6.62</v>
+        <v>6.33</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>43.62</v>
+        <v>42.89</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.62</v>
+        <v>12.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.25</v>
+        <v>4.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.62</v>
+        <v>19.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF12" t="n">
         <v>0.17</v>
@@ -5574,70 +5574,70 @@
         <v>1.33</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.93</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
         <v>5.18</v>
@@ -5646,19 +5646,19 @@
         <v>5.52</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CH12" t="n">
         <v>1.39</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.86</v>
@@ -5667,37 +5667,37 @@
         <v>1.52</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM12" t="n">
         <v>2.39</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO12" t="n">
         <v>1.33</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="CR12" t="n">
         <v>1.46</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU12" t="n">
         <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW12" t="n">
         <v>1.91</v>
@@ -5706,19 +5706,19 @@
         <v>1.61</v>
       </c>
       <c r="CY12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.31</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DD12" t="n">
         <v>3.27</v>
@@ -5727,76 +5727,76 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.06999999999999</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.21</v>
+        <v>4.33</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="DM12" t="n">
-        <v>48.43</v>
+        <v>48.27</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.29</v>
+        <v>13.66</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.93</v>
+        <v>11.6</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.78</v>
+        <v>6.6</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>41.35</v>
+        <v>41.07</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.64</v>
+        <v>4.47</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.35</v>
+        <v>20.4</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="13">
@@ -5962,16 +5962,16 @@
         <v>11.12</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.75</v>
+        <v>6.62</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" t="n">
         <v>18.25</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BF13" t="n">
         <v>1.88</v>
@@ -6187,10 +6187,10 @@
         <v>10.53</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="EA13" t="n">
         <v>18.93</v>
@@ -6209,13 +6209,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6302,136 +6302,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>90.62</v>
+        <v>91.44</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.5</v>
+        <v>3.11</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.25</v>
+        <v>4.89</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.25</v>
+        <v>41.11</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.88</v>
+        <v>14.78</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.380000000000001</v>
+        <v>10.44</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>53.38</v>
+        <v>54.44</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.5</v>
+        <v>10.89</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.88</v>
+        <v>7.44</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.88</v>
+        <v>19.44</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.79</v>
+        <v>11.53</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.79</v>
+        <v>5.73</v>
       </c>
       <c r="BR14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY14" t="n">
         <v>3.35</v>
@@ -6440,34 +6440,34 @@
         <v>3.51</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.93</v>
+        <v>3.84</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.09</v>
+        <v>3.99</v>
       </c>
       <c r="CE14" t="n">
         <v>1.41</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK14" t="n">
         <v>1.46</v>
@@ -6476,7 +6476,7 @@
         <v>1.86</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN14" t="n">
         <v>1.96</v>
@@ -6485,28 +6485,28 @@
         <v>1.31</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
       <c r="CR14" t="n">
         <v>1.44</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX14" t="n">
         <v>1.53</v>
@@ -6518,13 +6518,13 @@
         <v>2.46</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB14" t="n">
         <v>1.39</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD14" t="n">
         <v>3.14</v>
@@ -6533,43 +6533,43 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.92</v>
+        <v>94.2</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.43</v>
+        <v>6.13</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.79</v>
+        <v>46.33</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.36</v>
+        <v>13.94</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.65</v>
+        <v>10.26</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.289999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.07000000000000001</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.5</v>
+        <v>54.13</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.14</v>
+        <v>12.67</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.859999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.28</v>
+        <v>4.13</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.36</v>
+        <v>20.6</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="15">
@@ -6612,94 +6612,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="F15" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>111.14</v>
+        <v>107</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.43</v>
+        <v>4.75</v>
       </c>
       <c r="L15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M15" t="n">
-        <v>50</v>
+        <v>50.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="O15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="P15" t="n">
-        <v>8.57</v>
+        <v>9.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>14.57</v>
+        <v>13.75</v>
       </c>
       <c r="R15" t="n">
-        <v>7</v>
+        <v>6.62</v>
       </c>
       <c r="S15" t="n">
-        <v>0.86</v>
+        <v>1.38</v>
       </c>
       <c r="T15" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>51.86</v>
+        <v>50.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.14</v>
+        <v>16.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.14</v>
+        <v>17.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6783,70 +6783,70 @@
         <v>2.57</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.57</v>
+        <v>2.93</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.14</v>
+        <v>10.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.57</v>
+        <v>2.93</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.21</v>
+        <v>4.4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.61</v>
+        <v>3.65</v>
       </c>
       <c r="CC15" t="n">
         <v>2.69</v>
@@ -6855,61 +6855,61 @@
         <v>2.7</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="CK15" t="n">
         <v>1.5</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM15" t="n">
         <v>2.42</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="CT15" t="n">
         <v>2.99</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
@@ -6918,7 +6918,7 @@
         <v>1.93</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA15" t="n">
         <v>1.91</v>
@@ -6927,85 +6927,85 @@
         <v>1.31</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="DH15" t="n">
-        <v>100.86</v>
+        <v>99.33</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DM15" t="n">
-        <v>49.36</v>
+        <v>49.53</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.07</v>
+        <v>10.33</v>
       </c>
       <c r="DQ15" t="n">
-        <v>14.57</v>
+        <v>14.13</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.5</v>
+        <v>7.26</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>51.22</v>
+        <v>50.33</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.72</v>
+        <v>14.87</v>
       </c>
       <c r="DY15" t="n">
-        <v>10</v>
+        <v>10.13</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
       <c r="EA15" t="n">
-        <v>17</v>
+        <v>17.33</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="EC15" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="16">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -7027,82 +7027,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="G16" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="H16" t="n">
-        <v>131.33</v>
+        <v>128.86</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5</v>
+        <v>3.29</v>
       </c>
       <c r="K16" t="n">
-        <v>6.5</v>
+        <v>6.71</v>
       </c>
       <c r="L16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M16" t="n">
-        <v>80.5</v>
+        <v>80</v>
       </c>
       <c r="N16" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O16" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="P16" t="n">
-        <v>11.17</v>
+        <v>10.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="T16" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>61.33</v>
+        <v>60.86</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.17</v>
+        <v>20.57</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.67</v>
+        <v>13.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.5</v>
+        <v>7.43</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.67</v>
+        <v>17.43</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="AF16" t="n">
         <v>0.11</v>
@@ -7186,70 +7186,70 @@
         <v>1.22</v>
       </c>
       <c r="BG16" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.470000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="BI16" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.87</v>
+        <v>4.94</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS16" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT16" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX16" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
         <v>1.28</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.26</v>
+        <v>5.33</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.63</v>
+        <v>5.67</v>
       </c>
       <c r="CC16" t="n">
         <v>1.56</v>
@@ -7261,22 +7261,22 @@
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.76</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL16" t="n">
         <v>1.74</v>
@@ -7291,10 +7291,10 @@
         <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
@@ -7330,85 +7330,85 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DH16" t="n">
-        <v>121.6</v>
+        <v>121.13</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.2</v>
+        <v>6.31</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM16" t="n">
-        <v>69.47</v>
+        <v>69.94</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.33</v>
+        <v>13.25</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.94</v>
+        <v>6.69</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>59.87</v>
+        <v>59.75</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="DX16" t="n">
-        <v>19.67</v>
+        <v>19.87</v>
       </c>
       <c r="DY16" t="n">
-        <v>12.53</v>
+        <v>12.75</v>
       </c>
       <c r="DZ16" t="n">
         <v>7.13</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.2</v>
+        <v>16.75</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="17">
@@ -7652,7 +7652,7 @@
         <v>3.84</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="CC17" t="n">
         <v>7.14</v>
@@ -7733,7 +7733,7 @@
         <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD17" t="n">
         <v>3.14</v>
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7914,136 +7914,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="AI18" t="n">
-        <v>91.43000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.57</v>
+        <v>5.88</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AN18" t="n">
-        <v>44.57</v>
+        <v>44.88</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.71</v>
+        <v>14.88</v>
       </c>
       <c r="AR18" t="n">
-        <v>8.57</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.43</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>46.86</v>
+        <v>48.75</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.710000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.29</v>
+        <v>4.75</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.29</v>
+        <v>17.88</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.29</v>
+        <v>10.47</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.21</v>
+        <v>5.47</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BY18" t="n">
         <v>2.57</v>
@@ -8052,73 +8052,73 @@
         <v>2.74</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.97</v>
+        <v>3.84</v>
       </c>
       <c r="CE18" t="n">
         <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CN18" t="n">
         <v>1.92</v>
       </c>
-      <c r="CJ18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="CN18" t="n">
-        <v>1.93</v>
-      </c>
       <c r="CO18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CS18" t="n">
         <v>2.91</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="CU18" t="n">
         <v>1.45</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CX18" t="n">
         <v>1.6</v>
@@ -8133,10 +8133,10 @@
         <v>1.92</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DD18" t="n">
         <v>3.15</v>
@@ -8145,76 +8145,76 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.36</v>
+        <v>3.53</v>
       </c>
       <c r="DH18" t="n">
-        <v>100</v>
+        <v>100.13</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.36</v>
+        <v>6.47</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DM18" t="n">
-        <v>47.36</v>
+        <v>47.33</v>
       </c>
       <c r="DN18" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DO18" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.42</v>
+        <v>15.47</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.36</v>
+        <v>11.93</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.5</v>
+        <v>7.87</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.43</v>
+        <v>52.13</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.93</v>
+        <v>13.67</v>
       </c>
       <c r="DY18" t="n">
         <v>8.93</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.79</v>
+        <v>19.47</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="19">
@@ -8224,13 +8224,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8314,52 +8314,52 @@
         <v>3.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>86.56999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.43</v>
+        <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AN19" t="n">
-        <v>33.86</v>
+        <v>37.62</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.29</v>
+        <v>13.88</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.86</v>
+        <v>6.25</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8371,82 +8371,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>51.86</v>
+        <v>51.88</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.86</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.57</v>
+        <v>7</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.86</v>
+        <v>19.25</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="BG19" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.86</v>
+        <v>10.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM19" t="n">
         <v>1.07</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.36</v>
+        <v>5.2</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV19" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY19" t="n">
         <v>2.76</v>
@@ -8455,16 +8455,16 @@
         <v>2.93</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.77</v>
+        <v>4.65</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.05</v>
+        <v>4.93</v>
       </c>
       <c r="CE19" t="n">
         <v>1.42</v>
@@ -8473,7 +8473,7 @@
         <v>2.99</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CH19" t="n">
         <v>1.39</v>
@@ -8485,37 +8485,37 @@
         <v>1.9</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP19" t="n">
         <v>2.1</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CT19" t="n">
         <v>2.73</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV19" t="n">
         <v>1.95</v>
@@ -8524,16 +8524,16 @@
         <v>1.96</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB19" t="n">
         <v>1.39</v>
@@ -8542,49 +8542,49 @@
         <v>2.16</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.64</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.36</v>
+        <v>5.14</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM19" t="n">
-        <v>43</v>
+        <v>44.4</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.14</v>
+        <v>15.34</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.5</v>
+        <v>14.34</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.36</v>
+        <v>5.6</v>
       </c>
       <c r="DS19" t="n">
         <v>0.14</v>
@@ -8596,28 +8596,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.36</v>
+        <v>54.2</v>
       </c>
       <c r="DW19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.14</v>
+        <v>10.67</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.79</v>
+        <v>7.47</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.78</v>
+        <v>19.46</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.14</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="20">
@@ -8627,25 +8627,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F20" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="G20" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="H20" t="n">
-        <v>91.43000000000001</v>
+        <v>91.62</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -8654,34 +8654,34 @@
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>6.71</v>
+        <v>6.12</v>
       </c>
       <c r="L20" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M20" t="n">
-        <v>42.57</v>
+        <v>41.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O20" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="P20" t="n">
-        <v>13.14</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.86</v>
+        <v>11.75</v>
       </c>
       <c r="R20" t="n">
-        <v>6.86</v>
+        <v>6.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8693,25 +8693,25 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>53.14</v>
+        <v>52.5</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.29</v>
+        <v>13.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.57</v>
+        <v>10.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>17.71</v>
+        <v>18.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
         <v>2</v>
@@ -8798,70 +8798,70 @@
         <v>1.57</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH20" t="n">
-        <v>10.07</v>
+        <v>9.67</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BR20" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS20" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT20" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU20" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV20" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX20" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CC20" t="n">
         <v>5.63</v>
@@ -8873,52 +8873,52 @@
         <v>1.42</v>
       </c>
       <c r="CF20" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI20" t="n">
         <v>1.87</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CK20" t="n">
         <v>1.49</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM20" t="n">
         <v>2.48</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV20" t="n">
         <v>1.93</v>
@@ -8927,37 +8927,37 @@
         <v>1.97</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="DA20" t="n">
         <v>1.94</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC20" t="n">
         <v>2.18</v>
       </c>
       <c r="DD20" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.29</v>
+        <v>3.14</v>
       </c>
       <c r="DH20" t="n">
-        <v>85.78</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
@@ -8966,28 +8966,28 @@
         <v>1.93</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.07</v>
+        <v>4.86</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM20" t="n">
-        <v>37.79</v>
+        <v>37.53</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.14</v>
+        <v>12.13</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.36</v>
+        <v>11.8</v>
       </c>
       <c r="DR20" t="n">
-        <v>8</v>
+        <v>7.73</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8999,28 +8999,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.07</v>
+        <v>47.13</v>
       </c>
       <c r="DW20" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.72</v>
+        <v>7.73</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.21</v>
+        <v>18.6</v>
       </c>
       <c r="EB20" t="n">
         <v>1.15</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21">
@@ -9030,61 +9030,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>98</v>
+        <v>100.38</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="M21" t="n">
-        <v>59.14</v>
+        <v>56.88</v>
       </c>
       <c r="N21" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O21" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="P21" t="n">
-        <v>11.14</v>
+        <v>12.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.859999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="R21" t="n">
-        <v>6.71</v>
+        <v>6.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9096,28 +9096,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>53.43</v>
+        <v>54.38</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>17.29</v>
+        <v>16.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.71</v>
+        <v>6.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>17.57</v>
+        <v>19.12</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9201,70 +9201,70 @@
         <v>3.43</v>
       </c>
       <c r="BG21" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.289999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="BI21" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.43</v>
+        <v>4.27</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT21" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU21" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV21" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CC21" t="n">
         <v>3.16</v>
@@ -9273,124 +9273,124 @@
         <v>3.41</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CH21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CU21" t="n">
         <v>1.48</v>
       </c>
-      <c r="CI21" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CJ21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CK21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CL21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CM21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CN21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CO21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="CP21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CQ21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="CT21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="CU21" t="n">
-        <v>1.49</v>
-      </c>
       <c r="CV21" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DD21" t="n">
         <v>2.98</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="DH21" t="n">
-        <v>86.28</v>
+        <v>88.34</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.57</v>
+        <v>0.8</v>
       </c>
       <c r="DM21" t="n">
-        <v>47.28</v>
+        <v>46.87</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.14</v>
+        <v>12.6</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11</v>
+        <v>11.27</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.14</v>
+        <v>6.87</v>
       </c>
       <c r="DS21" t="n">
         <v>0.07000000000000001</v>
@@ -9402,28 +9402,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>45.78</v>
+        <v>46.8</v>
       </c>
       <c r="DW21" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.5</v>
+        <v>13.27</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.43</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ21" t="n">
         <v>5.07</v>
       </c>
       <c r="EA21" t="n">
-        <v>17</v>
+        <v>17.86</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F4" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="H4" t="n">
-        <v>93.67</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K4" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>46.29</v>
       </c>
       <c r="N4" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>13.33</v>
+        <v>13.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.83</v>
+        <v>10.29</v>
       </c>
       <c r="R4" t="n">
-        <v>7.17</v>
+        <v>7.57</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.5</v>
+        <v>48.29</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>12.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.5</v>
+        <v>7.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.12</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.36</v>
+        <v>7.27</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT4" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="CC4" t="n">
         <v>5.5</v>
@@ -2428,25 +2428,25 @@
         <v>5.69</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CH4" t="n">
         <v>1.35</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL4" t="n">
         <v>1.98</v>
@@ -2458,31 +2458,31 @@
         <v>1.78</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX4" t="n">
         <v>1.65</v>
@@ -2491,94 +2491,94 @@
         <v>2.03</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="DE4" t="n">
         <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.65000000000001</v>
+        <v>88</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="DK4" t="n">
         <v>3.07</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.43</v>
+        <v>42</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.86</v>
+        <v>13</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.64</v>
+        <v>46.27</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.35</v>
+        <v>10.6</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.07</v>
+        <v>7.13</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.29</v>
+        <v>3.47</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.85</v>
+        <v>19.86</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.33</v>
@@ -5096,46 +5096,46 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>81.5</v>
+        <v>84.78</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
         <v>2</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>36</v>
+        <v>38.44</v>
       </c>
       <c r="AO11" t="n">
         <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.38</v>
+        <v>12.67</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.62</v>
+        <v>12</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.62</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5147,82 +5147,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>41.12</v>
+        <v>43.11</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.38</v>
+        <v>10.44</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>6.89</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BF11" t="n">
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.79</v>
+        <v>10.47</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.43</v>
+        <v>5.33</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.36</v>
+        <v>5.13</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY11" t="n">
         <v>5.01</v>
@@ -5234,13 +5234,13 @@
         <v>3.94</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.94</v>
+        <v>4.96</v>
       </c>
       <c r="CE11" t="n">
         <v>1.37</v>
@@ -5249,13 +5249,13 @@
         <v>2.71</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CH11" t="n">
         <v>1.46</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.83</v>
@@ -5267,13 +5267,13 @@
         <v>1.91</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP11" t="n">
         <v>1.95</v>
@@ -5285,13 +5285,13 @@
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV11" t="n">
         <v>2.06</v>
@@ -5300,67 +5300,67 @@
         <v>1.85</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DC11" t="n">
         <v>1.9</v>
       </c>
-      <c r="DB11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="DD11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="DH11" t="n">
-        <v>79.64</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DK11" t="n">
         <v>3.14</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM11" t="n">
-        <v>35.36</v>
+        <v>36.86</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.65</v>
+        <v>12.27</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="DR11" t="n">
-        <v>10.14</v>
+        <v>9.67</v>
       </c>
       <c r="DS11" t="n">
         <v>0.07000000000000001</v>
@@ -5372,25 +5372,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>40.21</v>
+        <v>41.47</v>
       </c>
       <c r="DW11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.29</v>
+        <v>10.33</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.93</v>
+        <v>6.87</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.57</v>
+        <v>17.87</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="EC11" t="n">
         <v>2.07</v>
@@ -5469,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>42.89</v>
+        <v>42.78</v>
       </c>
       <c r="Y12" t="n">
         <v>0.22</v>
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>41.07</v>
+        <v>41</v>
       </c>
       <c r="DW12" t="n">
         <v>0.13</v>
@@ -6356,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>54.44</v>
+        <v>54.56</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.22</v>
@@ -6581,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.13</v>
+        <v>54.2</v>
       </c>
       <c r="DW14" t="n">
         <v>0.2</v>
@@ -7027,7 +7027,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="G16" t="n">
         <v>3.29</v>
@@ -7039,7 +7039,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.29</v>
+        <v>3.43</v>
       </c>
       <c r="K16" t="n">
         <v>6.71</v>
@@ -7084,7 +7084,7 @@
         <v>60.86</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="Z16" t="n">
         <v>20.57</v>
@@ -7339,7 +7339,7 @@
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="DG16" t="n">
         <v>2.88</v>
@@ -7351,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DK16" t="n">
         <v>6.31</v>
@@ -7390,7 +7390,7 @@
         <v>59.75</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DX16" t="n">
         <v>19.87</v>
@@ -8639,7 +8639,7 @@
         <v>0.12</v>
       </c>
       <c r="F20" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="G20" t="n">
         <v>3.88</v>
@@ -8651,7 +8651,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="K20" t="n">
         <v>6.12</v>
@@ -8714,7 +8714,7 @@
         <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="DG20" t="n">
         <v>3.14</v>
@@ -8963,7 +8963,7 @@
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DK20" t="n">
         <v>4.86</v>
@@ -9020,7 +9020,7 @@
         <v>1.15</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG10" t="n">
         <v>2</v>
@@ -4696,130 +4696,130 @@
         <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>74.29000000000001</v>
+        <v>86.62</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>33.57</v>
+        <v>39.25</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>11.12</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.57</v>
+        <v>13.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>12.43</v>
+        <v>11.38</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>42.86</v>
+        <v>44.12</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.859999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.71</v>
+        <v>5.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>15.71</v>
+        <v>15.62</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.47</v>
+        <v>5.25</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS10" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU10" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY10" t="n">
         <v>2.77</v>
@@ -4831,25 +4831,25 @@
         <v>3.9</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.31</v>
+        <v>6.08</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.56</v>
+        <v>6.38</v>
       </c>
       <c r="CE10" t="n">
         <v>1.37</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI10" t="n">
         <v>1.99</v>
@@ -4858,10 +4858,10 @@
         <v>1.79</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM10" t="n">
         <v>2.34</v>
@@ -4873,7 +4873,7 @@
         <v>1.27</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.27</v>
@@ -4885,112 +4885,112 @@
         <v>2.9</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW10" t="n">
         <v>1.84</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="DH10" t="n">
-        <v>82.06999999999999</v>
+        <v>87.75</v>
       </c>
       <c r="DI10" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="DK10" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.93</v>
+        <v>42.38</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.73</v>
+        <v>10.37</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.4</v>
+        <v>13.81</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.74</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>46.67</v>
+        <v>47.06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.33</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.6</v>
+        <v>5.94</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.87</v>
+        <v>16.75</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="11">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -7833,82 +7833,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="H18" t="n">
-        <v>108.57</v>
+        <v>117.12</v>
       </c>
       <c r="I18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J18" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="K18" t="n">
-        <v>7.14</v>
+        <v>6.75</v>
       </c>
       <c r="L18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M18" t="n">
-        <v>50.14</v>
+        <v>54.75</v>
       </c>
       <c r="N18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="P18" t="n">
-        <v>16.14</v>
+        <v>16.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.14</v>
+        <v>13</v>
       </c>
       <c r="R18" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="S18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T18" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>56</v>
+        <v>54.88</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.86</v>
+        <v>13.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.140000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.29</v>
+        <v>20.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7992,70 +7992,70 @@
         <v>2.62</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.47</v>
+        <v>10.25</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP18" t="n">
         <v>5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.47</v>
+        <v>5.25</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT18" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV18" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CC18" t="n">
         <v>3.9</v>
@@ -8067,7 +8067,7 @@
         <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG18" t="n">
         <v>2.83</v>
@@ -8076,10 +8076,10 @@
         <v>1.39</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CK18" t="n">
         <v>1.5</v>
@@ -8097,25 +8097,25 @@
         <v>1.33</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS18" t="n">
         <v>2.91</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CU18" t="n">
         <v>1.45</v>
       </c>
       <c r="CV18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW18" t="n">
         <v>1.91</v>
@@ -8127,7 +8127,7 @@
         <v>1.92</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DA18" t="n">
         <v>1.92</v>
@@ -8136,85 +8136,85 @@
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.53</v>
+        <v>3.37</v>
       </c>
       <c r="DH18" t="n">
-        <v>100.13</v>
+        <v>104.94</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.47</v>
+        <v>6.32</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM18" t="n">
-        <v>47.33</v>
+        <v>49.82</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.47</v>
+        <v>15.75</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.93</v>
+        <v>11.5</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.87</v>
+        <v>7.81</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.13</v>
+        <v>51.82</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.67</v>
+        <v>13.38</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.93</v>
+        <v>8.68</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.47</v>
+        <v>19.13</v>
       </c>
       <c r="EB18" t="n">
         <v>1.54</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.11</v>
@@ -1469,52 +1469,52 @@
         <v>1.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG2" t="n">
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>99.43000000000001</v>
+        <v>102.25</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>45.86</v>
+        <v>47.88</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.71</v>
+        <v>11.88</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.71</v>
+        <v>12.38</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.14</v>
+        <v>6.62</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>45.71</v>
+        <v>46.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>20.12</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="BH2" t="n">
-        <v>10</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.44</v>
+        <v>5.18</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS2" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT2" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU2" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BY2" t="n">
         <v>2.11</v>
@@ -1610,16 +1610,16 @@
         <v>2.09</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="CE2" t="n">
         <v>1.42</v>
@@ -1628,7 +1628,7 @@
         <v>3.02</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH2" t="n">
         <v>1.37</v>
@@ -1637,7 +1637,7 @@
         <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK2" t="n">
         <v>1.56</v>
@@ -1646,7 +1646,7 @@
         <v>2.05</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CN2" t="n">
         <v>1.8</v>
@@ -1655,121 +1655,121 @@
         <v>1.36</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CU2" t="n">
         <v>1.36</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX2" t="n">
         <v>1.65</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB2" t="n">
         <v>1.41</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DD2" t="n">
         <v>2.89</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DH2" t="n">
-        <v>110.44</v>
+        <v>111.12</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.38</v>
+        <v>5.3</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.38</v>
+        <v>52</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.87</v>
+        <v>12.89</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.37</v>
+        <v>12.24</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.18</v>
+        <v>48.29</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.94</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="EA2" t="n">
         <v>21.12</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="EC2" t="n">
         <v>1.88</v>
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G3" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="H3" t="n">
-        <v>105.12</v>
+        <v>105.33</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="K3" t="n">
-        <v>9.25</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M3" t="n">
-        <v>61.12</v>
+        <v>59.33</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>5.62</v>
+        <v>5.22</v>
       </c>
       <c r="P3" t="n">
-        <v>9.75</v>
+        <v>10.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.38</v>
+        <v>10.44</v>
       </c>
       <c r="R3" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="AB3" t="n">
         <v>7</v>
       </c>
-      <c r="S3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>56.12</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7.12</v>
-      </c>
       <c r="AC3" t="n">
-        <v>20.25</v>
+        <v>19.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF3" t="n">
         <v>0.38</v>
@@ -1953,70 +1953,70 @@
         <v>1.88</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.5</v>
+        <v>10.59</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX3" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.35</v>
+        <v>4.43</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.45</v>
+        <v>4.51</v>
       </c>
       <c r="CC3" t="n">
         <v>2.22</v>
@@ -2028,7 +2028,7 @@
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CG3" t="n">
         <v>3.09</v>
@@ -2037,112 +2037,112 @@
         <v>1.47</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX3" t="n">
         <v>1.63</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.31</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD3" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG3" t="n">
         <v>3.18</v>
       </c>
       <c r="DH3" t="n">
-        <v>102.12</v>
+        <v>102.41</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DK3" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="DM3" t="n">
-        <v>53.68</v>
+        <v>53.17</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.12</v>
+        <v>11.23</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.25</v>
+        <v>10.29</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.56</v>
+        <v>8.35</v>
       </c>
       <c r="DS3" t="n">
         <v>0.12</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.18</v>
+        <v>53.71</v>
       </c>
       <c r="DW3" t="n">
         <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.12</v>
+        <v>12.94</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.62</v>
+        <v>5.64</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.94</v>
+        <v>19.7</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.29</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.38</v>
+        <v>78.67</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AL4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BP4" t="n">
         <v>3.25</v>
       </c>
-      <c r="AM4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>3.13</v>
-      </c>
       <c r="BQ4" t="n">
-        <v>3.53</v>
+        <v>3.94</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS4" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY4" t="n">
         <v>2.25</v>
@@ -2416,169 +2416,169 @@
         <v>2.31</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.66</v>
+        <v>3.96</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.5</v>
+        <v>6.22</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.69</v>
+        <v>6.48</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="CI4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CN4" t="n">
         <v>1.8</v>
       </c>
-      <c r="CJ4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>1.78</v>
-      </c>
       <c r="CO4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="CR4" t="n">
         <v>1.49</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="CT4" t="n">
         <v>2.72</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CX4" t="n">
         <v>1.65</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.28</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DB4" t="n">
         <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.07</v>
+        <v>2.85</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DH4" t="n">
-        <v>88</v>
+        <v>86.06</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM4" t="n">
-        <v>42</v>
+        <v>40.38</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="DP4" t="n">
-        <v>13</v>
+        <v>12.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.2</v>
+        <v>10.81</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.6</v>
+        <v>9.06</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.27</v>
+        <v>44.63</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.6</v>
+        <v>10.12</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.13</v>
+        <v>6.75</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.47</v>
+        <v>3.37</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.86</v>
+        <v>19.38</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="H5" t="n">
-        <v>114.88</v>
+        <v>111.67</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="K5" t="n">
-        <v>5.38</v>
+        <v>4.89</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>53.75</v>
+        <v>50</v>
       </c>
       <c r="N5" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
         <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.38</v>
+        <v>12.44</v>
       </c>
       <c r="R5" t="n">
-        <v>5.75</v>
+        <v>6.22</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.12</v>
+        <v>54.56</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.75</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.119999999999999</v>
+        <v>7.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.25</v>
+        <v>20.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.43</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.130000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BU5" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX5" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CC5" t="n">
         <v>3.73</v>
@@ -2834,55 +2834,55 @@
         <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CG5" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.8</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL5" t="n">
         <v>2.12</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO5" t="n">
         <v>1.29</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW5" t="n">
         <v>1.81</v>
@@ -2891,19 +2891,19 @@
         <v>1.67</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DD5" t="n">
         <v>3.02</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="DH5" t="n">
-        <v>98.27</v>
+        <v>97.5</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.33</v>
+        <v>4.12</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DM5" t="n">
-        <v>44</v>
+        <v>42.5</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.13</v>
+        <v>12.06</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.8</v>
+        <v>11.87</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.87</v>
+        <v>8</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.86</v>
+        <v>50.82</v>
       </c>
       <c r="DW5" t="n">
         <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.93</v>
+        <v>10.56</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.07</v>
+        <v>6.82</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F6" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>108.75</v>
+        <v>106.33</v>
       </c>
       <c r="I6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="J6" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>44.25</v>
+        <v>45.56</v>
       </c>
       <c r="N6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="P6" t="n">
-        <v>15.75</v>
+        <v>15.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.88</v>
+        <v>14.67</v>
       </c>
       <c r="R6" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.5</v>
+        <v>50.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.25</v>
+        <v>11.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.75</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.25</v>
+        <v>21.11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF6" t="n">
         <v>0.14</v>
@@ -3162,49 +3162,49 @@
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.67</v>
+        <v>9.81</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.33</v>
+        <v>4.94</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS6" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="CC6" t="n">
         <v>4.91</v>
@@ -3234,43 +3234,43 @@
         <v>5.5</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CK6" t="n">
         <v>1.58</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM6" t="n">
         <v>2.27</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.88</v>
+        <v>4.76</v>
       </c>
       <c r="CR6" t="n">
         <v>1.54</v>
@@ -3285,106 +3285,106 @@
         <v>1.46</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY6" t="n">
         <v>2.07</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.06</v>
+        <v>2.57</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="DH6" t="n">
-        <v>102.07</v>
+        <v>101.12</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.13</v>
+        <v>43</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="DP6" t="n">
-        <v>16.33</v>
+        <v>16.06</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.74</v>
+        <v>13.69</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.6</v>
+        <v>7.81</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.13</v>
+        <v>49.31</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.34</v>
+        <v>11</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.93</v>
+        <v>7.69</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.53</v>
+        <v>20.06</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -3487,49 +3487,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" t="n">
-        <v>87.43000000000001</v>
+        <v>90.25</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>34.43</v>
+        <v>36.25</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.86</v>
+        <v>12.88</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.14</v>
+        <v>15.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,73 +3541,73 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>55.29</v>
+        <v>55.62</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.57</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.43</v>
+        <v>5.88</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.43</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.53</v>
+        <v>7.19</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.67</v>
+        <v>4.44</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS7" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY7" t="n">
         <v>3.13</v>
@@ -3625,16 +3625,16 @@
         <v>3.4</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.18</v>
+        <v>5.78</v>
       </c>
       <c r="CD7" t="n">
-        <v>6.82</v>
+        <v>6.36</v>
       </c>
       <c r="CE7" t="n">
         <v>1.44</v>
@@ -3643,7 +3643,7 @@
         <v>3.03</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH7" t="n">
         <v>1.39</v>
@@ -3664,52 +3664,52 @@
         <v>2.17</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO7" t="n">
         <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS7" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX7" t="n">
         <v>1.71</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DD7" t="n">
         <v>2.72</v>
@@ -3718,43 +3718,43 @@
         <v>0.06</v>
       </c>
       <c r="DF7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DG7" t="n">
         <v>1.13</v>
       </c>
-      <c r="DG7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="DH7" t="n">
-        <v>97.27</v>
+        <v>98.06</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.13</v>
+        <v>45.38</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.6</v>
+        <v>12.63</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.67</v>
+        <v>15.5</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.93</v>
+        <v>58.87</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="DY7" t="n">
-        <v>7</v>
+        <v>7.13</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.13</v>
+        <v>3.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.13</v>
+        <v>15.5</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="8">
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.75</v>
+        <v>3.44</v>
       </c>
       <c r="H8" t="n">
-        <v>114.75</v>
+        <v>117.44</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="K8" t="n">
-        <v>6.5</v>
+        <v>7.33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="M8" t="n">
-        <v>58.12</v>
+        <v>62.78</v>
       </c>
       <c r="N8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="P8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.62</v>
+        <v>11.22</v>
       </c>
       <c r="R8" t="n">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>66.25</v>
+        <v>67.78</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.25</v>
+        <v>20.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.75</v>
+        <v>18</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AF8" t="n">
         <v>0.25</v>
@@ -3968,37 +3968,37 @@
         <v>2.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.25</v>
+        <v>11.47</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>5.76</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4007,31 +4007,31 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BV8" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW8" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX8" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.47</v>
+        <v>5.58</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.79</v>
+        <v>5.94</v>
       </c>
       <c r="CC8" t="n">
         <v>1.67</v>
@@ -4043,28 +4043,28 @@
         <v>1.21</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="CH8" t="n">
         <v>1.81</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK8" t="n">
         <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CN8" t="n">
         <v>2.07</v>
@@ -4073,24 +4073,24 @@
         <v>1.1</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX8" t="n">
         <v>1.51</v>
@@ -4109,82 +4109,82 @@
         <v>1.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.12</v>
+        <v>3.47</v>
       </c>
       <c r="DH8" t="n">
-        <v>112.5</v>
+        <v>114.06</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.5</v>
+        <v>6.94</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="DM8" t="n">
-        <v>59.5</v>
+        <v>61.89</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.56</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.12</v>
+        <v>11.88</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.56</v>
+        <v>4.41</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>66.94</v>
+        <v>67.7</v>
       </c>
       <c r="DW8" t="n">
         <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>19.69</v>
+        <v>19.94</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.94</v>
+        <v>12.24</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.75</v>
+        <v>7.71</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.38</v>
+        <v>17.53</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="9">
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -4206,49 +4206,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G9" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="H9" t="n">
-        <v>101.43</v>
+        <v>103.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J9" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>16.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.43</v>
+        <v>15.62</v>
       </c>
       <c r="R9" t="n">
-        <v>6.86</v>
+        <v>6.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4260,28 +4260,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>41</v>
+        <v>42.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.14</v>
+        <v>10.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.29</v>
+        <v>7.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>25.71</v>
+        <v>26.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,46 +4365,46 @@
         <v>2.62</v>
       </c>
       <c r="BG9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.07</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4416,19 +4416,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="CC9" t="n">
         <v>5.36</v>
@@ -4437,19 +4437,19 @@
         <v>5.86</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CH9" t="n">
         <v>1.28</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CJ9" t="n">
         <v>2.32</v>
@@ -4467,22 +4467,22 @@
         <v>1.55</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.14</v>
+        <v>5.29</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CS9" t="n">
         <v>3.06</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CU9" t="n">
         <v>1.4</v>
@@ -4491,7 +4491,7 @@
         <v>1.62</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CX9" t="n">
         <v>1.96</v>
@@ -4506,10 +4506,10 @@
         <v>1.56</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="DD9" t="n">
         <v>2.81</v>
@@ -4518,43 +4518,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="DH9" t="n">
-        <v>98.59999999999999</v>
+        <v>99.94</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.8</v>
+        <v>41.06</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.14</v>
+        <v>15.32</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.67</v>
+        <v>14.81</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.73</v>
+        <v>6.5</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>40.2</v>
+        <v>41.19</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.54</v>
+        <v>6.75</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="EA9" t="n">
-        <v>24.66</v>
+        <v>24.94</v>
       </c>
       <c r="EB9" t="n">
         <v>1.08</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="10">
@@ -4831,13 +4831,13 @@
         <v>3.9</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CC10" t="n">
         <v>6.08</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.38</v>
+        <v>6.32</v>
       </c>
       <c r="CE10" t="n">
         <v>1.37</v>
@@ -4885,7 +4885,7 @@
         <v>2.9</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CU10" t="n">
         <v>1.45</v>
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5493,139 +5493,139 @@
         <v>2.33</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AH12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP12" t="n">
         <v>2</v>
       </c>
-      <c r="AI12" t="n">
-        <v>90.17</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>45.17</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>14.43</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.5</v>
+        <v>12.43</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>38.33</v>
+        <v>39.14</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>14.67</v>
+        <v>13.43</v>
       </c>
       <c r="BB12" t="n">
-        <v>10.83</v>
+        <v>9.57</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.33</v>
+        <v>21.71</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.869999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY12" t="n">
         <v>2.82</v>
@@ -5634,169 +5634,169 @@
         <v>2.79</v>
       </c>
       <c r="CA12" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="CB12" t="n">
         <v>3.57</v>
       </c>
-      <c r="CB12" t="n">
-        <v>3.62</v>
-      </c>
       <c r="CC12" t="n">
-        <v>5.18</v>
+        <v>4.9</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.52</v>
+        <v>5.2</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CJ12" t="n">
         <v>1.9</v>
       </c>
-      <c r="CJ12" t="n">
-        <v>1.86</v>
-      </c>
       <c r="CK12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.73</v>
+        <v>3.97</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CS12" t="n">
         <v>3.15</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="CU12" t="n">
         <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="DD12" t="n">
         <v>3.27</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.06999999999999</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>48.27</v>
+        <v>46.5</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.66</v>
+        <v>13.87</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.6</v>
+        <v>6.68</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>41</v>
+        <v>41.19</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.2</v>
+        <v>12.75</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.73</v>
+        <v>8.31</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.4</v>
+        <v>20.62</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="13">
@@ -5806,94 +5806,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F13" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="H13" t="n">
-        <v>89</v>
+        <v>90.88</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>39.71</v>
+        <v>40</v>
       </c>
       <c r="N13" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>11.57</v>
+        <v>11.75</v>
       </c>
       <c r="Q13" t="n">
         <v>13</v>
       </c>
       <c r="R13" t="n">
-        <v>7.57</v>
+        <v>7.38</v>
       </c>
       <c r="S13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>45</v>
+        <v>44.62</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.859999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.29</v>
+        <v>3.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.71</v>
+        <v>19.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AF13" t="n">
         <v>0.12</v>
@@ -5977,70 +5977,70 @@
         <v>1.88</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.07</v>
+        <v>9.56</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.4</v>
+        <v>4.19</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.67</v>
+        <v>5.38</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS13" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="BZ13" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="CB13" t="n">
         <v>3.88</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="CB13" t="n">
-        <v>3.94</v>
       </c>
       <c r="CC13" t="n">
         <v>6.24</v>
@@ -6049,10 +6049,10 @@
         <v>6.64</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG13" t="n">
         <v>2.76</v>
@@ -6067,16 +6067,16 @@
         <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL13" t="n">
         <v>1.95</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO13" t="n">
         <v>1.38</v>
@@ -6085,19 +6085,19 @@
         <v>2.2</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="CR13" t="n">
         <v>1.49</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV13" t="n">
         <v>1.83</v>
@@ -6106,100 +6106,100 @@
         <v>2.08</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="DB13" t="n">
         <v>1.44</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DD13" t="n">
         <v>2.71</v>
       </c>
       <c r="DE13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="DI13" t="n">
         <v>0.06</v>
       </c>
-      <c r="DF13" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="DH13" t="n">
-        <v>91.13</v>
-      </c>
-      <c r="DI13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="DJ13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.47</v>
+        <v>3.32</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.46</v>
+        <v>37.75</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.53</v>
+        <v>11.62</v>
       </c>
       <c r="DQ13" t="n">
         <v>13.06</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.93</v>
+        <v>7.82</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.87</v>
+        <v>44.68</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.53</v>
+        <v>10.81</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.6</v>
+        <v>6.62</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.94</v>
+        <v>4.19</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.93</v>
+        <v>19</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7105,139 +7105,139 @@
         <v>2.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG16" t="n">
         <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>115.11</v>
+        <v>113.1</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL16" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>62.11</v>
+        <v>59.7</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.890000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.779999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AU16" t="n">
         <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>58.89</v>
+        <v>57.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>19.33</v>
+        <v>18.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>12.44</v>
+        <v>11.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.22</v>
+        <v>16.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG16" t="n">
         <v>2.94</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.44</v>
+        <v>9.59</v>
       </c>
       <c r="BI16" t="n">
         <v>2.94</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.94</v>
+        <v>4.59</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS16" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY16" t="n">
         <v>1.28</v>
@@ -7246,13 +7246,13 @@
         <v>1.33</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.67</v>
+        <v>5.59</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CD16" t="n">
         <v>1.57</v>
@@ -7261,13 +7261,13 @@
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI16" t="n">
         <v>2.07</v>
@@ -7276,25 +7276,25 @@
         <v>1.76</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
@@ -7309,7 +7309,7 @@
         <v>1.67</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW16" t="n">
         <v>1.84</v>
@@ -7318,97 +7318,97 @@
         <v>1.59</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="DH16" t="n">
-        <v>121.13</v>
+        <v>119.59</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.31</v>
+        <v>6.35</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="DM16" t="n">
-        <v>69.94</v>
+        <v>68.06</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.56</v>
+        <v>9.77</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.25</v>
+        <v>13.18</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.69</v>
+        <v>6.71</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>59.75</v>
+        <v>59.06</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX16" t="n">
-        <v>19.87</v>
+        <v>19.47</v>
       </c>
       <c r="DY16" t="n">
-        <v>12.75</v>
+        <v>12.41</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.13</v>
+        <v>7.06</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.75</v>
+        <v>16.71</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="17">
@@ -7418,13 +7418,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7511,136 +7511,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="n">
         <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>72.43000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL17" t="n">
         <v>3</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.14</v>
+        <v>31.88</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.57</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>43</v>
+        <v>43.12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.289999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.86</v>
+        <v>19.38</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.27</v>
+        <v>10.12</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BO17" t="n">
         <v>1</v>
       </c>
-      <c r="BO17" t="n">
-        <v>0.93</v>
-      </c>
       <c r="BP17" t="n">
-        <v>5.47</v>
+        <v>5.25</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.13</v>
+        <v>4.25</v>
       </c>
       <c r="BR17" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS17" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BU17" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BV17" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX17" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BY17" t="n">
         <v>4.79</v>
@@ -7649,25 +7649,25 @@
         <v>5.16</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="CC17" t="n">
-        <v>7.14</v>
+        <v>6.77</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.99</v>
+        <v>6.62</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
         <v>3.03</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH17" t="n">
         <v>1.36</v>
@@ -7685,16 +7685,16 @@
         <v>2</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO17" t="n">
         <v>1.37</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CQ17" t="n">
         <v>3.99</v>
@@ -7703,37 +7703,37 @@
         <v>1.48</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB17" t="n">
         <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DD17" t="n">
         <v>3.14</v>
@@ -7742,76 +7742,76 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DH17" t="n">
-        <v>73.27</v>
+        <v>74.25</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.86</v>
+        <v>3.81</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DM17" t="n">
-        <v>35.13</v>
+        <v>35.25</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.6</v>
+        <v>11.62</v>
       </c>
       <c r="DQ17" t="n">
         <v>10.94</v>
       </c>
       <c r="DR17" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>44.8</v>
+        <v>44.75</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.07</v>
+        <v>8.75</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.27</v>
+        <v>6.06</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.34</v>
+        <v>18.63</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -8049,13 +8049,13 @@
         <v>2.47</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CA18" t="n">
         <v>3.43</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CC18" t="n">
         <v>3.9</v>
@@ -8115,10 +8115,10 @@
         <v>1.45</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX18" t="n">
         <v>1.6</v>
@@ -8224,94 +8224,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F19" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="G19" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="H19" t="n">
-        <v>100.71</v>
+        <v>98.62</v>
       </c>
       <c r="I19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>52.14</v>
+        <v>49.38</v>
       </c>
       <c r="N19" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O19" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="P19" t="n">
-        <v>17</v>
+        <v>16.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="R19" t="n">
-        <v>4.86</v>
+        <v>5.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>56.86</v>
+        <v>56.75</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.43</v>
+        <v>11.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.43</v>
+        <v>3.88</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.71</v>
+        <v>20.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="AF19" t="n">
         <v>0.12</v>
@@ -8395,70 +8395,70 @@
         <v>3.12</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.4</v>
+        <v>10.25</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV19" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CC19" t="n">
         <v>4.65</v>
@@ -8467,157 +8467,157 @@
         <v>4.93</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CH19" t="n">
         <v>1.39</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK19" t="n">
         <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO19" t="n">
         <v>1.35</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DB19" t="n">
         <v>1.4</v>
       </c>
-      <c r="CV19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CY19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CZ19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="DA19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DB19" t="n">
-        <v>1.39</v>
-      </c>
       <c r="DC19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DD19" t="n">
         <v>3.34</v>
       </c>
       <c r="DE19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="DW19" t="n">
         <v>0.06</v>
       </c>
-      <c r="DF19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="DG19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="DH19" t="n">
-        <v>95.26000000000001</v>
-      </c>
-      <c r="DI19" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DJ19" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="DK19" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="DL19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DM19" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="DN19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DO19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="DP19" t="n">
-        <v>15.34</v>
-      </c>
-      <c r="DQ19" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="DR19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="DS19" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DT19" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV19" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="DW19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="DX19" t="n">
-        <v>10.67</v>
+        <v>10.81</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.47</v>
+        <v>7.38</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.46</v>
+        <v>19.75</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.33</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="20">
@@ -8627,13 +8627,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
         <v>0.12</v>
@@ -8720,49 +8720,49 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>80.14</v>
+        <v>82.5</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.43</v>
+        <v>3.88</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>33</v>
+        <v>34.88</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.14</v>
+        <v>11.12</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.86</v>
+        <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8774,82 +8774,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>41</v>
+        <v>42.62</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA20" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.86</v>
+        <v>5.62</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.71</v>
+        <v>18.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.67</v>
+        <v>9.81</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.2</v>
+        <v>5.31</v>
       </c>
       <c r="BR20" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS20" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT20" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU20" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV20" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW20" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX20" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
         <v>2.51</v>
@@ -8858,40 +8858,40 @@
         <v>2.72</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="CC20" t="n">
-        <v>5.63</v>
+        <v>6.42</v>
       </c>
       <c r="CD20" t="n">
-        <v>6.63</v>
+        <v>7</v>
       </c>
       <c r="CE20" t="n">
         <v>1.42</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK20" t="n">
         <v>1.49</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM20" t="n">
         <v>2.48</v>
@@ -8900,28 +8900,28 @@
         <v>1.95</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW20" t="n">
         <v>1.97</v>
@@ -8930,64 +8930,64 @@
         <v>1.61</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.33</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.09</v>
+        <v>3.03</v>
       </c>
       <c r="DE20" t="n">
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="DH20" t="n">
-        <v>86.26000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM20" t="n">
-        <v>37.53</v>
+        <v>38.19</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.13</v>
+        <v>12.06</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.8</v>
+        <v>11.88</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.73</v>
+        <v>7.69</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8999,28 +8999,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.13</v>
+        <v>47.56</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.67</v>
+        <v>10.82</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.73</v>
+        <v>7.94</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.6</v>
+        <v>18.56</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -3219,7 +3219,7 @@
         <v>3.05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CA6" t="n">
         <v>3.33</v>
@@ -3285,7 +3285,7 @@
         <v>1.46</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW6" t="n">
         <v>2.17</v>
@@ -3294,7 +3294,7 @@
         <v>1.66</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.25</v>
@@ -3309,7 +3309,7 @@
         <v>2.5</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="DE6" t="n">
         <v>0.12</v>
@@ -6209,10 +6209,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
@@ -6221,49 +6221,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>98.33</v>
+        <v>99.14</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="K14" t="n">
         <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="M14" t="n">
-        <v>54.17</v>
+        <v>55.14</v>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>12.67</v>
+        <v>12.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>9.57</v>
       </c>
       <c r="R14" t="n">
-        <v>8.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="T14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6275,28 +6275,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>53.67</v>
+        <v>54.43</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.33</v>
+        <v>16.43</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.17</v>
+        <v>11</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="AC14" t="n">
-        <v>22.33</v>
+        <v>21.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6380,70 +6380,70 @@
         <v>2.78</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.53</v>
+        <v>11.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.8</v>
+        <v>5.69</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.73</v>
+        <v>5.81</v>
       </c>
       <c r="BR14" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BS14" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BT14" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV14" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.51</v>
+        <v>3.38</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CC14" t="n">
         <v>3.84</v>
@@ -6464,10 +6464,10 @@
         <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK14" t="n">
         <v>1.46</v>
@@ -6476,10 +6476,10 @@
         <v>1.86</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO14" t="n">
         <v>1.31</v>
@@ -6488,7 +6488,7 @@
         <v>2.02</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CR14" t="n">
         <v>1.44</v>
@@ -6512,10 +6512,10 @@
         <v>1.53</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DA14" t="n">
         <v>2</v>
@@ -6524,85 +6524,85 @@
         <v>1.39</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.2</v>
+        <v>94.81</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.13</v>
+        <v>6.25</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.33</v>
+        <v>47.25</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.94</v>
+        <v>13.69</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.26</v>
+        <v>10.06</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.67</v>
+        <v>13.31</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.529999999999999</v>
+        <v>9</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.13</v>
+        <v>4.31</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="15">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0.38</v>
@@ -6705,49 +6705,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>90.56999999999999</v>
+        <v>87.62</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>48.71</v>
+        <v>46.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.57</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.57</v>
+        <v>14</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6759,82 +6759,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>50.57</v>
+        <v>49.38</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.29</v>
+        <v>13.25</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.86</v>
+        <v>18.88</v>
       </c>
       <c r="BE15" t="n">
         <v>1.46</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.4</v>
+        <v>10.44</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="BR15" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS15" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY15" t="n">
         <v>2.38</v>
@@ -6843,55 +6843,55 @@
         <v>2.42</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CC15" t="n">
         <v>2.69</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="CE15" t="n">
         <v>1.36</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.74</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6906,73 +6906,73 @@
         <v>1.46</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB15" t="n">
         <v>1.31</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="DH15" t="n">
-        <v>99.33</v>
+        <v>97.31</v>
       </c>
       <c r="DI15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.93</v>
+        <v>4.81</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM15" t="n">
-        <v>49.53</v>
+        <v>48.38</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.33</v>
+        <v>10.12</v>
       </c>
       <c r="DQ15" t="n">
-        <v>14.13</v>
+        <v>13.88</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.26</v>
+        <v>7.5</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6984,28 +6984,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.33</v>
+        <v>49.75</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.87</v>
+        <v>14.75</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.13</v>
+        <v>9.93</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.73</v>
+        <v>4.81</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.33</v>
+        <v>18.31</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="16">
@@ -7249,13 +7249,13 @@
         <v>5.25</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.59</v>
+        <v>5.58</v>
       </c>
       <c r="CC16" t="n">
         <v>1.55</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CE16" t="n">
         <v>1.25</v>
@@ -7309,19 +7309,19 @@
         <v>1.67</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW16" t="n">
         <v>1.84</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA16" t="n">
         <v>2.13</v>
@@ -7330,10 +7330,10 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0.22</v>
@@ -1872,139 +1872,139 @@
         <v>1.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AI3" t="n">
-        <v>99.12</v>
+        <v>97.78</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>5</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>46.25</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>52.25</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>5.12</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY3" t="n">
         <v>1.54</v>
@@ -2013,25 +2013,25 @@
         <v>1.6</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
@@ -2040,142 +2040,142 @@
         <v>1.91</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK3" t="n">
         <v>1.56</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CN3" t="n">
         <v>1.84</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA3" t="n">
         <v>1.87</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.18</v>
+        <v>3.06</v>
       </c>
       <c r="DH3" t="n">
-        <v>102.41</v>
+        <v>101.56</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DK3" t="n">
-        <v>7</v>
+        <v>6.84</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DM3" t="n">
-        <v>53.17</v>
+        <v>53.56</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.82</v>
+        <v>3.77</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.23</v>
+        <v>11.39</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.29</v>
+        <v>10.11</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.35</v>
+        <v>8.23</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.71</v>
+        <v>53.44</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.3</v>
+        <v>7.34</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.64</v>
+        <v>5.66</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.7</v>
+        <v>19.17</v>
       </c>
       <c r="EB3" t="n">
         <v>1.6</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>0.57</v>
+        <v>1.12</v>
       </c>
       <c r="H4" t="n">
-        <v>95.56999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="K4" t="n">
-        <v>2.86</v>
+        <v>3.62</v>
       </c>
       <c r="L4" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>46.29</v>
+        <v>46.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="P4" t="n">
-        <v>13.57</v>
+        <v>13.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.29</v>
+        <v>10.25</v>
       </c>
       <c r="R4" t="n">
-        <v>7.57</v>
+        <v>7.62</v>
       </c>
       <c r="S4" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.29</v>
+        <v>48.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.29</v>
+        <v>12.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.71</v>
+        <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>23</v>
+        <v>22.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.75</v>
+        <v>7.82</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS4" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU4" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY4" t="n">
         <v>2.25</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="CC4" t="n">
         <v>6.22</v>
@@ -2428,61 +2428,61 @@
         <v>6.48</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF4" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.82</v>
+        <v>3.93</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS4" t="n">
         <v>2.92</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="CU4" t="n">
         <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CX4" t="n">
         <v>1.65</v>
@@ -2497,88 +2497,88 @@
         <v>1.86</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="DD4" t="n">
         <v>2.85</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.06</v>
+        <v>85.94</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.38</v>
+        <v>40.94</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.69</v>
+        <v>12.88</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.81</v>
+        <v>10.76</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.06</v>
+        <v>9</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.63</v>
+        <v>44.76</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.12</v>
+        <v>10.47</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.37</v>
+        <v>3.59</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.38</v>
+        <v>19.41</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AI5" t="n">
-        <v>79.29000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>32.86</v>
+        <v>32.25</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.43</v>
+        <v>12.62</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.14</v>
+        <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.29</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>46</v>
+        <v>45.75</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.14</v>
+        <v>17.12</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.880000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
       <c r="BR5" t="n">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="BS5" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BU5" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV5" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX5" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY5" t="n">
         <v>2.69</v>
@@ -2819,40 +2819,40 @@
         <v>2.78</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.73</v>
+        <v>3.53</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.07</v>
+        <v>3.85</v>
       </c>
       <c r="CE5" t="n">
         <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK5" t="n">
         <v>1.62</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM5" t="n">
         <v>2.2</v>
@@ -2861,13 +2861,13 @@
         <v>1.76</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2882,106 +2882,106 @@
         <v>1.45</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DH5" t="n">
-        <v>97.5</v>
+        <v>96.53</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="DL5" t="n">
         <v>0.06</v>
       </c>
       <c r="DM5" t="n">
-        <v>42.5</v>
+        <v>41.65</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.06</v>
+        <v>11.76</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.87</v>
+        <v>12</v>
       </c>
       <c r="DR5" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.82</v>
+        <v>50.41</v>
       </c>
       <c r="DW5" t="n">
         <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.56</v>
+        <v>10.29</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.82</v>
+        <v>6.65</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="EA5" t="n">
-        <v>19</v>
+        <v>18.88</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0.11</v>
@@ -3081,52 +3081,52 @@
         <v>1.89</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AI6" t="n">
-        <v>94.43000000000001</v>
+        <v>92.88</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.71</v>
+        <v>4.12</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>39.71</v>
+        <v>37.75</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17</v>
+        <v>16.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.43</v>
+        <v>12.88</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,55 +3138,55 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.57</v>
+        <v>48.25</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.29</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>6.62</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.71</v>
+        <v>18.38</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BF6" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.81</v>
+        <v>9.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BP6" t="n">
         <v>4</v>
@@ -3195,16 +3195,16 @@
         <v>4.94</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS6" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BT6" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU6" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY6" t="n">
         <v>3.05</v>
@@ -3222,73 +3222,73 @@
         <v>3.18</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ6" t="n">
         <v>2.1</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.76</v>
+        <v>4.81</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CS6" t="n">
         <v>3.05</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="CU6" t="n">
         <v>1.46</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CX6" t="n">
         <v>1.66</v>
@@ -3303,88 +3303,88 @@
         <v>1.81</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DD6" t="n">
         <v>2.51</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="DH6" t="n">
-        <v>101.12</v>
+        <v>100</v>
       </c>
       <c r="DI6" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.25</v>
+        <v>4.94</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM6" t="n">
-        <v>43</v>
+        <v>41.88</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="DP6" t="n">
-        <v>16.06</v>
+        <v>15.76</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.69</v>
+        <v>13.83</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.81</v>
+        <v>8.06</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.31</v>
+        <v>49.53</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>11</v>
+        <v>10.77</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.69</v>
+        <v>7.47</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.06</v>
+        <v>19.83</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.33</v>
@@ -3887,118 +3887,118 @@
         <v>0.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="AI8" t="n">
-        <v>110.25</v>
+        <v>115.22</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AL8" t="n">
-        <v>6.5</v>
+        <v>6.89</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.88</v>
+        <v>64.44</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP8" t="n">
         <v>3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.5</v>
+        <v>9.33</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.62</v>
+        <v>12.22</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>67.62</v>
+        <v>68.89</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA8" t="n">
-        <v>19.12</v>
+        <v>19.11</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.38</v>
+        <v>11.67</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.75</v>
+        <v>7.44</v>
       </c>
       <c r="BD8" t="n">
-        <v>17</v>
+        <v>16.56</v>
       </c>
       <c r="BE8" t="n">
         <v>2.19</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.47</v>
+        <v>11.67</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BK8" t="n">
         <v>1</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.71</v>
+        <v>5.78</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.76</v>
+        <v>5.89</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4007,19 +4007,19 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BV8" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW8" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
         <v>1.28</v>
@@ -4028,34 +4028,34 @@
         <v>1.33</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.58</v>
+        <v>5.51</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.94</v>
+        <v>5.86</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CD8" t="n">
         <v>1.76</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="CH8" t="n">
         <v>1.81</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CK8" t="n">
         <v>1.42</v>
@@ -4076,24 +4076,24 @@
         <v>1.39</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY8" t="n">
         <v>1.72</v>
@@ -4102,89 +4102,89 @@
         <v>2.52</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DB8" t="inlineStr"/>
       <c r="DC8" t="n">
         <v>1.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF8" t="n">
         <v>1</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.47</v>
+        <v>3.66</v>
       </c>
       <c r="DH8" t="n">
-        <v>114.06</v>
+        <v>116.33</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.94</v>
+        <v>7.11</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="DM8" t="n">
-        <v>61.89</v>
+        <v>63.61</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.289999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.88</v>
+        <v>11.72</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>67.7</v>
+        <v>68.33</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>19.94</v>
+        <v>19.89</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.24</v>
+        <v>12.34</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.71</v>
+        <v>7.56</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.53</v>
+        <v>17.28</v>
       </c>
       <c r="EB8" t="n">
         <v>2.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="9">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -4609,82 +4609,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="H10" t="n">
-        <v>88.88</v>
+        <v>90.44</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="K10" t="n">
-        <v>5.62</v>
+        <v>5.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="P10" t="n">
-        <v>9.619999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.12</v>
+        <v>14.11</v>
       </c>
       <c r="R10" t="n">
-        <v>7.38</v>
+        <v>7.22</v>
       </c>
       <c r="S10" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="U10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>50</v>
+        <v>50.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.75</v>
+        <v>9.67</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.38</v>
+        <v>6.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.88</v>
+        <v>17.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF10" t="n">
         <v>0.12</v>
@@ -4768,70 +4768,70 @@
         <v>2.38</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.619999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.25</v>
+        <v>5.12</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX10" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.87</v>
+        <v>3.11</v>
       </c>
       <c r="CA10" t="n">
         <v>3.9</v>
       </c>
       <c r="CB10" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC10" t="n">
         <v>6.08</v>
@@ -4843,10 +4843,10 @@
         <v>1.37</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CH10" t="n">
         <v>1.47</v>
@@ -4873,19 +4873,19 @@
         <v>1.27</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CU10" t="n">
         <v>1.45</v>
@@ -4897,94 +4897,94 @@
         <v>1.84</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY10" t="n">
         <v>1.99</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA10" t="n">
         <v>1.87</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC10" t="n">
         <v>1.9</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DG10" t="n">
         <v>1.88</v>
       </c>
       <c r="DH10" t="n">
-        <v>87.75</v>
+        <v>88.64</v>
       </c>
       <c r="DI10" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DM10" t="n">
-        <v>42.38</v>
+        <v>42.29</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.37</v>
+        <v>10.17</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.81</v>
+        <v>13.82</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.380000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47.06</v>
+        <v>47.29</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.619999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.75</v>
+        <v>16.53</v>
       </c>
       <c r="EB10" t="n">
         <v>1.17</v>
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="G11" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="H11" t="n">
-        <v>77.17</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>34.5</v>
+        <v>34.43</v>
       </c>
       <c r="N11" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O11" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="P11" t="n">
-        <v>11.67</v>
+        <v>12.29</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.5</v>
+        <v>12.43</v>
       </c>
       <c r="R11" t="n">
-        <v>9.5</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>39</v>
+        <v>39.71</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.17</v>
+        <v>10.57</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.83</v>
+        <v>7.29</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.67</v>
+        <v>17.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5171,70 +5171,70 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.47</v>
+        <v>10.88</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT11" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV11" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.01</v>
+        <v>4.71</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.48</v>
+        <v>5.15</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="CC11" t="n">
         <v>4.66</v>
@@ -5246,10 +5246,10 @@
         <v>1.37</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CG11" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CH11" t="n">
         <v>1.46</v>
@@ -5258,13 +5258,13 @@
         <v>1.96</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK11" t="n">
         <v>1.49</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM11" t="n">
         <v>2.48</v>
@@ -5273,25 +5273,25 @@
         <v>1.91</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV11" t="n">
         <v>2.06</v>
@@ -5303,97 +5303,97 @@
         <v>1.59</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DB11" t="n">
         <v>1.33</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="DE11" t="n">
         <v>0.13</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="DH11" t="n">
-        <v>81.73999999999999</v>
+        <v>82.88</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM11" t="n">
-        <v>36.86</v>
+        <v>36.69</v>
       </c>
       <c r="DN11" t="n">
         <v>0.87</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.27</v>
+        <v>12.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.2</v>
+        <v>12.19</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.67</v>
+        <v>9.57</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.47</v>
+        <v>41.62</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.87</v>
+        <v>7.06</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.87</v>
+        <v>17.62</v>
       </c>
       <c r="EB11" t="n">
         <v>1.17</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="12">
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.12</v>
@@ -5896,139 +5896,139 @@
         <v>2.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>35.5</v>
+        <v>34</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.5</v>
+        <v>11.56</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.12</v>
+        <v>12.78</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AU13" t="n">
         <v>1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>44.75</v>
+        <v>43</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.12</v>
+        <v>10.33</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.62</v>
+        <v>6.11</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>4.22</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.25</v>
+        <v>17.78</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.56</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.19</v>
+        <v>4.35</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.38</v>
+        <v>5.53</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT13" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY13" t="n">
         <v>3.58</v>
@@ -6037,67 +6037,67 @@
         <v>3.72</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="CC13" t="n">
-        <v>6.24</v>
+        <v>6.01</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.64</v>
+        <v>6.36</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI13" t="n">
         <v>1.77</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK13" t="n">
         <v>1.57</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CM13" t="n">
         <v>2.33</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="CR13" t="n">
         <v>1.49</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV13" t="n">
         <v>1.83</v>
@@ -6106,100 +6106,100 @@
         <v>2.08</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY13" t="n">
         <v>2.07</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA13" t="n">
         <v>1.81</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DD13" t="n">
         <v>2.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF13" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="DH13" t="n">
-        <v>91.94</v>
+        <v>89.88</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.75</v>
+        <v>36.82</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.62</v>
+        <v>11.65</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.06</v>
+        <v>12.88</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.82</v>
+        <v>7.88</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.68</v>
+        <v>43.76</v>
       </c>
       <c r="DW13" t="n">
         <v>0.18</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.81</v>
+        <v>10.41</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.62</v>
+        <v>6.35</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="EA13" t="n">
-        <v>19</v>
+        <v>18.71</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="14">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
@@ -7027,82 +7027,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="H16" t="n">
-        <v>128.86</v>
+        <v>126.25</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>6.71</v>
+        <v>6.62</v>
       </c>
       <c r="L16" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="M16" t="n">
-        <v>80</v>
+        <v>76.38</v>
       </c>
       <c r="N16" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>10.43</v>
+        <v>10.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>11.88</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>60.86</v>
+        <v>59.88</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.57</v>
+        <v>20.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.14</v>
+        <v>12.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.43</v>
+        <v>17.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
         <v>0.1</v>
@@ -7186,70 +7186,70 @@
         <v>1.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.59</v>
+        <v>9.67</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.18</v>
+        <v>4.28</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS16" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU16" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX16" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.58</v>
+        <v>5.67</v>
       </c>
       <c r="CC16" t="n">
         <v>1.55</v>
@@ -7261,40 +7261,40 @@
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.76</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM16" t="n">
         <v>2.72</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
@@ -7309,10 +7309,10 @@
         <v>1.67</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX16" t="n">
         <v>1.58</v>
@@ -7330,85 +7330,85 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="DH16" t="n">
-        <v>119.59</v>
+        <v>118.94</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.35</v>
+        <v>6.33</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DM16" t="n">
-        <v>68.06</v>
+        <v>67.11</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.77</v>
+        <v>9.94</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.18</v>
+        <v>13.45</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.71</v>
+        <v>6.67</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>59.06</v>
+        <v>58.72</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX16" t="n">
-        <v>19.47</v>
+        <v>19.39</v>
       </c>
       <c r="DY16" t="n">
-        <v>12.41</v>
+        <v>12.28</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.06</v>
+        <v>7.11</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.71</v>
+        <v>16.67</v>
       </c>
       <c r="EB16" t="n">
         <v>2.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="17">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -7430,49 +7430,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="H17" t="n">
-        <v>74</v>
+        <v>77.89</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="K17" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="L17" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M17" t="n">
-        <v>38.62</v>
+        <v>40.56</v>
       </c>
       <c r="N17" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="P17" t="n">
-        <v>10.75</v>
+        <v>11.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.38</v>
+        <v>10.89</v>
       </c>
       <c r="R17" t="n">
-        <v>7.12</v>
+        <v>6.89</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7484,28 +7484,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>46.38</v>
+        <v>47.44</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.75</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.88</v>
+        <v>18.78</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7589,70 +7589,70 @@
         <v>2.12</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.12</v>
+        <v>9.94</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.25</v>
+        <v>5.18</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="BR17" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BS17" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BT17" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU17" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV17" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX17" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.79</v>
+        <v>4.65</v>
       </c>
       <c r="BZ17" t="n">
-        <v>5.16</v>
+        <v>4.99</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CC17" t="n">
         <v>6.77</v>
@@ -7664,31 +7664,31 @@
         <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH17" t="n">
         <v>1.36</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL17" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CO17" t="n">
         <v>1.37</v>
@@ -7718,67 +7718,67 @@
         <v>2.15</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DH17" t="n">
-        <v>74.25</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DM17" t="n">
-        <v>35.25</v>
+        <v>36.48</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.62</v>
+        <v>11.76</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.94</v>
+        <v>10.71</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.75</v>
+        <v>7.59</v>
       </c>
       <c r="DS17" t="n">
         <v>0.06</v>
@@ -7790,25 +7790,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>44.75</v>
+        <v>45.41</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DX17" t="n">
-        <v>8.75</v>
+        <v>8.82</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.06</v>
+        <v>6.12</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.63</v>
+        <v>19.06</v>
       </c>
       <c r="EB17" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="EC17" t="n">
         <v>2</v>
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7914,136 +7914,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>92.75</v>
+        <v>92</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.88</v>
+        <v>6.33</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN18" t="n">
-        <v>44.88</v>
+        <v>44.11</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.88</v>
+        <v>14.67</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>10.67</v>
       </c>
       <c r="AS18" t="n">
-        <v>9</v>
+        <v>8.44</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU18" t="n">
         <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.75</v>
+        <v>49.56</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.75</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.88</v>
+        <v>17.89</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.25</v>
+        <v>10.65</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP18" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.25</v>
+        <v>5.59</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT18" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU18" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY18" t="n">
         <v>2.47</v>
@@ -8052,16 +8052,16 @@
         <v>2.63</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.84</v>
+        <v>3.69</v>
       </c>
       <c r="CE18" t="n">
         <v>1.42</v>
@@ -8070,7 +8070,7 @@
         <v>3</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH18" t="n">
         <v>1.39</v>
@@ -8079,13 +8079,13 @@
         <v>1.91</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM18" t="n">
         <v>2.45</v>
@@ -8097,7 +8097,7 @@
         <v>1.33</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ18" t="n">
         <v>3.74</v>
@@ -8106,13 +8106,13 @@
         <v>1.44</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CT18" t="n">
         <v>2.87</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV18" t="n">
         <v>2</v>
@@ -8121,13 +8121,13 @@
         <v>1.9</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY18" t="n">
         <v>1.92</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DA18" t="n">
         <v>1.92</v>
@@ -8139,7 +8139,7 @@
         <v>2.15</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
@@ -8148,40 +8148,40 @@
         <v>1.18</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.37</v>
+        <v>3.52</v>
       </c>
       <c r="DH18" t="n">
-        <v>104.94</v>
+        <v>103.82</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ18" t="n">
         <v>2.18</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.32</v>
+        <v>6.53</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM18" t="n">
-        <v>49.82</v>
+        <v>49.12</v>
       </c>
       <c r="DN18" t="n">
         <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.75</v>
+        <v>15.59</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.5</v>
+        <v>11.77</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.81</v>
+        <v>7.58</v>
       </c>
       <c r="DS18" t="n">
         <v>0.18</v>
@@ -8193,25 +8193,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.82</v>
+        <v>52.06</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.38</v>
+        <v>13.65</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.68</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.69</v>
+        <v>4.76</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.13</v>
+        <v>19.06</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="EC18" t="n">
         <v>2.18</v>
@@ -8224,13 +8224,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0.12</v>
@@ -8314,52 +8314,52 @@
         <v>3.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>90.5</v>
+        <v>87.56</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="AL19" t="n">
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AN19" t="n">
-        <v>37.62</v>
+        <v>36.56</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.88</v>
+        <v>14.44</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8371,52 +8371,52 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>51.88</v>
+        <v>51.33</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>10.44</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>7.22</v>
       </c>
       <c r="BC19" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.25</v>
+        <v>18.56</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="BG19" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.25</v>
+        <v>10.29</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL19" t="n">
         <v>0.88</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BO19" t="n">
         <v>1.12</v>
@@ -8425,28 +8425,28 @@
         <v>5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU19" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV19" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY19" t="n">
         <v>2.67</v>
@@ -8455,55 +8455,55 @@
         <v>2.83</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.46</v>
+        <v>3.67</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.65</v>
+        <v>5.58</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.93</v>
+        <v>5.91</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CI19" t="n">
         <v>1.89</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CL19" t="n">
         <v>1.98</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.72</v>
+        <v>3.61</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
@@ -8527,61 +8527,61 @@
         <v>1.59</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.34</v>
+        <v>3.21</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="DH19" t="n">
-        <v>94.56</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.31</v>
+        <v>3.41</v>
       </c>
       <c r="DK19" t="n">
         <v>5.12</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.5</v>
+        <v>42.59</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.07</v>
+        <v>15.29</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.19</v>
+        <v>14.12</v>
       </c>
       <c r="DR19" t="n">
         <v>5.88</v>
@@ -8596,28 +8596,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.32</v>
+        <v>53.88</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.81</v>
+        <v>11</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.38</v>
+        <v>7.47</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.75</v>
+        <v>19.36</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="20">
@@ -8627,61 +8627,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G20" t="n">
-        <v>3.88</v>
+        <v>4.22</v>
       </c>
       <c r="H20" t="n">
-        <v>91.62</v>
+        <v>95.22</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="K20" t="n">
-        <v>6.12</v>
+        <v>6.78</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M20" t="n">
-        <v>41.5</v>
+        <v>45.78</v>
       </c>
       <c r="N20" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="P20" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.75</v>
+        <v>11.78</v>
       </c>
       <c r="R20" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="S20" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="T20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8693,28 +8693,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>52.5</v>
+        <v>54.56</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>13.88</v>
+        <v>14.22</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.25</v>
+        <v>10.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AC20" t="n">
-        <v>18.5</v>
+        <v>19.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8798,70 +8798,70 @@
         <v>1.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.81</v>
+        <v>10.12</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="BL20" t="n">
         <v>1.12</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.44</v>
+        <v>4.59</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.31</v>
+        <v>5.47</v>
       </c>
       <c r="BR20" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS20" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU20" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV20" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW20" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX20" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="CC20" t="n">
         <v>6.42</v>
@@ -8873,76 +8873,76 @@
         <v>1.42</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CK20" t="n">
         <v>1.49</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.72</v>
+        <v>3.77</v>
       </c>
       <c r="CR20" t="n">
         <v>1.47</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX20" t="n">
         <v>1.61</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.33</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="DD20" t="n">
         <v>3.03</v>
@@ -8951,13 +8951,13 @@
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.19</v>
+        <v>3.41</v>
       </c>
       <c r="DH20" t="n">
-        <v>87.06</v>
+        <v>89.23</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
@@ -8966,28 +8966,28 @@
         <v>1.94</v>
       </c>
       <c r="DK20" t="n">
-        <v>5</v>
+        <v>5.42</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM20" t="n">
-        <v>38.19</v>
+        <v>40.65</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.06</v>
+        <v>11.94</v>
       </c>
       <c r="DQ20" t="n">
         <v>11.88</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.69</v>
+        <v>7.36</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8999,28 +8999,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.56</v>
+        <v>48.94</v>
       </c>
       <c r="DW20" t="n">
         <v>0.06</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.82</v>
+        <v>11.18</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.94</v>
+        <v>8.35</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.56</v>
+        <v>19.18</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="21">
@@ -9030,61 +9030,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G21" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>100.38</v>
+        <v>95.33</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="K21" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>56.88</v>
+        <v>54.78</v>
       </c>
       <c r="N21" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O21" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="P21" t="n">
-        <v>12.12</v>
+        <v>11.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="R21" t="n">
-        <v>6.25</v>
+        <v>6.89</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9096,28 +9096,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>54.38</v>
+        <v>50.67</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>16.38</v>
+        <v>16.11</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>19.12</v>
+        <v>18.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9201,70 +9201,70 @@
         <v>3.43</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.27</v>
+        <v>8.69</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP21" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT21" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV21" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="CC21" t="n">
         <v>3.16</v>
@@ -9273,157 +9273,157 @@
         <v>3.41</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="CI21" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CQ21" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="CR21" t="n">
         <v>1.38</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="CT21" t="n">
         <v>3.11</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DB21" t="n">
         <v>1.29</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DH21" t="n">
-        <v>88.34</v>
+        <v>86.25</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM21" t="n">
-        <v>46.87</v>
+        <v>46.31</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.6</v>
+        <v>12.44</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.27</v>
+        <v>11.06</v>
       </c>
       <c r="DR21" t="n">
-        <v>6.87</v>
+        <v>7.19</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.8</v>
+        <v>45.19</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.27</v>
+        <v>13.31</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="DZ21" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
       <c r="EA21" t="n">
-        <v>17.86</v>
+        <v>17.69</v>
       </c>
       <c r="EB21" t="n">
         <v>1.53</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="H2" t="n">
-        <v>119</v>
+        <v>120.7</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M2" t="n">
-        <v>55.67</v>
+        <v>56.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>13.78</v>
+        <v>13.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.11</v>
+        <v>11.8</v>
       </c>
       <c r="R2" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>50.11</v>
+        <v>51.7</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.44</v>
+        <v>9.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>22</v>
+        <v>21.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>0.12</v>
@@ -1550,70 +1550,70 @@
         <v>2.12</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.710000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.18</v>
+        <v>5.22</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.53</v>
+        <v>4.61</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS2" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT2" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU2" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CC2" t="n">
         <v>3.13</v>
@@ -1622,19 +1622,19 @@
         <v>3.18</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ2" t="n">
         <v>2.01</v>
@@ -1643,7 +1643,7 @@
         <v>1.56</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM2" t="n">
         <v>2.28</v>
@@ -1658,7 +1658,7 @@
         <v>2.18</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
@@ -1679,16 +1679,16 @@
         <v>2.07</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB2" t="n">
         <v>1.41</v>
@@ -1703,43 +1703,43 @@
         <v>0.11</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="DH2" t="n">
-        <v>111.12</v>
+        <v>112.5</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.3</v>
+        <v>5.44</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DM2" t="n">
-        <v>52</v>
+        <v>52.61</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.89</v>
+        <v>12.72</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.24</v>
+        <v>12.06</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
       <c r="DS2" t="n">
         <v>0.17</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.29</v>
+        <v>49.28</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>13</v>
+        <v>13.22</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.119999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.88</v>
+        <v>4.06</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.12</v>
+        <v>20.83</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="3">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F7" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="H7" t="n">
-        <v>105.88</v>
+        <v>103.11</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M7" t="n">
+        <v>53.11</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P7" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>60.33</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.62</v>
       </c>
-      <c r="K7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M7" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P7" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>62.12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,49 +3565,49 @@
         <v>1.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.19</v>
+        <v>7.29</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="BO7" t="n">
         <v>0.88</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT7" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU7" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,19 +3616,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="CC7" t="n">
         <v>5.78</v>
@@ -3637,16 +3637,16 @@
         <v>6.36</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI7" t="n">
         <v>1.82</v>
@@ -3658,22 +3658,22 @@
         <v>1.65</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN7" t="n">
         <v>1.72</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="CR7" t="n">
         <v>1.5</v>
@@ -3688,73 +3688,73 @@
         <v>1.44</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB7" t="n">
         <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="DD7" t="n">
         <v>2.72</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DH7" t="n">
-        <v>98.06</v>
+        <v>97.06</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DK7" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.38</v>
+        <v>45.18</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.63</v>
+        <v>12.77</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.5</v>
+        <v>15.24</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.12</v>
+        <v>7.18</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.87</v>
+        <v>58.11</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>11</v>
+        <v>11.41</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.13</v>
+        <v>7.42</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>15.5</v>
+        <v>15.59</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="8">
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4287,49 +4287,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="AI9" t="n">
-        <v>96.12</v>
+        <v>97.22</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.25</v>
+        <v>5.22</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.62</v>
+        <v>42.11</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.38</v>
+        <v>14.11</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>13.78</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4341,73 +4341,73 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>39.5</v>
+        <v>40.78</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.380000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.88</v>
+        <v>6.56</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BD9" t="n">
-        <v>23.75</v>
+        <v>23.67</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.119999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP9" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BY9" t="n">
         <v>3.17</v>
@@ -4434,13 +4434,13 @@
         <v>5.36</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CG9" t="n">
         <v>2.4</v>
@@ -4455,10 +4455,10 @@
         <v>2.32</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CM9" t="n">
         <v>1.91</v>
@@ -4467,49 +4467,49 @@
         <v>1.55</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CP9" t="n">
         <v>2.66</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.29</v>
+        <v>5.26</v>
       </c>
       <c r="CR9" t="n">
         <v>1.62</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.06</v>
+        <v>3.18</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CW9" t="n">
         <v>2.44</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="DD9" t="n">
         <v>2.81</v>
@@ -4518,43 +4518,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="DH9" t="n">
-        <v>99.94</v>
+        <v>100.29</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="DK9" t="n">
         <v>4.88</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.06</v>
+        <v>41.82</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.32</v>
+        <v>15.12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.81</v>
+        <v>14.65</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.5</v>
+        <v>6.53</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.19</v>
+        <v>41.77</v>
       </c>
       <c r="DW9" t="n">
         <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.32</v>
+        <v>9.65</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.75</v>
+        <v>7.06</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="EA9" t="n">
-        <v>24.94</v>
+        <v>24.82</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="10">
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5493,139 +5493,139 @@
         <v>2.33</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BL12" t="n">
         <v>0.71</v>
       </c>
-      <c r="AH12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>86.86</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>39.14</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.75</v>
-      </c>
       <c r="BM12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.62</v>
+        <v>4.71</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS12" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY12" t="n">
         <v>2.82</v>
@@ -5634,34 +5634,34 @@
         <v>2.79</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.9</v>
+        <v>4.88</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK12" t="n">
         <v>1.54</v>
@@ -5670,19 +5670,19 @@
         <v>1.95</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN12" t="n">
         <v>1.83</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5697,13 +5697,13 @@
         <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY12" t="n">
         <v>2.02</v>
@@ -5718,7 +5718,7 @@
         <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DD12" t="n">
         <v>3.27</v>
@@ -5727,73 +5727,73 @@
         <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.56999999999999</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM12" t="n">
-        <v>46.5</v>
+        <v>45.47</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.87</v>
+        <v>13.59</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.68</v>
+        <v>7.17</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>41.19</v>
+        <v>40.77</v>
       </c>
       <c r="DW12" t="n">
         <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.75</v>
+        <v>12.59</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.31</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.62</v>
+        <v>20.47</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC12" t="n">
         <v>1.88</v>
@@ -6209,13 +6209,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6302,136 +6302,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AI14" t="n">
-        <v>91.44</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.11</v>
+        <v>41.3</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.78</v>
+        <v>14.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.44</v>
+        <v>10.9</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>54.56</v>
+        <v>54.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.89</v>
+        <v>11.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.44</v>
+        <v>7.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>19.44</v>
+        <v>18.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.5</v>
+        <v>11.35</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.69</v>
+        <v>5.71</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.81</v>
+        <v>5.65</v>
       </c>
       <c r="BR14" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BT14" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BU14" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV14" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BY14" t="n">
         <v>3.24</v>
@@ -6440,55 +6440,55 @@
         <v>3.38</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.84</v>
+        <v>3.77</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.99</v>
+        <v>3.92</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK14" t="n">
         <v>1.46</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="CR14" t="n">
         <v>1.44</v>
@@ -6503,28 +6503,28 @@
         <v>1.39</v>
       </c>
       <c r="CV14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="DA14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DD14" t="n">
         <v>3.17</v>
@@ -6533,43 +6533,43 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="DG14" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.81</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.25</v>
+        <v>6.18</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.25</v>
+        <v>47</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.69</v>
+        <v>13.53</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.06</v>
+        <v>10.35</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.25</v>
+        <v>8.18</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.5</v>
+        <v>54.47</v>
       </c>
       <c r="DW14" t="n">
         <v>0.18</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.31</v>
+        <v>13.59</v>
       </c>
       <c r="DY14" t="n">
-        <v>9</v>
+        <v>9.06</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.31</v>
+        <v>4.53</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.5</v>
+        <v>20.12</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="15">
@@ -6612,94 +6612,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G15" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H15" t="n">
-        <v>107</v>
+        <v>103.67</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M15" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P15" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M15" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P15" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.75</v>
-      </c>
       <c r="U15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50.12</v>
+        <v>50</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.25</v>
+        <v>16.56</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.75</v>
+        <v>10.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.5</v>
+        <v>5.78</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.75</v>
+        <v>17.11</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6783,70 +6783,70 @@
         <v>2.38</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.44</v>
+        <v>10.53</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.06</v>
+        <v>6.12</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS15" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX15" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CC15" t="n">
         <v>2.69</v>
@@ -6855,124 +6855,124 @@
         <v>2.74</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="CH15" t="n">
         <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="DD15" t="n">
         <v>2.96</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DH15" t="n">
-        <v>97.31</v>
+        <v>96.12</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.81</v>
+        <v>4.94</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.38</v>
+        <v>47.59</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.12</v>
+        <v>10.3</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.88</v>
+        <v>13.77</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.5</v>
+        <v>7.42</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6984,28 +6984,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.75</v>
+        <v>49.71</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.81</v>
+        <v>5</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.31</v>
+        <v>17.94</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -1469,52 +1469,52 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG2" t="n">
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AI2" t="n">
-        <v>102.25</v>
+        <v>105.78</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.75</v>
+        <v>5.22</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>47.88</v>
+        <v>48.78</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.88</v>
+        <v>12.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.38</v>
+        <v>12.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46.25</v>
+        <v>46.78</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.25</v>
+        <v>12.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.75</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.12</v>
+        <v>20.89</v>
       </c>
       <c r="BE2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1.37</v>
       </c>
-      <c r="BF2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.39</v>
-      </c>
       <c r="BO2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT2" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY2" t="n">
         <v>2.07</v>
@@ -1610,25 +1610,25 @@
         <v>2.07</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="CE2" t="n">
         <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CH2" t="n">
         <v>1.36</v>
@@ -1640,25 +1640,25 @@
         <v>2.01</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
@@ -1679,100 +1679,100 @@
         <v>2.07</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB2" t="n">
         <v>1.41</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DD2" t="n">
         <v>2.89</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="DH2" t="n">
-        <v>112.5</v>
+        <v>113.63</v>
       </c>
       <c r="DI2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.44</v>
+        <v>5.63</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM2" t="n">
-        <v>52.61</v>
+        <v>52.79</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.72</v>
+        <v>13.05</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.06</v>
+        <v>12.05</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.28</v>
+        <v>49.37</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.22</v>
+        <v>13.37</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.17</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.06</v>
+        <v>4.16</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.83</v>
+        <v>21.16</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>94.12</v>
+        <v>91.44</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="K4" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M4" t="n">
-        <v>46.75</v>
+        <v>44.44</v>
       </c>
       <c r="N4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>13.88</v>
+        <v>13.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.25</v>
+        <v>11.22</v>
       </c>
       <c r="R4" t="n">
-        <v>7.62</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.12</v>
+        <v>48.22</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.75</v>
+        <v>12.56</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.62</v>
+        <v>21.89</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.82</v>
+        <v>7.94</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS4" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CC4" t="n">
         <v>6.22</v>
@@ -2431,16 +2431,16 @@
         <v>1.45</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.98</v>
@@ -2449,22 +2449,22 @@
         <v>1.59</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO4" t="n">
         <v>1.38</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.93</v>
+        <v>3.98</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
@@ -2488,97 +2488,97 @@
         <v>1.65</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB4" t="n">
         <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD4" t="n">
         <v>2.85</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.94</v>
+        <v>85.06</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.94</v>
+        <v>40.11</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.88</v>
+        <v>12.84</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.76</v>
+        <v>11.22</v>
       </c>
       <c r="DR4" t="n">
-        <v>9</v>
+        <v>9.16</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.76</v>
+        <v>45</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.47</v>
+        <v>10.5</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.41</v>
+        <v>19.22</v>
       </c>
       <c r="EB4" t="n">
         <v>1.21</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>111.67</v>
+        <v>110.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.89</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>50</v>
+        <v>47.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.44</v>
+        <v>12</v>
       </c>
       <c r="R5" t="n">
-        <v>6.22</v>
+        <v>6.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="U5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54.56</v>
+        <v>53.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.56</v>
+        <v>7.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.44</v>
+        <v>20.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.76</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.29</v>
+        <v>3.44</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.94</v>
+        <v>4.67</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BU5" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX5" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC5" t="n">
         <v>3.53</v>
@@ -2831,28 +2831,28 @@
         <v>3.85</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CH5" t="n">
         <v>1.43</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK5" t="n">
         <v>1.62</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM5" t="n">
         <v>2.2</v>
@@ -2864,10 +2864,10 @@
         <v>1.3</v>
       </c>
       <c r="CP5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2882,7 +2882,7 @@
         <v>1.45</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CW5" t="n">
         <v>1.83</v>
@@ -2897,91 +2897,91 @@
         <v>2.22</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB5" t="n">
         <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="DH5" t="n">
-        <v>96.53</v>
+        <v>96.56</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DM5" t="n">
-        <v>41.65</v>
+        <v>40.94</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.76</v>
+        <v>11.66</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12</v>
+        <v>11.78</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.94</v>
+        <v>7.78</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.41</v>
+        <v>49.83</v>
       </c>
       <c r="DW5" t="n">
         <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.29</v>
+        <v>10.39</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.65</v>
+        <v>6.61</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.88</v>
+        <v>18.78</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="6">
@@ -3394,61 +3394,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="H7" t="n">
-        <v>103.11</v>
+        <v>109.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>53.11</v>
+        <v>57.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>12.67</v>
+        <v>12.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.78</v>
+        <v>14.4</v>
       </c>
       <c r="R7" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>60.33</v>
+        <v>62.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.89</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.779999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.22</v>
+        <v>16.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,49 +3565,49 @@
         <v>1.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.29</v>
+        <v>7.33</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,19 +3616,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="BZ7" t="n">
         <v>3.31</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC7" t="n">
         <v>5.78</v>
@@ -3640,121 +3640,121 @@
         <v>1.45</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH7" t="n">
         <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CP7" t="n">
         <v>2.16</v>
       </c>
-      <c r="CN7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>2.18</v>
-      </c>
       <c r="CQ7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="CU7" t="n">
         <v>1.44</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="CX7" t="n">
         <v>1.73</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="DH7" t="n">
-        <v>97.06</v>
+        <v>100.72</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.06</v>
+        <v>3.22</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.18</v>
+        <v>48.06</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.77</v>
+        <v>12.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.24</v>
+        <v>15</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.11</v>
+        <v>59.22</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.41</v>
+        <v>11.61</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.42</v>
+        <v>7.72</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="EA7" t="n">
-        <v>15.59</v>
+        <v>16.22</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.33</v>
@@ -3887,118 +3887,118 @@
         <v>0.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>115.22</v>
+        <v>114.3</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.44</v>
+        <v>63.3</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>68.89</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>19.11</v>
+        <v>18.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.67</v>
+        <v>11.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.44</v>
+        <v>7.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.56</v>
+        <v>16.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="BF8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO8" t="n">
         <v>2.11</v>
       </c>
-      <c r="BG8" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BP8" t="n">
-        <v>5.78</v>
+        <v>5.74</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.89</v>
+        <v>5.95</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4007,19 +4007,19 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BU8" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV8" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW8" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY8" t="n">
         <v>1.28</v>
@@ -4028,16 +4028,16 @@
         <v>1.33</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.51</v>
+        <v>5.48</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.86</v>
+        <v>5.81</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CE8" t="n">
         <v>1.2</v>
@@ -4046,28 +4046,28 @@
         <v>2.01</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CH8" t="n">
         <v>1.81</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.65</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL8" t="n">
         <v>1.71</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO8" t="n">
         <v>1.1</v>
@@ -4076,15 +4076,15 @@
         <v>1.39</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CV8" t="n">
         <v>2.44</v>
@@ -4109,82 +4109,82 @@
         <v>1.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.66</v>
+        <v>3.79</v>
       </c>
       <c r="DH8" t="n">
-        <v>116.33</v>
+        <v>115.79</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DK8" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DM8" t="n">
-        <v>63.61</v>
+        <v>63.05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.220000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.72</v>
+        <v>11.63</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.33</v>
+        <v>4.21</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>68.33</v>
+        <v>68.37</v>
       </c>
       <c r="DW8" t="n">
         <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>19.89</v>
+        <v>19.63</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.34</v>
+        <v>12.16</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.56</v>
+        <v>7.48</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.28</v>
+        <v>17.21</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="9">
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4287,49 +4287,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>97.22</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.22</v>
+        <v>4.9</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>42.11</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.11</v>
+        <v>13.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.78</v>
+        <v>13.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.67</v>
+        <v>7.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4341,73 +4341,73 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>40.78</v>
+        <v>40.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.109999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="BD9" t="n">
-        <v>23.67</v>
+        <v>24.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="BG9" t="n">
         <v>2.06</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.289999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="BI9" t="n">
         <v>2.06</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.06</v>
+        <v>4.11</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.71</v>
+        <v>4.44</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BY9" t="n">
         <v>3.17</v>
@@ -4425,55 +4425,55 @@
         <v>3.24</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.36</v>
+        <v>5.28</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.85</v>
+        <v>5.73</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CN9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CO9" t="n">
         <v>1.55</v>
       </c>
-      <c r="CO9" t="n">
-        <v>1.54</v>
-      </c>
       <c r="CP9" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.26</v>
+        <v>5.39</v>
       </c>
       <c r="CR9" t="n">
         <v>1.62</v>
@@ -4491,25 +4491,25 @@
         <v>1.61</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="DD9" t="n">
         <v>2.81</v>
@@ -4518,43 +4518,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="DH9" t="n">
-        <v>100.29</v>
+        <v>101.06</v>
       </c>
       <c r="DI9" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.88</v>
+        <v>4.72</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.82</v>
+        <v>41.78</v>
       </c>
       <c r="DN9" t="n">
         <v>1.11</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.12</v>
+        <v>14.83</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.65</v>
+        <v>14.55</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.53</v>
+        <v>6.78</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.77</v>
+        <v>41.67</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.65</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.06</v>
+        <v>7.11</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="EA9" t="n">
-        <v>24.82</v>
+        <v>25.22</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="10">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
@@ -5415,82 +5415,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="H12" t="n">
-        <v>91.67</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="M12" t="n">
-        <v>50.33</v>
+        <v>48.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>13.44</v>
+        <v>13.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.67</v>
+        <v>11.9</v>
       </c>
       <c r="R12" t="n">
-        <v>6.33</v>
+        <v>6.6</v>
       </c>
       <c r="S12" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>42.78</v>
+        <v>41.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.22</v>
+        <v>12.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.33</v>
+        <v>7.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.89</v>
+        <v>5.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.78</v>
+        <v>19.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
         <v>0.12</v>
@@ -5574,70 +5574,70 @@
         <v>1.38</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.119999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS12" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU12" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.82</v>
+        <v>3.14</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="CC12" t="n">
         <v>4.88</v>
@@ -5646,157 +5646,157 @@
         <v>5.15</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CN12" t="n">
         <v>1.83</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="CT12" t="n">
         <v>2.73</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CX12" t="n">
         <v>1.63</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.28</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DB12" t="n">
         <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.23999999999999</v>
+        <v>87.94</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
       <c r="DM12" t="n">
-        <v>45.47</v>
+        <v>44.56</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.59</v>
+        <v>13.39</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.88</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.17</v>
+        <v>7.28</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>40.77</v>
+        <v>40.22</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.59</v>
+        <v>12.67</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.119999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.47</v>
+        <v>4.61</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.47</v>
+        <v>20.22</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="13">
@@ -6209,10 +6209,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
@@ -6221,49 +6221,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>101</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>99.14</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="K14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.86</v>
-      </c>
       <c r="M14" t="n">
-        <v>55.14</v>
+        <v>52.62</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="P14" t="n">
-        <v>12.29</v>
+        <v>12.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>8.289999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="T14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6275,28 +6275,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>54.43</v>
+        <v>55.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.43</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.86</v>
+        <v>23.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6383,67 +6383,67 @@
         <v>1.94</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.35</v>
+        <v>11</v>
       </c>
       <c r="BI14" t="n">
         <v>1.94</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.65</v>
+        <v>5.33</v>
       </c>
       <c r="BR14" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS14" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BT14" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
         <v>3.77</v>
@@ -6452,43 +6452,43 @@
         <v>3.92</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.68</v>
+        <v>3.89</v>
       </c>
       <c r="CR14" t="n">
         <v>1.44</v>
@@ -6503,28 +6503,28 @@
         <v>1.39</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="DD14" t="n">
         <v>3.17</v>
@@ -6533,43 +6533,43 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.81999999999999</v>
+        <v>94.94</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.18</v>
+        <v>6</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="DM14" t="n">
-        <v>47</v>
+        <v>46.33</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.53</v>
+        <v>13.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.35</v>
+        <v>10.33</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.18</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.47</v>
+        <v>54.78</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.59</v>
+        <v>13.56</v>
       </c>
       <c r="DY14" t="n">
         <v>9.06</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.12</v>
+        <v>20.78</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="15">
@@ -8627,13 +8627,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
         <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
         <v>0.11</v>
@@ -8720,49 +8720,49 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>82.5</v>
+        <v>83.89</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>34.88</v>
+        <v>37.44</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.12</v>
+        <v>10.89</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>11.67</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8774,82 +8774,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>42.62</v>
+        <v>44.56</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.75</v>
+        <v>8.67</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.62</v>
+        <v>6.22</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.62</v>
+        <v>18.11</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="BH20" t="n">
-        <v>10.12</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.59</v>
+        <v>4.67</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.47</v>
+        <v>5.17</v>
       </c>
       <c r="BR20" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS20" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT20" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU20" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BV20" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX20" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY20" t="n">
         <v>2.45</v>
@@ -8858,46 +8858,46 @@
         <v>2.66</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CC20" t="n">
-        <v>6.42</v>
+        <v>6.16</v>
       </c>
       <c r="CD20" t="n">
-        <v>7</v>
+        <v>6.69</v>
       </c>
       <c r="CE20" t="n">
         <v>1.42</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH20" t="n">
         <v>1.4</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CJ20" t="n">
         <v>1.92</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO20" t="n">
         <v>1.34</v>
@@ -8906,7 +8906,7 @@
         <v>2.1</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CR20" t="n">
         <v>1.47</v>
@@ -8927,67 +8927,67 @@
         <v>1.98</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB20" t="n">
         <v>1.4</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="DE20" t="n">
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="DH20" t="n">
-        <v>89.23</v>
+        <v>89.56</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.42</v>
+        <v>5.34</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="DM20" t="n">
-        <v>40.65</v>
+        <v>41.61</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.94</v>
+        <v>11.78</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.88</v>
+        <v>11.73</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.36</v>
+        <v>7.39</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8999,28 +8999,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>48.94</v>
+        <v>49.56</v>
       </c>
       <c r="DW20" t="n">
         <v>0.06</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.18</v>
+        <v>11.44</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.35</v>
+        <v>8.5</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.18</v>
+        <v>18.89</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="21">
@@ -9030,13 +9030,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
         <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>0.22</v>
@@ -9120,139 +9120,139 @@
         <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AH21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN21" t="n">
         <v>1.71</v>
       </c>
-      <c r="AI21" t="n">
-        <v>74.56999999999999</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>35.43</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>38.14</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>16.43</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BO21" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU21" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV21" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY21" t="n">
         <v>1.88</v>
@@ -9261,28 +9261,28 @@
         <v>1.98</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.16</v>
+        <v>3.03</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="CE21" t="n">
         <v>1.34</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI21" t="n">
         <v>2.12</v>
@@ -9291,16 +9291,16 @@
         <v>1.72</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO21" t="n">
         <v>1.23</v>
@@ -9318,28 +9318,28 @@
         <v>2.71</v>
       </c>
       <c r="CT21" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CU21" t="n">
         <v>1.51</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DB21" t="n">
         <v>1.29</v>
@@ -9351,46 +9351,46 @@
         <v>2.9</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="DH21" t="n">
-        <v>86.25</v>
+        <v>84.17</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DM21" t="n">
-        <v>46.31</v>
+        <v>45</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.44</v>
+        <v>12.36</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.06</v>
+        <v>10.88</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.19</v>
+        <v>7.65</v>
       </c>
       <c r="DS21" t="n">
         <v>0.06</v>
@@ -9402,28 +9402,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>45.19</v>
+        <v>43.82</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.31</v>
+        <v>13.23</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.25</v>
+        <v>8.24</v>
       </c>
       <c r="DZ21" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="EA21" t="n">
-        <v>17.69</v>
+        <v>17.47</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1667,13 +1667,13 @@
         <v>3.24</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU2" t="n">
         <v>1.36</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW2" t="n">
         <v>2.07</v>
@@ -1682,7 +1682,7 @@
         <v>1.65</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.25</v>
@@ -1694,7 +1694,7 @@
         <v>1.41</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DD2" t="n">
         <v>2.89</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0.22</v>
@@ -1872,16 +1872,16 @@
         <v>1.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AI3" t="n">
-        <v>97.78</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1890,34 +1890,34 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>47.78</v>
+        <v>46.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.67</v>
+        <v>12.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.779999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.67</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>51.89</v>
+        <v>52.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.89</v>
+        <v>10.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.56</v>
+        <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.39</v>
+        <v>10.47</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL3" t="n">
         <v>1.11</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.39</v>
+        <v>5.58</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX3" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY3" t="n">
         <v>1.54</v>
@@ -2013,16 +2013,16 @@
         <v>1.6</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.48</v>
+        <v>4.44</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CE3" t="n">
         <v>1.36</v>
@@ -2037,16 +2037,16 @@
         <v>1.47</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM3" t="n">
         <v>2.34</v>
@@ -2061,16 +2061,16 @@
         <v>1.86</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CU3" t="n">
         <v>1.48</v>
@@ -2082,100 +2082,100 @@
         <v>2</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY3" t="n">
         <v>1.98</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF3" t="n">
         <v>1.16</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.56</v>
+        <v>100.74</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.84</v>
+        <v>6.79</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DM3" t="n">
-        <v>53.56</v>
+        <v>52.68</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.39</v>
+        <v>11.47</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.11</v>
+        <v>10.16</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.23</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.44</v>
+        <v>53.53</v>
       </c>
       <c r="DW3" t="n">
         <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>13</v>
+        <v>12.84</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.34</v>
+        <v>7.37</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.66</v>
+        <v>5.47</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.17</v>
+        <v>19.11</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="4">
@@ -2197,10 +2197,10 @@
         <v>0.22</v>
       </c>
       <c r="F4" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="H4" t="n">
         <v>91.44</v>
@@ -2209,13 +2209,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="K4" t="n">
         <v>3.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="M4" t="n">
         <v>44.44</v>
@@ -2224,7 +2224,7 @@
         <v>0.67</v>
       </c>
       <c r="O4" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
         <v>13.67</v>
@@ -2254,7 +2254,7 @@
         <v>48.22</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="Z4" t="n">
         <v>12.56</v>
@@ -2383,10 +2383,10 @@
         <v>0.83</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.06</v>
+        <v>4.33</v>
       </c>
       <c r="BR4" t="n">
         <v>94.44</v>
@@ -2413,7 +2413,7 @@
         <v>2.34</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CA4" t="n">
         <v>3.71</v>
@@ -2482,22 +2482,22 @@
         <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY4" t="n">
         <v>2.02</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA4" t="n">
         <v>1.85</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC4" t="n">
         <v>2.3</v>
@@ -2509,10 +2509,10 @@
         <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="DH4" t="n">
         <v>85.06</v>
@@ -2521,13 +2521,13 @@
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="DK4" t="n">
         <v>3.16</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM4" t="n">
         <v>40.11</v>
@@ -2536,7 +2536,7 @@
         <v>0.78</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="DP4" t="n">
         <v>12.84</v>
@@ -2560,7 +2560,7 @@
         <v>45</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
         <v>10.5</v>
@@ -2684,7 +2684,7 @@
         <v>1.62</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AI5" t="n">
         <v>79.5</v>
@@ -2699,7 +2699,7 @@
         <v>3.12</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="AN5" t="n">
         <v>32.25</v>
@@ -2708,7 +2708,7 @@
         <v>0.62</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ5" t="n">
         <v>12.62</v>
@@ -2786,10 +2786,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.44</v>
+        <v>3.67</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.67</v>
+        <v>4.94</v>
       </c>
       <c r="BR5" t="n">
         <v>94.44</v>
@@ -2816,13 +2816,13 @@
         <v>2.61</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CA5" t="n">
         <v>3.54</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC5" t="n">
         <v>3.53</v>
@@ -2870,40 +2870,40 @@
         <v>3.4</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV5" t="n">
         <v>2.1</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA5" t="n">
         <v>1.78</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD5" t="n">
         <v>3.1</v>
@@ -2915,7 +2915,7 @@
         <v>1.44</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="DH5" t="n">
         <v>96.56</v>
@@ -2930,7 +2930,7 @@
         <v>3.94</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="DM5" t="n">
         <v>40.94</v>
@@ -2939,7 +2939,7 @@
         <v>0.44</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="DP5" t="n">
         <v>11.66</v>
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>106.33</v>
+        <v>107.9</v>
       </c>
       <c r="I6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
       <c r="L6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>45.56</v>
+        <v>46.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="P6" t="n">
-        <v>15.33</v>
+        <v>14.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.67</v>
+        <v>15.2</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.67</v>
+        <v>51.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.56</v>
+        <v>12.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.220000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.11</v>
+        <v>20.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3165,46 +3165,46 @@
         <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.76</v>
+        <v>9.94</v>
       </c>
       <c r="BI6" t="n">
         <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BP6" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS6" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BT6" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BZ6" t="n">
         <v>3.05</v>
       </c>
-      <c r="BZ6" t="n">
-        <v>3.18</v>
-      </c>
       <c r="CA6" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CC6" t="n">
         <v>4.75</v>
@@ -3237,40 +3237,40 @@
         <v>1.53</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH6" t="n">
         <v>1.31</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CK6" t="n">
         <v>1.59</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM6" t="n">
         <v>2.26</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.81</v>
+        <v>4.85</v>
       </c>
       <c r="CR6" t="n">
         <v>1.55</v>
@@ -3285,10 +3285,10 @@
         <v>1.46</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CX6" t="n">
         <v>1.66</v>
@@ -3297,16 +3297,16 @@
         <v>2.06</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DA6" t="n">
         <v>1.81</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DD6" t="n">
         <v>2.51</v>
@@ -3315,76 +3315,76 @@
         <v>0.11</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="DH6" t="n">
-        <v>100</v>
+        <v>101.22</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.88</v>
+        <v>42.78</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.76</v>
+        <v>15.5</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.83</v>
+        <v>14.17</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.06</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.53</v>
+        <v>49.94</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.77</v>
+        <v>11.17</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.47</v>
+        <v>7.66</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.83</v>
+        <v>19.72</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="7">
@@ -3406,7 +3406,7 @@
         <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
         <v>1.2</v>
@@ -3418,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>3.6</v>
@@ -3463,7 +3463,7 @@
         <v>62.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Z7" t="n">
         <v>14</v>
@@ -3622,7 +3622,7 @@
         <v>3.07</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CA7" t="n">
         <v>3.6</v>
@@ -3694,7 +3694,7 @@
         <v>2.01</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CY7" t="n">
         <v>2.16</v>
@@ -3706,19 +3706,19 @@
         <v>1.72</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="DE7" t="n">
         <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="DG7" t="n">
         <v>1.28</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DK7" t="n">
         <v>3.22</v>
@@ -3769,7 +3769,7 @@
         <v>59.22</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX7" t="n">
         <v>11.61</v>
@@ -4031,7 +4031,7 @@
         <v>5.48</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.81</v>
+        <v>5.8</v>
       </c>
       <c r="CC8" t="n">
         <v>1.66</v>
@@ -4206,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="G9" t="n">
         <v>2.62</v>
@@ -4218,7 +4218,7 @@
         <v>0.12</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K9" t="n">
         <v>4.5</v>
@@ -4263,7 +4263,7 @@
         <v>42.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="Z9" t="n">
         <v>10.25</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="DG9" t="n">
         <v>2.72</v>
@@ -4530,7 +4530,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="DK9" t="n">
         <v>4.72</v>
@@ -4569,7 +4569,7 @@
         <v>41.67</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DX9" t="n">
         <v>9.779999999999999</v>
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4687,139 +4687,139 @@
         <v>1.78</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG10" t="n">
         <v>2</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AU10" t="n">
         <v>1</v>
       </c>
-      <c r="AI10" t="n">
-        <v>86.62</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.88</v>
-      </c>
       <c r="AV10" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>44.12</v>
+        <v>44.89</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.5</v>
+        <v>9.44</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="BC10" t="n">
         <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>15.62</v>
+        <v>16.11</v>
       </c>
       <c r="BE10" t="n">
         <v>1.17</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.470000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.12</v>
+        <v>5.06</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY10" t="n">
         <v>2.98</v>
@@ -4828,55 +4828,55 @@
         <v>3.11</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.99</v>
+        <v>3.94</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.08</v>
+        <v>5.79</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.32</v>
+        <v>6.01</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM10" t="n">
         <v>2.34</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO10" t="n">
         <v>1.27</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="CR10" t="n">
         <v>1.42</v>
@@ -4909,10 +4909,10 @@
         <v>1.87</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DD10" t="n">
         <v>2.98</v>
@@ -4921,76 +4921,76 @@
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DH10" t="n">
-        <v>88.64</v>
+        <v>88.28</v>
       </c>
       <c r="DI10" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DM10" t="n">
-        <v>42.29</v>
+        <v>42.44</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.17</v>
+        <v>10.38</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.82</v>
+        <v>13.56</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.18</v>
+        <v>9.16</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47.29</v>
+        <v>47.5</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.59</v>
+        <v>9.56</v>
       </c>
       <c r="DY10" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.53</v>
+        <v>16.72</v>
       </c>
       <c r="EB10" t="n">
         <v>1.17</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="11">
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.29</v>
@@ -5093,49 +5093,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP11" t="n">
         <v>1</v>
       </c>
-      <c r="AH11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>84.78</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>38.44</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>12.67</v>
+        <v>12.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5147,82 +5147,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>43.11</v>
+        <v>42.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.44</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.89</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BF11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="BG11" t="n">
         <v>2.88</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.88</v>
+        <v>10.59</v>
       </c>
       <c r="BI11" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK11" t="n">
         <v>0.88</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.38</v>
+        <v>5.06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU11" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY11" t="n">
         <v>4.71</v>
@@ -5231,16 +5231,16 @@
         <v>5.15</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.66</v>
+        <v>4.63</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="CE11" t="n">
         <v>1.37</v>
@@ -5249,10 +5249,10 @@
         <v>2.72</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI11" t="n">
         <v>1.96</v>
@@ -5267,19 +5267,19 @@
         <v>1.92</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO11" t="n">
         <v>1.28</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5303,7 +5303,7 @@
         <v>1.59</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.38</v>
@@ -5318,82 +5318,82 @@
         <v>1.92</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.88</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="DL11" t="n">
         <v>0.12</v>
       </c>
       <c r="DM11" t="n">
-        <v>36.69</v>
+        <v>35.71</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.5</v>
+        <v>12.35</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.19</v>
+        <v>12.41</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.62</v>
+        <v>41.29</v>
       </c>
       <c r="DW11" t="n">
         <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.5</v>
+        <v>10.23</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.06</v>
+        <v>6.77</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.62</v>
+        <v>17.41</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="12">
@@ -5631,13 +5631,13 @@
         <v>3.14</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CA12" t="n">
         <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
         <v>4.88</v>
@@ -5806,94 +5806,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F13" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="G13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="H13" t="n">
-        <v>90.88</v>
+        <v>93</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="K13" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>40</v>
+        <v>40.78</v>
       </c>
       <c r="N13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>11.75</v>
+        <v>11.56</v>
       </c>
       <c r="Q13" t="n">
         <v>13</v>
       </c>
       <c r="R13" t="n">
-        <v>7.38</v>
+        <v>6.78</v>
       </c>
       <c r="S13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>44.62</v>
+        <v>45.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.75</v>
+        <v>19.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AF13" t="n">
         <v>0.11</v>
@@ -5977,70 +5977,70 @@
         <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.880000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS13" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.58</v>
+        <v>3.43</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CC13" t="n">
         <v>6.01</v>
@@ -6049,31 +6049,31 @@
         <v>6.36</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CH13" t="n">
         <v>1.37</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK13" t="n">
         <v>1.57</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CN13" t="n">
         <v>1.82</v>
@@ -6082,10 +6082,10 @@
         <v>1.39</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CR13" t="n">
         <v>1.49</v>
@@ -6103,7 +6103,7 @@
         <v>1.83</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX13" t="n">
         <v>1.69</v>
@@ -6118,7 +6118,7 @@
         <v>1.81</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC13" t="n">
         <v>2.25</v>
@@ -6130,76 +6130,76 @@
         <v>0.11</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.88</v>
+        <v>91</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.82</v>
+        <v>37.39</v>
       </c>
       <c r="DN13" t="n">
         <v>1.12</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.65</v>
+        <v>11.56</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.88</v>
+        <v>7.56</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>43.76</v>
+        <v>44.06</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.41</v>
+        <v>10.33</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.35</v>
+        <v>6.39</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.71</v>
+        <v>18.73</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="14">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0.33</v>
@@ -6705,49 +6705,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>87.62</v>
+        <v>86.67</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.88</v>
+        <v>5.22</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.5</v>
+        <v>46.22</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="AR15" t="n">
-        <v>14</v>
+        <v>13.56</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.380000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6759,82 +6759,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>49.38</v>
+        <v>48.22</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.25</v>
+        <v>13.22</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.88</v>
+        <v>17.89</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.53</v>
+        <v>10.67</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS15" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BX15" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY15" t="n">
         <v>2.3</v>
@@ -6843,136 +6843,136 @@
         <v>2.34</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.54</v>
+        <v>3.61</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.69</v>
+        <v>3.04</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI15" t="n">
         <v>2.1</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CN15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CP15" t="n">
         <v>1.89</v>
       </c>
-      <c r="CO15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>1.91</v>
-      </c>
       <c r="CQ15" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="CR15" t="n">
         <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="CT15" t="n">
         <v>2.94</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.42</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DB15" t="n">
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="DH15" t="n">
-        <v>96.12</v>
+        <v>95.17</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.59</v>
+        <v>47.39</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.3</v>
+        <v>10.39</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.77</v>
+        <v>13.56</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.42</v>
+        <v>7.28</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6984,28 +6984,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.71</v>
+        <v>49.11</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="DY15" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DZ15" t="n">
         <v>5</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.94</v>
+        <v>17.5</v>
       </c>
       <c r="EB15" t="n">
         <v>1.64</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="16">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
@@ -7027,82 +7027,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="G16" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>126.25</v>
+        <v>125.11</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="K16" t="n">
-        <v>6.62</v>
+        <v>6.44</v>
       </c>
       <c r="L16" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>76.38</v>
+        <v>75.22</v>
       </c>
       <c r="N16" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P16" t="n">
-        <v>10.75</v>
+        <v>10.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="R16" t="n">
-        <v>4.25</v>
+        <v>4.56</v>
       </c>
       <c r="S16" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>59.88</v>
+        <v>60</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.25</v>
+        <v>20.11</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.75</v>
+        <v>12.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.25</v>
+        <v>16.89</v>
       </c>
       <c r="AD16" t="n">
         <v>2.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AF16" t="n">
         <v>0.1</v>
@@ -7186,70 +7186,70 @@
         <v>1.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.67</v>
+        <v>9.84</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="BO16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>84.20999999999999</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>1.33</v>
       </c>
-      <c r="BP16" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>94.44</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1.31</v>
-      </c>
       <c r="CA16" t="n">
-        <v>5.35</v>
+        <v>5.31</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.67</v>
+        <v>5.61</v>
       </c>
       <c r="CC16" t="n">
         <v>1.55</v>
@@ -7264,13 +7264,13 @@
         <v>2.19</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="CH16" t="n">
         <v>1.67</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.76</v>
@@ -7282,10 +7282,10 @@
         <v>1.78</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CO16" t="n">
         <v>1.14</v>
@@ -7294,37 +7294,37 @@
         <v>1.52</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CT16" t="n">
         <v>3.26</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CX16" t="n">
         <v>1.58</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
@@ -7333,82 +7333,82 @@
         <v>1.56</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="DH16" t="n">
-        <v>118.94</v>
+        <v>118.79</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.33</v>
+        <v>6.26</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="DM16" t="n">
-        <v>67.11</v>
+        <v>67.05</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.45</v>
+        <v>13.37</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.67</v>
+        <v>6.69</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>58.72</v>
+        <v>58.84</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX16" t="n">
-        <v>19.39</v>
+        <v>19.37</v>
       </c>
       <c r="DY16" t="n">
-        <v>12.28</v>
+        <v>12.16</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.11</v>
+        <v>7.21</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.67</v>
+        <v>16.53</v>
       </c>
       <c r="EB16" t="n">
         <v>2.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="17">
@@ -7418,13 +7418,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7511,136 +7511,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" t="n">
-        <v>74.5</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AL17" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.88</v>
+        <v>34</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.5</v>
+        <v>13.33</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.380000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>43.12</v>
+        <v>43.11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.75</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>5.78</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.38</v>
+        <v>18.78</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.92</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG17" t="n">
         <v>1.94</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.94</v>
+        <v>10.11</v>
       </c>
       <c r="BI17" t="n">
         <v>1.94</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN17" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.18</v>
+        <v>4.39</v>
       </c>
       <c r="BR17" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BS17" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT17" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BU17" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX17" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BY17" t="n">
         <v>4.65</v>
@@ -7649,55 +7649,55 @@
         <v>4.99</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.77</v>
+        <v>6.51</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.62</v>
+        <v>6.46</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CK17" t="n">
         <v>1.54</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.99</v>
+        <v>4.07</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
@@ -7712,28 +7712,28 @@
         <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX17" t="n">
         <v>1.64</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DD17" t="n">
         <v>3.18</v>
@@ -7745,40 +7745,40 @@
         <v>1.94</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DH17" t="n">
-        <v>76.29000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM17" t="n">
-        <v>36.48</v>
+        <v>37.28</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.76</v>
+        <v>12.22</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.71</v>
+        <v>10.73</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.59</v>
+        <v>7.61</v>
       </c>
       <c r="DS17" t="n">
         <v>0.06</v>
@@ -7790,25 +7790,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.41</v>
+        <v>45.28</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="DX17" t="n">
-        <v>8.82</v>
+        <v>9.34</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.12</v>
+        <v>6.44</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.71</v>
+        <v>2.89</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.06</v>
+        <v>18.78</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="EC17" t="n">
         <v>2</v>
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
@@ -7833,82 +7833,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G18" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="H18" t="n">
-        <v>117.12</v>
+        <v>115.33</v>
       </c>
       <c r="I18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J18" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="K18" t="n">
-        <v>6.75</v>
+        <v>6.67</v>
       </c>
       <c r="L18" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M18" t="n">
-        <v>54.75</v>
+        <v>54.78</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O18" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="P18" t="n">
-        <v>16.62</v>
+        <v>16</v>
       </c>
       <c r="Q18" t="n">
         <v>13</v>
       </c>
       <c r="R18" t="n">
-        <v>6.62</v>
+        <v>6.78</v>
       </c>
       <c r="S18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>53.78</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.62</v>
       </c>
-      <c r="T18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>20.38</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7992,70 +7992,70 @@
         <v>2.56</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.65</v>
+        <v>10.72</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.06</v>
+        <v>5.28</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.59</v>
+        <v>5.44</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU18" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CC18" t="n">
         <v>3.73</v>
@@ -8067,25 +8067,25 @@
         <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CH18" t="n">
         <v>1.39</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK18" t="n">
         <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM18" t="n">
         <v>2.45</v>
@@ -8094,19 +8094,19 @@
         <v>1.92</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CR18" t="n">
         <v>1.44</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CT18" t="n">
         <v>2.87</v>
@@ -8121,100 +8121,100 @@
         <v>1.9</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="DH18" t="n">
-        <v>103.82</v>
+        <v>103.66</v>
       </c>
       <c r="DI18" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM18" t="n">
-        <v>49.12</v>
+        <v>49.44</v>
       </c>
       <c r="DN18" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DO18" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.59</v>
+        <v>15.34</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.77</v>
+        <v>11.84</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.58</v>
+        <v>7.61</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.06</v>
+        <v>51.67</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.65</v>
+        <v>13.89</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.880000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.76</v>
+        <v>4.94</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.06</v>
+        <v>18.94</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="19">
@@ -8224,100 +8224,100 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F19" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="G19" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="H19" t="n">
-        <v>98.62</v>
+        <v>100.56</v>
       </c>
       <c r="I19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="K19" t="n">
-        <v>5.25</v>
+        <v>5.22</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>49.38</v>
+        <v>50.78</v>
       </c>
       <c r="N19" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="O19" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>16.25</v>
+        <v>16.22</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.5</v>
+        <v>14.78</v>
       </c>
       <c r="R19" t="n">
-        <v>5.5</v>
+        <v>5.11</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="U19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>56.75</v>
+        <v>57.56</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.62</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.75</v>
+        <v>7.78</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.88</v>
+        <v>4.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.25</v>
+        <v>20.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AF19" t="n">
         <v>0.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="AH19" t="n">
         <v>2</v>
@@ -8329,7 +8329,7 @@
         <v>0.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="AL19" t="n">
         <v>5</v>
@@ -8392,73 +8392,73 @@
         <v>1.16</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="BG19" t="n">
         <v>2.94</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.29</v>
+        <v>10.06</v>
       </c>
       <c r="BI19" t="n">
         <v>2.94</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP19" t="n">
-        <v>5</v>
+        <v>4.72</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.29</v>
+        <v>5.33</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT19" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="CA19" t="n">
         <v>3.67</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CC19" t="n">
         <v>5.58</v>
@@ -8467,19 +8467,19 @@
         <v>5.91</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CH19" t="n">
         <v>1.41</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.9</v>
@@ -8491,19 +8491,19 @@
         <v>1.98</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO19" t="n">
         <v>1.33</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
@@ -8521,103 +8521,103 @@
         <v>1.94</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX19" t="n">
         <v>1.59</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="DE19" t="n">
         <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="DH19" t="n">
-        <v>92.76000000000001</v>
+        <v>94.06</v>
       </c>
       <c r="DI19" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.59</v>
+        <v>43.67</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.29</v>
+        <v>15.33</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.12</v>
+        <v>13.84</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.88</v>
+        <v>5.66</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.88</v>
+        <v>54.44</v>
       </c>
       <c r="DW19" t="n">
         <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>11</v>
+        <v>11.22</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.53</v>
+        <v>3.72</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.36</v>
+        <v>19.44</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="20">
@@ -8639,7 +8639,7 @@
         <v>0.11</v>
       </c>
       <c r="F20" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="G20" t="n">
         <v>4.22</v>
@@ -8651,7 +8651,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="K20" t="n">
         <v>6.78</v>
@@ -8714,7 +8714,7 @@
         <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8867,7 +8867,7 @@
         <v>6.16</v>
       </c>
       <c r="CD20" t="n">
-        <v>6.69</v>
+        <v>6.68</v>
       </c>
       <c r="CE20" t="n">
         <v>1.42</v>
@@ -8912,13 +8912,13 @@
         <v>1.47</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT20" t="n">
         <v>2.78</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV20" t="n">
         <v>1.91</v>
@@ -8927,16 +8927,16 @@
         <v>1.98</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB20" t="n">
         <v>1.4</v>
@@ -8951,7 +8951,7 @@
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="DG20" t="n">
         <v>3.22</v>
@@ -8963,7 +8963,7 @@
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DK20" t="n">
         <v>5.34</v>
@@ -9020,7 +9020,7 @@
         <v>1.24</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="21">
@@ -9264,13 +9264,13 @@
         <v>3.85</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CC21" t="n">
         <v>3.03</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CE21" t="n">
         <v>1.34</v>
@@ -9318,7 +9318,7 @@
         <v>2.71</v>
       </c>
       <c r="CT21" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CU21" t="n">
         <v>1.51</v>
@@ -9330,10 +9330,10 @@
         <v>1.77</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.33</v>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -2064,43 +2064,43 @@
         <v>3.12</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CU3" t="n">
         <v>1.48</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="DE3" t="n">
         <v>0.26</v>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.22</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>78.67</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AL4" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>35.78</v>
+        <v>37.9</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.22</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.22</v>
+        <v>9.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>41.78</v>
+        <v>43</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.11</v>
+        <v>6.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.56</v>
+        <v>16.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.94</v>
+        <v>7.68</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.61</v>
+        <v>3.47</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.33</v>
+        <v>4.21</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT4" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BY4" t="n">
         <v>2.34</v>
@@ -2416,25 +2416,25 @@
         <v>2.39</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.22</v>
+        <v>5.92</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.48</v>
+        <v>6.14</v>
       </c>
       <c r="CE4" t="n">
         <v>1.45</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CH4" t="n">
         <v>1.37</v>
@@ -2446,10 +2446,10 @@
         <v>1.98</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM4" t="n">
         <v>2.26</v>
@@ -2470,82 +2470,82 @@
         <v>1.5</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="CT4" t="n">
         <v>2.68</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX4" t="n">
         <v>1.66</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.26</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB4" t="n">
         <v>1.45</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.06</v>
+        <v>86.42</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.11</v>
+        <v>41</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="DP4" t="n">
         <v>12.84</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.22</v>
+        <v>11.37</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.16</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0.16</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45</v>
+        <v>45.47</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.5</v>
+        <v>10.58</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.89</v>
+        <v>7.16</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.22</v>
+        <v>19.21</v>
       </c>
       <c r="EB4" t="n">
         <v>1.21</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.1</v>
@@ -3063,10 +3063,10 @@
         <v>0.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AB6" t="n">
         <v>3.7</v>
@@ -3075,58 +3075,58 @@
         <v>20.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
         <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AI6" t="n">
-        <v>92.88</v>
+        <v>97.44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>37.75</v>
+        <v>38.78</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16.25</v>
+        <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.88</v>
+        <v>12.56</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.25</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,73 +3138,73 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.25</v>
+        <v>49.11</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.880000000000001</v>
+        <v>10.56</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.62</v>
+        <v>7.11</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.38</v>
+        <v>19</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BG6" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.94</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="BQ6" t="n">
         <v>5.11</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BT6" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU6" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,34 +3213,34 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY6" t="n">
         <v>2.93</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.75</v>
+        <v>4.96</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.3</v>
+        <v>5.58</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CH6" t="n">
         <v>1.31</v>
@@ -3261,16 +3261,16 @@
         <v>2.26</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.85</v>
+        <v>4.77</v>
       </c>
       <c r="CR6" t="n">
         <v>1.55</v>
@@ -3288,7 +3288,7 @@
         <v>1.75</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CX6" t="n">
         <v>1.66</v>
@@ -3309,82 +3309,82 @@
         <v>2.55</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.51</v>
+        <v>2.81</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="DH6" t="n">
-        <v>101.22</v>
+        <v>102.95</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DK6" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.78</v>
+        <v>43</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.5</v>
+        <v>15.42</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.17</v>
+        <v>13.95</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.109999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.94</v>
+        <v>50.26</v>
       </c>
       <c r="DW6" t="n">
         <v>0.11</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.17</v>
+        <v>11.48</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.66</v>
+        <v>7.89</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.72</v>
+        <v>19.95</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="7">
@@ -3466,10 +3466,10 @@
         <v>0.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB7" t="n">
         <v>4.8</v>
@@ -3478,7 +3478,7 @@
         <v>16.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="n">
         <v>1.7</v>
@@ -3772,10 +3772,10 @@
         <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.61</v>
+        <v>11.66</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.72</v>
+        <v>7.78</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.89</v>
@@ -3784,7 +3784,7 @@
         <v>16.22</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC7" t="n">
         <v>1.72</v>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
@@ -4206,49 +4206,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G9" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="H9" t="n">
-        <v>103.75</v>
+        <v>104.44</v>
       </c>
       <c r="I9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J9" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.22</v>
       </c>
       <c r="L9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M9" t="n">
-        <v>41.5</v>
+        <v>39.67</v>
       </c>
       <c r="N9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P9" t="n">
-        <v>16.25</v>
+        <v>16.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.62</v>
+        <v>15.78</v>
       </c>
       <c r="R9" t="n">
-        <v>6.38</v>
+        <v>6.67</v>
       </c>
       <c r="S9" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="T9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4260,28 +4260,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>42.88</v>
+        <v>42.89</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.62</v>
+        <v>7.11</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>26.12</v>
+        <v>25.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,49 +4365,49 @@
         <v>2.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.06</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT9" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4416,19 +4416,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CC9" t="n">
         <v>5.28</v>
@@ -4437,13 +4437,13 @@
         <v>5.73</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CH9" t="n">
         <v>1.27</v>
@@ -4455,25 +4455,25 @@
         <v>2.34</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM9" t="n">
         <v>1.93</v>
       </c>
       <c r="CN9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CO9" t="n">
         <v>1.56</v>
       </c>
-      <c r="CO9" t="n">
-        <v>1.55</v>
-      </c>
       <c r="CP9" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.39</v>
+        <v>5.43</v>
       </c>
       <c r="CR9" t="n">
         <v>1.62</v>
@@ -4482,7 +4482,7 @@
         <v>3.18</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CU9" t="n">
         <v>1.37</v>
@@ -4500,7 +4500,7 @@
         <v>2.41</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DA9" t="n">
         <v>1.58</v>
@@ -4509,7 +4509,7 @@
         <v>1.63</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DD9" t="n">
         <v>2.81</v>
@@ -4518,43 +4518,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="DH9" t="n">
-        <v>101.06</v>
+        <v>101.52</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.72</v>
+        <v>4.58</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.78</v>
+        <v>40.9</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.83</v>
+        <v>14.95</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.55</v>
+        <v>14.69</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.78</v>
+        <v>6.9</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.67</v>
+        <v>41.74</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.779999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.11</v>
+        <v>6.89</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="EA9" t="n">
-        <v>25.22</v>
+        <v>25.11</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="10">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -4609,82 +4609,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>90.44</v>
+        <v>89.3</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="K10" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>44.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>9.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.11</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>7.22</v>
+        <v>7.7</v>
       </c>
       <c r="S10" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="T10" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="U10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>50.11</v>
+        <v>49.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.44</v>
+        <v>6.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.33</v>
+        <v>16.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
         <v>0.11</v>
@@ -4768,85 +4768,85 @@
         <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.44</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.39</v>
+        <v>4.21</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.06</v>
+        <v>4.89</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU10" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX10" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="CC10" t="n">
         <v>5.79</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.01</v>
+        <v>6.02</v>
       </c>
       <c r="CE10" t="n">
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CH10" t="n">
         <v>1.46</v>
@@ -4861,133 +4861,133 @@
         <v>1.55</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CN10" t="n">
         <v>1.83</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX10" t="n">
         <v>1.62</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DH10" t="n">
-        <v>88.28</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="DK10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DM10" t="n">
-        <v>42.44</v>
+        <v>42.21</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.38</v>
+        <v>10.58</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.56</v>
+        <v>13.53</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.16</v>
+        <v>9.32</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47.5</v>
+        <v>47.42</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.94</v>
+        <v>5.84</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.72</v>
+        <v>16.53</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="EC10" t="n">
         <v>2.05</v>
@@ -5240,7 +5240,7 @@
         <v>4.63</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="CE11" t="n">
         <v>1.37</v>
@@ -5297,13 +5297,13 @@
         <v>2.06</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX11" t="n">
         <v>1.59</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.38</v>
@@ -5318,7 +5318,7 @@
         <v>1.92</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="DE11" t="n">
         <v>0.12</v>
@@ -6034,13 +6034,13 @@
         <v>3.43</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CA13" t="n">
         <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC13" t="n">
         <v>6.01</v>
@@ -6091,19 +6091,19 @@
         <v>1.49</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CT13" t="n">
         <v>2.69</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV13" t="n">
         <v>1.83</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX13" t="n">
         <v>1.69</v>
@@ -6121,7 +6121,7 @@
         <v>1.44</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DD13" t="n">
         <v>2.71</v>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.33</v>
@@ -6705,49 +6705,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AI15" t="n">
-        <v>86.67</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.22</v>
+        <v>4.9</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.22</v>
+        <v>46.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.11</v>
+        <v>10.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.56</v>
+        <v>13.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6759,82 +6759,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.22</v>
+        <v>49.2</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.22</v>
+        <v>13.4</v>
       </c>
       <c r="BB15" t="n">
         <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.89</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.67</v>
+        <v>10.47</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.11</v>
+        <v>5.95</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX15" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY15" t="n">
         <v>2.3</v>
@@ -6843,40 +6843,40 @@
         <v>2.34</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CC15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="CD15" t="n">
         <v>3.04</v>
-      </c>
-      <c r="CD15" t="n">
-        <v>3.15</v>
       </c>
       <c r="CE15" t="n">
         <v>1.37</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK15" t="n">
         <v>1.5</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CM15" t="n">
         <v>2.44</v>
@@ -6885,31 +6885,31 @@
         <v>1.91</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CR15" t="n">
         <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="CT15" t="n">
         <v>2.94</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
@@ -6918,7 +6918,7 @@
         <v>1.91</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA15" t="n">
         <v>1.93</v>
@@ -6927,85 +6927,85 @@
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="DE15" t="n">
         <v>0.16</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="DH15" t="n">
-        <v>95.17</v>
+        <v>94.84</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.11</v>
+        <v>4.95</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.39</v>
+        <v>47.48</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.39</v>
+        <v>10.26</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.56</v>
+        <v>13.63</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.28</v>
+        <v>7.27</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.11</v>
+        <v>49.58</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.89</v>
+        <v>14.9</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.890000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.5</v>
+        <v>17.58</v>
       </c>
       <c r="EB15" t="n">
         <v>1.64</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16">
@@ -7243,7 +7243,7 @@
         <v>1.3</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CA16" t="n">
         <v>5.31</v>
@@ -7300,19 +7300,19 @@
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CT16" t="n">
         <v>3.26</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CV16" t="n">
         <v>2.15</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX16" t="n">
         <v>1.58</v>
@@ -7333,7 +7333,7 @@
         <v>1.56</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -7430,49 +7430,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
-        <v>77.89</v>
+        <v>80.8</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K17" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="M17" t="n">
-        <v>40.56</v>
+        <v>41.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="P17" t="n">
-        <v>11.11</v>
+        <v>11.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.89</v>
+        <v>10.6</v>
       </c>
       <c r="R17" t="n">
-        <v>6.89</v>
+        <v>7.2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7484,28 +7484,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.44</v>
+        <v>46.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.779999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.11</v>
+        <v>7.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.78</v>
+        <v>18.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7589,76 +7589,76 @@
         <v>2.11</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.11</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="BR17" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS17" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT17" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BU17" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX17" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CC17" t="n">
         <v>6.51</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.46</v>
+        <v>6.48</v>
       </c>
       <c r="CE17" t="n">
         <v>1.47</v>
@@ -7667,13 +7667,13 @@
         <v>3.08</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ17" t="n">
         <v>2.08</v>
@@ -7682,10 +7682,10 @@
         <v>1.54</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN17" t="n">
         <v>1.86</v>
@@ -7697,7 +7697,7 @@
         <v>2.23</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
@@ -7715,103 +7715,103 @@
         <v>1.77</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CX17" t="n">
         <v>1.64</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.28</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DH17" t="n">
-        <v>77.94</v>
+        <v>79.47</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DK17" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DM17" t="n">
-        <v>37.28</v>
+        <v>38.05</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO17" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.22</v>
+        <v>12.37</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.61</v>
+        <v>7.74</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.28</v>
+        <v>45.1</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.34</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.44</v>
+        <v>6.63</v>
       </c>
       <c r="DZ17" t="n">
         <v>2.89</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.78</v>
+        <v>18.79</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="18">
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7914,232 +7914,232 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>92</v>
+        <v>94.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AL18" t="n">
-        <v>6.33</v>
+        <v>6.1</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN18" t="n">
-        <v>44.11</v>
+        <v>46.2</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.67</v>
+        <v>14.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.67</v>
+        <v>11.3</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.44</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>49.56</v>
+        <v>50.3</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.109999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.89</v>
+        <v>18.9</v>
       </c>
       <c r="BE18" t="n">
         <v>1.55</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.72</v>
+        <v>10.47</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO18" t="n">
         <v>1.11</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.28</v>
+        <v>5.16</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.44</v>
+        <v>5.32</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT18" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU18" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BY18" t="n">
         <v>2.63</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.73</v>
+        <v>3.6</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.69</v>
+        <v>3.56</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CU18" t="n">
         <v>1.44</v>
       </c>
       <c r="CV18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DA18" t="n">
         <v>1.9</v>
       </c>
-      <c r="CX18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CY18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CZ18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="DA18" t="n">
-        <v>1.93</v>
-      </c>
       <c r="DB18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
@@ -8148,40 +8148,40 @@
         <v>1.16</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="DH18" t="n">
-        <v>103.66</v>
+        <v>104.47</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.5</v>
+        <v>6.37</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM18" t="n">
-        <v>49.44</v>
+        <v>50.26</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.34</v>
+        <v>15.42</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.84</v>
+        <v>12.11</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.61</v>
+        <v>7.74</v>
       </c>
       <c r="DS18" t="n">
         <v>0.16</v>
@@ -8193,28 +8193,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.67</v>
+        <v>51.95</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.89</v>
+        <v>13.79</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.94</v>
+        <v>19.42</v>
       </c>
       <c r="EB18" t="n">
         <v>1.58</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="19">
@@ -8458,7 +8458,7 @@
         <v>3.67</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC19" t="n">
         <v>5.58</v>
@@ -8518,7 +8518,7 @@
         <v>1.39</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW19" t="n">
         <v>1.96</v>
@@ -8533,7 +8533,7 @@
         <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB19" t="n">
         <v>1.39</v>
@@ -8542,7 +8542,7 @@
         <v>2.12</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="DE19" t="n">
         <v>0.11</v>
@@ -9030,61 +9030,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F21" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H21" t="n">
-        <v>95.33</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K21" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="M21" t="n">
-        <v>54.78</v>
+        <v>52.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>11.89</v>
+        <v>11.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.22</v>
+        <v>10.6</v>
       </c>
       <c r="R21" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="S21" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9096,28 +9096,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>50.67</v>
+        <v>50</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>16.11</v>
+        <v>15.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.779999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.33</v>
+        <v>6.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>18.67</v>
+        <v>19.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AF21" t="n">
         <v>0.12</v>
@@ -9201,70 +9201,70 @@
         <v>3.38</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.65</v>
+        <v>8.56</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT21" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU21" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV21" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="CC21" t="n">
         <v>3.03</v>
@@ -9276,19 +9276,19 @@
         <v>1.34</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CH21" t="n">
         <v>1.49</v>
       </c>
       <c r="CI21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CK21" t="n">
         <v>1.55</v>
@@ -9297,7 +9297,7 @@
         <v>1.99</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CN21" t="n">
         <v>1.82</v>
@@ -9306,10 +9306,10 @@
         <v>1.23</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ21" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CR21" t="n">
         <v>1.38</v>
@@ -9324,16 +9324,16 @@
         <v>1.51</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.33</v>
@@ -9342,88 +9342,88 @@
         <v>1.88</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="DH21" t="n">
-        <v>84.17</v>
+        <v>84.28</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DM21" t="n">
-        <v>45</v>
+        <v>44.17</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.36</v>
+        <v>12.22</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.88</v>
+        <v>11.05</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.65</v>
+        <v>7.67</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>43.82</v>
+        <v>43.83</v>
       </c>
       <c r="DW21" t="n">
         <v>0.11</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.23</v>
+        <v>13.11</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.24</v>
+        <v>8.17</v>
       </c>
       <c r="DZ21" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="EA21" t="n">
-        <v>17.47</v>
+        <v>17.94</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI5" t="n">
-        <v>79.5</v>
+        <v>77.44</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>32.25</v>
+        <v>30.89</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.62</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>11.89</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45.75</v>
+        <v>45.22</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.5</v>
+        <v>9.44</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.62</v>
+        <v>5.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.88</v>
+        <v>4.22</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.12</v>
+        <v>16.22</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.609999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.94</v>
+        <v>4.79</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT5" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX5" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY5" t="n">
         <v>2.61</v>
@@ -2819,16 +2819,16 @@
         <v>2.71</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.53</v>
+        <v>3.47</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="CE5" t="n">
         <v>1.41</v>
@@ -2837,151 +2837,151 @@
         <v>2.88</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO5" t="n">
         <v>1.3</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW5" t="n">
         <v>1.84</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB5" t="n">
         <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="DH5" t="n">
-        <v>96.56</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.94</v>
+        <v>3.79</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM5" t="n">
-        <v>40.94</v>
+        <v>39.84</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.66</v>
+        <v>11.89</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.78</v>
+        <v>11.95</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.78</v>
+        <v>7.84</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.83</v>
+        <v>49.37</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.39</v>
+        <v>10.31</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.61</v>
+        <v>6.37</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.78</v>
+        <v>18.26</v>
       </c>
       <c r="EB5" t="n">
         <v>1.23</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0.2</v>
@@ -3487,49 +3487,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" t="n">
-        <v>90.25</v>
+        <v>90.67</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>36.25</v>
+        <v>36.56</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.88</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.75</v>
+        <v>15.56</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.25</v>
+        <v>7.78</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,73 +3541,73 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>55.62</v>
+        <v>56.22</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.619999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>15.78</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.33</v>
+        <v>7.68</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY7" t="n">
         <v>3.07</v>
@@ -3625,16 +3625,16 @@
         <v>3.3</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.78</v>
+        <v>5.56</v>
       </c>
       <c r="CD7" t="n">
-        <v>6.36</v>
+        <v>6.12</v>
       </c>
       <c r="CE7" t="n">
         <v>1.45</v>
@@ -3643,7 +3643,7 @@
         <v>3.02</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CH7" t="n">
         <v>1.38</v>
@@ -3664,13 +3664,13 @@
         <v>2.15</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO7" t="n">
         <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ7" t="n">
         <v>3.9</v>
@@ -3694,13 +3694,13 @@
         <v>2.01</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA7" t="n">
         <v>1.72</v>
@@ -3718,43 +3718,43 @@
         <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DH7" t="n">
-        <v>100.72</v>
+        <v>100.37</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DO7" t="n">
         <v>2</v>
       </c>
-      <c r="DK7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1.95</v>
-      </c>
       <c r="DP7" t="n">
-        <v>12.5</v>
+        <v>12.58</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15</v>
+        <v>14.95</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.17</v>
+        <v>7.42</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.22</v>
+        <v>59.31</v>
       </c>
       <c r="DW7" t="n">
         <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.66</v>
+        <v>11.31</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.78</v>
+        <v>7.58</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.22</v>
+        <v>16.11</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="8">
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="G11" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="n">
-        <v>80.43000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="K11" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>34.43</v>
+        <v>33.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O11" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.43</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>39.71</v>
+        <v>40.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.57</v>
+        <v>10.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.29</v>
+        <v>7.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.14</v>
+        <v>17.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5171,70 +5171,70 @@
         <v>2.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.59</v>
+        <v>10.39</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.06</v>
+        <v>4.83</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.71</v>
+        <v>4.52</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.15</v>
+        <v>4.91</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="CC11" t="n">
         <v>4.63</v>
@@ -5246,10 +5246,10 @@
         <v>1.37</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CH11" t="n">
         <v>1.45</v>
@@ -5261,7 +5261,7 @@
         <v>1.82</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL11" t="n">
         <v>1.92</v>
@@ -5276,10 +5276,10 @@
         <v>1.28</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5300,100 +5300,100 @@
         <v>1.84</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB11" t="n">
         <v>1.33</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.23999999999999</v>
+        <v>82.17</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM11" t="n">
-        <v>35.71</v>
+        <v>35.22</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.35</v>
+        <v>12.22</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.41</v>
+        <v>12.22</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.29</v>
+        <v>41.72</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.23</v>
+        <v>10.11</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.77</v>
+        <v>6.72</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.41</v>
+        <v>17.61</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="12">
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5493,139 +5493,139 @@
         <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AI12" t="n">
-        <v>86.5</v>
+        <v>88</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.75</v>
+        <v>13.22</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.12</v>
+        <v>11.89</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.119999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>38.5</v>
+        <v>39.89</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>13.67</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.25</v>
+        <v>20.67</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.279999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.72</v>
+        <v>4.53</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT12" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY12" t="n">
         <v>3.14</v>
@@ -5634,25 +5634,25 @@
         <v>3.11</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.88</v>
+        <v>4.61</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.15</v>
+        <v>4.84</v>
       </c>
       <c r="CE12" t="n">
         <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CH12" t="n">
         <v>1.39</v>
@@ -5670,19 +5670,19 @@
         <v>1.94</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO12" t="n">
         <v>1.35</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5697,73 +5697,73 @@
         <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="DE12" t="n">
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="DH12" t="n">
-        <v>87.94</v>
+        <v>88.58</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.34</v>
+        <v>4.26</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM12" t="n">
-        <v>44.56</v>
+        <v>44.79</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.39</v>
+        <v>13.16</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.28</v>
+        <v>7.37</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5775,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>40.22</v>
+        <v>40.79</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.22</v>
+        <v>20</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="13">
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.11</v>
@@ -5896,139 +5896,139 @@
         <v>2.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>89</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.56</v>
+        <v>11.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.78</v>
+        <v>12.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AU13" t="n">
         <v>1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.33</v>
+        <v>10.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.11</v>
+        <v>6.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>17.78</v>
+        <v>18.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BF13" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.83</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY13" t="n">
         <v>3.43</v>
@@ -6037,136 +6037,136 @@
         <v>3.57</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CC13" t="n">
-        <v>6.01</v>
+        <v>5.87</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.36</v>
+        <v>6.22</v>
       </c>
       <c r="CE13" t="n">
         <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH13" t="n">
         <v>1.37</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO13" t="n">
         <v>1.39</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS13" t="n">
         <v>3.02</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CU13" t="n">
         <v>1.42</v>
       </c>
       <c r="CV13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DA13" t="n">
         <v>1.83</v>
       </c>
-      <c r="CW13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>1.81</v>
-      </c>
       <c r="DB13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="DD13" t="n">
         <v>2.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DH13" t="n">
-        <v>91</v>
+        <v>90.84</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="DL13" t="n">
         <v>0.16</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.39</v>
+        <v>37.32</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.56</v>
+        <v>11.69</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.89</v>
+        <v>12.95</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.56</v>
+        <v>7.69</v>
       </c>
       <c r="DS13" t="n">
         <v>0.16</v>
@@ -6178,28 +6178,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.06</v>
+        <v>44.21</v>
       </c>
       <c r="DW13" t="n">
         <v>0.16</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.33</v>
+        <v>10.26</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.39</v>
+        <v>6.42</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.73</v>
+        <v>18.84</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="14">
@@ -6209,22 +6209,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="H14" t="n">
         <v>101</v>
@@ -6233,70 +6233,70 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="K14" t="n">
-        <v>7.38</v>
+        <v>7.22</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="M14" t="n">
-        <v>52.62</v>
+        <v>50.33</v>
       </c>
       <c r="N14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="O14" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="P14" t="n">
-        <v>12.38</v>
+        <v>12.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>8.5</v>
+        <v>8.56</v>
       </c>
       <c r="S14" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="T14" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>55.12</v>
+        <v>54.89</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>15.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.75</v>
+        <v>10.56</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.25</v>
+        <v>5.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>23.12</v>
+        <v>22.89</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6380,70 +6380,70 @@
         <v>2.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BH14" t="n">
         <v>11</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.67</v>
+        <v>5.63</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.33</v>
+        <v>5.37</v>
       </c>
       <c r="BR14" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BT14" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.23</v>
+        <v>3.08</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CC14" t="n">
         <v>3.77</v>
@@ -6455,154 +6455,154 @@
         <v>1.44</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM14" t="n">
         <v>2.5</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.89</v>
+        <v>3.96</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CS14" t="n">
         <v>3.12</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="CU14" t="n">
         <v>1.39</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB14" t="n">
         <v>1.43</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DD14" t="n">
         <v>3.17</v>
       </c>
       <c r="DE14" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.94</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DK14" t="n">
         <v>6</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.33</v>
+        <v>45.58</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.5</v>
+        <v>13.53</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.33</v>
+        <v>10.47</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.279999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.78</v>
+        <v>54.68</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.56</v>
+        <v>13.58</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.78</v>
+        <v>20.79</v>
       </c>
       <c r="EB14" t="n">
         <v>1.51</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="15">
@@ -8224,94 +8224,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F19" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>100.56</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M19" t="n">
-        <v>50.78</v>
+        <v>51.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="P19" t="n">
-        <v>16.22</v>
+        <v>16.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.78</v>
+        <v>14.9</v>
       </c>
       <c r="R19" t="n">
-        <v>5.11</v>
+        <v>4.9</v>
       </c>
       <c r="S19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>57.56</v>
+        <v>57.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.78</v>
+        <v>7.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.33</v>
+        <v>19.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AF19" t="n">
         <v>0.11</v>
@@ -8395,70 +8395,70 @@
         <v>3.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.06</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM19" t="n">
         <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.33</v>
+        <v>5.16</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU19" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CC19" t="n">
         <v>5.58</v>
@@ -8467,13 +8467,13 @@
         <v>5.91</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF19" t="n">
         <v>2.9</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CH19" t="n">
         <v>1.41</v>
@@ -8485,31 +8485,31 @@
         <v>1.9</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CO19" t="n">
         <v>1.33</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CT19" t="n">
         <v>2.72</v>
@@ -8524,67 +8524,67 @@
         <v>1.96</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB19" t="n">
         <v>1.39</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="DH19" t="n">
-        <v>94.06</v>
+        <v>94.11</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.11</v>
+        <v>5.16</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.67</v>
+        <v>44.48</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.33</v>
+        <v>15.37</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.84</v>
+        <v>13.95</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.66</v>
+        <v>5.53</v>
       </c>
       <c r="DS19" t="n">
         <v>0.11</v>
@@ -8596,28 +8596,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.44</v>
+        <v>54.68</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.5</v>
+        <v>7.37</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.44</v>
+        <v>19.27</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="20">
@@ -8627,94 +8627,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G20" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="H20" t="n">
-        <v>95.22</v>
+        <v>95.2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="K20" t="n">
-        <v>6.78</v>
+        <v>6.9</v>
       </c>
       <c r="L20" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M20" t="n">
-        <v>45.78</v>
+        <v>46.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>12.67</v>
+        <v>12.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.78</v>
+        <v>11.9</v>
       </c>
       <c r="R20" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>54.56</v>
+        <v>53</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.22</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.78</v>
+        <v>10.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.67</v>
+        <v>19.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8798,70 +8798,70 @@
         <v>1.67</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.890000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.67</v>
+        <v>4.84</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="BR20" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU20" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV20" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX20" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CC20" t="n">
         <v>6.16</v>
@@ -8870,43 +8870,43 @@
         <v>6.68</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH20" t="n">
         <v>1.4</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ20" t="n">
         <v>1.92</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CL20" t="n">
         <v>1.93</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO20" t="n">
         <v>1.34</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="CR20" t="n">
         <v>1.47</v>
@@ -8924,40 +8924,40 @@
         <v>1.91</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX20" t="n">
         <v>1.63</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB20" t="n">
         <v>1.4</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DD20" t="n">
         <v>3.08</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DH20" t="n">
-        <v>89.56</v>
+        <v>89.84</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
@@ -8966,61 +8966,61 @@
         <v>2.05</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.34</v>
+        <v>5.47</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DM20" t="n">
-        <v>41.61</v>
+        <v>42.26</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.78</v>
+        <v>11.9</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.73</v>
+        <v>11.79</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.39</v>
+        <v>7.05</v>
       </c>
       <c r="DS20" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DT20" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>49.56</v>
+        <v>49</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.44</v>
+        <v>11.69</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.5</v>
+        <v>8.68</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.89</v>
+        <v>18.79</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -2873,7 +2873,7 @@
         <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CT5" t="n">
         <v>2.93</v>
@@ -8509,10 +8509,10 @@
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU19" t="n">
         <v>1.39</v>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4687,139 +4687,139 @@
         <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.11</v>
+        <v>86.2</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>39.89</v>
+        <v>39.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.44</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.11</v>
+        <v>11.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>44.89</v>
+        <v>45.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="BC10" t="n">
         <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>16.11</v>
+        <v>15.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS10" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU10" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
         <v>2.91</v>
@@ -4828,40 +4828,40 @@
         <v>3.06</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.79</v>
+        <v>5.61</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.02</v>
+        <v>5.87</v>
       </c>
       <c r="CE10" t="n">
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK10" t="n">
         <v>1.55</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CM10" t="n">
         <v>2.33</v>
@@ -4876,7 +4876,7 @@
         <v>1.94</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
@@ -4891,10 +4891,10 @@
         <v>1.44</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.62</v>
@@ -4912,85 +4912,85 @@
         <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="DE10" t="n">
         <v>0.05</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DH10" t="n">
-        <v>87.79000000000001</v>
+        <v>87.75</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="DK10" t="n">
         <v>3.9</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>42.21</v>
+        <v>41.85</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="DO10" t="n">
         <v>2.05</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.58</v>
+        <v>10.9</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.53</v>
+        <v>13.6</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.32</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47.42</v>
+        <v>47.6</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.470000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.84</v>
+        <v>5.7</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.53</v>
+        <v>16.25</v>
       </c>
       <c r="EB10" t="n">
         <v>1.16</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
@@ -5415,82 +5415,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="H12" t="n">
-        <v>89.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="M12" t="n">
-        <v>48.2</v>
+        <v>48.82</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="P12" t="n">
-        <v>13.1</v>
+        <v>13.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.9</v>
+        <v>12.36</v>
       </c>
       <c r="R12" t="n">
-        <v>6.6</v>
+        <v>6.36</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>41.6</v>
+        <v>42.27</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.4</v>
+        <v>12.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.3</v>
+        <v>7.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.1</v>
+        <v>4.82</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.4</v>
+        <v>19.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5574,70 +5574,70 @@
         <v>1.33</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.16</v>
+        <v>9.15</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.63</v>
+        <v>4.65</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="CA12" t="n">
         <v>3.56</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CC12" t="n">
         <v>4.61</v>
@@ -5649,10 +5649,10 @@
         <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH12" t="n">
         <v>1.39</v>
@@ -5667,7 +5667,7 @@
         <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM12" t="n">
         <v>2.39</v>
@@ -5679,10 +5679,10 @@
         <v>1.35</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5697,10 +5697,10 @@
         <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX12" t="n">
         <v>1.62</v>
@@ -5709,7 +5709,7 @@
         <v>1.99</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA12" t="n">
         <v>1.87</v>
@@ -5721,82 +5721,82 @@
         <v>2.2</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="DE12" t="n">
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="DH12" t="n">
-        <v>88.58</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM12" t="n">
-        <v>44.79</v>
+        <v>45.3</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.16</v>
+        <v>13.35</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.9</v>
+        <v>12.15</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.37</v>
+        <v>7.2</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>40.79</v>
+        <v>41.2</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>13</v>
+        <v>13.05</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.470000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.53</v>
+        <v>4.4</v>
       </c>
       <c r="EA12" t="n">
-        <v>20</v>
+        <v>19.95</v>
       </c>
       <c r="EB12" t="n">
         <v>1.46</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -1469,52 +1469,52 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>105.78</v>
+        <v>109.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.22</v>
+        <v>5.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.78</v>
+        <v>50.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.67</v>
+        <v>12.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.33</v>
+        <v>12.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.56</v>
+        <v>6.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46.78</v>
+        <v>47</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.67</v>
+        <v>13.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.89</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.84</v>
+        <v>9.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.21</v>
+        <v>5.1</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.63</v>
+        <v>4.75</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS2" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT2" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU2" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
         <v>2.07</v>
@@ -1610,16 +1610,16 @@
         <v>2.07</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="CE2" t="n">
         <v>1.43</v>
@@ -1628,25 +1628,25 @@
         <v>3.07</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH2" t="n">
         <v>1.36</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK2" t="n">
         <v>1.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN2" t="n">
         <v>1.79</v>
@@ -1655,7 +1655,7 @@
         <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ2" t="n">
         <v>3.95</v>
@@ -1664,13 +1664,13 @@
         <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT2" t="n">
         <v>2.72</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV2" t="n">
         <v>1.85</v>
@@ -1682,10 +1682,10 @@
         <v>1.65</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DA2" t="n">
         <v>1.79</v>
@@ -1700,79 +1700,79 @@
         <v>2.89</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="DH2" t="n">
-        <v>113.63</v>
+        <v>115</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.63</v>
+        <v>5.7</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DM2" t="n">
-        <v>52.79</v>
+        <v>53.3</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.05</v>
+        <v>12.9</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.05</v>
+        <v>11.95</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.53</v>
+        <v>5.55</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.37</v>
+        <v>49.35</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.37</v>
+        <v>13.75</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.210000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.16</v>
+        <v>4.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.16</v>
+        <v>21.2</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="H3" t="n">
-        <v>105.33</v>
+        <v>106.5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="K3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>59.33</v>
+        <v>60.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5.22</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>10.11</v>
+        <v>10.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.44</v>
+        <v>9.9</v>
       </c>
       <c r="R3" t="n">
-        <v>6.78</v>
+        <v>7.1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.11</v>
+        <v>15.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.78</v>
+        <v>19.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AF3" t="n">
         <v>0.3</v>
@@ -1953,70 +1953,70 @@
         <v>1.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.47</v>
+        <v>10.55</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.89</v>
+        <v>5.05</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="CC3" t="n">
         <v>2.14</v>
@@ -2031,22 +2031,22 @@
         <v>2.68</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK3" t="n">
         <v>1.55</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM3" t="n">
         <v>2.34</v>
@@ -2061,13 +2061,13 @@
         <v>1.86</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CT3" t="n">
         <v>3.08</v>
@@ -2076,19 +2076,19 @@
         <v>1.48</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DA3" t="n">
         <v>1.87</v>
@@ -2100,49 +2100,49 @@
         <v>1.93</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="DG3" t="n">
         <v>3.05</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.74</v>
+        <v>101.55</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.79</v>
+        <v>6.75</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DM3" t="n">
-        <v>52.68</v>
+        <v>53.55</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.47</v>
+        <v>11.55</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.16</v>
+        <v>9.9</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.369999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0.1</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.53</v>
+        <v>53.55</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.84</v>
+        <v>13.35</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.37</v>
+        <v>7.85</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.11</v>
+        <v>19.2</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H4" t="n">
-        <v>91.44</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>44.44</v>
+        <v>44.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>13.67</v>
+        <v>13.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.22</v>
+        <v>11.6</v>
       </c>
       <c r="R4" t="n">
-        <v>8.109999999999999</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.22</v>
+        <v>48.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.56</v>
+        <v>12.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.89</v>
+        <v>21.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.68</v>
+        <v>7.75</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS4" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT4" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU4" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC4" t="n">
         <v>5.92</v>
@@ -2434,7 +2434,7 @@
         <v>3.08</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CH4" t="n">
         <v>1.37</v>
@@ -2452,52 +2452,52 @@
         <v>1.98</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO4" t="n">
         <v>1.38</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="CT4" t="n">
         <v>2.68</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX4" t="n">
         <v>1.66</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC4" t="n">
         <v>2.31</v>
@@ -2512,73 +2512,73 @@
         <v>1.9</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.42</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DK4" t="n">
         <v>3.05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.84</v>
+        <v>12.9</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.37</v>
+        <v>11.55</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.890000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.47</v>
+        <v>45.75</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.58</v>
+        <v>10.85</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.16</v>
+        <v>7.35</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.21</v>
+        <v>19.2</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="H5" t="n">
-        <v>110.2</v>
+        <v>107.55</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>47.9</v>
+        <v>46.45</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="P5" t="n">
-        <v>10.9</v>
+        <v>10.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>12.09</v>
       </c>
       <c r="R5" t="n">
-        <v>6.1</v>
+        <v>6.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.1</v>
+        <v>52.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.4</v>
+        <v>7.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.1</v>
+        <v>19.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.33</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.529999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.79</v>
+        <v>4.7</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS5" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BU5" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CC5" t="n">
         <v>3.47</v>
@@ -2831,31 +2831,31 @@
         <v>3.74</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF5" t="n">
         <v>2.88</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH5" t="n">
         <v>1.42</v>
       </c>
       <c r="CI5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.83</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN5" t="n">
         <v>1.75</v>
@@ -2867,43 +2867,43 @@
         <v>2.03</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="CR5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CU5" t="n">
         <v>1.42</v>
       </c>
-      <c r="CS5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1.43</v>
-      </c>
       <c r="CV5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX5" t="n">
         <v>1.7</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.2</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB5" t="n">
         <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD5" t="n">
         <v>3.13</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="DH5" t="n">
-        <v>94.68000000000001</v>
+        <v>94</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DM5" t="n">
-        <v>39.84</v>
+        <v>39.45</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.89</v>
+        <v>11.65</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.95</v>
+        <v>12</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.84</v>
+        <v>7.8</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.37</v>
+        <v>49.35</v>
       </c>
       <c r="DW5" t="n">
         <v>0.05</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.31</v>
+        <v>10.35</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.37</v>
+        <v>6.25</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.26</v>
+        <v>18.15</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0.1</v>
@@ -3081,52 +3081,52 @@
         <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>97.44</v>
+        <v>97.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.78</v>
+        <v>38.6</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16</v>
+        <v>14.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.56</v>
+        <v>12.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.779999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,73 +3138,73 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>49.11</v>
+        <v>48.8</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.56</v>
+        <v>10.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.11</v>
+        <v>7.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.789999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BP6" t="n">
         <v>3.95</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.11</v>
+        <v>5.25</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS6" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BT6" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>2.93</v>
@@ -3222,28 +3222,28 @@
         <v>3.06</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.96</v>
+        <v>5.27</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.58</v>
+        <v>5.97</v>
       </c>
       <c r="CE6" t="n">
         <v>1.52</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI6" t="n">
         <v>1.7</v>
@@ -3252,139 +3252,139 @@
         <v>2.12</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.77</v>
+        <v>4.69</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CT6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DC6" t="n">
         <v>2.52</v>
       </c>
-      <c r="CU6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>2.55</v>
-      </c>
       <c r="DD6" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="DE6" t="n">
         <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="DH6" t="n">
-        <v>102.95</v>
+        <v>102.85</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DM6" t="n">
-        <v>43</v>
+        <v>42.7</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.42</v>
+        <v>14.9</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.26</v>
+        <v>50.05</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.48</v>
+        <v>11.3</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.89</v>
+        <v>7.9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.95</v>
+        <v>19.75</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.33</v>
@@ -3887,118 +3887,118 @@
         <v>0.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="AI8" t="n">
-        <v>114.3</v>
+        <v>115.09</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AL8" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AN8" t="n">
-        <v>63.3</v>
+        <v>64.36</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>12</v>
+        <v>12.09</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>68.90000000000001</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA8" t="n">
-        <v>18.7</v>
+        <v>19.27</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.4</v>
+        <v>11.82</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.3</v>
+        <v>7.45</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.5</v>
+        <v>16.64</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.68</v>
+        <v>11.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.95</v>
+        <v>6.05</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4007,19 +4007,19 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BU8" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW8" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX8" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY8" t="n">
         <v>1.28</v>
@@ -4028,10 +4028,10 @@
         <v>1.33</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.48</v>
+        <v>5.43</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.8</v>
+        <v>5.73</v>
       </c>
       <c r="CC8" t="n">
         <v>1.66</v>
@@ -4046,16 +4046,16 @@
         <v>2.01</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK8" t="n">
         <v>1.41</v>
@@ -4064,10 +4064,10 @@
         <v>1.71</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO8" t="n">
         <v>1.1</v>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX8" t="n">
         <v>1.5</v>
@@ -4109,82 +4109,82 @@
         <v>1.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="DH8" t="n">
-        <v>115.79</v>
+        <v>116.15</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="DK8" t="n">
-        <v>7.1</v>
+        <v>7.15</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DM8" t="n">
-        <v>63.05</v>
+        <v>63.65</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.470000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.63</v>
+        <v>11.7</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>68.37</v>
+        <v>68.55</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>19.63</v>
+        <v>19.9</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.16</v>
+        <v>12.35</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.48</v>
+        <v>7.55</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.21</v>
+        <v>17.25</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="9">
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
@@ -4206,49 +4206,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
-        <v>104.44</v>
+        <v>105.6</v>
       </c>
       <c r="I9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>4.22</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M9" t="n">
-        <v>39.67</v>
+        <v>42.1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>16.33</v>
+        <v>15.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.78</v>
+        <v>16</v>
       </c>
       <c r="R9" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4260,28 +4260,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>42.89</v>
+        <v>44.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.779999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.11</v>
+        <v>7.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>25.78</v>
+        <v>26.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,49 +4365,49 @@
         <v>2.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.890000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.37</v>
+        <v>4.5</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BT9" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4416,19 +4416,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.29</v>
+        <v>3.21</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="CC9" t="n">
         <v>5.28</v>
@@ -4440,10 +4440,10 @@
         <v>1.6</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CH9" t="n">
         <v>1.27</v>
@@ -4452,37 +4452,37 @@
         <v>1.59</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CM9" t="n">
         <v>1.93</v>
       </c>
       <c r="CN9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CO9" t="n">
         <v>1.57</v>
       </c>
-      <c r="CO9" t="n">
-        <v>1.56</v>
-      </c>
       <c r="CP9" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.43</v>
+        <v>5.51</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CS9" t="n">
         <v>3.18</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CU9" t="n">
         <v>1.37</v>
@@ -4500,7 +4500,7 @@
         <v>2.41</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DA9" t="n">
         <v>1.58</v>
@@ -4518,43 +4518,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="DH9" t="n">
-        <v>101.52</v>
+        <v>102.25</v>
       </c>
       <c r="DI9" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.58</v>
+        <v>4.8</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.9</v>
+        <v>42.05</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.95</v>
+        <v>14.6</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.69</v>
+        <v>14.85</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.74</v>
+        <v>42.4</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.89</v>
+        <v>7.1</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="EA9" t="n">
-        <v>25.11</v>
+        <v>25.4</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="10">
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5093,49 +5093,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" t="n">
-        <v>83.5</v>
+        <v>81.55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>36.6</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.4</v>
+        <v>12.55</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.6</v>
+        <v>10.55</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>42.4</v>
+        <v>41.27</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -5156,73 +5156,73 @@
         <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>6.73</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.6</v>
+        <v>16.82</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.39</v>
+        <v>10.26</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.83</v>
+        <v>4.68</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.56</v>
+        <v>5.58</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY11" t="n">
         <v>4.52</v>
@@ -5231,28 +5231,28 @@
         <v>4.91</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.02</v>
+        <v>4.31</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.63</v>
+        <v>5.56</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.96</v>
+        <v>6.05</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CI11" t="n">
         <v>1.96</v>
@@ -5264,22 +5264,22 @@
         <v>1.48</v>
       </c>
       <c r="CL11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CP11" t="n">
         <v>1.92</v>
       </c>
-      <c r="CM11" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CP11" t="n">
-        <v>1.96</v>
-      </c>
       <c r="CQ11" t="n">
-        <v>3.37</v>
+        <v>3.29</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5303,13 +5303,13 @@
         <v>1.58</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.4</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DB11" t="n">
         <v>1.33</v>
@@ -5318,49 +5318,49 @@
         <v>1.93</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="DE11" t="n">
         <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.17</v>
+        <v>81.11</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM11" t="n">
-        <v>35.22</v>
+        <v>34.95</v>
       </c>
       <c r="DN11" t="n">
         <v>0.89</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.22</v>
+        <v>12.32</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.22</v>
+        <v>12.21</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.56</v>
+        <v>10.11</v>
       </c>
       <c r="DS11" t="n">
         <v>0.11</v>
@@ -5372,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.72</v>
+        <v>41.11</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
@@ -5381,19 +5381,19 @@
         <v>10.11</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.72</v>
+        <v>6.89</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.61</v>
+        <v>17.16</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="12">
@@ -5806,94 +5806,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>93</v>
+        <v>91.7</v>
       </c>
       <c r="I13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="K13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>40.78</v>
+        <v>39.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P13" t="n">
-        <v>11.56</v>
+        <v>11.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="R13" t="n">
-        <v>6.78</v>
+        <v>7.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>45.11</v>
+        <v>45.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.33</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.67</v>
+        <v>4.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.67</v>
+        <v>19.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>0.1</v>
@@ -5977,70 +5977,70 @@
         <v>2.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.890000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.47</v>
+        <v>5.55</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY13" t="n">
         <v>3.43</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CC13" t="n">
         <v>5.87</v>
@@ -6055,19 +6055,19 @@
         <v>3.12</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI13" t="n">
         <v>1.77</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL13" t="n">
         <v>1.96</v>
@@ -6085,34 +6085,34 @@
         <v>2.24</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="CR13" t="n">
         <v>1.5</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="CT13" t="n">
         <v>2.67</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV13" t="n">
         <v>1.82</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DA13" t="n">
         <v>1.83</v>
@@ -6127,79 +6127,79 @@
         <v>2.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.84</v>
+        <v>90.3</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.32</v>
+        <v>36.75</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.69</v>
+        <v>11.6</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.95</v>
+        <v>12.7</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.69</v>
+        <v>7.8</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.21</v>
+        <v>44.55</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.26</v>
+        <v>10.6</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.42</v>
+        <v>6.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.84</v>
+        <v>18.7</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="14">
@@ -6209,13 +6209,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.11</v>
@@ -6302,136 +6302,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AI14" t="n">
-        <v>90.09999999999999</v>
+        <v>90.55</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="AM14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BJ14" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN14" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="AO14" t="n">
+      <c r="BK14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BO14" t="n">
         <v>0.9</v>
       </c>
-      <c r="AP14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>0.89</v>
-      </c>
       <c r="BP14" t="n">
-        <v>5.63</v>
+        <v>5.8</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="BR14" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS14" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BT14" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY14" t="n">
         <v>2.97</v>
@@ -6440,16 +6440,16 @@
         <v>3.08</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.92</v>
+        <v>3.99</v>
       </c>
       <c r="CE14" t="n">
         <v>1.44</v>
@@ -6458,7 +6458,7 @@
         <v>3.01</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH14" t="n">
         <v>1.37</v>
@@ -6470,16 +6470,16 @@
         <v>1.91</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CO14" t="n">
         <v>1.35</v>
@@ -6488,19 +6488,19 @@
         <v>2.14</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CR14" t="n">
         <v>1.46</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV14" t="n">
         <v>1.94</v>
@@ -6509,16 +6509,16 @@
         <v>1.98</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DB14" t="n">
         <v>1.43</v>
@@ -6533,43 +6533,43 @@
         <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DH14" t="n">
-        <v>95.26000000000001</v>
+        <v>95.25</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="DK14" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.58</v>
+        <v>45.7</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.53</v>
+        <v>13.55</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.47</v>
+        <v>10.3</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0.1</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.68</v>
+        <v>54.5</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.58</v>
+        <v>13.6</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.050000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.79</v>
+        <v>20.65</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -6612,94 +6612,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>103.67</v>
+        <v>106.4</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M15" t="n">
-        <v>48.56</v>
+        <v>48.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>9.67</v>
+        <v>10.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.56</v>
+        <v>13.5</v>
       </c>
       <c r="R15" t="n">
-        <v>6.56</v>
+        <v>6.5</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.56</v>
+        <v>16.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.78</v>
+        <v>5.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.11</v>
+        <v>16.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1.8</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6783,67 +6783,67 @@
         <v>2.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.47</v>
+        <v>10.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS15" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU15" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX15" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CB15" t="n">
         <v>3.65</v>
@@ -6858,121 +6858,121 @@
         <v>1.37</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CG15" t="n">
         <v>3.03</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL15" t="n">
         <v>2</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CN15" t="n">
         <v>1.91</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CR15" t="n">
         <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY15" t="n">
         <v>1.91</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DB15" t="n">
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>94.84</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.48</v>
+        <v>47.7</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.26</v>
+        <v>10.45</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.63</v>
+        <v>13.6</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.27</v>
+        <v>7.2</v>
       </c>
       <c r="DS15" t="n">
         <v>0.05</v>
@@ -6984,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.58</v>
+        <v>50.1</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
@@ -6993,19 +6993,19 @@
         <v>14.9</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.84</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.58</v>
+        <v>17.25</v>
       </c>
       <c r="EB15" t="n">
         <v>1.64</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="16">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
@@ -7027,82 +7027,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
-        <v>125.11</v>
+        <v>127.5</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="K16" t="n">
-        <v>6.44</v>
+        <v>6.6</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M16" t="n">
-        <v>75.22</v>
+        <v>73.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>10.67</v>
+        <v>10.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.89</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>4.56</v>
+        <v>4.8</v>
       </c>
       <c r="S16" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.11</v>
+        <v>20.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.44</v>
+        <v>12.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.89</v>
+        <v>16.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AF16" t="n">
         <v>0.1</v>
@@ -7186,70 +7186,70 @@
         <v>1.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.84</v>
+        <v>9.75</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BO16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>85</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>60</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>1.32</v>
       </c>
-      <c r="BP16" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>84.20999999999999</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>63.16</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>52.63</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1.34</v>
-      </c>
       <c r="CA16" t="n">
-        <v>5.31</v>
+        <v>5.47</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.61</v>
+        <v>5.8</v>
       </c>
       <c r="CC16" t="n">
         <v>1.55</v>
@@ -7258,43 +7258,43 @@
         <v>1.58</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.76</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CO16" t="n">
         <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
@@ -7309,7 +7309,7 @@
         <v>1.67</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW16" t="n">
         <v>1.84</v>
@@ -7318,13 +7318,13 @@
         <v>1.58</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
@@ -7333,82 +7333,82 @@
         <v>1.56</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="DH16" t="n">
-        <v>118.79</v>
+        <v>120.3</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.26</v>
+        <v>6.35</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM16" t="n">
-        <v>67.05</v>
+        <v>66.5</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.949999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.37</v>
+        <v>13.35</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.69</v>
+        <v>6.7</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>58.84</v>
+        <v>59.4</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX16" t="n">
-        <v>19.37</v>
+        <v>19.7</v>
       </c>
       <c r="DY16" t="n">
-        <v>12.16</v>
+        <v>12.3</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.21</v>
+        <v>7.4</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.53</v>
+        <v>16.4</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="17">
@@ -7418,13 +7418,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7511,136 +7511,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>34</v>
+        <v>34.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.33</v>
+        <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.56</v>
+        <v>10.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.33</v>
+        <v>8.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>43.11</v>
+        <v>43.7</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.890000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.78</v>
+        <v>19.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.949999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.32</v>
+        <v>4.25</v>
       </c>
       <c r="BR17" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS17" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT17" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BU17" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX17" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BY17" t="n">
         <v>4.61</v>
@@ -7649,25 +7649,25 @@
         <v>4.9</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.51</v>
+        <v>6.31</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.48</v>
+        <v>6.38</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
         <v>3.08</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
@@ -7676,19 +7676,19 @@
         <v>1.74</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL17" t="n">
         <v>2.04</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO17" t="n">
         <v>1.39</v>
@@ -7697,19 +7697,19 @@
         <v>2.23</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV17" t="n">
         <v>1.77</v>
@@ -7721,7 +7721,7 @@
         <v>1.64</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.28</v>
@@ -7742,43 +7742,43 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DH17" t="n">
-        <v>79.47</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM17" t="n">
-        <v>38.05</v>
+        <v>38.15</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.37</v>
+        <v>12.5</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.58</v>
+        <v>10.75</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.74</v>
+        <v>7.9</v>
       </c>
       <c r="DS17" t="n">
         <v>0.05</v>
@@ -7790,28 +7790,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.529999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.63</v>
+        <v>6.7</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.79</v>
+        <v>19</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="18">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
@@ -7833,82 +7833,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="G18" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>115.33</v>
+        <v>110.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="K18" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M18" t="n">
-        <v>54.78</v>
+        <v>52.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="R18" t="n">
-        <v>6.78</v>
+        <v>7.9</v>
       </c>
       <c r="S18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>53.78</v>
+        <v>51.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.78</v>
+        <v>13.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.779999999999999</v>
+        <v>8</v>
       </c>
       <c r="AB18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7992,70 +7992,70 @@
         <v>2.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.47</v>
+        <v>10.65</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.16</v>
+        <v>5.2</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.32</v>
+        <v>5.45</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU18" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV18" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="CC18" t="n">
         <v>3.6</v>
@@ -8064,157 +8064,157 @@
         <v>3.56</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.83</v>
+        <v>3.74</v>
       </c>
       <c r="CR18" t="n">
         <v>1.45</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="CT18" t="n">
         <v>2.85</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX18" t="n">
         <v>1.6</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.32</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB18" t="n">
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="DH18" t="n">
-        <v>104.47</v>
+        <v>102.45</v>
       </c>
       <c r="DI18" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.37</v>
+        <v>6.35</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM18" t="n">
-        <v>50.26</v>
+        <v>49.35</v>
       </c>
       <c r="DN18" t="n">
         <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.42</v>
+        <v>15.3</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.11</v>
+        <v>11.9</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.74</v>
+        <v>8.25</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.95</v>
+        <v>50.75</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.79</v>
+        <v>13.45</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.84</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.42</v>
+        <v>19.35</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="19">
@@ -8627,13 +8627,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
         <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
         <v>0.1</v>
@@ -8720,49 +8720,49 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>83.89</v>
+        <v>82.3</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN20" t="n">
-        <v>37.44</v>
+        <v>38.1</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.89</v>
+        <v>11.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.67</v>
+        <v>11.3</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.779999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8774,82 +8774,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>44.56</v>
+        <v>44.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.11</v>
+        <v>19.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>10.11</v>
+        <v>10.2</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.21</v>
+        <v>5.3</v>
       </c>
       <c r="BR20" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS20" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT20" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU20" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV20" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX20" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY20" t="n">
         <v>2.42</v>
@@ -8858,85 +8858,85 @@
         <v>2.6</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="CC20" t="n">
-        <v>6.16</v>
+        <v>5.86</v>
       </c>
       <c r="CD20" t="n">
-        <v>6.68</v>
+        <v>6.38</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS20" t="n">
         <v>2.96</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="CU20" t="n">
         <v>1.45</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CW20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CY20" t="n">
         <v>1.99</v>
       </c>
-      <c r="CX20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CY20" t="n">
-        <v>1.96</v>
-      </c>
       <c r="CZ20" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="DB20" t="n">
         <v>1.4</v>
@@ -8951,43 +8951,43 @@
         <v>0.05</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="DH20" t="n">
-        <v>89.84</v>
+        <v>88.75</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.47</v>
+        <v>5.35</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.26</v>
+        <v>42.35</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.79</v>
+        <v>11.6</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.05</v>
+        <v>7.2</v>
       </c>
       <c r="DS20" t="n">
         <v>0.05</v>
@@ -8999,28 +8999,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.69</v>
+        <v>11.45</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.68</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.79</v>
+        <v>19.35</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -9030,13 +9030,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>0.2</v>
@@ -9120,139 +9120,139 @@
         <v>1.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" t="n">
-        <v>71.62</v>
+        <v>71.89</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AN21" t="n">
-        <v>34</v>
+        <v>33.33</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="AR21" t="n">
-        <v>11.62</v>
+        <v>11.89</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>36.12</v>
+        <v>36.56</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BA21" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="BD21" t="n">
-        <v>16.12</v>
+        <v>16.78</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="BG21" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.56</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.5</v>
+        <v>4.37</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU21" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV21" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY21" t="n">
         <v>1.84</v>
@@ -9261,16 +9261,16 @@
         <v>1.93</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="CE21" t="n">
         <v>1.34</v>
@@ -9285,61 +9285,61 @@
         <v>1.49</v>
       </c>
       <c r="CI21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL21" t="n">
         <v>1.99</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO21" t="n">
         <v>1.23</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ21" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CR21" t="n">
         <v>1.38</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CT21" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CU21" t="n">
         <v>1.51</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY21" t="n">
         <v>1.97</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB21" t="n">
         <v>1.3</v>
@@ -9348,49 +9348,49 @@
         <v>1.83</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="DE21" t="n">
         <v>0.16</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DH21" t="n">
-        <v>84.28</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="DM21" t="n">
-        <v>44.17</v>
+        <v>43.31</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.22</v>
+        <v>12.26</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.05</v>
+        <v>11.21</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.67</v>
+        <v>7.68</v>
       </c>
       <c r="DS21" t="n">
         <v>0.05</v>
@@ -9402,28 +9402,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>43.83</v>
+        <v>43.63</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.11</v>
+        <v>12.9</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.17</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4.94</v>
+        <v>4.84</v>
       </c>
       <c r="EA21" t="n">
-        <v>17.94</v>
+        <v>18.16</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="G5" t="n">
         <v>2.91</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="K5" t="n">
         <v>4.64</v>
@@ -2675,7 +2675,7 @@
         <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DG5" t="n">
         <v>2.35</v>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
         <v>3.85</v>
@@ -2981,7 +2981,7 @@
         <v>1.24</v>
       </c>
       <c r="EC5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="6">
@@ -3394,61 +3394,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="H7" t="n">
-        <v>109.1</v>
+        <v>108.27</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>4.09</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M7" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="P7" t="n">
-        <v>12.2</v>
+        <v>12.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.4</v>
+        <v>14.18</v>
       </c>
       <c r="R7" t="n">
-        <v>7.1</v>
+        <v>7.82</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>62.1</v>
+        <v>61</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.1</v>
+        <v>13.73</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.4</v>
+        <v>16.64</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,49 +3565,49 @@
         <v>1.89</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.68</v>
+        <v>8.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BO7" t="n">
         <v>0.95</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS7" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,19 +3616,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="CC7" t="n">
         <v>5.56</v>
@@ -3640,7 +3640,7 @@
         <v>1.45</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CG7" t="n">
         <v>2.76</v>
@@ -3652,19 +3652,19 @@
         <v>1.84</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CO7" t="n">
         <v>1.38</v>
@@ -3673,16 +3673,16 @@
         <v>2.17</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="CR7" t="n">
         <v>1.49</v>
       </c>
       <c r="CS7" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CU7" t="n">
         <v>1.44</v>
@@ -3691,10 +3691,10 @@
         <v>1.89</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CY7" t="n">
         <v>2.17</v>
@@ -3703,58 +3703,58 @@
         <v>2.12</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB7" t="n">
         <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="DH7" t="n">
-        <v>100.37</v>
+        <v>100.35</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.37</v>
+        <v>3.65</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.58</v>
+        <v>47.25</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.58</v>
+        <v>12.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.95</v>
+        <v>14.8</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.42</v>
+        <v>7.8</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.31</v>
+        <v>58.85</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.31</v>
+        <v>11.25</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.58</v>
+        <v>7.45</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.11</v>
+        <v>16.25</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="8">
@@ -6302,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AH14" t="n">
         <v>2.27</v>
@@ -6314,7 +6314,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="AL14" t="n">
         <v>5.09</v>
@@ -6377,7 +6377,7 @@
         <v>1.32</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="BG14" t="n">
         <v>2.05</v>
@@ -6533,7 +6533,7 @@
         <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="DG14" t="n">
         <v>2.8</v>
@@ -6545,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DK14" t="n">
         <v>6.05</v>
@@ -6602,7 +6602,7 @@
         <v>1.5</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="15">
@@ -8224,13 +8224,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.1</v>
@@ -8314,139 +8314,139 @@
         <v>3.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>87.56</v>
+        <v>88</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AN19" t="n">
-        <v>36.56</v>
+        <v>38.7</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.44</v>
+        <v>14.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.89</v>
+        <v>12.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.22</v>
+        <v>6.3</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>51.33</v>
+        <v>51.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.44</v>
+        <v>11.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="BD19" t="n">
-        <v>18.56</v>
+        <v>18.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.890000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="BO19" t="n">
         <v>1.05</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.16</v>
+        <v>5.35</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT19" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV19" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY19" t="n">
         <v>2.57</v>
@@ -8455,169 +8455,169 @@
         <v>2.72</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="CC19" t="n">
-        <v>5.58</v>
+        <v>5.35</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.91</v>
+        <v>5.65</v>
       </c>
       <c r="CE19" t="n">
         <v>1.42</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.9</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO19" t="n">
         <v>1.33</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU19" t="n">
         <v>1.39</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW19" t="n">
         <v>1.96</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DB19" t="n">
         <v>1.39</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="DE19" t="n">
         <v>0.1</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="DH19" t="n">
-        <v>94.11</v>
+        <v>94</v>
       </c>
       <c r="DI19" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.16</v>
+        <v>5.25</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.48</v>
+        <v>45.15</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.37</v>
+        <v>15.2</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.95</v>
+        <v>13.75</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.53</v>
+        <v>5.6</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.68</v>
+        <v>54.45</v>
       </c>
       <c r="DW19" t="n">
         <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.37</v>
+        <v>7.85</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.63</v>
+        <v>3.85</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.27</v>
+        <v>19.4</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0.18</v>
@@ -3487,49 +3487,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>90.67</v>
+        <v>90.5</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>36.56</v>
+        <v>35.7</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.56</v>
+        <v>15.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.22</v>
+        <v>56.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.220000000000001</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>15.78</v>
+        <v>16.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.1</v>
+        <v>8.19</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="BO7" t="n">
         <v>0.95</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.8</v>
+        <v>4.86</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BR7" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU7" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
         <v>3.01</v>
@@ -3625,22 +3625,22 @@
         <v>3.22</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.56</v>
+        <v>5.3</v>
       </c>
       <c r="CD7" t="n">
-        <v>6.12</v>
+        <v>5.84</v>
       </c>
       <c r="CE7" t="n">
         <v>1.45</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CG7" t="n">
         <v>2.76</v>
@@ -3649,7 +3649,7 @@
         <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.94</v>
@@ -3667,13 +3667,13 @@
         <v>1.71</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CR7" t="n">
         <v>1.49</v>
@@ -3688,13 +3688,13 @@
         <v>1.44</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY7" t="n">
         <v>2.17</v>
@@ -3703,58 +3703,58 @@
         <v>2.12</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB7" t="n">
         <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="DH7" t="n">
-        <v>100.35</v>
+        <v>99.81</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.25</v>
+        <v>46.33</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.5</v>
+        <v>12.52</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.8</v>
+        <v>14.71</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.85</v>
+        <v>58.81</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.45</v>
+        <v>7.24</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.25</v>
+        <v>16.48</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="8">
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G11" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
-        <v>80.5</v>
+        <v>82.11</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="K11" t="n">
-        <v>4.38</v>
+        <v>4.89</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>33.5</v>
+        <v>36.56</v>
       </c>
       <c r="N11" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="P11" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Q11" t="n">
-        <v>12</v>
-      </c>
-      <c r="R11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>40.88</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>10.25</v>
-      </c>
       <c r="AA11" t="n">
-        <v>7.12</v>
+        <v>8.56</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.62</v>
+        <v>18.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5171,70 +5171,70 @@
         <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.68</v>
+        <v>4.75</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV11" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.52</v>
+        <v>4.27</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.91</v>
+        <v>4.62</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="CC11" t="n">
         <v>5.56</v>
@@ -5243,13 +5243,13 @@
         <v>6.05</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF11" t="n">
         <v>2.7</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
@@ -5264,22 +5264,22 @@
         <v>1.48</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP11" t="n">
         <v>1.92</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5303,13 +5303,13 @@
         <v>1.58</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB11" t="n">
         <v>1.33</v>
@@ -5318,82 +5318,82 @@
         <v>1.93</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="DH11" t="n">
-        <v>81.11</v>
+        <v>81.8</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="DL11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="DS11" t="n">
         <v>0.1</v>
       </c>
-      <c r="DM11" t="n">
-        <v>34.95</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>12.21</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0.11</v>
-      </c>
       <c r="DT11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.11</v>
+        <v>41.15</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.11</v>
+        <v>10.9</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.89</v>
+        <v>7.55</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.16</v>
+        <v>17.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -1469,52 +1469,52 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
         <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>109.3</v>
+        <v>109.18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.2</v>
+        <v>50.27</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.1</v>
+        <v>12.45</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>47</v>
+        <v>47.27</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.5</v>
+        <v>13.64</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>21.91</v>
       </c>
       <c r="BE2" t="n">
         <v>1.54</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="BR2" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU2" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV2" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BY2" t="n">
         <v>2.07</v>
@@ -1610,28 +1610,28 @@
         <v>2.07</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI2" t="n">
         <v>1.81</v>
@@ -1643,10 +1643,10 @@
         <v>1.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN2" t="n">
         <v>1.79</v>
@@ -1658,7 +1658,7 @@
         <v>2.21</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
@@ -1685,94 +1685,94 @@
         <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA2" t="n">
         <v>1.79</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="DD2" t="n">
         <v>2.89</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DH2" t="n">
-        <v>115</v>
+        <v>114.67</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.7</v>
+        <v>5.66</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.3</v>
+        <v>53.19</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.9</v>
+        <v>12.86</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.95</v>
+        <v>12.14</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.55</v>
+        <v>5.62</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.35</v>
+        <v>49.38</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.75</v>
+        <v>13.81</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.2</v>
+        <v>21.67</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H3" t="n">
-        <v>106.5</v>
+        <v>107.73</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="K3" t="n">
-        <v>8.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>60.4</v>
+        <v>61.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
       <c r="P3" t="n">
-        <v>10.4</v>
+        <v>10.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.9</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>7.1</v>
+        <v>7.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>54.9</v>
+        <v>55.45</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
         <v>9</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.9</v>
+        <v>20.45</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AF3" t="n">
         <v>0.3</v>
@@ -1953,34 +1953,34 @@
         <v>1.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.55</v>
+        <v>10.67</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="BQ3" t="n">
         <v>5.05</v>
@@ -1989,34 +1989,34 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV3" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW3" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX3" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.47</v>
+        <v>4.51</v>
       </c>
       <c r="CC3" t="n">
         <v>2.14</v>
@@ -2028,31 +2028,31 @@
         <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.93</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CO3" t="n">
         <v>1.26</v>
@@ -2061,7 +2061,7 @@
         <v>1.86</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
@@ -2076,22 +2076,22 @@
         <v>1.48</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX3" t="n">
         <v>1.61</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.34</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
@@ -2103,79 +2103,79 @@
         <v>3.01</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.55</v>
+        <v>102.43</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.75</v>
+        <v>6.91</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>53.55</v>
+        <v>54.48</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.55</v>
+        <v>11.47</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.9</v>
+        <v>9.76</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.449999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.55</v>
+        <v>53.9</v>
       </c>
       <c r="DW3" t="n">
         <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.35</v>
+        <v>13.52</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.85</v>
+        <v>7.9</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.2</v>
+        <v>19.52</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.2</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.90000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>37.9</v>
+        <v>38.64</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.1</v>
+        <v>12.36</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>11.55</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.6</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43</v>
+        <v>42.09</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.7</v>
+        <v>6.91</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.8</v>
+        <v>18.18</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.75</v>
+        <v>7.71</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="BO4" t="n">
         <v>0.9</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="BR4" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV4" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BY4" t="n">
         <v>2.28</v>
@@ -2416,16 +2416,16 @@
         <v>2.33</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CC4" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="CD4" t="n">
         <v>5.92</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>6.14</v>
       </c>
       <c r="CE4" t="n">
         <v>1.45</v>
@@ -2434,10 +2434,10 @@
         <v>3.08</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI4" t="n">
         <v>1.81</v>
@@ -2446,25 +2446,25 @@
         <v>1.98</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL4" t="n">
         <v>1.98</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO4" t="n">
         <v>1.38</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
@@ -2473,7 +2473,7 @@
         <v>3</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CU4" t="n">
         <v>1.45</v>
@@ -2485,22 +2485,22 @@
         <v>2.07</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB4" t="n">
         <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DD4" t="n">
         <v>2.96</v>
@@ -2509,76 +2509,76 @@
         <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.40000000000001</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="DK4" t="n">
         <v>3.05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.1</v>
+        <v>41.34</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.55</v>
+        <v>11.57</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.75</v>
+        <v>45.14</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.35</v>
+        <v>7.43</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.2</v>
+        <v>19.81</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>77.44</v>
+        <v>82.2</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>30.89</v>
+        <v>36.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.89</v>
+        <v>11.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45.22</v>
+        <v>47.1</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.44</v>
+        <v>10.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.22</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.22</v>
+        <v>16.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BO5" t="n">
         <v>0.9</v>
       </c>
       <c r="BP5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="BR5" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT5" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY5" t="n">
         <v>2.55</v>
@@ -2819,13 +2819,13 @@
         <v>2.64</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="CD5" t="n">
         <v>3.74</v>
@@ -2849,10 +2849,10 @@
         <v>1.83</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM5" t="n">
         <v>2.18</v>
@@ -2864,7 +2864,7 @@
         <v>1.3</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ5" t="n">
         <v>3.44</v>
@@ -2873,7 +2873,7 @@
         <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CT5" t="n">
         <v>2.91</v>
@@ -2888,16 +2888,16 @@
         <v>1.85</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB5" t="n">
         <v>1.36</v>
@@ -2906,82 +2906,82 @@
         <v>2.08</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="DH5" t="n">
-        <v>94</v>
+        <v>95.48</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DM5" t="n">
-        <v>39.45</v>
+        <v>41.66</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.65</v>
+        <v>11.72</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12</v>
+        <v>11.76</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.35</v>
+        <v>50.05</v>
       </c>
       <c r="DW5" t="n">
         <v>0.05</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.35</v>
+        <v>10.67</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.25</v>
+        <v>6.57</v>
       </c>
       <c r="DZ5" t="n">
         <v>4.1</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.15</v>
+        <v>18.05</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="H6" t="n">
-        <v>107.9</v>
+        <v>107.82</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="K6" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>46.8</v>
+        <v>46.82</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="P6" t="n">
-        <v>14.9</v>
+        <v>15.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.2</v>
+        <v>14.82</v>
       </c>
       <c r="R6" t="n">
-        <v>7.2</v>
+        <v>7.27</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.3</v>
+        <v>50.73</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.3</v>
+        <v>12.73</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.7</v>
+        <v>4.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.8</v>
+        <v>21.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF6" t="n">
         <v>0.1</v>
@@ -3162,49 +3162,49 @@
         <v>2.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BH6" t="n">
         <v>9.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP6" t="n">
         <v>3.95</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="BR6" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BT6" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU6" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CC6" t="n">
         <v>5.27</v>
@@ -3234,13 +3234,13 @@
         <v>5.97</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CF6" t="n">
         <v>3.3</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CH6" t="n">
         <v>1.32</v>
@@ -3249,16 +3249,16 @@
         <v>1.7</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CK6" t="n">
         <v>1.58</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN6" t="n">
         <v>1.8</v>
@@ -3267,7 +3267,7 @@
         <v>1.46</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CQ6" t="n">
         <v>4.69</v>
@@ -3285,22 +3285,22 @@
         <v>1.45</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DB6" t="n">
         <v>1.51</v>
@@ -3312,79 +3312,79 @@
         <v>2.95</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="DH6" t="n">
-        <v>102.85</v>
+        <v>103.05</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.7</v>
+        <v>42.91</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.9</v>
+        <v>13.76</v>
       </c>
       <c r="DR6" t="n">
         <v>8</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.05</v>
+        <v>49.81</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.3</v>
+        <v>11.57</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.75</v>
+        <v>20.09</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7">
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.1</v>
@@ -3712,7 +3712,7 @@
         <v>2.25</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="DE7" t="n">
         <v>0.09</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.81</v>
+        <v>58.86</v>
       </c>
       <c r="DW7" t="n">
         <v>0.14</v>
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="n">
-        <v>117.44</v>
+        <v>117.7</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="K8" t="n">
-        <v>7.33</v>
+        <v>7.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>62.78</v>
+        <v>61.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.22</v>
+        <v>12.2</v>
       </c>
       <c r="R8" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>67.78</v>
+        <v>68.3</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.67</v>
+        <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.67</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AF8" t="n">
         <v>0.18</v>
@@ -3968,37 +3968,37 @@
         <v>2</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.8</v>
+        <v>11.76</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.75</v>
+        <v>5.62</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.05</v>
+        <v>6.14</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4007,31 +4007,31 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BV8" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW8" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX8" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.43</v>
+        <v>5.7</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.73</v>
+        <v>5.97</v>
       </c>
       <c r="CC8" t="n">
         <v>1.66</v>
@@ -4043,40 +4043,40 @@
         <v>1.2</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL8" t="n">
         <v>1.71</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
@@ -4087,104 +4087,104 @@
         <v>1.85</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CX8" t="n">
         <v>1.5</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.52</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DB8" t="inlineStr"/>
       <c r="DC8" t="n">
         <v>1.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="DH8" t="n">
-        <v>116.15</v>
+        <v>116.33</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DK8" t="n">
-        <v>7.15</v>
+        <v>7.29</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DM8" t="n">
-        <v>63.65</v>
+        <v>63.14</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.4</v>
+        <v>9.34</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.7</v>
+        <v>12.14</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>68.55</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>19.9</v>
+        <v>19.67</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.35</v>
+        <v>12.14</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.55</v>
+        <v>7.52</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.25</v>
+        <v>17.57</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="9">
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>41</v>
+        <v>40.89</v>
       </c>
       <c r="Y11" t="n">
         <v>0.11</v>
@@ -5234,7 +5234,7 @@
         <v>4.06</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="CC11" t="n">
         <v>5.56</v>
@@ -5372,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.15</v>
+        <v>41.1</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5493,139 +5493,139 @@
         <v>2.45</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>88</v>
+        <v>89.2</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>41</v>
+        <v>41.9</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.22</v>
+        <v>12.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.89</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.220000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>39.89</v>
+        <v>41.2</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.67</v>
+        <v>13.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.67</v>
+        <v>21.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.15</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BR12" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU12" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BV12" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY12" t="n">
         <v>3.02</v>
@@ -5634,31 +5634,31 @@
         <v>3</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.61</v>
+        <v>4.46</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.84</v>
+        <v>4.68</v>
       </c>
       <c r="CE12" t="n">
         <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH12" t="n">
         <v>1.39</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.89</v>
@@ -5679,22 +5679,22 @@
         <v>1.35</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CT12" t="n">
         <v>2.73</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV12" t="n">
         <v>1.96</v>
@@ -5703,13 +5703,13 @@
         <v>1.95</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA12" t="n">
         <v>1.87</v>
@@ -5718,7 +5718,7 @@
         <v>1.4</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DD12" t="n">
         <v>3.26</v>
@@ -5727,76 +5727,76 @@
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.09999999999999</v>
+        <v>89.62</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM12" t="n">
-        <v>45.3</v>
+        <v>45.52</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.35</v>
+        <v>13.19</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.15</v>
+        <v>12.19</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.2</v>
+        <v>7.09</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>41.2</v>
+        <v>41.76</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.05</v>
+        <v>13.19</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.65</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.95</v>
+        <v>20.28</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="13">
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.2</v>
@@ -5896,139 +5896,139 @@
         <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AI13" t="n">
-        <v>88.90000000000001</v>
+        <v>90.09</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>34.2</v>
+        <v>33.36</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.8</v>
+        <v>11.36</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.9</v>
+        <v>12.64</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.5</v>
+        <v>8.27</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>43.4</v>
+        <v>43</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.2</v>
+        <v>9.82</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.2</v>
+        <v>6.09</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.1</v>
+        <v>17.82</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.9</v>
+        <v>10.05</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.35</v>
+        <v>4.52</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
       <c r="BR13" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
         <v>3.43</v>
@@ -6037,28 +6037,28 @@
         <v>3.59</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.87</v>
+        <v>6.16</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.22</v>
+        <v>6.61</v>
       </c>
       <c r="CE13" t="n">
         <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI13" t="n">
         <v>1.77</v>
@@ -6067,25 +6067,25 @@
         <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.09</v>
+        <v>4.02</v>
       </c>
       <c r="CR13" t="n">
         <v>1.5</v>
@@ -6103,103 +6103,103 @@
         <v>1.82</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CX13" t="n">
         <v>1.66</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.26</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DB13" t="n">
         <v>1.45</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF13" t="n">
         <v>1.15</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.3</v>
+        <v>90.86</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.75</v>
+        <v>36.19</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.6</v>
+        <v>11.38</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.7</v>
+        <v>12.57</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.8</v>
+        <v>7.71</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.55</v>
+        <v>44.29</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.6</v>
+        <v>10.38</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.7</v>
+        <v>18.52</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="14">
@@ -6209,94 +6209,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="K14" t="n">
-        <v>7.22</v>
+        <v>6.9</v>
       </c>
       <c r="L14" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M14" t="n">
-        <v>50.33</v>
+        <v>49.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>12.56</v>
+        <v>12.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R14" t="n">
-        <v>8.56</v>
+        <v>9</v>
       </c>
       <c r="S14" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="T14" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="U14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>54.89</v>
+        <v>56.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.78</v>
+        <v>15.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.56</v>
+        <v>10.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>22.89</v>
+        <v>22.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6380,70 +6380,70 @@
         <v>2.73</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.05</v>
+        <v>10.86</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="BO14" t="n">
         <v>0.9</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.8</v>
+        <v>5.62</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="BR14" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT14" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV14" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CC14" t="n">
         <v>3.85</v>
@@ -6458,7 +6458,7 @@
         <v>3.01</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CH14" t="n">
         <v>1.37</v>
@@ -6485,10 +6485,10 @@
         <v>1.35</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="CR14" t="n">
         <v>1.46</v>
@@ -6497,16 +6497,16 @@
         <v>3.14</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CU14" t="n">
         <v>1.38</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX14" t="n">
         <v>1.57</v>
@@ -6524,7 +6524,7 @@
         <v>1.43</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DD14" t="n">
         <v>3.17</v>
@@ -6533,76 +6533,76 @@
         <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DH14" t="n">
-        <v>95.25</v>
+        <v>95.48</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.7</v>
+        <v>45.67</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.55</v>
+        <v>13.47</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.3</v>
+        <v>10.53</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.050000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.5</v>
+        <v>55.09</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.6</v>
+        <v>13.48</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.15</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.65</v>
+        <v>20.76</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="15">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0.3</v>
@@ -6705,49 +6705,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AI15" t="n">
-        <v>86.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.9</v>
+        <v>4.82</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.5</v>
+        <v>45.82</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.8</v>
+        <v>10.82</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.9</v>
+        <v>7.55</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6759,82 +6759,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>49.2</v>
+        <v>49.73</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.4</v>
+        <v>13.82</v>
       </c>
       <c r="BB15" t="n">
-        <v>9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="BD15" t="n">
-        <v>18</v>
+        <v>18.09</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="BG15" t="n">
         <v>2.9</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="BI15" t="n">
         <v>2.9</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL15" t="n">
         <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.75</v>
+        <v>5.76</v>
       </c>
       <c r="BR15" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT15" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU15" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX15" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY15" t="n">
         <v>2.33</v>
@@ -6843,40 +6843,40 @@
         <v>2.37</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CD15" t="n">
         <v>3.04</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM15" t="n">
         <v>2.45</v>
@@ -6885,13 +6885,13 @@
         <v>1.91</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="CR15" t="n">
         <v>1.42</v>
@@ -6906,10 +6906,10 @@
         <v>1.46</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CX15" t="n">
         <v>1.55</v>
@@ -6924,55 +6924,55 @@
         <v>1.94</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="DD15" t="n">
         <v>2.97</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DH15" t="n">
-        <v>96.65000000000001</v>
+        <v>97.81</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.7</v>
+        <v>47.29</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.6</v>
+        <v>13.76</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.2</v>
+        <v>7.05</v>
       </c>
       <c r="DS15" t="n">
         <v>0.05</v>
@@ -6984,28 +6984,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.1</v>
+        <v>50.33</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.9</v>
+        <v>15.05</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.25</v>
+        <v>17.33</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16">
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7105,139 +7105,139 @@
         <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG16" t="n">
         <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AI16" t="n">
-        <v>113.1</v>
+        <v>113.91</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN16" t="n">
-        <v>59.7</v>
+        <v>61.18</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AP16" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="n">
         <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>57.8</v>
+        <v>57.82</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA16" t="n">
-        <v>18.7</v>
+        <v>18.27</v>
       </c>
       <c r="BB16" t="n">
-        <v>11.9</v>
+        <v>11.73</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.8</v>
+        <v>6.55</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.2</v>
+        <v>15.82</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG16" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.75</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="BR16" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU16" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV16" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW16" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY16" t="n">
         <v>1.28</v>
@@ -7246,16 +7246,16 @@
         <v>1.32</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.47</v>
+        <v>5.4</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.8</v>
+        <v>5.72</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="CE16" t="n">
         <v>1.24</v>
@@ -7270,25 +7270,25 @@
         <v>1.68</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP16" t="n">
         <v>1.51</v>
@@ -7300,31 +7300,31 @@
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CT16" t="n">
         <v>3.26</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY16" t="n">
         <v>1.72</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
@@ -7339,76 +7339,76 @@
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="DH16" t="n">
-        <v>120.3</v>
+        <v>120.38</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.35</v>
+        <v>6.33</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM16" t="n">
-        <v>66.5</v>
+        <v>66.95</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="DP16" t="n">
         <v>10.05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.35</v>
+        <v>13.57</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>59.4</v>
+        <v>59.33</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX16" t="n">
-        <v>19.7</v>
+        <v>19.43</v>
       </c>
       <c r="DY16" t="n">
-        <v>12.3</v>
+        <v>12.19</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.4</v>
+        <v>7.24</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.4</v>
+        <v>16.19</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="17">
@@ -7418,13 +7418,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7511,136 +7511,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI17" t="n">
-        <v>78.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN17" t="n">
-        <v>34.6</v>
+        <v>33.27</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.5</v>
+        <v>14.18</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.9</v>
+        <v>10.64</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.6</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>43.7</v>
+        <v>42.18</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>6.27</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.9</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.25</v>
+        <v>4.43</v>
       </c>
       <c r="BR17" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS17" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV17" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW17" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX17" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BY17" t="n">
         <v>4.61</v>
@@ -7649,55 +7649,55 @@
         <v>4.9</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.69</v>
+        <v>4.04</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.81</v>
+        <v>4.13</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.31</v>
+        <v>6.69</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.38</v>
+        <v>7.6</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.07</v>
+        <v>3.95</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
@@ -7712,22 +7712,22 @@
         <v>1.42</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CX17" t="n">
         <v>1.64</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.28</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DB17" t="n">
         <v>1.44</v>
@@ -7736,49 +7736,49 @@
         <v>2.31</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DH17" t="n">
-        <v>79.59999999999999</v>
+        <v>78.81</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM17" t="n">
-        <v>38.15</v>
+        <v>37.28</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.75</v>
+        <v>10.62</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.9</v>
+        <v>7.81</v>
       </c>
       <c r="DS17" t="n">
         <v>0.05</v>
@@ -7790,28 +7790,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.3</v>
+        <v>44.43</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.699999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.7</v>
+        <v>6.81</v>
       </c>
       <c r="DZ17" t="n">
         <v>3</v>
       </c>
       <c r="EA17" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="EB17" t="n">
         <v>1.1</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="18">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
@@ -7833,82 +7833,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="H18" t="n">
-        <v>110.2</v>
+        <v>106.45</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="K18" t="n">
-        <v>6.6</v>
+        <v>6.18</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="M18" t="n">
-        <v>52.5</v>
+        <v>50.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="P18" t="n">
-        <v>15.7</v>
+        <v>14.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.5</v>
+        <v>12.45</v>
       </c>
       <c r="R18" t="n">
-        <v>7.9</v>
+        <v>7.73</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>51.2</v>
+        <v>49.82</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.1</v>
+        <v>12.82</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>7.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.8</v>
+        <v>19.36</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7992,70 +7992,70 @@
         <v>2.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.65</v>
+        <v>10.67</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BO18" t="n">
         <v>1.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT18" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV18" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC18" t="n">
         <v>3.6</v>
@@ -8067,7 +8067,7 @@
         <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CG18" t="n">
         <v>2.87</v>
@@ -8088,10 +8088,10 @@
         <v>1.93</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO18" t="n">
         <v>1.33</v>
@@ -8100,13 +8100,13 @@
         <v>2.14</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CR18" t="n">
         <v>1.45</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CT18" t="n">
         <v>2.85</v>
@@ -8118,7 +8118,7 @@
         <v>2.02</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX18" t="n">
         <v>1.6</v>
@@ -8136,85 +8136,85 @@
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="DH18" t="n">
-        <v>102.45</v>
+        <v>100.85</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.35</v>
+        <v>6.14</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DM18" t="n">
-        <v>49.35</v>
+        <v>48.48</v>
       </c>
       <c r="DN18" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.3</v>
+        <v>14.91</v>
       </c>
       <c r="DQ18" t="n">
         <v>11.9</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.25</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.75</v>
+        <v>50.05</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.45</v>
+        <v>13.29</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.35</v>
+        <v>19.14</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="19">
@@ -8224,94 +8224,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="K19" t="n">
-        <v>5.3</v>
+        <v>5.27</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M19" t="n">
-        <v>51.6</v>
+        <v>49.82</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O19" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="P19" t="n">
-        <v>16.2</v>
+        <v>16.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.9</v>
+        <v>14.55</v>
       </c>
       <c r="R19" t="n">
-        <v>4.9</v>
+        <v>5.27</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>57.7</v>
+        <v>57</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.5</v>
+        <v>11.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.5</v>
+        <v>7.09</v>
       </c>
       <c r="AB19" t="n">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.9</v>
+        <v>19.91</v>
       </c>
       <c r="AD19" t="n">
         <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AF19" t="n">
         <v>0.1</v>
@@ -8398,67 +8398,67 @@
         <v>2.9</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="BI19" t="n">
         <v>2.9</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.35</v>
+        <v>5.38</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV19" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CC19" t="n">
         <v>5.35</v>
@@ -8467,13 +8467,13 @@
         <v>5.65</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH19" t="n">
         <v>1.4</v>
@@ -8488,22 +8488,22 @@
         <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
@@ -8518,10 +8518,10 @@
         <v>1.39</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX19" t="n">
         <v>1.62</v>
@@ -8530,94 +8530,94 @@
         <v>1.98</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA19" t="n">
         <v>1.88</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DD19" t="n">
         <v>3.26</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DG19" t="n">
         <v>2.85</v>
       </c>
       <c r="DH19" t="n">
-        <v>94</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM19" t="n">
-        <v>45.15</v>
+        <v>44.52</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.2</v>
+        <v>15.24</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.75</v>
+        <v>13.62</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.6</v>
+        <v>5.76</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.45</v>
+        <v>54.24</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.7</v>
+        <v>11.62</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.85</v>
+        <v>7.62</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.4</v>
+        <v>19.43</v>
       </c>
       <c r="EB19" t="n">
         <v>1.34</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="20">
@@ -8627,94 +8627,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G20" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="H20" t="n">
-        <v>95.2</v>
+        <v>93.27</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="K20" t="n">
-        <v>6.9</v>
+        <v>6.45</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M20" t="n">
-        <v>46.6</v>
+        <v>45.18</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P20" t="n">
-        <v>12.8</v>
+        <v>12.82</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.9</v>
+        <v>11.64</v>
       </c>
       <c r="R20" t="n">
-        <v>5.5</v>
+        <v>6.27</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>53</v>
+        <v>52.45</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.9</v>
+        <v>10.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.4</v>
+        <v>19.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8798,70 +8798,70 @@
         <v>1.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BH20" t="n">
-        <v>10.2</v>
+        <v>10.14</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="BR20" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT20" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU20" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV20" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BW20" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX20" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CC20" t="n">
         <v>5.86</v>
@@ -8876,10 +8876,10 @@
         <v>3.06</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI20" t="n">
         <v>1.83</v>
@@ -8894,31 +8894,31 @@
         <v>1.96</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO20" t="n">
         <v>1.37</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV20" t="n">
         <v>1.89</v>
@@ -8927,22 +8927,22 @@
         <v>2.01</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB20" t="n">
         <v>1.4</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DD20" t="n">
         <v>3.08</v>
@@ -8951,76 +8951,76 @@
         <v>0.05</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="DH20" t="n">
-        <v>88.75</v>
+        <v>88.05</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.35</v>
+        <v>5.19</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.35</v>
+        <v>41.81</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.2</v>
+        <v>12.24</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.6</v>
+        <v>11.48</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.2</v>
+        <v>7.52</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>48.8</v>
+        <v>48.71</v>
       </c>
       <c r="DW20" t="n">
         <v>0.1</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.45</v>
+        <v>11.38</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.550000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.35</v>
+        <v>19.53</v>
       </c>
       <c r="EB20" t="n">
         <v>1.24</v>
       </c>
       <c r="EC20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="21">
@@ -9030,61 +9030,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H21" t="n">
-        <v>94.40000000000001</v>
+        <v>91.55</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="K21" t="n">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>52.3</v>
+        <v>50.73</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P21" t="n">
-        <v>11.7</v>
+        <v>12.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.6</v>
+        <v>10.55</v>
       </c>
       <c r="R21" t="n">
         <v>7</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9096,28 +9096,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>50</v>
+        <v>49.27</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z21" t="n">
-        <v>15.6</v>
+        <v>14.91</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.1</v>
+        <v>5.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>19.4</v>
+        <v>18.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AF21" t="n">
         <v>0.11</v>
@@ -9201,70 +9201,70 @@
         <v>3.22</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.369999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.37</v>
+        <v>4.45</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT21" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV21" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="CA21" t="n">
         <v>3.85</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="CC21" t="n">
         <v>2.98</v>
@@ -9273,22 +9273,22 @@
         <v>3.21</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK21" t="n">
         <v>1.54</v>
@@ -9297,49 +9297,49 @@
         <v>1.99</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CQ21" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CR21" t="n">
         <v>1.38</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="CT21" t="n">
         <v>3.14</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CX21" t="n">
         <v>1.6</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB21" t="n">
         <v>1.3</v>
@@ -9351,46 +9351,46 @@
         <v>2.93</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.73999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="DI21" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DM21" t="n">
-        <v>43.31</v>
+        <v>42.9</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.26</v>
+        <v>12.6</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.21</v>
+        <v>11.15</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.68</v>
+        <v>7.65</v>
       </c>
       <c r="DS21" t="n">
         <v>0.05</v>
@@ -9402,28 +9402,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>43.63</v>
+        <v>43.55</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.9</v>
+        <v>12.65</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4.84</v>
+        <v>4.65</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.16</v>
+        <v>17.95</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4287,49 +4287,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AI9" t="n">
-        <v>98.90000000000001</v>
+        <v>97.36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.9</v>
+        <v>4.82</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>42</v>
+        <v>40.27</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.7</v>
+        <v>13.82</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.7</v>
+        <v>13.64</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.1</v>
+        <v>7.18</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4341,73 +4341,73 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>40.7</v>
+        <v>39.82</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.4</v>
+        <v>9.27</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BD9" t="n">
-        <v>24.5</v>
+        <v>23.73</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BG9" t="n">
         <v>2.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI9" t="n">
         <v>2.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BP9" t="n">
         <v>4.1</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY9" t="n">
         <v>3.15</v>
@@ -4425,31 +4425,31 @@
         <v>3.21</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.28</v>
+        <v>5.14</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.73</v>
+        <v>5.58</v>
       </c>
       <c r="CE9" t="n">
         <v>1.6</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CJ9" t="n">
         <v>2.35</v>
@@ -4458,7 +4458,7 @@
         <v>1.82</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CM9" t="n">
         <v>1.93</v>
@@ -4467,13 +4467,13 @@
         <v>1.56</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.51</v>
+        <v>5.55</v>
       </c>
       <c r="CR9" t="n">
         <v>1.63</v>
@@ -4482,7 +4482,7 @@
         <v>3.18</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CU9" t="n">
         <v>1.37</v>
@@ -4500,7 +4500,7 @@
         <v>2.41</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DA9" t="n">
         <v>1.58</v>
@@ -4518,43 +4518,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="DH9" t="n">
-        <v>102.25</v>
+        <v>101.28</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM9" t="n">
-        <v>42.05</v>
+        <v>41.14</v>
       </c>
       <c r="DN9" t="n">
         <v>1.05</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.6</v>
+        <v>14.62</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.85</v>
+        <v>14.76</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.8</v>
+        <v>6.86</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.4</v>
+        <v>41.86</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.1</v>
+        <v>7.05</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="EA9" t="n">
-        <v>25.4</v>
+        <v>24.95</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="10">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -4609,82 +4609,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>89.3</v>
+        <v>94.45</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>44.3</v>
+        <v>46.91</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>14.09</v>
       </c>
       <c r="R10" t="n">
-        <v>7.7</v>
+        <v>7.36</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>49.7</v>
+        <v>51.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.5</v>
+        <v>9.73</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.2</v>
+        <v>6.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.9</v>
+        <v>17.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AF10" t="n">
         <v>0.1</v>
@@ -4768,70 +4768,70 @@
         <v>2.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.9</v>
+        <v>4.81</v>
       </c>
       <c r="BR10" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV10" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX10" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="CC10" t="n">
         <v>5.61</v>
@@ -4840,79 +4840,79 @@
         <v>5.87</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="CH10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="CR10" t="n">
         <v>1.45</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>2</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>1.43</v>
       </c>
       <c r="CS10" t="n">
         <v>2.96</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="CU10" t="n">
         <v>1.44</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CY10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="DD10" t="n">
         <v>3.08</v>
@@ -4921,76 +4921,76 @@
         <v>0.05</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DH10" t="n">
-        <v>87.75</v>
+        <v>90.52</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.85</v>
+        <v>43.33</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO10" t="n">
         <v>2.05</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.6</v>
+        <v>13.67</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.449999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47.6</v>
+        <v>48.62</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.35</v>
+        <v>9.48</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.7</v>
+        <v>5.81</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.25</v>
+        <v>16.57</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.18</v>
@@ -3081,52 +3081,52 @@
         <v>1.64</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AI6" t="n">
-        <v>97.8</v>
+        <v>98.45</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.5</v>
+        <v>4.27</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.6</v>
+        <v>37.18</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.9</v>
+        <v>14.91</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.6</v>
+        <v>12.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,73 +3138,73 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.8</v>
+        <v>48.91</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.3</v>
+        <v>10.36</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.2</v>
+        <v>6.91</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.7</v>
+        <v>18.09</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.9</v>
+        <v>9.73</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.95</v>
+        <v>3.77</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.29</v>
+        <v>5.32</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS6" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BT6" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU6" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY6" t="n">
         <v>2.9</v>
@@ -3222,22 +3222,22 @@
         <v>3.03</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.27</v>
+        <v>5.21</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.97</v>
+        <v>5.87</v>
       </c>
       <c r="CE6" t="n">
         <v>1.51</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CG6" t="n">
         <v>2.55</v>
@@ -3249,13 +3249,13 @@
         <v>1.7</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CK6" t="n">
         <v>1.58</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM6" t="n">
         <v>2.28</v>
@@ -3270,7 +3270,7 @@
         <v>2.43</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="CR6" t="n">
         <v>1.54</v>
@@ -3285,7 +3285,7 @@
         <v>1.45</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW6" t="n">
         <v>2.22</v>
@@ -3300,91 +3300,91 @@
         <v>2.29</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB6" t="n">
         <v>1.51</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="DD6" t="n">
         <v>2.95</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.05</v>
+        <v>103.14</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.91</v>
+        <v>42</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="DP6" t="n">
         <v>15</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.76</v>
+        <v>13.82</v>
       </c>
       <c r="DR6" t="n">
-        <v>8</v>
+        <v>7.95</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.81</v>
+        <v>49.82</v>
       </c>
       <c r="DW6" t="n">
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.57</v>
+        <v>11.54</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.91</v>
+        <v>7.73</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.67</v>
+        <v>3.82</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.09</v>
+        <v>19.72</v>
       </c>
       <c r="EB6" t="n">
         <v>1.31</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="7">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -5415,82 +5415,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="G12" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>90</v>
+        <v>90.25</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="K12" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="L12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="M12" t="n">
-        <v>48.82</v>
+        <v>47.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="P12" t="n">
-        <v>13.45</v>
+        <v>13.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.36</v>
+        <v>12.58</v>
       </c>
       <c r="R12" t="n">
-        <v>6.36</v>
+        <v>6.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="U12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>42.27</v>
+        <v>42.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.55</v>
+        <v>12.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.73</v>
+        <v>7.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.36</v>
+        <v>20</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AF12" t="n">
         <v>0.1</v>
@@ -5574,70 +5574,70 @@
         <v>1.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.140000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM12" t="n">
         <v>0.86</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.48</v>
+        <v>4.27</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU12" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CC12" t="n">
         <v>4.46</v>
@@ -5646,43 +5646,43 @@
         <v>4.68</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CK12" t="n">
         <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5697,28 +5697,28 @@
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CX12" t="n">
         <v>1.61</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DD12" t="n">
         <v>3.26</v>
@@ -5727,43 +5727,43 @@
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.62</v>
+        <v>89.77</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>45.52</v>
+        <v>45.09</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.19</v>
+        <v>13.27</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.19</v>
+        <v>12.32</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.09</v>
+        <v>7.14</v>
       </c>
       <c r="DS12" t="n">
         <v>0.14</v>
@@ -5775,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>41.76</v>
+        <v>42.14</v>
       </c>
       <c r="DW12" t="n">
         <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.19</v>
+        <v>13.04</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.720000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.28</v>
+        <v>20.59</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="H2" t="n">
-        <v>120.7</v>
+        <v>124.55</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="M2" t="n">
-        <v>56.4</v>
+        <v>58.45</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="P2" t="n">
-        <v>13.4</v>
+        <v>13.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>14.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AF2" t="n">
         <v>0.18</v>
@@ -1550,28 +1550,28 @@
         <v>2.36</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.859999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO2" t="n">
         <v>1.05</v>
@@ -1580,40 +1580,40 @@
         <v>5.05</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU2" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CA2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="CB2" t="n">
         <v>3.5</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>3.52</v>
       </c>
       <c r="CC2" t="n">
         <v>2.93</v>
@@ -1625,16 +1625,16 @@
         <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH2" t="n">
         <v>1.35</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ2" t="n">
         <v>2</v>
@@ -1643,7 +1643,7 @@
         <v>1.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM2" t="n">
         <v>2.27</v>
@@ -1655,19 +1655,19 @@
         <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CU2" t="n">
         <v>1.35</v>
@@ -1676,19 +1676,19 @@
         <v>1.85</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB2" t="n">
         <v>1.42</v>
@@ -1700,46 +1700,46 @@
         <v>2.89</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="DG2" t="n">
         <v>2.86</v>
       </c>
       <c r="DH2" t="n">
-        <v>114.67</v>
+        <v>116.86</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.66</v>
+        <v>5.68</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.19</v>
+        <v>54.36</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO2" t="n">
         <v>2.81</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.86</v>
+        <v>12.9</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.14</v>
+        <v>12.22</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.62</v>
+        <v>5.55</v>
       </c>
       <c r="DS2" t="n">
         <v>0.14</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.38</v>
+        <v>49.64</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.81</v>
+        <v>14.04</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.67</v>
+        <v>21.73</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0.18</v>
@@ -1872,52 +1872,52 @@
         <v>1.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>96.59999999999999</v>
+        <v>95.36</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL3" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.7</v>
+        <v>12.64</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.2</v>
+        <v>52.45</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.8</v>
+        <v>10.73</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>18.55</v>
       </c>
       <c r="BE3" t="n">
         <v>1.31</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.67</v>
+        <v>10.68</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO3" t="n">
         <v>1.14</v>
       </c>
-      <c r="BM3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BP3" t="n">
-        <v>5.62</v>
+        <v>5.59</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="BS3" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU3" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>1.51</v>
@@ -2013,43 +2013,43 @@
         <v>1.55</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="CE3" t="n">
         <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK3" t="n">
         <v>1.54</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN3" t="n">
         <v>1.86</v>
@@ -2058,10 +2058,10 @@
         <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
@@ -2070,7 +2070,7 @@
         <v>2.73</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CU3" t="n">
         <v>1.48</v>
@@ -2079,13 +2079,13 @@
         <v>1.93</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX3" t="n">
         <v>1.61</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.34</v>
@@ -2097,52 +2097,52 @@
         <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD3" t="n">
         <v>3.01</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="DG3" t="n">
         <v>3.1</v>
       </c>
       <c r="DH3" t="n">
-        <v>102.43</v>
+        <v>101.54</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="DK3" t="n">
         <v>6.91</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="DM3" t="n">
-        <v>54.48</v>
+        <v>54.1</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.47</v>
+        <v>11.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.76</v>
+        <v>9.82</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.43</v>
+        <v>8.32</v>
       </c>
       <c r="DS3" t="n">
         <v>0.09</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.9</v>
+        <v>53.95</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.52</v>
+        <v>13.36</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.9</v>
+        <v>7.82</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.62</v>
+        <v>5.54</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.52</v>
+        <v>19.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="H4" t="n">
-        <v>90.90000000000001</v>
+        <v>90.09</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="M4" t="n">
-        <v>44.3</v>
+        <v>44.18</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="P4" t="n">
-        <v>13.7</v>
+        <v>13.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.6</v>
+        <v>11.18</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>7.64</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.5</v>
+        <v>48.36</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.9</v>
+        <v>13.09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.6</v>
+        <v>21.27</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.71</v>
+        <v>7.73</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.52</v>
+        <v>3.59</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CC4" t="n">
         <v>5.68</v>
@@ -2428,61 +2428,61 @@
         <v>5.92</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM4" t="n">
         <v>2.26</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO4" t="n">
         <v>1.38</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
       </c>
       <c r="CS4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CU4" t="n">
         <v>1.45</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CX4" t="n">
         <v>1.65</v>
@@ -2494,91 +2494,91 @@
         <v>2.26</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB4" t="n">
         <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.43000000000001</v>
+        <v>86.22</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.34</v>
+        <v>41.41</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="DP4" t="n">
-        <v>13</v>
+        <v>13.09</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.57</v>
+        <v>11.36</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.859999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.14</v>
+        <v>45.22</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>11</v>
+        <v>11.18</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.43</v>
+        <v>7.55</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.57</v>
+        <v>3.64</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.81</v>
+        <v>19.72</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BN5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BO5" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS5" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BU5" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY5" t="n">
         <v>2.55</v>
@@ -2819,55 +2819,55 @@
         <v>2.64</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.74</v>
+        <v>3.67</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
@@ -2882,28 +2882,28 @@
         <v>1.42</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="DD5" t="n">
         <v>3.17</v>
@@ -2912,73 +2912,73 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="DH5" t="n">
-        <v>95.48</v>
+        <v>95.55</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM5" t="n">
-        <v>41.66</v>
+        <v>40.95</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.72</v>
+        <v>11.82</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.76</v>
+        <v>11.96</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.9</v>
+        <v>7.95</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.05</v>
+        <v>50.59</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.67</v>
+        <v>10.41</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.57</v>
+        <v>6.45</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.05</v>
+        <v>18.28</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="EC5" t="n">
         <v>1.91</v>
@@ -3225,13 +3225,13 @@
         <v>3.38</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CC6" t="n">
         <v>5.21</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="CE6" t="n">
         <v>1.51</v>
@@ -3294,7 +3294,7 @@
         <v>1.64</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.29</v>
@@ -3394,61 +3394,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>108.27</v>
+        <v>106</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="K7" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="L7" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>56</v>
+        <v>53.42</v>
       </c>
       <c r="N7" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="P7" t="n">
-        <v>12.09</v>
+        <v>12.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.18</v>
+        <v>13.75</v>
       </c>
       <c r="R7" t="n">
-        <v>7.82</v>
+        <v>8.42</v>
       </c>
       <c r="S7" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>61</v>
+        <v>59.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.73</v>
+        <v>13.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.91</v>
+        <v>8.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.64</v>
+        <v>16.08</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.19</v>
+        <v>8.27</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.33</v>
+        <v>3.45</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS7" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU7" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BV7" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.01</v>
+        <v>3.42</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.22</v>
+        <v>3.67</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="CC7" t="n">
         <v>5.3</v>
@@ -3637,124 +3637,124 @@
         <v>5.84</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="CR7" t="n">
         <v>1.49</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="CT7" t="n">
         <v>2.71</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CW7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CX7" t="n">
         <v>1.73</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.12</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DB7" t="n">
         <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="DE7" t="n">
         <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DH7" t="n">
-        <v>99.81</v>
+        <v>98.95</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.33</v>
+        <v>45.37</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.52</v>
+        <v>12.63</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.71</v>
+        <v>14.45</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.76</v>
+        <v>8.09</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.86</v>
+        <v>57.96</v>
       </c>
       <c r="DW7" t="n">
         <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.24</v>
+        <v>7.18</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.48</v>
+        <v>16.18</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
         <v>1.91</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.3</v>
@@ -3887,115 +3887,115 @@
         <v>0.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="AI8" t="n">
-        <v>115.09</v>
+        <v>111.83</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AL8" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.36</v>
+        <v>63.83</v>
       </c>
       <c r="AO8" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BM8" t="n">
         <v>0.64</v>
       </c>
-      <c r="AP8" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>69.18000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>19.27</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF8" t="n">
+      <c r="BN8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO8" t="n">
         <v>2</v>
       </c>
-      <c r="BG8" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BP8" t="n">
-        <v>5.62</v>
+        <v>5.55</v>
       </c>
       <c r="BQ8" t="n">
         <v>6.14</v>
@@ -4007,19 +4007,19 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW8" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX8" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY8" t="n">
         <v>1.26</v>
@@ -4028,16 +4028,16 @@
         <v>1.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="CE8" t="n">
         <v>1.2</v>
@@ -4046,7 +4046,7 @@
         <v>2</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="CH8" t="n">
         <v>1.82</v>
@@ -4055,13 +4055,13 @@
         <v>2.32</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK8" t="n">
         <v>1.4</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM8" t="n">
         <v>2.76</v>
@@ -4076,21 +4076,21 @@
         <v>1.38</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CV8" t="n">
         <v>2.42</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX8" t="n">
         <v>1.5</v>
@@ -4102,89 +4102,89 @@
         <v>2.52</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB8" t="inlineStr"/>
       <c r="DC8" t="n">
         <v>1.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DF8" t="n">
         <v>1</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="DH8" t="n">
-        <v>116.33</v>
+        <v>114.5</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>7.29</v>
+        <v>7.32</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DM8" t="n">
-        <v>63.14</v>
+        <v>62.91</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.34</v>
+        <v>9.32</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.14</v>
+        <v>12.27</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>68.76000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="DW8" t="n">
         <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>19.67</v>
+        <v>20.14</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.14</v>
+        <v>12.59</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.52</v>
+        <v>7.55</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.57</v>
+        <v>17.32</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="9">
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
@@ -4206,49 +4206,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="H9" t="n">
-        <v>105.6</v>
+        <v>103.55</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="M9" t="n">
-        <v>42.1</v>
+        <v>40.55</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
-        <v>15.5</v>
+        <v>15.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>15.82</v>
       </c>
       <c r="R9" t="n">
-        <v>6.5</v>
+        <v>6.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4260,28 +4260,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>44.1</v>
+        <v>43.55</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.2</v>
+        <v>10.09</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AC9" t="n">
-        <v>26.3</v>
+        <v>25.36</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,49 +4365,49 @@
         <v>2.64</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.949999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="BR9" t="n">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BT9" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4416,19 +4416,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CC9" t="n">
         <v>5.14</v>
@@ -4443,7 +4443,7 @@
         <v>3.71</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CH9" t="n">
         <v>1.26</v>
@@ -4452,16 +4452,16 @@
         <v>1.58</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CL9" t="n">
         <v>2.52</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CN9" t="n">
         <v>1.56</v>
@@ -4470,10 +4470,10 @@
         <v>1.58</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.55</v>
+        <v>5.61</v>
       </c>
       <c r="CR9" t="n">
         <v>1.63</v>
@@ -4491,25 +4491,25 @@
         <v>1.61</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CY9" t="n">
         <v>2.41</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB9" t="n">
         <v>1.63</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DD9" t="n">
         <v>2.81</v>
@@ -4518,43 +4518,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="DH9" t="n">
-        <v>101.28</v>
+        <v>100.46</v>
       </c>
       <c r="DI9" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.14</v>
+        <v>40.41</v>
       </c>
       <c r="DN9" t="n">
         <v>1.05</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.62</v>
+        <v>14.69</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.76</v>
+        <v>14.73</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.86</v>
+        <v>6.77</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.86</v>
+        <v>41.68</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.710000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="DY9" t="n">
         <v>7.05</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="EA9" t="n">
-        <v>24.95</v>
+        <v>24.54</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4687,139 +4687,139 @@
         <v>2.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.2</v>
+        <v>86.64</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>39.4</v>
+        <v>40.18</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>12.36</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.2</v>
+        <v>13.09</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.2</v>
+        <v>10.45</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>45.5</v>
+        <v>47.36</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="BD10" t="n">
-        <v>15.6</v>
+        <v>15.55</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="BH10" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.19</v>
+        <v>4.09</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.81</v>
+        <v>4.86</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS10" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY10" t="n">
         <v>2.85</v>
@@ -4828,25 +4828,25 @@
         <v>2.98</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.61</v>
+        <v>5.35</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.87</v>
+        <v>5.6</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF10" t="n">
         <v>2.83</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH10" t="n">
         <v>1.44</v>
@@ -4861,40 +4861,40 @@
         <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM10" t="n">
         <v>2.32</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO10" t="n">
         <v>1.3</v>
       </c>
       <c r="CP10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX10" t="n">
         <v>1.64</v>
@@ -4912,85 +4912,85 @@
         <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DD10" t="n">
         <v>3.08</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DH10" t="n">
-        <v>90.52</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="DK10" t="n">
         <v>3.86</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DM10" t="n">
-        <v>43.33</v>
+        <v>43.54</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>11</v>
+        <v>11.22</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.67</v>
+        <v>13.59</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.19</v>
+        <v>8.9</v>
       </c>
       <c r="DS10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="DW10" t="n">
         <v>0.28</v>
       </c>
-      <c r="DT10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>48.62</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>0.29</v>
-      </c>
       <c r="DX10" t="n">
-        <v>9.48</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.81</v>
+        <v>5.91</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.57</v>
+        <v>16.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="11">
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>82.11</v>
+        <v>83.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="K11" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="L11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M11" t="n">
-        <v>36.56</v>
+        <v>36.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>12.11</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.11</v>
+        <v>12.1</v>
       </c>
       <c r="R11" t="n">
-        <v>9.109999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="S11" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>40.89</v>
+        <v>41.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.56</v>
+        <v>8.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.33</v>
+        <v>18.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5171,70 +5171,70 @@
         <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.25</v>
+        <v>10.29</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>5.52</v>
       </c>
       <c r="BR11" t="n">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU11" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV11" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.27</v>
+        <v>4.32</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="CC11" t="n">
         <v>5.56</v>
@@ -5243,22 +5243,22 @@
         <v>6.05</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK11" t="n">
         <v>1.48</v>
@@ -5273,37 +5273,37 @@
         <v>1.94</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS11" t="n">
         <v>2.73</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CU11" t="n">
         <v>1.52</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX11" t="n">
         <v>1.58</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.39</v>
@@ -5315,7 +5315,7 @@
         <v>1.33</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD11" t="n">
         <v>3</v>
@@ -5324,43 +5324,43 @@
         <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>81.8</v>
+        <v>82.48</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM11" t="n">
-        <v>36.25</v>
+        <v>36.05</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.35</v>
+        <v>12.29</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.25</v>
+        <v>12.24</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.9</v>
+        <v>9.76</v>
       </c>
       <c r="DS11" t="n">
         <v>0.1</v>
@@ -5372,28 +5372,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.1</v>
+        <v>41.28</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.9</v>
+        <v>10.86</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.55</v>
+        <v>7.57</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.5</v>
+        <v>17.43</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="12">
@@ -5415,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -5427,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
         <v>4.67</v>
@@ -5490,7 +5490,7 @@
         <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
         <v>0.1</v>
@@ -5703,7 +5703,7 @@
         <v>1.97</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY12" t="n">
         <v>1.99</v>
@@ -5727,7 +5727,7 @@
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="DG12" t="n">
         <v>2.05</v>
@@ -5739,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="DK12" t="n">
         <v>4.41</v>
@@ -5796,7 +5796,7 @@
         <v>1.46</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6209,13 +6209,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.1</v>
@@ -6302,136 +6302,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>88.67</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BG14" t="n">
         <v>2.18</v>
       </c>
-      <c r="AH14" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>90.55</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="AM14" t="n">
+      <c r="BH14" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM14" t="n">
         <v>0.45</v>
       </c>
-      <c r="AN14" t="n">
-        <v>41.91</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>54.18</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>18.82</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.43</v>
-      </c>
       <c r="BN14" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.62</v>
+        <v>5.64</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="BR14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS14" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT14" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV14" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY14" t="n">
         <v>2.9</v>
@@ -6440,136 +6440,136 @@
         <v>3</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.85</v>
+        <v>4.19</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.99</v>
+        <v>4.59</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CI14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CL14" t="n">
         <v>1.88</v>
       </c>
-      <c r="CJ14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>1.9</v>
-      </c>
       <c r="CM14" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="CR14" t="n">
         <v>1.46</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="CT14" t="n">
         <v>2.8</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX14" t="n">
         <v>1.57</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.41</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="DB14" t="n">
         <v>1.43</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="DE14" t="n">
         <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="DH14" t="n">
-        <v>95.48</v>
+        <v>94.23</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.95</v>
+        <v>5.86</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.67</v>
+        <v>45.32</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.47</v>
+        <v>13.68</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.53</v>
+        <v>10.32</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.289999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.09</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>55.09</v>
+        <v>54.55</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.48</v>
+        <v>13.36</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.050000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.76</v>
+        <v>20.46</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="15">
@@ -6612,94 +6612,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
-        <v>106.4</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M15" t="n">
-        <v>48.9</v>
+        <v>48.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="O15" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="P15" t="n">
-        <v>10.1</v>
+        <v>10.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.5</v>
+        <v>13.36</v>
       </c>
       <c r="R15" t="n">
-        <v>6.5</v>
+        <v>6.64</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>51</v>
+        <v>51.18</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.4</v>
+        <v>16.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.6</v>
+        <v>10.73</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.8</v>
+        <v>5.45</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.5</v>
+        <v>16.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6783,67 +6783,67 @@
         <v>2.09</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.19</v>
+        <v>10.09</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL15" t="n">
         <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.76</v>
+        <v>5.64</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS15" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX15" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB15" t="n">
         <v>3.62</v>
@@ -6861,52 +6861,52 @@
         <v>2.72</v>
       </c>
       <c r="CG15" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CH15" t="n">
         <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.77</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM15" t="n">
         <v>2.45</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO15" t="n">
         <v>1.28</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CR15" t="n">
         <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CT15" t="n">
         <v>2.97</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW15" t="n">
         <v>1.79</v>
@@ -6915,7 +6915,7 @@
         <v>1.55</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.44</v>
@@ -6930,82 +6930,82 @@
         <v>1.96</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="DE15" t="n">
         <v>0.14</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="DH15" t="n">
-        <v>97.81</v>
+        <v>93.41</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.29</v>
+        <v>47.14</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.48</v>
+        <v>10.68</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.76</v>
+        <v>13.68</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.05</v>
+        <v>7.09</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.33</v>
+        <v>50.46</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.05</v>
+        <v>15</v>
       </c>
       <c r="DY15" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.33</v>
+        <v>17.27</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="16">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -7027,82 +7027,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="H16" t="n">
-        <v>127.5</v>
+        <v>126.91</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="K16" t="n">
-        <v>6.6</v>
+        <v>6.82</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="M16" t="n">
-        <v>73.3</v>
+        <v>74.55</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P16" t="n">
-        <v>10.8</v>
+        <v>10.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>12.45</v>
       </c>
       <c r="R16" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>61</v>
+        <v>60.64</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.7</v>
+        <v>20.27</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.7</v>
+        <v>12.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>8</v>
+        <v>7.82</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.6</v>
+        <v>16.09</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF16" t="n">
         <v>0.09</v>
@@ -7189,67 +7189,67 @@
         <v>2.95</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI16" t="n">
         <v>2.95</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL16" t="n">
         <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.52</v>
+        <v>4.59</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS16" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU16" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV16" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX16" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BZ16" t="n">
         <v>1.32</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.72</v>
+        <v>5.76</v>
       </c>
       <c r="CC16" t="n">
         <v>1.58</v>
@@ -7261,10 +7261,10 @@
         <v>1.24</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="CH16" t="n">
         <v>1.68</v>
@@ -7273,40 +7273,40 @@
         <v>2.09</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CO16" t="n">
         <v>1.13</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CT16" t="n">
         <v>3.26</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CV16" t="n">
         <v>2.18</v>
@@ -7318,13 +7318,13 @@
         <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.41</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
@@ -7333,82 +7333,82 @@
         <v>1.56</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="DH16" t="n">
-        <v>120.38</v>
+        <v>120.41</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.33</v>
+        <v>6.45</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="DM16" t="n">
-        <v>66.95</v>
+        <v>67.86</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.05</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.57</v>
+        <v>13.72</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.71</v>
+        <v>6.64</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>59.33</v>
+        <v>59.23</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX16" t="n">
-        <v>19.43</v>
+        <v>19.27</v>
       </c>
       <c r="DY16" t="n">
-        <v>12.19</v>
+        <v>12.09</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.24</v>
+        <v>7.18</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.19</v>
+        <v>15.96</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="17">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
@@ -7430,49 +7430,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="H17" t="n">
-        <v>80.8</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M17" t="n">
-        <v>41.7</v>
+        <v>40.73</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="O17" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="P17" t="n">
-        <v>11.5</v>
+        <v>11.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.6</v>
+        <v>11.09</v>
       </c>
       <c r="R17" t="n">
-        <v>7.2</v>
+        <v>7.73</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7484,28 +7484,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>46.9</v>
+        <v>45.73</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.4</v>
+        <v>7.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.8</v>
+        <v>18.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7589,70 +7589,70 @@
         <v>2.27</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.949999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.05</v>
+        <v>4.91</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="BR17" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BT17" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BU17" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX17" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.61</v>
+        <v>4.44</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.9</v>
+        <v>4.72</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="CC17" t="n">
         <v>6.69</v>
@@ -7664,28 +7664,28 @@
         <v>1.45</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG17" t="n">
         <v>2.83</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI17" t="n">
         <v>1.75</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL17" t="n">
         <v>2.02</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN17" t="n">
         <v>1.88</v>
@@ -7694,16 +7694,16 @@
         <v>1.37</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
       </c>
       <c r="CS17" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CT17" t="n">
         <v>2.75</v>
@@ -7715,7 +7715,7 @@
         <v>1.78</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX17" t="n">
         <v>1.64</v>
@@ -7733,7 +7733,7 @@
         <v>1.44</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DD17" t="n">
         <v>3.09</v>
@@ -7742,76 +7742,76 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="DH17" t="n">
-        <v>78.81</v>
+        <v>78.91</v>
       </c>
       <c r="DI17" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="DK17" t="n">
         <v>4</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM17" t="n">
-        <v>37.28</v>
+        <v>37</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.9</v>
+        <v>12.86</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.62</v>
+        <v>10.86</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.81</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>44.43</v>
+        <v>43.96</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.81</v>
+        <v>9.73</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.81</v>
+        <v>6.68</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.9</v>
+        <v>18.55</v>
       </c>
       <c r="EB17" t="n">
         <v>1.1</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="18">
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7914,136 +7914,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AI18" t="n">
-        <v>94.7</v>
+        <v>91.09</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AL18" t="n">
-        <v>6.1</v>
+        <v>5.82</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN18" t="n">
-        <v>46.2</v>
+        <v>44</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.9</v>
+        <v>14.82</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.3</v>
+        <v>11.55</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.6</v>
+        <v>8.91</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>50.3</v>
+        <v>49.82</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.8</v>
+        <v>13.27</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.9</v>
+        <v>8.27</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.9</v>
+        <v>19.18</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.67</v>
+        <v>10.59</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU18" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV18" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY18" t="n">
         <v>2.78</v>
@@ -8052,10 +8052,10 @@
         <v>2.93</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CC18" t="n">
         <v>3.6</v>
@@ -8064,55 +8064,55 @@
         <v>3.56</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF18" t="n">
         <v>2.98</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CK18" t="n">
         <v>1.5</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM18" t="n">
         <v>2.43</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO18" t="n">
         <v>1.33</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="CR18" t="n">
         <v>1.45</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV18" t="n">
         <v>2.02</v>
@@ -8127,7 +8127,7 @@
         <v>1.93</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA18" t="n">
         <v>1.91</v>
@@ -8145,76 +8145,76 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
       <c r="DH18" t="n">
-        <v>100.85</v>
+        <v>98.77</v>
       </c>
       <c r="DI18" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM18" t="n">
-        <v>48.48</v>
+        <v>47.28</v>
       </c>
       <c r="DN18" t="n">
         <v>1.05</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.91</v>
+        <v>14.86</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.140000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.05</v>
+        <v>49.82</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.29</v>
+        <v>13.04</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.33</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.14</v>
+        <v>19.27</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="19">
@@ -8627,13 +8627,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
         <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
         <v>0.09</v>
@@ -8720,49 +8720,49 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>82.3</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.1</v>
+        <v>37.64</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.6</v>
+        <v>11.73</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.3</v>
+        <v>11.55</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.9</v>
+        <v>8.73</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8774,82 +8774,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>44.6</v>
+        <v>44.82</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.5</v>
+        <v>9.09</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.2</v>
+        <v>6.64</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="BD20" t="n">
-        <v>19.3</v>
+        <v>18.73</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH20" t="n">
-        <v>10.14</v>
+        <v>10.05</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.29</v>
+        <v>5.18</v>
       </c>
       <c r="BR20" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS20" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU20" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV20" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX20" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY20" t="n">
         <v>2.41</v>
@@ -8858,64 +8858,64 @@
         <v>2.59</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC20" t="n">
-        <v>5.86</v>
+        <v>5.72</v>
       </c>
       <c r="CD20" t="n">
-        <v>6.38</v>
+        <v>6.23</v>
       </c>
       <c r="CE20" t="n">
         <v>1.44</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK20" t="n">
         <v>1.53</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM20" t="n">
         <v>2.41</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CU20" t="n">
         <v>1.44</v>
@@ -8930,13 +8930,13 @@
         <v>1.65</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.27</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB20" t="n">
         <v>1.4</v>
@@ -8945,49 +8945,49 @@
         <v>2.19</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="DH20" t="n">
-        <v>88.05</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DM20" t="n">
-        <v>41.81</v>
+        <v>41.41</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.24</v>
+        <v>12.28</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.48</v>
+        <v>11.6</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="DS20" t="n">
         <v>0.09</v>
@@ -8999,28 +8999,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>48.71</v>
+        <v>48.64</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.38</v>
+        <v>11.54</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.380000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.53</v>
+        <v>19.23</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -9030,13 +9030,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
         <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>0.18</v>
@@ -9120,139 +9120,139 @@
         <v>1.45</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" t="n">
-        <v>71.89</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN21" t="n">
-        <v>33.33</v>
+        <v>32.9</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.89</v>
+        <v>12.3</v>
       </c>
       <c r="AR21" t="n">
-        <v>11.89</v>
+        <v>12.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.44</v>
+        <v>8.9</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>36.56</v>
+        <v>38.2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.890000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.44</v>
+        <v>5.9</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>16.78</v>
+        <v>17.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.550000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.45</v>
+        <v>4.38</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU21" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV21" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY21" t="n">
         <v>2</v>
@@ -9261,16 +9261,16 @@
         <v>2.11</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CC21" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="CE21" t="n">
         <v>1.33</v>
@@ -9279,49 +9279,49 @@
         <v>2.55</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CH21" t="n">
         <v>1.5</v>
       </c>
       <c r="CI21" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ21" t="n">
         <v>1.72</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ21" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CR21" t="n">
         <v>1.38</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CT21" t="n">
         <v>3.14</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV21" t="n">
         <v>2.24</v>
@@ -9333,13 +9333,13 @@
         <v>1.6</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB21" t="n">
         <v>1.3</v>
@@ -9348,82 +9348,82 @@
         <v>1.83</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DH21" t="n">
-        <v>82.7</v>
+        <v>83.38</v>
       </c>
       <c r="DI21" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DM21" t="n">
-        <v>42.9</v>
+        <v>42.24</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.6</v>
+        <v>12.33</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.15</v>
+        <v>11.29</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.65</v>
+        <v>7.9</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>43.55</v>
+        <v>44</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.65</v>
+        <v>12.29</v>
       </c>
       <c r="DY21" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="EA21" t="n">
-        <v>17.95</v>
+        <v>18.1</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1667,13 +1667,13 @@
         <v>3.26</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CU2" t="n">
         <v>1.35</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW2" t="n">
         <v>2.06</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.45</v>
+        <v>48.36</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.59</v>
+        <v>50.54</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>43.55</v>
+        <v>43.64</v>
       </c>
       <c r="Y9" t="n">
         <v>0.27</v>
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.68</v>
+        <v>41.73</v>
       </c>
       <c r="DW9" t="n">
         <v>0.18</v>
@@ -5806,94 +5806,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>91.7</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="M13" t="n">
-        <v>39.3</v>
+        <v>38</v>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="P13" t="n">
-        <v>11.4</v>
+        <v>11.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>7.1</v>
+        <v>7.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>45.7</v>
+        <v>44.55</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z13" t="n">
         <v>11</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.8</v>
+        <v>6.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.3</v>
+        <v>19.36</v>
       </c>
       <c r="AD13" t="n">
         <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF13" t="n">
         <v>0.09</v>
@@ -5977,70 +5977,70 @@
         <v>2.18</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.05</v>
+        <v>10.14</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="BJ13" t="n">
         <v>0.86</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.52</v>
+        <v>4.55</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.52</v>
+        <v>5.59</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS13" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.43</v>
+        <v>3.36</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.59</v>
+        <v>3.51</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CC13" t="n">
         <v>6.16</v>
@@ -6055,7 +6055,7 @@
         <v>3.09</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH13" t="n">
         <v>1.37</v>
@@ -6070,10 +6070,10 @@
         <v>1.56</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN13" t="n">
         <v>1.85</v>
@@ -6085,13 +6085,13 @@
         <v>2.22</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="CR13" t="n">
         <v>1.5</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="CT13" t="n">
         <v>2.67</v>
@@ -6115,91 +6115,91 @@
         <v>2.26</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB13" t="n">
         <v>1.45</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.86</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.19</v>
+        <v>35.68</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.38</v>
+        <v>11.59</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.57</v>
+        <v>12.32</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.71</v>
+        <v>7.72</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.29</v>
+        <v>43.78</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.38</v>
+        <v>10.41</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.43</v>
+        <v>6.36</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.52</v>
+        <v>18.59</v>
       </c>
       <c r="EB13" t="n">
         <v>1.2</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="14">
@@ -8061,7 +8061,7 @@
         <v>3.6</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CE18" t="n">
         <v>1.43</v>
@@ -8224,13 +8224,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.09</v>
@@ -8314,139 +8314,139 @@
         <v>3.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>88</v>
+        <v>91.36</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.7</v>
+        <v>40.36</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP19" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF19" t="n">
         <v>3</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BG19" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.19</v>
+        <v>10.27</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.38</v>
+        <v>5.45</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV19" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY19" t="n">
         <v>2.6</v>
@@ -8455,31 +8455,31 @@
         <v>2.71</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CC19" t="n">
-        <v>5.35</v>
+        <v>5.12</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.65</v>
+        <v>5.41</v>
       </c>
       <c r="CE19" t="n">
         <v>1.43</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.9</v>
@@ -8488,10 +8488,10 @@
         <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN19" t="n">
         <v>1.85</v>
@@ -8500,22 +8500,22 @@
         <v>1.34</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV19" t="n">
         <v>1.93</v>
@@ -8527,19 +8527,19 @@
         <v>1.62</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.32</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DD19" t="n">
         <v>3.26</v>
@@ -8548,76 +8548,76 @@
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.76000000000001</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.24</v>
+        <v>5.36</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.52</v>
+        <v>45.09</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.24</v>
+        <v>14.91</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.62</v>
+        <v>13.73</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.76</v>
+        <v>5.68</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.24</v>
+        <v>54.82</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.62</v>
+        <v>11.77</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.62</v>
+        <v>7.72</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.43</v>
+        <v>19.59</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.18</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>82.36</v>
+        <v>81.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.64</v>
+        <v>40</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.36</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.55</v>
+        <v>11.33</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.09</v>
+        <v>42.17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.27</v>
+        <v>9.17</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.91</v>
+        <v>6.83</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.18</v>
+        <v>17.75</v>
       </c>
       <c r="BE4" t="n">
         <v>1.04</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.73</v>
+        <v>7.83</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BO4" t="n">
         <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.14</v>
+        <v>4.22</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY4" t="n">
         <v>2.32</v>
@@ -2416,16 +2416,16 @@
         <v>2.37</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.68</v>
+        <v>5.55</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.92</v>
+        <v>5.76</v>
       </c>
       <c r="CE4" t="n">
         <v>1.44</v>
@@ -2434,7 +2434,7 @@
         <v>3.06</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH4" t="n">
         <v>1.37</v>
@@ -2449,10 +2449,10 @@
         <v>1.6</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CN4" t="n">
         <v>1.77</v>
@@ -2461,10 +2461,10 @@
         <v>1.38</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
@@ -2482,70 +2482,70 @@
         <v>1.86</v>
       </c>
       <c r="CW4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CY4" t="n">
         <v>2.05</v>
       </c>
-      <c r="CX4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>2.03</v>
-      </c>
       <c r="CZ4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.99</v>
+        <v>3.09</v>
       </c>
       <c r="DE4" t="n">
         <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.22</v>
+        <v>85.61</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.41</v>
+        <v>42</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.09</v>
+        <v>13.13</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.36</v>
+        <v>11.26</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="DS4" t="n">
         <v>0.13</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.22</v>
+        <v>45.13</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.18</v>
+        <v>11.04</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.55</v>
+        <v>7.48</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.72</v>
+        <v>19.43</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="G5" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>107.55</v>
+        <v>107.67</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.64</v>
+        <v>4.83</v>
       </c>
       <c r="L5" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>46.45</v>
+        <v>46.83</v>
       </c>
       <c r="N5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="P5" t="n">
-        <v>10.55</v>
+        <v>10.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.09</v>
+        <v>12.17</v>
       </c>
       <c r="R5" t="n">
-        <v>6.18</v>
+        <v>6.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>52.73</v>
+        <v>53.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.09</v>
+        <v>11.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.09</v>
+        <v>7.67</v>
       </c>
       <c r="AB5" t="n">
         <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.73</v>
+        <v>19.17</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.77</v>
+        <v>8.83</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP5" t="n">
         <v>4.09</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="BR5" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS5" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="CA5" t="n">
         <v>3.47</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC5" t="n">
         <v>3.43</v>
@@ -2834,16 +2834,16 @@
         <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CH5" t="n">
         <v>1.41</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.85</v>
@@ -2852,10 +2852,10 @@
         <v>1.65</v>
       </c>
       <c r="CL5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CM5" t="n">
         <v>2.15</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>2.16</v>
       </c>
       <c r="CN5" t="n">
         <v>1.73</v>
@@ -2882,43 +2882,43 @@
         <v>1.42</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC5" t="n">
         <v>2.13</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="DH5" t="n">
-        <v>95.55</v>
+        <v>96.13</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2927,58 +2927,58 @@
         <v>1.96</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.05</v>
+        <v>4.17</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DM5" t="n">
-        <v>40.95</v>
+        <v>41.39</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.82</v>
+        <v>11.7</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.96</v>
+        <v>12</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.95</v>
+        <v>7.83</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.54</v>
+        <v>50.82</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.41</v>
+        <v>10.74</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.45</v>
+        <v>6.79</v>
       </c>
       <c r="DZ5" t="n">
         <v>3.96</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.28</v>
+        <v>18.05</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="EC5" t="n">
         <v>1.91</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.17</v>
@@ -3487,46 +3487,46 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AI7" t="n">
-        <v>90.5</v>
+        <v>92.45</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>35.7</v>
+        <v>35.45</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>12.55</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.3</v>
+        <v>15.18</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.7</v>
+        <v>7.82</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
         <v>1</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.5</v>
+        <v>57.36</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>8.27</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.3</v>
+        <v>16.64</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="BF7" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.27</v>
+        <v>8.17</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.82</v>
+        <v>4.74</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT7" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU7" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BV7" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY7" t="n">
         <v>3.42</v>
@@ -3625,136 +3625,136 @@
         <v>3.67</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.3</v>
+        <v>5.27</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK7" t="n">
         <v>1.65</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CU7" t="n">
         <v>1.47</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW7" t="n">
         <v>1.98</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CZ7" t="n">
         <v>2.15</v>
       </c>
-      <c r="CZ7" t="n">
-        <v>2.12</v>
-      </c>
       <c r="DA7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="DE7" t="n">
         <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DH7" t="n">
-        <v>98.95</v>
+        <v>99.52</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.37</v>
+        <v>44.83</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="DO7" t="n">
         <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.63</v>
+        <v>12.44</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.45</v>
+        <v>14.43</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.09</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57.96</v>
+        <v>58.3</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX7" t="n">
         <v>10.91</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.18</v>
+        <v>7.13</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.73</v>
+        <v>3.79</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.18</v>
+        <v>16.35</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8</v>
+        <v>4.18</v>
       </c>
       <c r="H8" t="n">
-        <v>117.7</v>
+        <v>119.55</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="M8" t="n">
-        <v>61.8</v>
+        <v>61.73</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.2</v>
+        <v>11.91</v>
       </c>
       <c r="R8" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>68.3</v>
+        <v>69</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.1</v>
+        <v>20.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.5</v>
+        <v>12.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.6</v>
+        <v>18.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AF8" t="n">
         <v>0.25</v>
@@ -3968,37 +3968,37 @@
         <v>1.92</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.68</v>
+        <v>11.83</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="BJ8" t="n">
         <v>1.09</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BO8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.55</v>
+        <v>5.57</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.14</v>
+        <v>6.26</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4007,31 +4007,31 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV8" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.71</v>
+        <v>5.83</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.98</v>
+        <v>6.14</v>
       </c>
       <c r="CC8" t="n">
         <v>1.63</v>
@@ -4046,16 +4046,16 @@
         <v>2</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="CH8" t="n">
         <v>1.82</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK8" t="n">
         <v>1.4</v>
@@ -4064,127 +4064,127 @@
         <v>1.7</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CO8" t="n">
         <v>1.09</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CX8" t="n">
         <v>1.5</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.52</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DB8" t="inlineStr"/>
       <c r="DC8" t="n">
         <v>1.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DG8" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="DH8" t="n">
-        <v>114.5</v>
+        <v>115.52</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DK8" t="n">
-        <v>7.32</v>
+        <v>7.52</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="DM8" t="n">
-        <v>62.91</v>
+        <v>62.83</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.32</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.27</v>
+        <v>12.13</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>68.41</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="DW8" t="n">
         <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>20.14</v>
+        <v>20.3</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.59</v>
+        <v>12.78</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.55</v>
+        <v>7.52</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.32</v>
+        <v>17.39</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="9">
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.18</v>
@@ -5896,139 +5896,139 @@
         <v>1.91</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>90.09</v>
+        <v>88.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>33.36</v>
+        <v>32.17</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.36</v>
+        <v>11.17</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.64</v>
+        <v>12.17</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AU13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BL13" t="n">
         <v>0.91</v>
       </c>
-      <c r="AV13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>43</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>17.82</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.86</v>
-      </c>
       <c r="BM13" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.59</v>
+        <v>5.74</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT13" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU13" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BY13" t="n">
         <v>3.36</v>
@@ -6037,85 +6037,85 @@
         <v>3.51</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.66</v>
+        <v>3.87</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.79</v>
+        <v>4.04</v>
       </c>
       <c r="CC13" t="n">
-        <v>6.16</v>
+        <v>6.69</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.61</v>
+        <v>7.53</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="CH13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>2</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CO13" t="n">
         <v>1.37</v>
       </c>
-      <c r="CI13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>1.38</v>
-      </c>
       <c r="CP13" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="CR13" t="n">
         <v>1.5</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="CT13" t="n">
         <v>2.67</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX13" t="n">
         <v>1.66</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.26</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="DB13" t="n">
         <v>1.45</v>
@@ -6124,82 +6124,82 @@
         <v>2.27</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="DE13" t="n">
         <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.04000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="DL13" t="n">
         <v>0.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>35.68</v>
+        <v>34.96</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.59</v>
+        <v>11.48</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.32</v>
+        <v>12.09</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.72</v>
+        <v>7.78</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>43.78</v>
+        <v>42.92</v>
       </c>
       <c r="DW13" t="n">
         <v>0.13</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.41</v>
+        <v>10.35</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.36</v>
+        <v>6.31</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.59</v>
+        <v>18.48</v>
       </c>
       <c r="EB13" t="n">
         <v>1.2</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="14">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
@@ -7833,82 +7833,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="G18" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="H18" t="n">
-        <v>106.45</v>
+        <v>102.33</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="K18" t="n">
-        <v>6.18</v>
+        <v>5.83</v>
       </c>
       <c r="L18" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M18" t="n">
-        <v>50.55</v>
+        <v>49.75</v>
       </c>
       <c r="N18" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O18" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="P18" t="n">
-        <v>14.91</v>
+        <v>14.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.45</v>
+        <v>12.08</v>
       </c>
       <c r="R18" t="n">
-        <v>7.73</v>
+        <v>7.5</v>
       </c>
       <c r="S18" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>49.82</v>
+        <v>48.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.82</v>
+        <v>12.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.82</v>
+        <v>7.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.36</v>
+        <v>19.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7992,70 +7992,70 @@
         <v>2.36</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.59</v>
+        <v>10.39</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL18" t="n">
         <v>0.91</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.23</v>
+        <v>5.13</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT18" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU18" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV18" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CC18" t="n">
         <v>3.6</v>
@@ -8064,52 +8064,52 @@
         <v>3.57</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI18" t="n">
         <v>1.93</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK18" t="n">
         <v>1.5</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM18" t="n">
         <v>2.43</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO18" t="n">
         <v>1.33</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="CR18" t="n">
         <v>1.45</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CU18" t="n">
         <v>1.45</v>
@@ -8121,22 +8121,22 @@
         <v>1.89</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY18" t="n">
         <v>1.93</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB18" t="n">
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD18" t="n">
         <v>3.15</v>
@@ -8145,76 +8145,76 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DH18" t="n">
-        <v>98.77</v>
+        <v>96.95</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="DK18" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM18" t="n">
-        <v>47.28</v>
+        <v>47</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.86</v>
+        <v>14.83</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.32</v>
+        <v>8.17</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.82</v>
+        <v>49.13</v>
       </c>
       <c r="DW18" t="n">
         <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.04</v>
+        <v>12.96</v>
       </c>
       <c r="DY18" t="n">
         <v>8.039999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.27</v>
+        <v>19.31</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="H2" t="n">
-        <v>124.55</v>
+        <v>121.67</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="L2" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="M2" t="n">
-        <v>58.45</v>
+        <v>57.08</v>
       </c>
       <c r="N2" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O2" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>13.45</v>
+        <v>13.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="R2" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="S2" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="U2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>52</v>
+        <v>52.25</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.45</v>
+        <v>15.08</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>10.42</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.45</v>
+        <v>4.67</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.55</v>
+        <v>21.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AF2" t="n">
         <v>0.18</v>
@@ -1550,70 +1550,70 @@
         <v>2.36</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.05</v>
+        <v>4.87</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.77</v>
+        <v>4.83</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU2" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BX2" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CC2" t="n">
         <v>2.93</v>
@@ -1625,40 +1625,40 @@
         <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CN2" t="n">
         <v>1.8</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.79</v>
       </c>
       <c r="CO2" t="n">
         <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
@@ -1691,88 +1691,88 @@
         <v>1.8</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="DE2" t="n">
         <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="DH2" t="n">
-        <v>116.86</v>
+        <v>115.7</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.68</v>
+        <v>5.61</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="DM2" t="n">
-        <v>54.36</v>
+        <v>53.82</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.9</v>
+        <v>13.09</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.22</v>
+        <v>12.13</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.55</v>
+        <v>5.48</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.64</v>
+        <v>49.87</v>
       </c>
       <c r="DW2" t="n">
         <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.04</v>
+        <v>14.39</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.640000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.4</v>
+        <v>4.52</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.73</v>
+        <v>21.48</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H3" t="n">
-        <v>107.73</v>
+        <v>111.25</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="K3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>61.55</v>
+        <v>62.67</v>
       </c>
       <c r="N3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>10.36</v>
+        <v>10.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="R3" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="T3" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="U3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>55.45</v>
+        <v>56.25</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>6.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.45</v>
+        <v>20</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
         <v>0.27</v>
@@ -1953,70 +1953,70 @@
         <v>1.64</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.68</v>
+        <v>10.65</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.59</v>
+        <v>5.61</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BT3" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>1.55</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="CC3" t="n">
         <v>2.1</v>
@@ -2028,70 +2028,70 @@
         <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
       </c>
       <c r="CI3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CJ3" t="n">
         <v>1.91</v>
       </c>
-      <c r="CJ3" t="n">
-        <v>1.92</v>
-      </c>
       <c r="CK3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP3" t="n">
         <v>1.85</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CU3" t="n">
         <v>1.48</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX3" t="n">
         <v>1.61</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.34</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
@@ -2106,43 +2106,43 @@
         <v>0.22</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.54</v>
+        <v>103.65</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="DK3" t="n">
         <v>6.91</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="DM3" t="n">
-        <v>54.1</v>
+        <v>55</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.5</v>
+        <v>11.52</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.82</v>
+        <v>9.52</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.32</v>
+        <v>8.17</v>
       </c>
       <c r="DS3" t="n">
         <v>0.09</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.95</v>
+        <v>54.43</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.36</v>
+        <v>13.22</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.82</v>
+        <v>7.7</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.5</v>
+        <v>19.31</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="4">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="G6" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="H6" t="n">
-        <v>107.82</v>
+        <v>107.33</v>
       </c>
       <c r="I6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="K6" t="n">
-        <v>5.73</v>
+        <v>5.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>46.82</v>
+        <v>45.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O6" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="P6" t="n">
-        <v>15.09</v>
+        <v>15.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.82</v>
+        <v>15.25</v>
       </c>
       <c r="R6" t="n">
-        <v>7.27</v>
+        <v>7.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="U6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.73</v>
+        <v>51.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.73</v>
+        <v>12.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.550000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.36</v>
+        <v>21.75</v>
       </c>
       <c r="AD6" t="n">
         <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF6" t="n">
         <v>0.09</v>
@@ -3162,49 +3162,49 @@
         <v>2.45</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.73</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.32</v>
+        <v>5.26</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BT6" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU6" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="CC6" t="n">
         <v>5.21</v>
@@ -3234,43 +3234,43 @@
         <v>5.86</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.7</v>
+        <v>4.89</v>
       </c>
       <c r="CR6" t="n">
         <v>1.54</v>
@@ -3285,28 +3285,28 @@
         <v>1.45</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="DD6" t="n">
         <v>2.95</v>
@@ -3315,73 +3315,73 @@
         <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.14</v>
+        <v>103.08</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ6" t="n">
         <v>2.13</v>
       </c>
       <c r="DK6" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM6" t="n">
-        <v>42</v>
+        <v>41.52</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="DP6" t="n">
-        <v>15</v>
+        <v>15.22</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.82</v>
+        <v>14.09</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.95</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.82</v>
+        <v>50.26</v>
       </c>
       <c r="DW6" t="n">
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.54</v>
+        <v>11.61</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.73</v>
+        <v>7.74</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.82</v>
+        <v>3.87</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.72</v>
+        <v>20</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
         <v>2.04</v>
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4287,127 +4287,127 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AI9" t="n">
-        <v>97.36</v>
+        <v>97.33</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.27</v>
+        <v>40.42</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.82</v>
+        <v>14.33</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.64</v>
+        <v>14.08</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.18</v>
+        <v>7.42</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>39.82</v>
+        <v>39.83</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.27</v>
+        <v>9.92</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.64</v>
+        <v>7.08</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="BD9" t="n">
-        <v>23.73</v>
+        <v>23.58</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BH9" t="n">
         <v>8.91</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT9" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY9" t="n">
         <v>3.14</v>
@@ -4425,25 +4425,25 @@
         <v>3.19</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.14</v>
+        <v>5.05</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.58</v>
+        <v>5.46</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.71</v>
+        <v>3.78</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CH9" t="n">
         <v>1.26</v>
@@ -4452,13 +4452,13 @@
         <v>1.58</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CK9" t="n">
         <v>1.83</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CM9" t="n">
         <v>1.92</v>
@@ -4467,13 +4467,13 @@
         <v>1.56</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.61</v>
+        <v>5.76</v>
       </c>
       <c r="CR9" t="n">
         <v>1.63</v>
@@ -4488,10 +4488,10 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="CX9" t="n">
         <v>1.94</v>
@@ -4506,10 +4506,10 @@
         <v>1.57</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="DD9" t="n">
         <v>2.81</v>
@@ -4518,76 +4518,76 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="DH9" t="n">
-        <v>100.46</v>
+        <v>100.3</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.41</v>
+        <v>40.48</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.69</v>
+        <v>14.91</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.73</v>
+        <v>14.91</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.77</v>
+        <v>6.91</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.73</v>
+        <v>41.65</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.68</v>
+        <v>10</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.05</v>
+        <v>7.26</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="EA9" t="n">
-        <v>24.54</v>
+        <v>24.43</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="10">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4687,139 +4687,139 @@
         <v>2.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.64</v>
+        <v>85.75</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.18</v>
+        <v>38.58</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.36</v>
+        <v>12.42</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.09</v>
+        <v>13.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.45</v>
+        <v>10.25</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.36</v>
+        <v>47.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.18</v>
+        <v>9.67</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="BD10" t="n">
-        <v>15.55</v>
+        <v>15.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.949999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.86</v>
+        <v>4.96</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS10" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU10" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX10" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY10" t="n">
         <v>2.85</v>
@@ -4828,16 +4828,16 @@
         <v>2.98</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.35</v>
+        <v>5.18</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.6</v>
+        <v>5.44</v>
       </c>
       <c r="CE10" t="n">
         <v>1.4</v>
@@ -4849,7 +4849,7 @@
         <v>2.96</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI10" t="n">
         <v>1.95</v>
@@ -4861,10 +4861,10 @@
         <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN10" t="n">
         <v>1.81</v>
@@ -4891,10 +4891,10 @@
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX10" t="n">
         <v>1.64</v>
@@ -4912,85 +4912,85 @@
         <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="DF10" t="n">
         <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="DH10" t="n">
-        <v>90.54000000000001</v>
+        <v>89.91</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM10" t="n">
-        <v>43.54</v>
+        <v>42.56</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.22</v>
+        <v>11.31</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.59</v>
+        <v>13.65</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.4</v>
+        <v>49.39</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.460000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.91</v>
+        <v>6.04</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="11">
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.2</v>
@@ -5093,136 +5093,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>81.17</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO11" t="n">
         <v>1.18</v>
       </c>
-      <c r="AH11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>81.55</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>41.27</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>16.82</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BP11" t="n">
-        <v>4.76</v>
+        <v>4.59</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.52</v>
+        <v>5.55</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS11" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY11" t="n">
         <v>4.32</v>
@@ -5231,31 +5231,31 @@
         <v>4.67</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.56</v>
+        <v>5.53</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.05</v>
+        <v>6.03</v>
       </c>
       <c r="CE11" t="n">
         <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.81</v>
@@ -5264,22 +5264,22 @@
         <v>1.48</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CN11" t="n">
         <v>1.94</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP11" t="n">
         <v>1.91</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
@@ -5294,10 +5294,10 @@
         <v>1.52</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX11" t="n">
         <v>1.58</v>
@@ -5318,82 +5318,82 @@
         <v>1.92</v>
       </c>
       <c r="DD11" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG11" t="n">
         <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.48</v>
+        <v>82.23</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM11" t="n">
-        <v>36.05</v>
+        <v>35.36</v>
       </c>
       <c r="DN11" t="n">
         <v>0.86</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.29</v>
+        <v>12.18</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.24</v>
+        <v>12.45</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.76</v>
+        <v>9.91</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.28</v>
+        <v>41.45</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.86</v>
+        <v>10.64</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.57</v>
+        <v>7.37</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.43</v>
+        <v>17.18</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="12">
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5493,139 +5493,139 @@
         <v>2.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AI12" t="n">
-        <v>89.2</v>
+        <v>89.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>41.9</v>
+        <v>40.91</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.9</v>
+        <v>12.73</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>12.55</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.9</v>
+        <v>7.82</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>41.2</v>
+        <v>42.09</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.9</v>
+        <v>13.45</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.3</v>
+        <v>20.73</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="BH12" t="n">
-        <v>9</v>
+        <v>9.17</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.27</v>
+        <v>4.3</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.73</v>
+        <v>4.87</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT12" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY12" t="n">
         <v>2.93</v>
@@ -5634,40 +5634,40 @@
         <v>2.92</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.46</v>
+        <v>4.49</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CH12" t="n">
         <v>1.38</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK12" t="n">
         <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM12" t="n">
         <v>2.38</v>
@@ -5676,34 +5676,34 @@
         <v>1.83</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY12" t="n">
         <v>1.99</v>
@@ -5715,88 +5715,88 @@
         <v>1.86</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.77</v>
+        <v>90</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM12" t="n">
-        <v>45.09</v>
+        <v>44.48</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.27</v>
+        <v>13.17</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.32</v>
+        <v>12.57</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.14</v>
+        <v>42.52</v>
       </c>
       <c r="DW12" t="n">
         <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.04</v>
+        <v>12.87</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.640000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.59</v>
+        <v>20.35</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="13">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0.27</v>
@@ -6705,49 +6705,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AI15" t="n">
-        <v>90</v>
+        <v>88.17</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>45.82</v>
+        <v>42.92</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.82</v>
+        <v>10.17</v>
       </c>
       <c r="AR15" t="n">
-        <v>14</v>
+        <v>13.83</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.55</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6759,82 +6759,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>49.73</v>
+        <v>48.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.82</v>
+        <v>13.33</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.449999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.09</v>
+        <v>17.58</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BH15" t="n">
         <v>10.09</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.64</v>
+        <v>5.57</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS15" t="n">
-        <v>90.91</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX15" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BY15" t="n">
         <v>2.29</v>
@@ -6843,25 +6843,25 @@
         <v>2.32</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.04</v>
+        <v>3.36</v>
       </c>
       <c r="CE15" t="n">
         <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CH15" t="n">
         <v>1.45</v>
@@ -6876,52 +6876,52 @@
         <v>1.49</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CO15" t="n">
         <v>1.28</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX15" t="n">
         <v>1.55</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.44</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
@@ -6933,46 +6933,46 @@
         <v>3</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.41</v>
+        <v>92.31</v>
       </c>
       <c r="DI15" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.68</v>
+        <v>4.61</v>
       </c>
       <c r="DL15" t="n">
         <v>0.22</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.14</v>
+        <v>45.56</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DO15" t="n">
         <v>2.22</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.68</v>
+        <v>10.35</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.68</v>
+        <v>13.61</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.09</v>
+        <v>7.35</v>
       </c>
       <c r="DS15" t="n">
         <v>0.09</v>
@@ -6984,28 +6984,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.46</v>
+        <v>49.78</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>15</v>
+        <v>14.69</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.09</v>
+        <v>9.83</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.9</v>
+        <v>4.87</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.27</v>
+        <v>17.04</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="16">
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7105,139 +7105,139 @@
         <v>2.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG16" t="n">
         <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AI16" t="n">
-        <v>113.91</v>
+        <v>112.83</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.09</v>
+        <v>6.25</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>61.18</v>
+        <v>60.67</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.359999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="AR16" t="n">
-        <v>15</v>
+        <v>14.58</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AU16" t="n">
         <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>57.82</v>
+        <v>58</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA16" t="n">
-        <v>18.27</v>
+        <v>17.67</v>
       </c>
       <c r="BB16" t="n">
-        <v>11.73</v>
+        <v>11.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.82</v>
+        <v>15.83</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BH16" t="n">
-        <v>10</v>
+        <v>10.13</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.73</v>
+        <v>4.96</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS16" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU16" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY16" t="n">
         <v>1.27</v>
@@ -7246,10 +7246,10 @@
         <v>1.32</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.76</v>
+        <v>5.7</v>
       </c>
       <c r="CC16" t="n">
         <v>1.58</v>
@@ -7261,10 +7261,10 @@
         <v>1.24</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CH16" t="n">
         <v>1.68</v>
@@ -7285,7 +7285,7 @@
         <v>2.78</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO16" t="n">
         <v>1.13</v>
@@ -7294,25 +7294,25 @@
         <v>1.5</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CT16" t="n">
         <v>3.26</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CV16" t="n">
         <v>2.18</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX16" t="n">
         <v>1.57</v>
@@ -7333,82 +7333,82 @@
         <v>1.56</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DH16" t="n">
-        <v>120.41</v>
+        <v>119.56</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.45</v>
+        <v>6.52</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>67.86</v>
+        <v>67.31</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.72</v>
+        <v>13.56</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>59.23</v>
+        <v>59.26</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX16" t="n">
-        <v>19.27</v>
+        <v>18.91</v>
       </c>
       <c r="DY16" t="n">
-        <v>12.09</v>
+        <v>11.78</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.18</v>
+        <v>7.13</v>
       </c>
       <c r="EA16" t="n">
-        <v>15.96</v>
+        <v>15.95</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="17">
@@ -8224,94 +8224,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F19" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="G19" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>99</v>
+        <v>99.58</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J19" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="K19" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M19" t="n">
-        <v>49.82</v>
+        <v>49.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O19" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="P19" t="n">
-        <v>16.18</v>
+        <v>16.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.55</v>
+        <v>14.42</v>
       </c>
       <c r="R19" t="n">
-        <v>5.27</v>
+        <v>5.58</v>
       </c>
       <c r="S19" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.36</v>
+        <v>11.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.09</v>
+        <v>7.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.91</v>
+        <v>20</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="AF19" t="n">
         <v>0.09</v>
@@ -8395,70 +8395,70 @@
         <v>3</v>
       </c>
       <c r="BG19" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.27</v>
+        <v>10.35</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL19" t="n">
         <v>0.91</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.45</v>
+        <v>5.52</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BU19" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV19" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CC19" t="n">
         <v>5.12</v>
@@ -8473,37 +8473,37 @@
         <v>2.95</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH19" t="n">
         <v>1.39</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.9</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CM19" t="n">
         <v>2.35</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO19" t="n">
         <v>1.34</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
@@ -8518,10 +8518,10 @@
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX19" t="n">
         <v>1.62</v>
@@ -8539,85 +8539,85 @@
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="DH19" t="n">
-        <v>95.18000000000001</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM19" t="n">
-        <v>45.09</v>
+        <v>45.26</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.91</v>
+        <v>14.96</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.73</v>
+        <v>13.7</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.68</v>
+        <v>5.82</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.82</v>
+        <v>54.65</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.77</v>
+        <v>11.74</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.72</v>
+        <v>7.74</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.59</v>
+        <v>19.65</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -8627,94 +8627,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F20" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G20" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="H20" t="n">
-        <v>93.27</v>
+        <v>92.42</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>6.45</v>
+        <v>6.33</v>
       </c>
       <c r="L20" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M20" t="n">
-        <v>45.18</v>
+        <v>45.08</v>
       </c>
       <c r="N20" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O20" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>12.82</v>
+        <v>12.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.64</v>
+        <v>11.75</v>
       </c>
       <c r="R20" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T20" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="U20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>52.45</v>
+        <v>51.42</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>14</v>
+        <v>13.42</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.36</v>
+        <v>10.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.64</v>
+        <v>3.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.73</v>
+        <v>19.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8798,70 +8798,70 @@
         <v>1.91</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="BH20" t="n">
-        <v>10.05</v>
+        <v>10.17</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.82</v>
+        <v>5.04</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
       <c r="BR20" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS20" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT20" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU20" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV20" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX20" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CC20" t="n">
         <v>5.72</v>
@@ -8870,49 +8870,49 @@
         <v>6.23</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CH20" t="n">
         <v>1.39</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CL20" t="n">
         <v>1.94</v>
       </c>
-      <c r="CK20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CL20" t="n">
-        <v>1.95</v>
-      </c>
       <c r="CM20" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.91</v>
+        <v>3.85</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CT20" t="n">
         <v>2.74</v>
@@ -8921,10 +8921,10 @@
         <v>1.44</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CX20" t="n">
         <v>1.65</v>
@@ -8942,52 +8942,52 @@
         <v>1.4</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="DE20" t="n">
         <v>0.04</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="DH20" t="n">
-        <v>84.04000000000001</v>
+        <v>84</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM20" t="n">
-        <v>41.41</v>
+        <v>41.52</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.28</v>
+        <v>12.17</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.6</v>
+        <v>11.65</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.5</v>
+        <v>7.44</v>
       </c>
       <c r="DS20" t="n">
         <v>0.09</v>
@@ -8999,28 +8999,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>48.64</v>
+        <v>48.26</v>
       </c>
       <c r="DW20" t="n">
         <v>0.09</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.54</v>
+        <v>11.35</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.5</v>
+        <v>8.43</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.23</v>
+        <v>19.3</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="EC20" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="21">
@@ -9030,61 +9030,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F21" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="G21" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>91.55</v>
+        <v>90.25</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J21" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="K21" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
-        <v>50.73</v>
+        <v>48.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="P21" t="n">
-        <v>12.36</v>
+        <v>12.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.55</v>
+        <v>10.58</v>
       </c>
       <c r="R21" t="n">
         <v>7</v>
       </c>
       <c r="S21" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="T21" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9096,28 +9096,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>49.27</v>
+        <v>49.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.91</v>
+        <v>14.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.27</v>
+        <v>9.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.64</v>
+        <v>5.42</v>
       </c>
       <c r="AC21" t="n">
-        <v>18.91</v>
+        <v>18.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AF21" t="n">
         <v>0.1</v>
@@ -9201,70 +9201,70 @@
         <v>3.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.52</v>
+        <v>8.73</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.38</v>
+        <v>4.55</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT21" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU21" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV21" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="CC21" t="n">
         <v>2.95</v>
@@ -9279,13 +9279,13 @@
         <v>2.55</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI21" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ21" t="n">
         <v>1.72</v>
@@ -9312,13 +9312,13 @@
         <v>2.88</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CT21" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CU21" t="n">
         <v>1.52</v>
@@ -9342,10 +9342,10 @@
         <v>1.89</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD21" t="n">
         <v>2.95</v>
@@ -9354,76 +9354,76 @@
         <v>0.14</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.38</v>
+        <v>83.05</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="DM21" t="n">
-        <v>42.24</v>
+        <v>41.41</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.33</v>
+        <v>12.59</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.29</v>
+        <v>11.27</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.9</v>
+        <v>7.86</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44</v>
+        <v>44.23</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.29</v>
+        <v>12.18</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.67</v>
+        <v>7.63</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.1</v>
+        <v>17.77</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>0.18</v>
@@ -2278,49 +2278,49 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.5</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN4" t="n">
-        <v>40</v>
+        <v>39.46</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>12.92</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.33</v>
+        <v>11.46</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.75</v>
+        <v>9.92</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AV4" t="n">
         <v>0.08</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.17</v>
+        <v>41.69</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.17</v>
+        <v>8.92</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.83</v>
+        <v>6.62</v>
       </c>
       <c r="BC4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG4" t="n">
         <v>2.33</v>
       </c>
-      <c r="BD4" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.43</v>
-      </c>
       <c r="BH4" t="n">
-        <v>7.83</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.22</v>
+        <v>4.42</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY4" t="n">
         <v>2.32</v>
@@ -2416,16 +2416,16 @@
         <v>2.37</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.55</v>
+        <v>5.33</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.76</v>
+        <v>5.52</v>
       </c>
       <c r="CE4" t="n">
         <v>1.44</v>
@@ -2434,37 +2434,37 @@
         <v>3.06</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CH4" t="n">
         <v>1.37</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP4" t="n">
         <v>2.21</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
@@ -2479,22 +2479,22 @@
         <v>1.45</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB4" t="n">
         <v>1.43</v>
@@ -2503,49 +2503,49 @@
         <v>2.29</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.61</v>
+        <v>84.92</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="DK4" t="n">
         <v>3.17</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>42</v>
+        <v>41.62</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.13</v>
+        <v>13.33</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.26</v>
+        <v>11.33</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.74</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0.13</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.13</v>
+        <v>44.75</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.04</v>
+        <v>10.83</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.48</v>
+        <v>7.34</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.43</v>
+        <v>19.25</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
         <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>83.55</v>
+        <v>85.17</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>35.45</v>
+        <v>36.33</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.09</v>
+        <v>12.92</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.82</v>
+        <v>11.58</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.73</v>
+        <v>9.58</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.36</v>
+        <v>49.08</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.73</v>
+        <v>10.08</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.82</v>
+        <v>6.08</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.82</v>
+        <v>16.67</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.83</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.09</v>
+        <v>3.96</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.74</v>
+        <v>4.67</v>
       </c>
       <c r="BR5" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS5" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT5" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>17.39</v>
+        <v>20.83</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX5" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY5" t="n">
         <v>2.48</v>
@@ -2819,64 +2819,64 @@
         <v>2.6</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="CE5" t="n">
         <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI5" t="n">
         <v>1.96</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK5" t="n">
         <v>1.65</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM5" t="n">
         <v>2.15</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CU5" t="n">
         <v>1.42</v>
@@ -2900,10 +2900,10 @@
         <v>1.74</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DD5" t="n">
         <v>3.21</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DH5" t="n">
-        <v>96.13</v>
+        <v>96.42</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM5" t="n">
-        <v>41.39</v>
+        <v>41.58</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.7</v>
+        <v>11.67</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="DR5" t="n">
         <v>7.83</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.82</v>
+        <v>51.08</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.74</v>
+        <v>10.88</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.79</v>
+        <v>6.88</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.05</v>
+        <v>17.92</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.17</v>
@@ -3081,52 +3081,52 @@
         <v>1.67</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>98.45</v>
+        <v>97.42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>37.18</v>
+        <v>36.83</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.91</v>
+        <v>14.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.82</v>
+        <v>13.08</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.640000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,73 +3138,73 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.91</v>
+        <v>51.08</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.36</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.91</v>
+        <v>7.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.09</v>
+        <v>18.83</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.699999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.26</v>
+        <v>5.12</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS6" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY6" t="n">
         <v>2.85</v>
@@ -3222,22 +3222,22 @@
         <v>2.97</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.21</v>
+        <v>5.1</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.86</v>
+        <v>5.71</v>
       </c>
       <c r="CE6" t="n">
         <v>1.53</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CG6" t="n">
         <v>2.52</v>
@@ -3249,13 +3249,13 @@
         <v>1.69</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CK6" t="n">
         <v>1.59</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM6" t="n">
         <v>2.26</v>
@@ -3267,10 +3267,10 @@
         <v>1.48</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.89</v>
+        <v>4.86</v>
       </c>
       <c r="CR6" t="n">
         <v>1.54</v>
@@ -3291,13 +3291,13 @@
         <v>2.25</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA6" t="n">
         <v>1.81</v>
@@ -3312,79 +3312,79 @@
         <v>2.95</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.08</v>
+        <v>102.38</v>
       </c>
       <c r="DI6" t="n">
         <v>0.17</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.52</v>
+        <v>41.16</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.22</v>
+        <v>15.12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.09</v>
+        <v>14.16</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.050000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.26</v>
+        <v>51.29</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.74</v>
+        <v>7.88</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="EA6" t="n">
-        <v>20</v>
+        <v>20.29</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="7">
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="H7" t="n">
-        <v>106</v>
+        <v>105.38</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3421,34 +3421,34 @@
         <v>2.08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.92</v>
+        <v>4.38</v>
       </c>
       <c r="L7" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>53.42</v>
+        <v>52.92</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="O7" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="P7" t="n">
-        <v>12.33</v>
+        <v>12.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.75</v>
+        <v>14.08</v>
       </c>
       <c r="R7" t="n">
-        <v>8.42</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>59.17</v>
+        <v>59.54</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.33</v>
+        <v>13.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.67</v>
+        <v>8.92</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.08</v>
+        <v>15.77</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>2.18</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.17</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.43</v>
+        <v>3.67</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BS7" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BT7" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU7" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV7" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CC7" t="n">
         <v>5.27</v>
@@ -3637,13 +3637,13 @@
         <v>5.8</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
@@ -3658,13 +3658,13 @@
         <v>1.65</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO7" t="n">
         <v>1.35</v>
@@ -3673,7 +3673,7 @@
         <v>2.11</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
@@ -3688,43 +3688,43 @@
         <v>1.47</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="DH7" t="n">
-        <v>99.52</v>
+        <v>99.45</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
@@ -3733,28 +3733,28 @@
         <v>2.21</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM7" t="n">
-        <v>44.83</v>
+        <v>44.91</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.44</v>
+        <v>12.46</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.43</v>
+        <v>14.58</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.130000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.3</v>
+        <v>58.54</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.91</v>
+        <v>11.17</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.13</v>
+        <v>7.33</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.35</v>
+        <v>16.17</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="EC7" t="n">
         <v>2</v>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
@@ -4206,82 +4206,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="H9" t="n">
-        <v>103.55</v>
+        <v>101.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="K9" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="L9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M9" t="n">
-        <v>40.55</v>
+        <v>41.92</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="O9" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>15.55</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.82</v>
+        <v>15.83</v>
       </c>
       <c r="R9" t="n">
-        <v>6.36</v>
+        <v>6.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="T9" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>43.64</v>
+        <v>43.67</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.09</v>
+        <v>9.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.45</v>
+        <v>7.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AC9" t="n">
-        <v>25.36</v>
+        <v>25.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,49 +4365,49 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
         <v>0.17</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.39</v>
+        <v>4.46</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS9" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BY9" t="n">
         <v>3.14</v>
@@ -4425,10 +4425,10 @@
         <v>3.19</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CC9" t="n">
         <v>5.05</v>
@@ -4440,7 +4440,7 @@
         <v>1.61</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CG9" t="n">
         <v>2.33</v>
@@ -4452,28 +4452,28 @@
         <v>1.58</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CK9" t="n">
         <v>1.83</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM9" t="n">
         <v>1.92</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CP9" t="n">
         <v>2.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.76</v>
+        <v>5.71</v>
       </c>
       <c r="CR9" t="n">
         <v>1.63</v>
@@ -4491,7 +4491,7 @@
         <v>1.6</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CX9" t="n">
         <v>1.94</v>
@@ -4518,76 +4518,76 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DH9" t="n">
-        <v>100.3</v>
+        <v>99.2</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.48</v>
+        <v>41.17</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.91</v>
+        <v>15.16</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.91</v>
+        <v>14.96</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.91</v>
+        <v>6.96</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.65</v>
+        <v>41.75</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.26</v>
+        <v>7.08</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="EA9" t="n">
-        <v>24.43</v>
+        <v>24.33</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="10">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -5415,55 +5415,55 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="H12" t="n">
-        <v>90.25</v>
+        <v>91.23</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="K12" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="L12" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="M12" t="n">
-        <v>47.75</v>
+        <v>47.77</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="P12" t="n">
-        <v>13.58</v>
+        <v>13.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.58</v>
+        <v>12.46</v>
       </c>
       <c r="R12" t="n">
-        <v>6.5</v>
+        <v>6.62</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="U12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -5472,25 +5472,25 @@
         <v>42.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.33</v>
+        <v>12.08</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.67</v>
+        <v>7.54</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.67</v>
+        <v>4.54</v>
       </c>
       <c r="AC12" t="n">
-        <v>20</v>
+        <v>19.46</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF12" t="n">
         <v>0.09</v>
@@ -5574,70 +5574,70 @@
         <v>1.82</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.17</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.3</v>
+        <v>4.17</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.87</v>
+        <v>4.79</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV12" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC12" t="n">
         <v>4.49</v>
@@ -5646,13 +5646,13 @@
         <v>4.7</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CH12" t="n">
         <v>1.38</v>
@@ -5661,52 +5661,52 @@
         <v>1.88</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN12" t="n">
         <v>1.83</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="CR12" t="n">
         <v>1.48</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW12" t="n">
         <v>1.96</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.31</v>
@@ -5715,10 +5715,10 @@
         <v>1.86</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DD12" t="n">
         <v>3.24</v>
@@ -5727,76 +5727,76 @@
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DH12" t="n">
-        <v>90</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.56</v>
+        <v>4.46</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DM12" t="n">
-        <v>44.48</v>
+        <v>44.63</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.17</v>
+        <v>13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.57</v>
+        <v>12.5</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.13</v>
+        <v>7.17</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.52</v>
+        <v>42.54</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.87</v>
+        <v>12.71</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.57</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.31</v>
+        <v>4.25</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.35</v>
+        <v>20.04</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -7015,94 +7015,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="H16" t="n">
-        <v>126.91</v>
+        <v>123.17</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="K16" t="n">
-        <v>6.82</v>
+        <v>6.58</v>
       </c>
       <c r="L16" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M16" t="n">
-        <v>74.55</v>
+        <v>71.83</v>
       </c>
       <c r="N16" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O16" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>10.36</v>
+        <v>10.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.45</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>4.82</v>
+        <v>5.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="T16" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="U16" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="V16" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>60.64</v>
+        <v>59.92</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.27</v>
+        <v>19.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.45</v>
+        <v>11.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.82</v>
+        <v>7.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.09</v>
+        <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AF16" t="n">
         <v>0.08</v>
@@ -7186,58 +7186,58 @@
         <v>1.17</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.13</v>
+        <v>10.12</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BL16" t="n">
         <v>0.96</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.96</v>
+        <v>4.88</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.52</v>
+        <v>4.62</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS16" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX16" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
         <v>1.27</v>
@@ -7246,10 +7246,10 @@
         <v>1.32</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.4</v>
+        <v>5.42</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="CC16" t="n">
         <v>1.58</v>
@@ -7276,7 +7276,7 @@
         <v>1.74</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL16" t="n">
         <v>1.77</v>
@@ -7285,7 +7285,7 @@
         <v>2.78</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CO16" t="n">
         <v>1.13</v>
@@ -7294,7 +7294,7 @@
         <v>1.5</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
@@ -7309,7 +7309,7 @@
         <v>1.68</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW16" t="n">
         <v>1.81</v>
@@ -7330,85 +7330,85 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DD16" t="n">
         <v>2.38</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="DH16" t="n">
-        <v>119.56</v>
+        <v>118</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.52</v>
+        <v>6.42</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM16" t="n">
-        <v>67.31</v>
+        <v>66.25</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="DP16" t="n">
         <v>10</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.56</v>
+        <v>13.29</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.65</v>
+        <v>6.79</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>59.26</v>
+        <v>58.96</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX16" t="n">
-        <v>18.91</v>
+        <v>18.58</v>
       </c>
       <c r="DY16" t="n">
-        <v>11.78</v>
+        <v>11.54</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7.13</v>
+        <v>7.04</v>
       </c>
       <c r="EA16" t="n">
-        <v>15.95</v>
+        <v>15.66</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="17">
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
         <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7914,136 +7914,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>91.09</v>
+        <v>91.58</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN18" t="n">
-        <v>44</v>
+        <v>44.17</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.82</v>
+        <v>14.33</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.55</v>
+        <v>11.33</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.91</v>
+        <v>8.42</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>49.82</v>
+        <v>49.67</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.27</v>
+        <v>13.25</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.27</v>
+        <v>8.42</v>
       </c>
       <c r="BC18" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.18</v>
+        <v>18.83</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.39</v>
+        <v>10.38</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.13</v>
+        <v>5.04</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.26</v>
+        <v>5.33</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BY18" t="n">
         <v>2.69</v>
@@ -8052,28 +8052,28 @@
         <v>2.82</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.46</v>
+        <v>3.55</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.52</v>
+        <v>3.59</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.57</v>
+        <v>3.93</v>
       </c>
       <c r="CE18" t="n">
         <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI18" t="n">
         <v>1.93</v>
@@ -8082,25 +8082,25 @@
         <v>1.87</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="CR18" t="n">
         <v>1.45</v>
@@ -8124,22 +8124,22 @@
         <v>1.59</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.35</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB18" t="n">
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
@@ -8148,73 +8148,73 @@
         <v>1.17</v>
       </c>
       <c r="DG18" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="DH18" t="n">
-        <v>96.95</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="DI18" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="DK18" t="n">
         <v>5.83</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM18" t="n">
-        <v>47</v>
+        <v>46.96</v>
       </c>
       <c r="DN18" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.83</v>
+        <v>14.58</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.83</v>
+        <v>11.7</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.17</v>
+        <v>7.96</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.13</v>
+        <v>49.08</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX18" t="n">
         <v>12.96</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.039999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.31</v>
+        <v>19.12</v>
       </c>
       <c r="EB18" t="n">
         <v>1.5</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
@@ -8236,82 +8236,82 @@
         <v>0.08</v>
       </c>
       <c r="F19" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="H19" t="n">
-        <v>99.58</v>
+        <v>96.77</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="J19" t="n">
-        <v>3.17</v>
+        <v>3.46</v>
       </c>
       <c r="K19" t="n">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="L19" t="n">
         <v>0.08</v>
       </c>
       <c r="M19" t="n">
-        <v>49.75</v>
+        <v>50.77</v>
       </c>
       <c r="N19" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="P19" t="n">
-        <v>16.17</v>
+        <v>16.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.42</v>
+        <v>14.31</v>
       </c>
       <c r="R19" t="n">
-        <v>5.58</v>
+        <v>6.08</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="U19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>56.5</v>
+        <v>54.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.33</v>
+        <v>10.77</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.17</v>
+        <v>6.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AC19" t="n">
-        <v>20</v>
+        <v>19.54</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AF19" t="n">
         <v>0.09</v>
@@ -8395,70 +8395,70 @@
         <v>3</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.35</v>
+        <v>10.04</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.83</v>
+        <v>4.67</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.52</v>
+        <v>5.38</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV19" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CC19" t="n">
         <v>5.12</v>
@@ -8473,13 +8473,13 @@
         <v>2.95</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH19" t="n">
         <v>1.39</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.9</v>
@@ -8491,7 +8491,7 @@
         <v>2.06</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN19" t="n">
         <v>1.84</v>
@@ -8500,10 +8500,10 @@
         <v>1.34</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
@@ -8518,10 +8518,10 @@
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX19" t="n">
         <v>1.62</v>
@@ -8539,7 +8539,7 @@
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DD19" t="n">
         <v>3.28</v>
@@ -8548,43 +8548,43 @@
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="DH19" t="n">
-        <v>95.65000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.13</v>
+        <v>3.29</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.35</v>
+        <v>5.12</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM19" t="n">
-        <v>45.26</v>
+        <v>46</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.96</v>
+        <v>15</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.7</v>
+        <v>13.67</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.82</v>
+        <v>6.08</v>
       </c>
       <c r="DS19" t="n">
         <v>0.17</v>
@@ -8596,28 +8596,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.65</v>
+        <v>53.42</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.74</v>
+        <v>11.42</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.74</v>
+        <v>7.5</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.65</v>
+        <v>19.42</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="EC19" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="20">
@@ -9030,13 +9030,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
         <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
         <v>0.17</v>
@@ -9120,139 +9120,139 @@
         <v>1.58</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" t="n">
-        <v>74.40000000000001</v>
+        <v>74.64</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN21" t="n">
-        <v>32.9</v>
+        <v>32.55</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.3</v>
+        <v>12.73</v>
       </c>
       <c r="AR21" t="n">
-        <v>12.1</v>
+        <v>12.91</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>38.2</v>
+        <v>39.82</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.4</v>
+        <v>9.27</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BD21" t="n">
-        <v>17.2</v>
+        <v>18.64</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.73</v>
+        <v>8.65</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.18</v>
+        <v>4.04</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU21" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV21" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY21" t="n">
         <v>1.98</v>
@@ -9261,55 +9261,55 @@
         <v>2.08</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="CC21" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CQ21" t="n">
         <v>2.95</v>
-      </c>
-      <c r="CD21" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="CE21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CF21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="CG21" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="CH21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CI21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CJ21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CK21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CL21" t="n">
-        <v>2</v>
-      </c>
-      <c r="CM21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CN21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CO21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="CP21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CQ21" t="n">
-        <v>2.88</v>
       </c>
       <c r="CR21" t="n">
         <v>1.37</v>
@@ -9324,49 +9324,49 @@
         <v>1.52</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="DD21" t="n">
         <v>2.95</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.05</v>
+        <v>82.78</v>
       </c>
       <c r="DI21" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DK21" t="n">
         <v>4.13</v>
@@ -9375,22 +9375,22 @@
         <v>0.82</v>
       </c>
       <c r="DM21" t="n">
-        <v>41.41</v>
+        <v>40.87</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.59</v>
+        <v>12.78</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.27</v>
+        <v>11.69</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.86</v>
+        <v>7.69</v>
       </c>
       <c r="DS21" t="n">
         <v>0.09</v>
@@ -9402,28 +9402,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44.23</v>
+        <v>44.74</v>
       </c>
       <c r="DW21" t="n">
         <v>0.13</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.18</v>
+        <v>12</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.63</v>
+        <v>7.56</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4.55</v>
+        <v>4.43</v>
       </c>
       <c r="EA21" t="n">
-        <v>17.77</v>
+        <v>18.44</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.08</v>
@@ -1469,139 +1469,139 @@
         <v>2.17</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG2" t="n">
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>109.18</v>
+        <v>108.33</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.36</v>
+        <v>5.17</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.27</v>
+        <v>50</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.36</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.45</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>47.27</v>
+        <v>47.17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.64</v>
+        <v>13.58</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.27</v>
+        <v>9.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.91</v>
+        <v>22.08</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.87</v>
+        <v>4.83</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.83</v>
+        <v>4.67</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS2" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT2" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV2" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX2" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>2.04</v>
@@ -1610,31 +1610,31 @@
         <v>2.05</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="CE2" t="n">
         <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.99</v>
@@ -1649,16 +1649,16 @@
         <v>2.3</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO2" t="n">
         <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
@@ -1694,85 +1694,85 @@
         <v>1.41</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="DD2" t="n">
         <v>3.02</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
       <c r="DH2" t="n">
-        <v>115.7</v>
+        <v>115</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.61</v>
+        <v>5.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.82</v>
+        <v>53.54</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.09</v>
+        <v>13.38</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.13</v>
+        <v>11.92</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.48</v>
+        <v>5.62</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.87</v>
+        <v>49.71</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.39</v>
+        <v>14.33</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.869999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.48</v>
+        <v>21.58</v>
       </c>
       <c r="EB2" t="n">
         <v>1.62</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0.17</v>
@@ -1872,52 +1872,52 @@
         <v>1.92</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>96.17</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="AM3" t="n">
         <v>1</v>
       </c>
-      <c r="AH3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>95.36</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AN3" t="n">
-        <v>46.64</v>
+        <v>47.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.64</v>
+        <v>12.67</v>
       </c>
       <c r="AR3" t="n">
         <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.45</v>
+        <v>53</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.64</v>
+        <v>6.58</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.55</v>
+        <v>19.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.65</v>
+        <v>10.71</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL3" t="n">
         <v>1.04</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS3" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY3" t="n">
         <v>1.5</v>
@@ -2013,16 +2013,16 @@
         <v>1.55</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.41</v>
+        <v>4.37</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CE3" t="n">
         <v>1.36</v>
@@ -2031,7 +2031,7 @@
         <v>2.65</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
@@ -2049,19 +2049,19 @@
         <v>1.97</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP3" t="n">
         <v>1.85</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
@@ -2076,106 +2076,106 @@
         <v>1.48</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW3" t="n">
         <v>2</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.65</v>
+        <v>103.71</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.91</v>
+        <v>6.96</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="DM3" t="n">
-        <v>55</v>
+        <v>55.17</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.52</v>
+        <v>11.58</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.52</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.17</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.43</v>
+        <v>54.62</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.22</v>
+        <v>13.04</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.7</v>
+        <v>7.62</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.52</v>
+        <v>5.42</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.31</v>
+        <v>19.62</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="4">
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>51.08</v>
+        <v>51</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>3.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.83</v>
+        <v>18.75</v>
       </c>
       <c r="BE6" t="n">
         <v>1.17</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.29</v>
+        <v>51.25</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
@@ -3378,7 +3378,7 @@
         <v>3.75</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.29</v>
+        <v>20.25</v>
       </c>
       <c r="EB6" t="n">
         <v>1.3</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>0.27</v>
@@ -3887,16 +3887,16 @@
         <v>0.73</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.17</v>
+        <v>4.31</v>
       </c>
       <c r="AI8" t="n">
-        <v>111.83</v>
+        <v>113.08</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -3908,97 +3908,97 @@
         <v>7.08</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>63.83</v>
+        <v>65.38</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.58</v>
+        <v>9.31</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.33</v>
+        <v>12.08</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>68.5</v>
+        <v>68.69</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA8" t="n">
-        <v>20.17</v>
+        <v>20.69</v>
       </c>
       <c r="BB8" t="n">
-        <v>12.67</v>
+        <v>13.46</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.25</v>
+        <v>16.08</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BF8" t="n">
         <v>1.92</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.83</v>
+        <v>11.75</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.57</v>
+        <v>5.42</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.26</v>
+        <v>6.33</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4007,19 +4007,19 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV8" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY8" t="n">
         <v>1.25</v>
@@ -4028,16 +4028,16 @@
         <v>1.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.83</v>
+        <v>5.81</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="CE8" t="n">
         <v>1.2</v>
@@ -4052,7 +4052,7 @@
         <v>1.82</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.65</v>
@@ -4061,10 +4061,10 @@
         <v>1.4</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CN8" t="n">
         <v>2.12</v>
@@ -4090,7 +4090,7 @@
         <v>2.4</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX8" t="n">
         <v>1.5</v>
@@ -4109,49 +4109,49 @@
         <v>1.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DG8" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="DH8" t="n">
-        <v>115.52</v>
+        <v>116.05</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="DK8" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DM8" t="n">
-        <v>62.83</v>
+        <v>63.71</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.220000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.13</v>
+        <v>12</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="DS8" t="n">
         <v>0.17</v>
@@ -4163,28 +4163,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>68.73999999999999</v>
+        <v>68.83</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>20.3</v>
+        <v>20.58</v>
       </c>
       <c r="DY8" t="n">
-        <v>12.78</v>
+        <v>13.21</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.52</v>
+        <v>7.38</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.39</v>
+        <v>17.25</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="9">
@@ -4242,7 +4242,7 @@
         <v>15.83</v>
       </c>
       <c r="R9" t="n">
-        <v>6.5</v>
+        <v>6.58</v>
       </c>
       <c r="S9" t="n">
         <v>0.83</v>
@@ -4554,7 +4554,7 @@
         <v>14.96</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.96</v>
+        <v>7</v>
       </c>
       <c r="DS9" t="n">
         <v>0.08</v>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
@@ -4609,82 +4609,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="H10" t="n">
-        <v>94.45</v>
+        <v>91.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="L10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>46.91</v>
+        <v>46.83</v>
       </c>
       <c r="N10" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O10" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="P10" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.09</v>
+        <v>13.42</v>
       </c>
       <c r="R10" t="n">
-        <v>7.36</v>
+        <v>7.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="T10" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51.45</v>
+        <v>49.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.73</v>
+        <v>10</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.36</v>
+        <v>6.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.36</v>
+        <v>3.83</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.45</v>
+        <v>16.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>0.17</v>
@@ -4768,70 +4768,70 @@
         <v>2.42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.09</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS10" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX10" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.71</v>
+        <v>3.78</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="CC10" t="n">
         <v>5.18</v>
@@ -4840,43 +4840,43 @@
         <v>5.44</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CK10" t="n">
         <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
@@ -4891,106 +4891,106 @@
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
         <v>1.64</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.28</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB10" t="n">
         <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
         <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DH10" t="n">
-        <v>89.91</v>
+        <v>88.42</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="DK10" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>42.56</v>
+        <v>42.71</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.31</v>
+        <v>11.25</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.65</v>
+        <v>13.34</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.869999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.39</v>
+        <v>48.54</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.04</v>
+        <v>5.96</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.3</v>
+        <v>15.96</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="11">
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="H11" t="n">
-        <v>83.5</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>4.64</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M11" t="n">
-        <v>36.1</v>
+        <v>37.18</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>11.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.1</v>
+        <v>11.91</v>
       </c>
       <c r="R11" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>41.3</v>
+        <v>41.82</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.8</v>
+        <v>11.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.5</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.1</v>
+        <v>18.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5171,70 +5171,70 @@
         <v>2.17</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.14</v>
+        <v>9.91</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.55</v>
+        <v>5.39</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS11" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU11" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX11" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.32</v>
+        <v>4.17</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="CC11" t="n">
         <v>5.53</v>
@@ -5243,13 +5243,13 @@
         <v>6.03</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
@@ -5264,7 +5264,7 @@
         <v>1.48</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM11" t="n">
         <v>2.52</v>
@@ -5276,22 +5276,22 @@
         <v>1.27</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CT11" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV11" t="n">
         <v>2.06</v>
@@ -5306,61 +5306,61 @@
         <v>1.91</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DB11" t="n">
         <v>1.33</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="DE11" t="n">
         <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="DG11" t="n">
         <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.23</v>
+        <v>82.92</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM11" t="n">
-        <v>35.36</v>
+        <v>35.91</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.18</v>
+        <v>12.13</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.45</v>
+        <v>12.35</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.91</v>
+        <v>9.74</v>
       </c>
       <c r="DS11" t="n">
         <v>0.09</v>
@@ -5372,28 +5372,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.45</v>
+        <v>41.69</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.37</v>
+        <v>7.39</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.18</v>
+        <v>17.52</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="12">
@@ -5806,94 +5806,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F13" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>94.25</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="K13" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M13" t="n">
-        <v>38</v>
+        <v>41.33</v>
       </c>
       <c r="N13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="O13" t="n">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>11.82</v>
+        <v>12.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="R13" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>44.55</v>
+        <v>46.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.64</v>
+        <v>7</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.36</v>
+        <v>19.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AF13" t="n">
         <v>0.08</v>
@@ -5980,67 +5980,67 @@
         <v>2.83</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.35</v>
+        <v>10.33</v>
       </c>
       <c r="BI13" t="n">
         <v>2.83</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.61</v>
+        <v>4.67</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.74</v>
+        <v>5.67</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="CC13" t="n">
         <v>6.69</v>
@@ -6055,7 +6055,7 @@
         <v>3.04</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH13" t="n">
         <v>1.39</v>
@@ -6064,7 +6064,7 @@
         <v>1.78</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK13" t="n">
         <v>1.54</v>
@@ -6085,7 +6085,7 @@
         <v>2.18</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CR13" t="n">
         <v>1.5</v>
@@ -6100,22 +6100,22 @@
         <v>1.45</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY13" t="n">
         <v>1.99</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB13" t="n">
         <v>1.45</v>
@@ -6127,79 +6127,79 @@
         <v>2.61</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.22</v>
+        <v>91.38</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM13" t="n">
-        <v>34.96</v>
+        <v>36.75</v>
       </c>
       <c r="DN13" t="n">
         <v>1.04</v>
       </c>
       <c r="DO13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>4</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="EB13" t="n">
         <v>1.22</v>
       </c>
-      <c r="DP13" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="DQ13" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="DR13" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="DS13" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DT13" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV13" t="n">
-        <v>42.92</v>
-      </c>
-      <c r="DW13" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DX13" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="DY13" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="DZ13" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="EA13" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="EB13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="EC13" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="14">
@@ -6209,94 +6209,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="H14" t="n">
-        <v>100.9</v>
+        <v>99.09</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="K14" t="n">
-        <v>6.9</v>
+        <v>6.64</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M14" t="n">
-        <v>49.8</v>
+        <v>48.09</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>12.5</v>
+        <v>12.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.5</v>
+        <v>10.73</v>
       </c>
       <c r="R14" t="n">
-        <v>9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>56.1</v>
+        <v>54.73</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.3</v>
+        <v>15.09</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.2</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.1</v>
+        <v>5.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>22.9</v>
+        <v>22.18</v>
       </c>
       <c r="AD14" t="n">
         <v>1.68</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6380,64 +6380,64 @@
         <v>3.08</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.95</v>
+        <v>11</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.27</v>
+        <v>5.3</v>
       </c>
       <c r="BR14" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT14" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV14" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="CA14" t="n">
         <v>3.54</v>
@@ -6455,10 +6455,10 @@
         <v>1.43</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CH14" t="n">
         <v>1.39</v>
@@ -6467,7 +6467,7 @@
         <v>1.89</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
@@ -6488,7 +6488,7 @@
         <v>2.12</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CR14" t="n">
         <v>1.46</v>
@@ -6509,13 +6509,13 @@
         <v>1.98</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA14" t="n">
         <v>1.98</v>
@@ -6527,82 +6527,82 @@
         <v>2.22</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.23</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.86</v>
+        <v>5.78</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.32</v>
+        <v>44.69</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.68</v>
+        <v>13.52</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.32</v>
+        <v>10.44</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.449999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.55</v>
+        <v>53.96</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.36</v>
+        <v>13.35</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.960000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.41</v>
+        <v>4.6</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.46</v>
+        <v>20.22</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="15">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0.27</v>
@@ -6705,49 +6705,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AI15" t="n">
-        <v>88.17</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="AJ15" t="n">
         <v>0.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.67</v>
+        <v>4.54</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN15" t="n">
-        <v>42.92</v>
+        <v>41.62</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.17</v>
+        <v>10.15</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.83</v>
+        <v>14</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6759,82 +6759,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.5</v>
+        <v>47.46</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.33</v>
+        <v>13.62</v>
       </c>
       <c r="BB15" t="n">
         <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.33</v>
+        <v>4.62</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.58</v>
+        <v>16.85</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BF15" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BG15" t="n">
         <v>2.83</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
       <c r="BI15" t="n">
         <v>2.83</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
         <v>0.96</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.52</v>
+        <v>4.58</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS15" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY15" t="n">
         <v>2.29</v>
@@ -6843,31 +6843,31 @@
         <v>2.32</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.36</v>
+        <v>3.29</v>
       </c>
       <c r="CE15" t="n">
         <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH15" t="n">
         <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.77</v>
@@ -6882,16 +6882,16 @@
         <v>2.46</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO15" t="n">
         <v>1.28</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6933,79 +6933,79 @@
         <v>3</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="DH15" t="n">
-        <v>92.31</v>
+        <v>90.67</v>
       </c>
       <c r="DI15" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.56</v>
+        <v>44.75</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.35</v>
+        <v>10.33</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.61</v>
+        <v>13.71</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.35</v>
+        <v>7.67</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.78</v>
+        <v>49.16</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.69</v>
+        <v>14.79</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.83</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.87</v>
+        <v>5</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.04</v>
+        <v>16.67</v>
       </c>
       <c r="EB15" t="n">
         <v>1.6</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="16">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
@@ -7430,49 +7430,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G17" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="H17" t="n">
-        <v>80.81999999999999</v>
+        <v>83.08</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="K17" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="L17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="M17" t="n">
-        <v>40.73</v>
+        <v>40.08</v>
       </c>
       <c r="N17" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O17" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="P17" t="n">
-        <v>11.55</v>
+        <v>11.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.09</v>
+        <v>11.83</v>
       </c>
       <c r="R17" t="n">
-        <v>7.73</v>
+        <v>7.5</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T17" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7484,28 +7484,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>45.73</v>
+        <v>46.42</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.91</v>
+        <v>9.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.09</v>
+        <v>18.67</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7589,70 +7589,70 @@
         <v>2.27</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.859999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="BR17" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS17" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT17" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BU17" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX17" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.72</v>
+        <v>4.6</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.08</v>
+        <v>4.03</v>
       </c>
       <c r="CC17" t="n">
         <v>6.69</v>
@@ -7664,10 +7664,10 @@
         <v>1.45</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CH17" t="n">
         <v>1.38</v>
@@ -7679,10 +7679,10 @@
         <v>2.05</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM17" t="n">
         <v>2.39</v>
@@ -7697,7 +7697,7 @@
         <v>2.19</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
@@ -7712,7 +7712,7 @@
         <v>1.42</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CW17" t="n">
         <v>2.15</v>
@@ -7733,7 +7733,7 @@
         <v>1.44</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DD17" t="n">
         <v>3.09</v>
@@ -7742,43 +7742,43 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="DH17" t="n">
-        <v>78.91</v>
+        <v>80.17</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="DK17" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM17" t="n">
-        <v>37</v>
+        <v>36.82</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.86</v>
+        <v>12.65</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.86</v>
+        <v>11.26</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.039999999999999</v>
+        <v>7.91</v>
       </c>
       <c r="DS17" t="n">
         <v>0.04</v>
@@ -7790,25 +7790,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.96</v>
+        <v>44.39</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.73</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.68</v>
+        <v>6.65</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.55</v>
+        <v>18.83</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="EC17" t="n">
         <v>2.09</v>
@@ -8290,7 +8290,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>54.08</v>
+        <v>54.15</v>
       </c>
       <c r="Y19" t="n">
         <v>0.23</v>
@@ -8596,7 +8596,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.42</v>
+        <v>53.46</v>
       </c>
       <c r="DW19" t="n">
         <v>0.17</v>
@@ -8627,13 +8627,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="n">
         <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
         <v>0.08</v>
@@ -8720,49 +8720,49 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AI20" t="n">
-        <v>74.81999999999999</v>
+        <v>74.92</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN20" t="n">
-        <v>37.64</v>
+        <v>36.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.73</v>
+        <v>11.58</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.55</v>
+        <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.73</v>
+        <v>8.67</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8774,82 +8774,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>44.82</v>
+        <v>45.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.09</v>
+        <v>8.75</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.64</v>
+        <v>6.33</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.73</v>
+        <v>18.33</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BH20" t="n">
-        <v>10.17</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK20" t="n">
         <v>0.17</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.09</v>
+        <v>4.96</v>
       </c>
       <c r="BR20" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS20" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT20" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU20" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV20" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX20" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY20" t="n">
         <v>2.66</v>
@@ -8858,16 +8858,16 @@
         <v>2.81</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CC20" t="n">
-        <v>5.72</v>
+        <v>5.47</v>
       </c>
       <c r="CD20" t="n">
-        <v>6.23</v>
+        <v>5.94</v>
       </c>
       <c r="CE20" t="n">
         <v>1.43</v>
@@ -8885,7 +8885,7 @@
         <v>1.85</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK20" t="n">
         <v>1.52</v>
@@ -8912,28 +8912,28 @@
         <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU20" t="n">
         <v>1.44</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW20" t="n">
         <v>1.99</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="DA20" t="n">
         <v>1.9</v>
@@ -8945,79 +8945,79 @@
         <v>2.16</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="DE20" t="n">
         <v>0.04</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="DH20" t="n">
-        <v>84</v>
+        <v>83.67</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.17</v>
+        <v>5.04</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM20" t="n">
-        <v>41.52</v>
+        <v>40.79</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.17</v>
+        <v>12.08</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.65</v>
+        <v>11.62</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.44</v>
+        <v>7.46</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>48.26</v>
+        <v>48.46</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.35</v>
+        <v>11.08</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.43</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.3</v>
+        <v>19.08</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC20" t="n">
         <v>1.96</v>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -4609,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="G10" t="n">
         <v>2.33</v>
@@ -4621,7 +4621,7 @@
         <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K10" t="n">
         <v>4.67</v>
@@ -4684,7 +4684,7 @@
         <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF10" t="n">
         <v>0.17</v>
@@ -4921,7 +4921,7 @@
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DG10" t="n">
         <v>1.92</v>
@@ -4933,7 +4933,7 @@
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="DK10" t="n">
         <v>3.96</v>
@@ -4990,7 +4990,7 @@
         <v>1.2</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="11">
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="G11" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="n">
-        <v>84.81999999999999</v>
+        <v>88</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="K11" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>37.18</v>
+        <v>38.42</v>
       </c>
       <c r="N11" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="O11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
-        <v>11.91</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.91</v>
+        <v>12.58</v>
       </c>
       <c r="R11" t="n">
-        <v>8.640000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="U11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>41.82</v>
+        <v>43.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.55</v>
+        <v>11.92</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.449999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.73</v>
+        <v>19</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5171,70 +5171,70 @@
         <v>2.17</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.91</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.39</v>
+        <v>5.29</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS11" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU11" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="CB11" t="n">
         <v>4.17</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>4.2</v>
       </c>
       <c r="CC11" t="n">
         <v>5.53</v>
@@ -5252,22 +5252,22 @@
         <v>3.05</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK11" t="n">
         <v>1.48</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN11" t="n">
         <v>1.94</v>
@@ -5279,7 +5279,7 @@
         <v>1.92</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
@@ -5288,7 +5288,7 @@
         <v>2.75</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CU11" t="n">
         <v>1.51</v>
@@ -5300,13 +5300,13 @@
         <v>1.84</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY11" t="n">
         <v>1.91</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DA11" t="n">
         <v>1.96</v>
@@ -5318,82 +5318,82 @@
         <v>1.93</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DG11" t="n">
         <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.92</v>
+        <v>84.58</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DM11" t="n">
-        <v>35.91</v>
+        <v>36.58</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.13</v>
+        <v>12.16</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.35</v>
+        <v>12.66</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.74</v>
+        <v>9.75</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.69</v>
+        <v>42.42</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.57</v>
+        <v>10.8</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.39</v>
+        <v>7.58</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.52</v>
+        <v>17.71</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="12">
@@ -9030,13 +9030,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
         <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
         <v>0.17</v>
@@ -9120,139 +9120,139 @@
         <v>1.58</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>74.64</v>
+        <v>76.25</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN21" t="n">
-        <v>32.55</v>
+        <v>32.42</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.73</v>
+        <v>13.33</v>
       </c>
       <c r="AR21" t="n">
-        <v>12.91</v>
+        <v>12.92</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.449999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>39.82</v>
+        <v>39.92</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.27</v>
+        <v>9.75</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.91</v>
+        <v>6.17</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.64</v>
+        <v>18</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.65</v>
+        <v>8.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BT21" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU21" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV21" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
         <v>1.98</v>
@@ -9264,19 +9264,19 @@
         <v>3.79</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CC21" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="CE21" t="n">
         <v>1.34</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG21" t="n">
         <v>3.11</v>
@@ -9294,7 +9294,7 @@
         <v>1.56</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM21" t="n">
         <v>2.32</v>
@@ -9318,7 +9318,7 @@
         <v>2.68</v>
       </c>
       <c r="CT21" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CU21" t="n">
         <v>1.52</v>
@@ -9330,16 +9330,16 @@
         <v>1.79</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.34</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB21" t="n">
         <v>1.32</v>
@@ -9348,82 +9348,82 @@
         <v>1.9</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DH21" t="n">
-        <v>82.78</v>
+        <v>83.25</v>
       </c>
       <c r="DI21" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="DM21" t="n">
-        <v>40.87</v>
+        <v>40.46</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.78</v>
+        <v>13.08</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.69</v>
+        <v>11.75</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.69</v>
+        <v>7.71</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44.74</v>
+        <v>44.58</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX21" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.56</v>
+        <v>7.62</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.44</v>
+        <v>18.12</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_La_Liga_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
@@ -1391,82 +1391,82 @@
         <v>0.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="G2" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="H2" t="n">
-        <v>121.67</v>
+        <v>119.77</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="K2" t="n">
-        <v>5.83</v>
+        <v>5.69</v>
       </c>
       <c r="L2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>57.08</v>
+        <v>57.62</v>
       </c>
       <c r="N2" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P2" t="n">
-        <v>13.75</v>
+        <v>14.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.83</v>
+        <v>11.54</v>
       </c>
       <c r="R2" t="n">
-        <v>4.5</v>
+        <v>4.23</v>
       </c>
       <c r="S2" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="U2" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="V2" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>52.25</v>
+        <v>51.77</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.08</v>
+        <v>15.31</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.42</v>
+        <v>10.38</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.08</v>
+        <v>20.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AF2" t="n">
         <v>0.17</v>
@@ -1550,70 +1550,70 @@
         <v>2.42</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.5</v>
+        <v>9.32</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.83</v>
+        <v>4.72</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS2" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT2" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BU2" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CC2" t="n">
         <v>2.87</v>
@@ -1625,154 +1625,154 @@
         <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK2" t="n">
         <v>1.56</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO2" t="n">
         <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV2" t="n">
         <v>1.86</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB2" t="n">
         <v>1.41</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="DE2" t="n">
         <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DH2" t="n">
-        <v>115</v>
+        <v>114.28</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.54</v>
+        <v>53.96</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.38</v>
+        <v>13.56</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.92</v>
+        <v>11.76</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.71</v>
+        <v>49.56</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.33</v>
+        <v>14.48</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.58</v>
+        <v>21.48</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="H3" t="n">
-        <v>111.25</v>
+        <v>113.46</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="K3" t="n">
-        <v>8.5</v>
+        <v>8.23</v>
       </c>
       <c r="L3" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="M3" t="n">
-        <v>62.67</v>
+        <v>62.62</v>
       </c>
       <c r="N3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="P3" t="n">
-        <v>10.5</v>
+        <v>10.31</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.08</v>
+        <v>9.15</v>
       </c>
       <c r="R3" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>56.62</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="AB3" t="n">
         <v>7</v>
       </c>
-      <c r="S3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>56.25</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>6.83</v>
-      </c>
       <c r="AC3" t="n">
-        <v>20</v>
+        <v>19.92</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AF3" t="n">
         <v>0.25</v>
@@ -1953,70 +1953,70 @@
         <v>1.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.71</v>
+        <v>10.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.62</v>
+        <v>5.52</v>
       </c>
       <c r="BQ3" t="n">
         <v>5.08</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT3" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.33</v>
+        <v>12</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.17</v>
+        <v>8</v>
       </c>
       <c r="BX3" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BY3" t="n">
         <v>1.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CA3" t="n">
         <v>4.37</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="CC3" t="n">
         <v>2.08</v>
@@ -2028,31 +2028,31 @@
         <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.91</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO3" t="n">
         <v>1.26</v>
@@ -2061,7 +2061,7 @@
         <v>1.85</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
@@ -2070,7 +2070,7 @@
         <v>2.72</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CU3" t="n">
         <v>1.48</v>
@@ -2094,55 +2094,55 @@
         <v>1.92</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD3" t="n">
         <v>3.04</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.71</v>
+        <v>105.16</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.96</v>
+        <v>6.88</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="DM3" t="n">
-        <v>55.17</v>
+        <v>55.44</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.58</v>
+        <v>11.44</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.039999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.62</v>
+        <v>54.88</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.04</v>
+        <v>13.24</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.62</v>
+        <v>7.68</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.42</v>
+        <v>5.56</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.62</v>
+        <v>19.6</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="H4" t="n">
-        <v>90.09</v>
+        <v>90</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="M4" t="n">
-        <v>44.18</v>
+        <v>44.17</v>
       </c>
       <c r="N4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="P4" t="n">
-        <v>13.82</v>
+        <v>14.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.18</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
       <c r="S4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.36</v>
+        <v>47.58</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.09</v>
+        <v>13.08</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.18</v>
+        <v>8.42</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.27</v>
+        <v>20.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.62</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.039999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BO4" t="n">
         <v>0.96</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BT4" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.37</v>
+        <v>2.59</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CC4" t="n">
         <v>5.33</v>
@@ -2431,154 +2431,154 @@
         <v>1.44</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CH4" t="n">
         <v>1.37</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO4" t="n">
         <v>1.37</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CT4" t="n">
         <v>2.7</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB4" t="n">
         <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="DH4" t="n">
-        <v>84.92</v>
+        <v>85.08</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.62</v>
+        <v>41.72</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.33</v>
+        <v>13.48</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.33</v>
+        <v>11.24</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.880000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.75</v>
+        <v>44.52</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.83</v>
+        <v>10.92</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.34</v>
+        <v>7.48</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.25</v>
+        <v>18.88</v>
       </c>
       <c r="EB4" t="n">
         <v>1.24</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>107.67</v>
+        <v>108.85</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="K5" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>46.83</v>
+        <v>47</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="O5" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.17</v>
+        <v>11.92</v>
       </c>
       <c r="R5" t="n">
-        <v>6.08</v>
+        <v>5.92</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T5" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="U5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.08</v>
+        <v>53.38</v>
       </c>
       <c r="Y5" t="n">
         <v>0.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.67</v>
+        <v>12.31</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.67</v>
+        <v>8.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>4.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.17</v>
+        <v>19.08</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,67 +2759,67 @@
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BP5" t="n">
         <v>3.96</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="BR5" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS5" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BU5" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX5" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CB5" t="n">
         <v>3.51</v>
@@ -2831,19 +2831,19 @@
         <v>3.61</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH5" t="n">
         <v>1.4</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.86</v>
@@ -2852,52 +2852,52 @@
         <v>1.65</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO5" t="n">
         <v>1.33</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT5" t="n">
         <v>2.89</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY5" t="n">
         <v>2.14</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB5" t="n">
         <v>1.38</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DH5" t="n">
-        <v>96.42</v>
+        <v>97.48</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>41.58</v>
+        <v>41.88</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.67</v>
+        <v>11.64</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.88</v>
+        <v>11.76</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.83</v>
+        <v>7.68</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.08</v>
+        <v>51.32</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.88</v>
+        <v>11.24</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.88</v>
+        <v>7.12</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="EA5" t="n">
         <v>17.92</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="F6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G6" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="H6" t="n">
-        <v>107.33</v>
+        <v>106.69</v>
       </c>
       <c r="I6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="K6" t="n">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="L6" t="n">
         <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>45.5</v>
+        <v>45.69</v>
       </c>
       <c r="N6" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="O6" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="P6" t="n">
-        <v>15.5</v>
+        <v>15.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.25</v>
+        <v>14.54</v>
       </c>
       <c r="R6" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="T6" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="U6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.5</v>
+        <v>50.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.75</v>
+        <v>13.08</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.5</v>
+        <v>8.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.75</v>
+        <v>21.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AF6" t="n">
         <v>0.08</v>
@@ -3162,49 +3162,49 @@
         <v>2.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.42</v>
+        <v>9.56</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.12</v>
+        <v>5.28</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS6" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BT6" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BU6" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CC6" t="n">
         <v>5.1</v>
@@ -3237,7 +3237,7 @@
         <v>1.53</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CG6" t="n">
         <v>2.52</v>
@@ -3249,16 +3249,16 @@
         <v>1.69</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CK6" t="n">
         <v>1.59</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN6" t="n">
         <v>1.79</v>
@@ -3270,88 +3270,88 @@
         <v>2.48</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.86</v>
+        <v>4.84</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="DD6" t="n">
         <v>2.95</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="DH6" t="n">
-        <v>102.38</v>
+        <v>102.24</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ6" t="n">
         <v>2.04</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.96</v>
+        <v>5.04</v>
       </c>
       <c r="DL6" t="n">
         <v>0.2</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.16</v>
+        <v>41.44</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.12</v>
+        <v>15.24</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.16</v>
+        <v>13.84</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.75</v>
+        <v>7.6</v>
       </c>
       <c r="DS6" t="n">
         <v>0.16</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.25</v>
+        <v>50.96</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.62</v>
+        <v>11.84</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.88</v>
+        <v>8</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.25</v>
+        <v>20.12</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="EC6" t="n">
         <v>1.96</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.15</v>
@@ -3487,43 +3487,43 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>92.45</v>
+        <v>93.42</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>35.45</v>
+        <v>34.92</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.55</v>
+        <v>12.25</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.18</v>
+        <v>15.33</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.82</v>
+        <v>7.83</v>
       </c>
       <c r="AT7" t="n">
         <v>2</v>
@@ -3532,91 +3532,91 @@
         <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>57.36</v>
+        <v>57.08</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.27</v>
+        <v>7.75</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.64</v>
+        <v>17.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.380000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="BR7" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS7" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BU7" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV7" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BY7" t="n">
         <v>3.38</v>
@@ -3631,19 +3631,19 @@
         <v>3.8</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.27</v>
+        <v>5.24</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
@@ -3658,7 +3658,7 @@
         <v>1.65</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CM7" t="n">
         <v>2.17</v>
@@ -3670,19 +3670,19 @@
         <v>1.35</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS7" t="n">
         <v>2.94</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CU7" t="n">
         <v>1.47</v>
@@ -3691,103 +3691,103 @@
         <v>1.94</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX7" t="n">
         <v>1.73</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB7" t="n">
         <v>1.41</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="DE7" t="n">
         <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DH7" t="n">
-        <v>99.45</v>
+        <v>99.64</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM7" t="n">
-        <v>44.91</v>
+        <v>44.28</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.46</v>
+        <v>12.32</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.58</v>
+        <v>14.68</v>
       </c>
       <c r="DR7" t="n">
         <v>7.92</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.54</v>
+        <v>58.36</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.17</v>
+        <v>10.8</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.33</v>
+        <v>7.04</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.17</v>
+        <v>16.6</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="8">
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="F8" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="G8" t="n">
-        <v>4.18</v>
+        <v>4.58</v>
       </c>
       <c r="H8" t="n">
-        <v>119.55</v>
+        <v>120.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>8.42</v>
       </c>
       <c r="L8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="M8" t="n">
-        <v>61.73</v>
+        <v>62.83</v>
       </c>
       <c r="N8" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="O8" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="P8" t="n">
-        <v>8.82</v>
+        <v>9.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.91</v>
+        <v>11.75</v>
       </c>
       <c r="R8" t="n">
-        <v>4.27</v>
+        <v>4.08</v>
       </c>
       <c r="S8" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="T8" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>69</v>
+        <v>69.33</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.45</v>
+        <v>20.58</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.91</v>
+        <v>12.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.55</v>
+        <v>7.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.64</v>
+        <v>18.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AF8" t="n">
         <v>0.23</v>
@@ -3968,37 +3968,37 @@
         <v>1.92</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.75</v>
+        <v>12.04</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BO8" t="n">
         <v>1.88</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.33</v>
+        <v>6.64</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4007,31 +4007,31 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BU8" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV8" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX8" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.81</v>
+        <v>5.95</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.13</v>
+        <v>6.35</v>
       </c>
       <c r="CC8" t="n">
         <v>1.61</v>
@@ -4040,34 +4040,34 @@
         <v>1.67</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CF8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CO8" t="n">
         <v>1.09</v>
@@ -4076,7 +4076,7 @@
         <v>1.37</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
@@ -4087,104 +4087,104 @@
         <v>1.87</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX8" t="n">
         <v>1.5</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.52</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DB8" t="inlineStr"/>
       <c r="DC8" t="n">
         <v>1.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DF8" t="n">
         <v>0.96</v>
       </c>
       <c r="DG8" t="n">
-        <v>4.25</v>
+        <v>4.44</v>
       </c>
       <c r="DH8" t="n">
-        <v>116.05</v>
+        <v>116.64</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="DK8" t="n">
-        <v>7.5</v>
+        <v>7.72</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DM8" t="n">
-        <v>63.71</v>
+        <v>64.16</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.09</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12</v>
+        <v>11.92</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>68.83</v>
+        <v>69</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>20.58</v>
+        <v>20.64</v>
       </c>
       <c r="DY8" t="n">
-        <v>13.21</v>
+        <v>13.2</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.25</v>
+        <v>17.16</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
@@ -4206,49 +4206,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="G9" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>101.08</v>
+        <v>97.92</v>
       </c>
       <c r="I9" t="n">
         <v>0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="K9" t="n">
-        <v>4.58</v>
+        <v>4.38</v>
       </c>
       <c r="L9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="M9" t="n">
-        <v>41.92</v>
+        <v>40.38</v>
       </c>
       <c r="N9" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="Q9" t="n">
         <v>16</v>
       </c>
-      <c r="Q9" t="n">
-        <v>15.83</v>
-      </c>
       <c r="R9" t="n">
-        <v>6.58</v>
+        <v>6.62</v>
       </c>
       <c r="S9" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="T9" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="U9" t="n">
         <v>0.08</v>
@@ -4260,28 +4260,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>43.67</v>
+        <v>42.69</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.67</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.08</v>
+        <v>6.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>25.08</v>
+        <v>24.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,50 +4365,50 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.83</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BP9" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>96</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>64</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BU9" t="n">
         <v>4</v>
       </c>
-      <c r="BQ9" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>95.83</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.17</v>
-      </c>
       <c r="BV9" t="n">
         <v>0</v>
       </c>
@@ -4416,19 +4416,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CC9" t="n">
         <v>5.05</v>
@@ -4458,31 +4458,31 @@
         <v>1.83</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CP9" t="n">
         <v>2.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.71</v>
+        <v>5.72</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CS9" t="n">
         <v>3.18</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CU9" t="n">
         <v>1.37</v>
@@ -4491,7 +4491,7 @@
         <v>1.6</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CX9" t="n">
         <v>1.94</v>
@@ -4506,10 +4506,10 @@
         <v>1.57</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="DD9" t="n">
         <v>2.81</v>
@@ -4518,13 +4518,13 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="DH9" t="n">
-        <v>99.2</v>
+        <v>97.64</v>
       </c>
       <c r="DI9" t="n">
         <v>0.12</v>
@@ -4533,25 +4533,25 @@
         <v>2.8</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.62</v>
+        <v>4.52</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.17</v>
+        <v>40.4</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.16</v>
+        <v>14.76</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.96</v>
+        <v>15.08</v>
       </c>
       <c r="DR9" t="n">
         <v>7</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.75</v>
+        <v>41.32</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.08</v>
+        <v>6.92</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="EA9" t="n">
-        <v>24.33</v>
+        <v>24.28</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="10">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4687,139 +4687,139 @@
         <v>1.92</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG10" t="n">
         <v>2.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI10" t="n">
-        <v>85.75</v>
+        <v>88.77</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>38.58</v>
+        <v>40.15</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.42</v>
+        <v>11.92</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.25</v>
+        <v>13.62</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.25</v>
+        <v>10.31</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.5</v>
+        <v>48.15</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.67</v>
+        <v>9.69</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.75</v>
+        <v>5.69</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>15.25</v>
+        <v>15.69</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.119999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BP10" t="n">
         <v>4.04</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.08</v>
+        <v>5.24</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS10" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU10" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>3.12</v>
@@ -4828,34 +4828,34 @@
         <v>3.42</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.18</v>
+        <v>5.04</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.44</v>
+        <v>5.28</v>
       </c>
       <c r="CE10" t="n">
         <v>1.39</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK10" t="n">
         <v>1.57</v>
@@ -4870,19 +4870,19 @@
         <v>1.82</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT10" t="n">
         <v>2.85</v>
@@ -4912,7 +4912,7 @@
         <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD10" t="n">
         <v>3.03</v>
@@ -4927,70 +4927,70 @@
         <v>1.92</v>
       </c>
       <c r="DH10" t="n">
-        <v>88.42</v>
+        <v>89.88</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM10" t="n">
-        <v>42.71</v>
+        <v>43.36</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.25</v>
+        <v>11.04</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.34</v>
+        <v>13.52</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.880000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.54</v>
+        <v>48.84</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.96</v>
+        <v>16.16</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="11">
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0.17</v>
@@ -5093,28 +5093,28 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" t="n">
-        <v>81.17</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>34.75</v>
+        <v>34</v>
       </c>
       <c r="AO11" t="n">
         <v>1.08</v>
@@ -5123,19 +5123,19 @@
         <v>0.92</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.33</v>
+        <v>12.15</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.75</v>
+        <v>12.69</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.75</v>
+        <v>10.85</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5147,82 +5147,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>41.58</v>
+        <v>40.46</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.67</v>
+        <v>9.31</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.42</v>
+        <v>6.15</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BD11" t="n">
-        <v>16.42</v>
+        <v>15.77</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.710000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.29</v>
+        <v>5.64</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS11" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BT11" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BU11" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY11" t="n">
         <v>4.12</v>
@@ -5231,55 +5231,55 @@
         <v>4.48</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.99</v>
+        <v>4.2</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.17</v>
+        <v>4.47</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.53</v>
+        <v>6.56</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.03</v>
+        <v>7.2</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
@@ -5303,13 +5303,13 @@
         <v>1.57</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.41</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
         <v>1.33</v>
@@ -5318,49 +5318,49 @@
         <v>1.93</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DG11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DH11" t="n">
-        <v>84.58</v>
+        <v>82.88</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM11" t="n">
-        <v>36.58</v>
+        <v>36.12</v>
       </c>
       <c r="DN11" t="n">
         <v>0.88</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.16</v>
+        <v>12.08</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.66</v>
+        <v>12.64</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.75</v>
+        <v>9.84</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5372,28 +5372,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>42.42</v>
+        <v>41.8</v>
       </c>
       <c r="DW11" t="n">
         <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.8</v>
+        <v>10.56</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.58</v>
+        <v>7.4</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.71</v>
+        <v>17.32</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5493,139 +5493,139 @@
         <v>2.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AI12" t="n">
-        <v>89.73</v>
+        <v>89.17</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>40.91</v>
+        <v>40.25</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.73</v>
+        <v>12.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.55</v>
+        <v>12.17</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.82</v>
+        <v>7.83</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>42.09</v>
+        <v>41.83</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.45</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.73</v>
+        <v>20.17</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.960000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="BM12" t="n">
         <v>0.88</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BV12" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BX12" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY12" t="n">
         <v>2.9</v>
@@ -5634,22 +5634,22 @@
         <v>2.91</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.49</v>
+        <v>4.62</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.7</v>
+        <v>4.98</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG12" t="n">
         <v>2.79</v>
@@ -5658,40 +5658,40 @@
         <v>1.38</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.91</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL12" t="n">
         <v>1.99</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO12" t="n">
         <v>1.36</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CR12" t="n">
         <v>1.48</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
@@ -5715,55 +5715,55 @@
         <v>1.86</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DH12" t="n">
-        <v>90.54000000000001</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.46</v>
+        <v>4.